--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -487,14 +487,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="58" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -721,6 +722,11 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
+          <t>Tilmeldt</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
           <t>Note</t>
         </is>
       </c>
@@ -736,9 +742,18 @@
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr"/>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>2000m</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -751,14 +766,23 @@
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr"/>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>42.2km</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Stelvio Gran Fondo</t>
+          <t>Santini Stelvio Gran Fondo (lang rute)</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -771,10 +795,19 @@
           <t>B</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Hyggetur med Eva + form-check.</t>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>130km / 4500hm</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Ja (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>B-løb. TILMELDT 16/7-2026 (med Eva). Hyggeløb + form-check mod TdS.</t>
         </is>
       </c>
     </row>
@@ -796,12 +829,17 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>242 km / 8.848 hm</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Start 02:30. Sæsonens hovedmål.</t>
+          <t>242km / 8848hm</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>A-løb. IKKE TILMELDT — 2027 åbner først ca. sep-26. Tjek 20/9. Cutoff 20:30 Croix-de-Cœur. Start 02:30 (18 t margin).</t>
         </is>
       </c>
     </row>
@@ -2927,7 +2965,7 @@
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>STELVIO GRAN FONDO søn 6/6 — B-løb. Hyggetur med Eva + form-check.</t>
+          <t>LA STELVIO SANTINI (Santini Stelvio Gran Fondo, lang rute) søn 6/6 — 130 km / 4.500 hm. B-løb, tilmeldt 16/7-2026 sammen med Eva. Form-check mod TdS: kør den som hårdt træningspas, ikke som A-løb.</t>
         </is>
       </c>
     </row>
@@ -5948,8 +5986,12 @@
       <c r="F5" s="4" t="n">
         <v>290</v>
       </c>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="11" t="n"/>
+      <c r="G5" s="4" t="n">
+        <v>284</v>
+      </c>
+      <c r="H5" s="11" t="n">
+        <v>-6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -5974,8 +6016,12 @@
       <c r="F6" s="4" t="n">
         <v>340</v>
       </c>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="11" t="n"/>
+      <c r="G6" s="4" t="n">
+        <v>451</v>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -6000,8 +6046,12 @@
       <c r="F7" s="4" t="n">
         <v>370</v>
       </c>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="11" t="n"/>
+      <c r="G7" s="4" t="n">
+        <v>386</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -6026,8 +6076,12 @@
       <c r="F8" s="4" t="n">
         <v>180</v>
       </c>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="11" t="n"/>
+      <c r="G8" s="4" t="n">
+        <v>367</v>
+      </c>
+      <c r="H8" s="11" t="n">
+        <v>187</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -6052,8 +6106,12 @@
       <c r="F9" s="4" t="n">
         <v>385</v>
       </c>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="11" t="n"/>
+      <c r="G9" s="4" t="n">
+        <v>558</v>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>173</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -6078,8 +6136,12 @@
       <c r="F10" s="4" t="n">
         <v>300</v>
       </c>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="11" t="n"/>
+      <c r="G10" s="4" t="n">
+        <v>267</v>
+      </c>
+      <c r="H10" s="11" t="n">
+        <v>-33</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -6104,8 +6166,12 @@
       <c r="F11" s="4" t="n">
         <v>430</v>
       </c>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="11" t="n"/>
+      <c r="G11" s="4" t="n">
+        <v>455</v>
+      </c>
+      <c r="H11" s="11" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -6130,8 +6196,12 @@
       <c r="F12" s="4" t="n">
         <v>480</v>
       </c>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="11" t="n"/>
+      <c r="G12" s="4" t="n">
+        <v>417</v>
+      </c>
+      <c r="H12" s="11" t="n">
+        <v>-63</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -6156,8 +6226,12 @@
       <c r="F13" s="4" t="n">
         <v>270</v>
       </c>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="11" t="n"/>
+      <c r="G13" s="4" t="n">
+        <v>363</v>
+      </c>
+      <c r="H13" s="11" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -6183,10 +6257,10 @@
         <v>420</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>-221</v>
+        <v>-186</v>
       </c>
     </row>
     <row r="15">

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>72.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>68</v>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>16</v>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3.85</v>
+        <v>3.89</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>4.71</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -3536,39 +3536,39 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>74.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-4.7</v>
+        <v>-2.8</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>75.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>75.09999999999999</v>
@@ -3577,22 +3577,22 @@
         <v>23.5</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>23.25</v>
+        <v>23.5</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>-2.8</v>
+        <v>-2.2</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
@@ -3602,257 +3602,253 @@
         <v>75.03</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>23.33</v>
+        <v>23.57</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-2.2</v>
+        <v>0.2</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>75</v>
+        <v>75.03</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>23.7</v>
+        <v>23.3</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>23.43</v>
+        <v>23.5</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>75</v>
+        <v>74.8</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>75</v>
+        <v>74.98</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>23.4</v>
+        <v>23.36</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>52</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n">
-        <v>74.8</v>
-      </c>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n"/>
       <c r="C10" s="7" t="n">
-        <v>74.97</v>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>22.8</v>
-      </c>
+        <v>74.98</v>
+      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="7" t="n">
-        <v>23.3</v>
+        <v>23.36</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>7.1</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
       <c r="C11" s="7" t="n">
-        <v>74.97</v>
+        <v>74.98</v>
       </c>
       <c r="D11" s="8" t="n"/>
       <c r="E11" s="7" t="n">
-        <v>23.3</v>
+        <v>23.36</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>6.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n"/>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>75.7</v>
+      </c>
       <c r="C12" s="7" t="n">
-        <v>74.98</v>
-      </c>
-      <c r="D12" s="8" t="n"/>
+        <v>75.06</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>22.3</v>
+      </c>
       <c r="E12" s="7" t="n">
-        <v>23.36</v>
+        <v>23.12</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n">
-        <v>75.7</v>
-      </c>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n"/>
       <c r="C13" s="7" t="n">
-        <v>75.06</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>22.3</v>
-      </c>
+        <v>75.09999999999999</v>
+      </c>
+      <c r="D13" s="8" t="n"/>
       <c r="E13" s="7" t="n">
-        <v>23.12</v>
+        <v>23.02</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
       <c r="C14" s="7" t="n">
-        <v>75.09999999999999</v>
+        <v>75.17</v>
       </c>
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="7" t="n">
-        <v>23.02</v>
+        <v>22.8</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>6.5</v>
+        <v>-1.4</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>6.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="7" t="n">
-        <v>75.17</v>
+        <v>75.25</v>
       </c>
       <c r="D15" s="8" t="n"/>
       <c r="E15" s="7" t="n">
-        <v>22.8</v>
+        <v>22.55</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-1.4</v>
+        <v>-1.3</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B16" s="8" t="n"/>
       <c r="C16" s="7" t="n">
-        <v>75.25</v>
+        <v>75.7</v>
       </c>
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="7" t="n">
-        <v>22.55</v>
+        <v>22.3</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>-1.3</v>
+        <v>-7.7</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B17" s="8" t="n"/>
@@ -3864,19 +3860,19 @@
         <v>22.3</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.6</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B18" s="8" t="n"/>
@@ -3888,43 +3884,39 @@
         <v>22.3</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>-8.6</v>
+        <v>-16.4</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B19" s="8" t="n"/>
-      <c r="C19" s="7" t="n">
-        <v>75.7</v>
-      </c>
+      <c r="C19" s="7" t="n"/>
       <c r="D19" s="8" t="n"/>
-      <c r="E19" s="7" t="n">
-        <v>22.3</v>
-      </c>
+      <c r="E19" s="7" t="n"/>
       <c r="F19" s="8" t="n">
         <v>-16.4</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B20" s="8" t="n"/>
@@ -3932,19 +3924,19 @@
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="8" t="n">
-        <v>-16.4</v>
+        <v>-14.3</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
@@ -3952,19 +3944,19 @@
       <c r="D21" s="8" t="n"/>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="8" t="n">
-        <v>-14.3</v>
+        <v>-9.1</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
@@ -3972,19 +3964,19 @@
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="8" t="n">
-        <v>-9.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
@@ -3992,39 +3984,47 @@
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="8" t="n">
-        <v>-8.300000000000001</v>
+        <v>-5</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="7" t="n"/>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>22</v>
+      </c>
       <c r="F24" s="8" t="n">
-        <v>-5</v>
+        <v>-1.8</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
@@ -4034,103 +4034,99 @@
         <v>74.5</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-1.8</v>
+        <v>-13.8</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="n">
-        <v>74.5</v>
-      </c>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n"/>
       <c r="C26" s="7" t="n">
         <v>74.5</v>
       </c>
-      <c r="D26" s="8" t="n">
-        <v>23</v>
-      </c>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="7" t="n">
         <v>22.5</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-13.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="H26" s="10" t="n">
-        <v>8.1</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="n"/>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>74.40000000000001</v>
+      </c>
       <c r="C27" s="7" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="D27" s="8" t="n"/>
+        <v>74.47</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>23.3</v>
+      </c>
       <c r="E27" s="7" t="n">
-        <v>22.5</v>
+        <v>22.77</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-15.7</v>
+        <v>-10.5</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="H27" s="10" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="n">
-        <v>74.40000000000001</v>
-      </c>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n"/>
       <c r="C28" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D28" s="8" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="D28" s="8" t="n"/>
       <c r="E28" s="7" t="n">
         <v>22.77</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-10.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B29" s="8" t="n"/>
@@ -4142,90 +4138,94 @@
         <v>22.77</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-9.4</v>
+        <v>-7.5</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="n"/>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="n">
+        <v>74.5</v>
+      </c>
       <c r="C30" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D30" s="8" t="n"/>
+      <c r="D30" s="8" t="n">
+        <v>22.9</v>
+      </c>
       <c r="E30" s="7" t="n">
-        <v>22.77</v>
+        <v>22.8</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-7.5</v>
+        <v>-4.5</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>74.47</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.2</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>23</v>
+        <v>22.93</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-2.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H32" s="10" t="n">
         <v>8</v>
@@ -4234,291 +4234,283 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C33" s="7" t="n">
         <v>74.7</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>22.93</v>
+        <v>22.78</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>74.7</v>
+        <v>74.64</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>22.78</v>
+        <v>22.6</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-11.9</v>
+        <v>-10.3</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>22.6</v>
+        <v>22.55</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-10.3</v>
+        <v>-13.7</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>74.65000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>22.55</v>
+        <v>22.57</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>-13.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="n">
-        <v>74.2</v>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n"/>
       <c r="C37" s="7" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="D37" s="8" t="n">
-        <v>22.7</v>
-      </c>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D37" s="8" t="n"/>
       <c r="E37" s="7" t="n">
-        <v>22.57</v>
+        <v>22.52</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-15.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.52</v>
       </c>
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="7" t="n">
-        <v>22.52</v>
+        <v>22.46</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B39" s="8" t="n"/>
       <c r="C39" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-18.2</v>
+        <v>-23.1</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B40" s="8" t="n"/>
       <c r="C40" s="7" t="n">
-        <v>74.42</v>
+        <v>74.33</v>
       </c>
       <c r="D40" s="8" t="n"/>
       <c r="E40" s="7" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="7" t="n">
-        <v>74.33</v>
+        <v>74.45</v>
       </c>
       <c r="D41" s="8" t="n"/>
       <c r="E41" s="7" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-18.2</v>
+        <v>-19.5</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B42" s="8" t="n"/>
       <c r="C42" s="7" t="n">
-        <v>74.45</v>
+        <v>74.2</v>
       </c>
       <c r="D42" s="8" t="n"/>
       <c r="E42" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>-19.5</v>
+        <v>-26.4</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B43" s="8" t="n"/>
-      <c r="C43" s="7" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="C43" s="7" t="n"/>
       <c r="D43" s="8" t="n"/>
-      <c r="E43" s="7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="E43" s="7" t="n"/>
       <c r="F43" s="8" t="n">
-        <v>-26.4</v>
+        <v>-19.9</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B44" s="8" t="n"/>
@@ -4526,807 +4518,811 @@
       <c r="D44" s="8" t="n"/>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="8" t="n">
-        <v>-19.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B45" s="8" t="n"/>
-      <c r="C45" s="7" t="n"/>
-      <c r="D45" s="8" t="n"/>
-      <c r="E45" s="7" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E45" s="7" t="n">
+        <v>21.7</v>
+      </c>
       <c r="F45" s="8" t="n">
-        <v>-15.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>21.7</v>
+        <v>22.05</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>-9.4</v>
+        <v>-12</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>73.2</v>
+        <v>73.33</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-12</v>
+        <v>-12.4</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>-12.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>73.31999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D52" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>22.26</v>
+        <v>22.4</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>73.16</v>
+        <v>73.2</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-10.9</v>
+        <v>-16</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>-16</v>
+        <v>-10.1</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>22.3</v>
+        <v>22.31</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>-10.1</v>
+        <v>-5.9</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>73.16</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>22.31</v>
+        <v>22.43</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>-5.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
         <v>72.8</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>73.06999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>22.43</v>
+        <v>22.41</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>-9.9</v>
+        <v>-13.3</v>
       </c>
       <c r="G57" s="9" t="n">
         <v>68</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C58" s="7" t="n">
-        <v>73.11</v>
+        <v>73.06</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>-13.3</v>
+        <v>-16.6</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
         <v>72.5</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>73.06</v>
+        <v>72.97</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>-16.6</v>
+        <v>-11.8</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B60" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C60" s="7" t="n">
-        <v>72.97</v>
+        <v>72.86</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>22.26</v>
+        <v>22.21</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>-11.8</v>
+        <v>-21.1</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>72.86</v>
+        <v>72.8</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>-21.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B62" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C62" s="7" t="n">
-        <v>72.8</v>
+        <v>72.69</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>22.24</v>
+        <v>22.19</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>-25.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B63" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>72.69</v>
+        <v>72.61</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>-18.3</v>
+        <v>-16</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B64" s="8" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C64" s="7" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="D64" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>-16</v>
+        <v>-10.4</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B65" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="n"/>
       <c r="C65" s="7" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="D65" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="D65" s="8" t="n"/>
       <c r="E65" s="7" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>-10.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B66" s="8" t="n"/>
       <c r="C66" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="7" t="n">
-        <v>21.85</v>
+        <v>21.7</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B67" s="8" t="n"/>
       <c r="C67" s="7" t="n">
-        <v>72.58</v>
+        <v>72.5</v>
       </c>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>-12.3</v>
+        <v>-6.6</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B68" s="8" t="n"/>
       <c r="C68" s="7" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="7" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B69" s="8" t="n"/>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C69" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D69" s="8" t="n"/>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="D69" s="8" t="n">
+        <v>21.2</v>
+      </c>
       <c r="E69" s="7" t="n">
-        <v>21.73</v>
+        <v>21.63</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C70" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>21.63</v>
+        <v>21.57</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E71" s="7" t="n">
         <v>21.57</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>-7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B72" s="8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C72" s="7" t="n">
-        <v>72.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D72" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E72" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E72" s="7" t="n">
-        <v>21.57</v>
-      </c>
       <c r="F72" s="8" t="n">
-        <v>-10.9</v>
+        <v>-7.7</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="n"/>
       <c r="C73" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D73" s="8" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D73" s="8" t="n"/>
       <c r="E73" s="7" t="n">
         <v>21.8</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.9</v>
       </c>
       <c r="G73" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B74" s="8" t="n"/>
@@ -5338,19 +5334,19 @@
         <v>21.8</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>-8.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B75" s="8" t="n"/>
@@ -5362,274 +5358,278 @@
         <v>21.8</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>-12.5</v>
+        <v>-11.2</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B76" s="8" t="n"/>
       <c r="C76" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="D76" s="8" t="n"/>
       <c r="E76" s="7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>-11.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G76" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B77" s="8" t="n"/>
       <c r="C77" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="7" t="n">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>-13.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B78" s="8" t="n"/>
       <c r="C78" s="7" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D78" s="8" t="n"/>
       <c r="E78" s="7" t="n">
-        <v>22.15</v>
+        <v>22.5</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="G78" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B79" s="8" t="n"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="C79" s="7" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="D79" s="8" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D79" s="8" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E79" s="7" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>-12.4</v>
+        <v>-7.8</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C80" s="7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>20.5</v>
+        <v>20.95</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>-7.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>20.95</v>
+        <v>21.13</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>-3.1</v>
+        <v>-11.8</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B82" s="8" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>-11.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B83" s="8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D83" s="8" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B84" s="8" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C84" s="7" t="n">
-        <v>72.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D84" s="8" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>-8.6</v>
+        <v>-13.5</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B85" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="D85" s="8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>21.33</v>
+        <v>21.43</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H85" s="10" t="n">
         <v>7.7</v>
@@ -5638,249 +5638,249 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B86" s="8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="C86" s="7" t="n">
-        <v>72.23</v>
+        <v>72.39</v>
       </c>
       <c r="D86" s="8" t="n">
         <v>22</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>21.43</v>
+        <v>21.64</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>-7.1</v>
+        <v>-12.5</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B87" s="8" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C87" s="7" t="n">
         <v>72.39</v>
       </c>
       <c r="D87" s="8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>21.64</v>
+        <v>21.69</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>-12.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B88" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C88" s="7" t="n">
-        <v>72.39</v>
+        <v>72.36</v>
       </c>
       <c r="D88" s="8" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>21.69</v>
+        <v>21.56</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>-6.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B89" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="n"/>
       <c r="C89" s="7" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="D89" s="8" t="n">
-        <v>20.6</v>
-      </c>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="D89" s="8" t="n"/>
       <c r="E89" s="7" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B90" s="8" t="n"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="C90" s="7" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="D90" s="8" t="n"/>
+        <v>72.45</v>
+      </c>
+      <c r="D90" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E90" s="7" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B91" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>72.45</v>
+        <v>72.47</v>
       </c>
       <c r="D91" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>21.67</v>
+        <v>21.53</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B92" s="8" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C92" s="7" t="n">
-        <v>72.47</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D92" s="8" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>21.53</v>
+        <v>21.47</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B93" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D93" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B94" s="8" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C94" s="7" t="n">
-        <v>72.31999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="D94" s="8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>-4.1</v>
+        <v>-2.9</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H94" s="10" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -6251,7 +6251,7 @@
         <v>50</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>420</v>

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>68</v>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>21.5</v>
+        <v>21.2</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>16</v>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3.89</v>
+        <v>3.81</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>4.71</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>51</v>
+        <v>52.8</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -3536,14 +3536,14 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>75.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>75.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>23.5</v>
@@ -3552,279 +3552,275 @@
         <v>23.5</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-2.8</v>
+        <v>-2.2</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
         <v>74.90000000000001</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>75.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>-2.2</v>
+        <v>0.2</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>75.03</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>23.7</v>
+        <v>23.3</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>23.57</v>
+        <v>23.5</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>75</v>
+        <v>74.8</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>75.03</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>23.5</v>
+        <v>23.32</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>52</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n">
-        <v>74.8</v>
-      </c>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n"/>
       <c r="C9" s="7" t="n">
-        <v>74.98</v>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>22.8</v>
-      </c>
+        <v>74.90000000000001</v>
+      </c>
+      <c r="D9" s="8" t="n"/>
       <c r="E9" s="7" t="n">
-        <v>23.36</v>
+        <v>23.32</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>7.1</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
       <c r="C10" s="7" t="n">
-        <v>74.98</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D10" s="8" t="n"/>
       <c r="E10" s="7" t="n">
-        <v>23.36</v>
+        <v>23.32</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>6.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n"/>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>75.7</v>
+      </c>
       <c r="C11" s="7" t="n">
-        <v>74.98</v>
-      </c>
-      <c r="D11" s="8" t="n"/>
+        <v>75.06</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>22.3</v>
+      </c>
       <c r="E11" s="7" t="n">
-        <v>23.36</v>
+        <v>23.12</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n">
-        <v>75.7</v>
-      </c>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n"/>
       <c r="C12" s="7" t="n">
-        <v>75.06</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>22.3</v>
-      </c>
+        <v>75.09999999999999</v>
+      </c>
+      <c r="D12" s="8" t="n"/>
       <c r="E12" s="7" t="n">
-        <v>23.12</v>
+        <v>23.02</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="7" t="n">
-        <v>75.09999999999999</v>
+        <v>75.17</v>
       </c>
       <c r="D13" s="8" t="n"/>
       <c r="E13" s="7" t="n">
-        <v>23.02</v>
+        <v>22.8</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>6.5</v>
+        <v>-1.4</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>6.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
       <c r="C14" s="7" t="n">
-        <v>75.17</v>
+        <v>75.25</v>
       </c>
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="7" t="n">
-        <v>22.8</v>
+        <v>22.55</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>-1.4</v>
+        <v>-1.3</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="7" t="n">
-        <v>75.25</v>
+        <v>75.7</v>
       </c>
       <c r="D15" s="8" t="n"/>
       <c r="E15" s="7" t="n">
-        <v>22.55</v>
+        <v>22.3</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-1.3</v>
+        <v>-7.7</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B16" s="8" t="n"/>
@@ -3836,19 +3832,19 @@
         <v>22.3</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.6</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B17" s="8" t="n"/>
@@ -3860,43 +3856,39 @@
         <v>22.3</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-8.6</v>
+        <v>-16.4</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B18" s="8" t="n"/>
-      <c r="C18" s="7" t="n">
-        <v>75.7</v>
-      </c>
+      <c r="C18" s="7" t="n"/>
       <c r="D18" s="8" t="n"/>
-      <c r="E18" s="7" t="n">
-        <v>22.3</v>
-      </c>
+      <c r="E18" s="7" t="n"/>
       <c r="F18" s="8" t="n">
         <v>-16.4</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B19" s="8" t="n"/>
@@ -3904,19 +3896,19 @@
       <c r="D19" s="8" t="n"/>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="8" t="n">
-        <v>-16.4</v>
+        <v>-14.3</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B20" s="8" t="n"/>
@@ -3924,19 +3916,19 @@
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="8" t="n">
-        <v>-14.3</v>
+        <v>-9.1</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
@@ -3944,19 +3936,19 @@
       <c r="D21" s="8" t="n"/>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="8" t="n">
-        <v>-9.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
@@ -3964,39 +3956,47 @@
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="8" t="n">
-        <v>-8.300000000000001</v>
+        <v>-5</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="7" t="n"/>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>22</v>
+      </c>
       <c r="F23" s="8" t="n">
-        <v>-5</v>
+        <v>-1.8</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
@@ -4006,103 +4006,99 @@
         <v>74.5</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>-1.8</v>
+        <v>-13.8</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="n">
-        <v>74.5</v>
-      </c>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="7" t="n">
         <v>74.5</v>
       </c>
-      <c r="D25" s="8" t="n">
-        <v>23</v>
-      </c>
+      <c r="D25" s="8" t="n"/>
       <c r="E25" s="7" t="n">
         <v>22.5</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-13.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="H25" s="10" t="n">
-        <v>8.1</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="n"/>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n">
+        <v>74.40000000000001</v>
+      </c>
       <c r="C26" s="7" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="D26" s="8" t="n"/>
+        <v>74.47</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>23.3</v>
+      </c>
       <c r="E26" s="7" t="n">
-        <v>22.5</v>
+        <v>22.77</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-15.7</v>
+        <v>-10.5</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="H26" s="10" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="H26" s="10" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="n">
-        <v>74.40000000000001</v>
-      </c>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n"/>
       <c r="C27" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D27" s="8" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="D27" s="8" t="n"/>
       <c r="E27" s="7" t="n">
         <v>22.77</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-10.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B28" s="8" t="n"/>
@@ -4114,90 +4110,94 @@
         <v>22.77</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-9.4</v>
+        <v>-7.5</v>
       </c>
       <c r="G28" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="n"/>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>74.5</v>
+      </c>
       <c r="C29" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D29" s="8" t="n"/>
+      <c r="D29" s="8" t="n">
+        <v>22.9</v>
+      </c>
       <c r="E29" s="7" t="n">
-        <v>22.77</v>
+        <v>22.8</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-7.5</v>
+        <v>-4.5</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>74.47</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.2</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>23</v>
+        <v>22.93</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-2.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H31" s="10" t="n">
         <v>8</v>
@@ -4206,291 +4206,283 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C32" s="7" t="n">
         <v>74.7</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>22.93</v>
+        <v>22.78</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>74.7</v>
+        <v>74.64</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>22.78</v>
+        <v>22.6</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-11.9</v>
+        <v>-10.3</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>22.6</v>
+        <v>22.55</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-10.3</v>
+        <v>-13.7</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>74.65000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>22.55</v>
+        <v>22.57</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-13.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="n">
-        <v>74.2</v>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="n"/>
       <c r="C36" s="7" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="D36" s="8" t="n">
-        <v>22.7</v>
-      </c>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D36" s="8" t="n"/>
       <c r="E36" s="7" t="n">
-        <v>22.57</v>
+        <v>22.52</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>-15.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.52</v>
       </c>
       <c r="D37" s="8" t="n"/>
       <c r="E37" s="7" t="n">
-        <v>22.52</v>
+        <v>22.46</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>-18.2</v>
+        <v>-23.1</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B39" s="8" t="n"/>
       <c r="C39" s="7" t="n">
-        <v>74.42</v>
+        <v>74.33</v>
       </c>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="7" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B40" s="8" t="n"/>
       <c r="C40" s="7" t="n">
-        <v>74.33</v>
+        <v>74.45</v>
       </c>
       <c r="D40" s="8" t="n"/>
       <c r="E40" s="7" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>-18.2</v>
+        <v>-19.5</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="7" t="n">
-        <v>74.45</v>
+        <v>74.2</v>
       </c>
       <c r="D41" s="8" t="n"/>
       <c r="E41" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-19.5</v>
+        <v>-26.4</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B42" s="8" t="n"/>
-      <c r="C42" s="7" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="C42" s="7" t="n"/>
       <c r="D42" s="8" t="n"/>
-      <c r="E42" s="7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="E42" s="7" t="n"/>
       <c r="F42" s="8" t="n">
-        <v>-26.4</v>
+        <v>-19.9</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B43" s="8" t="n"/>
@@ -4498,807 +4490,811 @@
       <c r="D43" s="8" t="n"/>
       <c r="E43" s="7" t="n"/>
       <c r="F43" s="8" t="n">
-        <v>-19.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="n"/>
-      <c r="C44" s="7" t="n"/>
-      <c r="D44" s="8" t="n"/>
-      <c r="E44" s="7" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>21.7</v>
+      </c>
       <c r="F44" s="8" t="n">
-        <v>-15.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>21.7</v>
+        <v>22.05</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-9.4</v>
+        <v>-12</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>73.2</v>
+        <v>73.33</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>-12</v>
+        <v>-12.4</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-12.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>73.31999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>-7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D51" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>22.26</v>
+        <v>22.4</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>73.16</v>
+        <v>73.2</v>
       </c>
       <c r="D52" s="8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>-10.9</v>
+        <v>-16</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-16</v>
+        <v>-10.1</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>22.3</v>
+        <v>22.31</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>-10.1</v>
+        <v>-5.9</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>73.16</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>22.31</v>
+        <v>22.43</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>-5.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B56" s="8" t="n">
         <v>72.8</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>73.06999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>22.43</v>
+        <v>22.41</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>-9.9</v>
+        <v>-13.3</v>
       </c>
       <c r="G56" s="9" t="n">
         <v>68</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>73.11</v>
+        <v>73.06</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>-13.3</v>
+        <v>-16.6</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B58" s="8" t="n">
         <v>72.5</v>
       </c>
       <c r="C58" s="7" t="n">
-        <v>73.06</v>
+        <v>72.97</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>-16.6</v>
+        <v>-11.8</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>72.97</v>
+        <v>72.86</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>22.26</v>
+        <v>22.21</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>-11.8</v>
+        <v>-21.1</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B60" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C60" s="7" t="n">
-        <v>72.86</v>
+        <v>72.8</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>-21.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>72.8</v>
+        <v>72.69</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>22.24</v>
+        <v>22.19</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>-25.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B62" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C62" s="7" t="n">
-        <v>72.69</v>
+        <v>72.61</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>-18.3</v>
+        <v>-16</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B63" s="8" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>-16</v>
+        <v>-10.4</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="n"/>
       <c r="C64" s="7" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="D64" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="D64" s="8" t="n"/>
       <c r="E64" s="7" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>-10.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B65" s="8" t="n"/>
       <c r="C65" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="7" t="n">
-        <v>21.85</v>
+        <v>21.7</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B66" s="8" t="n"/>
       <c r="C66" s="7" t="n">
-        <v>72.58</v>
+        <v>72.5</v>
       </c>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>-12.3</v>
+        <v>-6.6</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B67" s="8" t="n"/>
       <c r="C67" s="7" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="7" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="n"/>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C68" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D68" s="8" t="n"/>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="D68" s="8" t="n">
+        <v>21.2</v>
+      </c>
       <c r="E68" s="7" t="n">
-        <v>21.73</v>
+        <v>21.63</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B69" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>21.63</v>
+        <v>21.57</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="C70" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E70" s="7" t="n">
         <v>21.57</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>-7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>72.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D71" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E71" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E71" s="7" t="n">
-        <v>21.57</v>
-      </c>
       <c r="F71" s="8" t="n">
-        <v>-10.9</v>
+        <v>-7.7</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B72" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="n"/>
       <c r="C72" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D72" s="8" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D72" s="8" t="n"/>
       <c r="E72" s="7" t="n">
         <v>21.8</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.9</v>
       </c>
       <c r="G72" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B73" s="8" t="n"/>
@@ -5310,19 +5306,19 @@
         <v>21.8</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>-8.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B74" s="8" t="n"/>
@@ -5334,274 +5330,278 @@
         <v>21.8</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>-12.5</v>
+        <v>-11.2</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B75" s="8" t="n"/>
       <c r="C75" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>-11.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G75" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B76" s="8" t="n"/>
       <c r="C76" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D76" s="8" t="n"/>
       <c r="E76" s="7" t="n">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>-13.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B77" s="8" t="n"/>
       <c r="C77" s="7" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="7" t="n">
-        <v>22.15</v>
+        <v>22.5</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="G77" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B78" s="8" t="n"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="C78" s="7" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="D78" s="8" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D78" s="8" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E78" s="7" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>-12.4</v>
+        <v>-7.8</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D79" s="8" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>20.5</v>
+        <v>20.95</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>-7.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C80" s="7" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>20.95</v>
+        <v>21.13</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>-3.1</v>
+        <v>-11.8</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>-11.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B82" s="8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B83" s="8" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>72.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D83" s="8" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>-8.6</v>
+        <v>-13.5</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B84" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C84" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="D84" s="8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>21.33</v>
+        <v>21.43</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H84" s="10" t="n">
         <v>7.7</v>
@@ -5610,277 +5610,277 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B85" s="8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>72.23</v>
+        <v>72.39</v>
       </c>
       <c r="D85" s="8" t="n">
         <v>22</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>21.43</v>
+        <v>21.64</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>-7.1</v>
+        <v>-12.5</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B86" s="8" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C86" s="7" t="n">
         <v>72.39</v>
       </c>
       <c r="D86" s="8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>21.64</v>
+        <v>21.69</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>-12.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B87" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>72.39</v>
+        <v>72.36</v>
       </c>
       <c r="D87" s="8" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>21.69</v>
+        <v>21.56</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>-6.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B88" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="n"/>
       <c r="C88" s="7" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="D88" s="8" t="n">
-        <v>20.6</v>
-      </c>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="D88" s="8" t="n"/>
       <c r="E88" s="7" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B89" s="8" t="n"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="C89" s="7" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="D89" s="8" t="n"/>
+        <v>72.45</v>
+      </c>
+      <c r="D89" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E89" s="7" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B90" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C90" s="7" t="n">
-        <v>72.45</v>
+        <v>72.47</v>
       </c>
       <c r="D90" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>21.67</v>
+        <v>21.53</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B91" s="8" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>72.47</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D91" s="8" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>21.53</v>
+        <v>21.47</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B92" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C92" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D92" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B93" s="8" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>72.31999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="D93" s="8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>-4.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B94" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="C94" s="7" t="n">
-        <v>72.23</v>
+        <v>72.3</v>
       </c>
       <c r="D94" s="8" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="E94" s="7" t="n">
         <v>21.5</v>
       </c>
-      <c r="E94" s="7" t="n">
-        <v>21.4</v>
-      </c>
       <c r="F94" s="8" t="n">
-        <v>-2.9</v>
+        <v>-11.4</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H94" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
   </sheetData>
@@ -6251,16 +6251,16 @@
         <v>50</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>51</v>
+        <v>52.8</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>420</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>234</v>
+        <v>267</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>-186</v>
+        <v>-153</v>
       </c>
     </row>
     <row r="15">

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>68</v>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>21.2</v>
+        <v>22.5</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>16</v>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>4.71</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>52.8</v>
+        <v>52.4</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -3536,7 +3536,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B5" s="8" t="n">
@@ -3546,109 +3546,105 @@
         <v>74.90000000000001</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-2.2</v>
+        <v>0.2</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>74.90000000000001</v>
+        <v>74.95</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>23.7</v>
+        <v>23.3</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>75</v>
+        <v>74.8</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>74.93000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>23.5</v>
+        <v>23.27</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>52</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n">
-        <v>74.8</v>
-      </c>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n"/>
       <c r="C8" s="7" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="D8" s="8" t="n">
-        <v>22.8</v>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="7" t="n">
-        <v>23.32</v>
+        <v>23.27</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>7.1</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B9" s="8" t="n"/>
@@ -3657,146 +3653,146 @@
       </c>
       <c r="D9" s="8" t="n"/>
       <c r="E9" s="7" t="n">
-        <v>23.32</v>
+        <v>23.27</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>6.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n"/>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>75.7</v>
+      </c>
       <c r="C10" s="7" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="D10" s="8" t="n"/>
+        <v>75.09999999999999</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>22.3</v>
+      </c>
       <c r="E10" s="7" t="n">
-        <v>23.32</v>
+        <v>23.02</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n">
-        <v>75.7</v>
-      </c>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n"/>
       <c r="C11" s="7" t="n">
-        <v>75.06</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>22.3</v>
-      </c>
+        <v>75.09999999999999</v>
+      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="7" t="n">
-        <v>23.12</v>
+        <v>23.02</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="7" t="n">
-        <v>75.09999999999999</v>
+        <v>75.17</v>
       </c>
       <c r="D12" s="8" t="n"/>
       <c r="E12" s="7" t="n">
-        <v>23.02</v>
+        <v>22.8</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>6.5</v>
+        <v>-1.4</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>6.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="7" t="n">
-        <v>75.17</v>
+        <v>75.25</v>
       </c>
       <c r="D13" s="8" t="n"/>
       <c r="E13" s="7" t="n">
-        <v>22.8</v>
+        <v>22.55</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-1.4</v>
+        <v>-1.3</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
       <c r="C14" s="7" t="n">
-        <v>75.25</v>
+        <v>75.7</v>
       </c>
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="7" t="n">
-        <v>22.55</v>
+        <v>22.3</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>-1.3</v>
+        <v>-7.7</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B15" s="8" t="n"/>
@@ -3808,19 +3804,19 @@
         <v>22.3</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.6</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B16" s="8" t="n"/>
@@ -3832,43 +3828,39 @@
         <v>22.3</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>-8.6</v>
+        <v>-16.4</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B17" s="8" t="n"/>
-      <c r="C17" s="7" t="n">
-        <v>75.7</v>
-      </c>
+      <c r="C17" s="7" t="n"/>
       <c r="D17" s="8" t="n"/>
-      <c r="E17" s="7" t="n">
-        <v>22.3</v>
-      </c>
+      <c r="E17" s="7" t="n"/>
       <c r="F17" s="8" t="n">
         <v>-16.4</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B18" s="8" t="n"/>
@@ -3876,19 +3868,19 @@
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="8" t="n">
-        <v>-16.4</v>
+        <v>-14.3</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B19" s="8" t="n"/>
@@ -3896,19 +3888,19 @@
       <c r="D19" s="8" t="n"/>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="8" t="n">
-        <v>-14.3</v>
+        <v>-9.1</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B20" s="8" t="n"/>
@@ -3916,19 +3908,19 @@
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="8" t="n">
-        <v>-9.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
@@ -3936,39 +3928,47 @@
       <c r="D21" s="8" t="n"/>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="8" t="n">
-        <v>-8.300000000000001</v>
+        <v>-5</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="7" t="n"/>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>22</v>
+      </c>
       <c r="F22" s="8" t="n">
-        <v>-5</v>
+        <v>-1.8</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
@@ -3978,103 +3978,99 @@
         <v>74.5</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-1.8</v>
+        <v>-13.8</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="n">
-        <v>74.5</v>
-      </c>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="7" t="n">
         <v>74.5</v>
       </c>
-      <c r="D24" s="8" t="n">
-        <v>23</v>
-      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="7" t="n">
         <v>22.5</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>-13.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="H24" s="10" t="n">
-        <v>8.1</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H24" s="10" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="n"/>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>74.40000000000001</v>
+      </c>
       <c r="C25" s="7" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="D25" s="8" t="n"/>
+        <v>74.47</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>23.3</v>
+      </c>
       <c r="E25" s="7" t="n">
-        <v>22.5</v>
+        <v>22.77</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-15.7</v>
+        <v>-10.5</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="H25" s="10" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="n">
-        <v>74.40000000000001</v>
-      </c>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n"/>
       <c r="C26" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D26" s="8" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="7" t="n">
         <v>22.77</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-10.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B27" s="8" t="n"/>
@@ -4086,90 +4082,94 @@
         <v>22.77</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-9.4</v>
+        <v>-7.5</v>
       </c>
       <c r="G27" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="n"/>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n">
+        <v>74.5</v>
+      </c>
       <c r="C28" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D28" s="8" t="n"/>
+      <c r="D28" s="8" t="n">
+        <v>22.9</v>
+      </c>
       <c r="E28" s="7" t="n">
-        <v>22.77</v>
+        <v>22.8</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-7.5</v>
+        <v>-4.5</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>74.47</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.2</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>23</v>
+        <v>22.93</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-2.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H30" s="10" t="n">
         <v>8</v>
@@ -4178,291 +4178,283 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C31" s="7" t="n">
         <v>74.7</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>22.93</v>
+        <v>22.78</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>74.7</v>
+        <v>74.64</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>22.78</v>
+        <v>22.6</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-11.9</v>
+        <v>-10.3</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>22.6</v>
+        <v>22.55</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-10.3</v>
+        <v>-13.7</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>74.65000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>22.55</v>
+        <v>22.57</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-13.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="n">
-        <v>74.2</v>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n"/>
       <c r="C35" s="7" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="D35" s="8" t="n">
-        <v>22.7</v>
-      </c>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D35" s="8" t="n"/>
       <c r="E35" s="7" t="n">
-        <v>22.57</v>
+        <v>22.52</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-15.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B36" s="8" t="n"/>
       <c r="C36" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.52</v>
       </c>
       <c r="D36" s="8" t="n"/>
       <c r="E36" s="7" t="n">
-        <v>22.52</v>
+        <v>22.46</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D37" s="8" t="n"/>
       <c r="E37" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-18.2</v>
+        <v>-23.1</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="7" t="n">
-        <v>74.42</v>
+        <v>74.33</v>
       </c>
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="7" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B39" s="8" t="n"/>
       <c r="C39" s="7" t="n">
-        <v>74.33</v>
+        <v>74.45</v>
       </c>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="7" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-18.2</v>
+        <v>-19.5</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B40" s="8" t="n"/>
       <c r="C40" s="7" t="n">
-        <v>74.45</v>
+        <v>74.2</v>
       </c>
       <c r="D40" s="8" t="n"/>
       <c r="E40" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>-19.5</v>
+        <v>-26.4</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B41" s="8" t="n"/>
-      <c r="C41" s="7" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="C41" s="7" t="n"/>
       <c r="D41" s="8" t="n"/>
-      <c r="E41" s="7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="E41" s="7" t="n"/>
       <c r="F41" s="8" t="n">
-        <v>-26.4</v>
+        <v>-19.9</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B42" s="8" t="n"/>
@@ -4470,807 +4462,811 @@
       <c r="D42" s="8" t="n"/>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="8" t="n">
-        <v>-19.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B43" s="8" t="n"/>
-      <c r="C43" s="7" t="n"/>
-      <c r="D43" s="8" t="n"/>
-      <c r="E43" s="7" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C43" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E43" s="7" t="n">
+        <v>21.7</v>
+      </c>
       <c r="F43" s="8" t="n">
-        <v>-15.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>21.7</v>
+        <v>22.05</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>-9.4</v>
+        <v>-12</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>73.2</v>
+        <v>73.33</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-12</v>
+        <v>-12.4</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>-12.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>73.31999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D50" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>22.26</v>
+        <v>22.4</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>73.16</v>
+        <v>73.2</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-10.9</v>
+        <v>-16</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="D52" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>-16</v>
+        <v>-10.1</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>22.3</v>
+        <v>22.31</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-10.1</v>
+        <v>-5.9</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>73.16</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>22.31</v>
+        <v>22.43</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>-5.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
         <v>72.8</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>73.06999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>22.43</v>
+        <v>22.41</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>-9.9</v>
+        <v>-13.3</v>
       </c>
       <c r="G55" s="9" t="n">
         <v>68</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>73.11</v>
+        <v>73.06</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>-13.3</v>
+        <v>-16.6</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
         <v>72.5</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>73.06</v>
+        <v>72.97</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>-16.6</v>
+        <v>-11.8</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C58" s="7" t="n">
-        <v>72.97</v>
+        <v>72.86</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>22.26</v>
+        <v>22.21</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>-11.8</v>
+        <v>-21.1</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>72.86</v>
+        <v>72.8</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>-21.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B60" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C60" s="7" t="n">
-        <v>72.8</v>
+        <v>72.69</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>22.24</v>
+        <v>22.19</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>-25.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>72.69</v>
+        <v>72.61</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>-18.3</v>
+        <v>-16</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B62" s="8" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C62" s="7" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>-16</v>
+        <v>-10.4</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B63" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="n"/>
       <c r="C63" s="7" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="D63" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="D63" s="8" t="n"/>
       <c r="E63" s="7" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>-10.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B64" s="8" t="n"/>
       <c r="C64" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="7" t="n">
-        <v>21.85</v>
+        <v>21.7</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B65" s="8" t="n"/>
       <c r="C65" s="7" t="n">
-        <v>72.58</v>
+        <v>72.5</v>
       </c>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>-12.3</v>
+        <v>-6.6</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B66" s="8" t="n"/>
       <c r="C66" s="7" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="7" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="n"/>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C67" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D67" s="8" t="n"/>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="D67" s="8" t="n">
+        <v>21.2</v>
+      </c>
       <c r="E67" s="7" t="n">
-        <v>21.73</v>
+        <v>21.63</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B68" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C68" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>21.63</v>
+        <v>21.57</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B69" s="8" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E69" s="7" t="n">
         <v>21.57</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>-7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C70" s="7" t="n">
-        <v>72.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D70" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E70" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E70" s="7" t="n">
-        <v>21.57</v>
-      </c>
       <c r="F70" s="8" t="n">
-        <v>-10.9</v>
+        <v>-7.7</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B71" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="n"/>
       <c r="C71" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D71" s="8" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D71" s="8" t="n"/>
       <c r="E71" s="7" t="n">
         <v>21.8</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.9</v>
       </c>
       <c r="G71" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B72" s="8" t="n"/>
@@ -5282,19 +5278,19 @@
         <v>21.8</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>-8.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B73" s="8" t="n"/>
@@ -5306,274 +5302,278 @@
         <v>21.8</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>-12.5</v>
+        <v>-11.2</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B74" s="8" t="n"/>
       <c r="C74" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>-11.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G74" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B75" s="8" t="n"/>
       <c r="C75" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="7" t="n">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>-13.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B76" s="8" t="n"/>
       <c r="C76" s="7" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D76" s="8" t="n"/>
       <c r="E76" s="7" t="n">
-        <v>22.15</v>
+        <v>22.5</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="G76" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B77" s="8" t="n"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="C77" s="7" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="D77" s="8" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D77" s="8" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E77" s="7" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>-12.4</v>
+        <v>-7.8</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C78" s="7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D78" s="8" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>20.5</v>
+        <v>20.95</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>-7.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D79" s="8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>20.95</v>
+        <v>21.13</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>-3.1</v>
+        <v>-11.8</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C80" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>-11.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B82" s="8" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>72.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>-8.6</v>
+        <v>-13.5</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B83" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="D83" s="8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>21.33</v>
+        <v>21.43</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H83" s="10" t="n">
         <v>7.7</v>
@@ -5582,305 +5582,305 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B84" s="8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="C84" s="7" t="n">
-        <v>72.23</v>
+        <v>72.39</v>
       </c>
       <c r="D84" s="8" t="n">
         <v>22</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>21.43</v>
+        <v>21.64</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>-7.1</v>
+        <v>-12.5</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B85" s="8" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C85" s="7" t="n">
         <v>72.39</v>
       </c>
       <c r="D85" s="8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>21.64</v>
+        <v>21.69</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>-12.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B86" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C86" s="7" t="n">
-        <v>72.39</v>
+        <v>72.36</v>
       </c>
       <c r="D86" s="8" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>21.69</v>
+        <v>21.56</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>-6.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B87" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="n"/>
       <c r="C87" s="7" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="D87" s="8" t="n">
-        <v>20.6</v>
-      </c>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="D87" s="8" t="n"/>
       <c r="E87" s="7" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B88" s="8" t="n"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="C88" s="7" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="D88" s="8" t="n"/>
+        <v>72.45</v>
+      </c>
+      <c r="D88" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E88" s="7" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B89" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>72.45</v>
+        <v>72.47</v>
       </c>
       <c r="D89" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>21.67</v>
+        <v>21.53</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B90" s="8" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C90" s="7" t="n">
-        <v>72.47</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D90" s="8" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>21.53</v>
+        <v>21.47</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B91" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D91" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B92" s="8" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C92" s="7" t="n">
-        <v>72.31999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="D92" s="8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>-4.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B93" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>72.23</v>
+        <v>72.3</v>
       </c>
       <c r="D93" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>21.4</v>
+        <v>21.55</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>-1.6</v>
+        <v>-15.1</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B94" s="8" t="n">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="C94" s="7" t="n">
-        <v>72.3</v>
+        <v>72.37</v>
       </c>
       <c r="D94" s="8" t="n">
-        <v>21.2</v>
+        <v>22.5</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>21.5</v>
+        <v>21.69</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>-11.4</v>
+        <v>-7.2</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H94" s="10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
   </sheetData>
@@ -6251,16 +6251,16 @@
         <v>50</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>52.8</v>
+        <v>52.4</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>420</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>267</v>
+        <v>443</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>-153</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -662,7 +662,7 @@
       </c>
       <c r="B10" s="4" t="n"/>
       <c r="C10" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>52.4</v>
+        <v>53</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -5874,7 +5874,7 @@
         <v>21.69</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>-7.2</v>
+        <v>-10.3</v>
       </c>
       <c r="G94" s="9" t="n">
         <v>45</v>
@@ -6251,16 +6251,16 @@
         <v>50</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>52.4</v>
+        <v>53</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>420</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>443</v>
+        <v>471</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>23</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15">

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>53</v>
+        <v>53.8</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -3536,91 +3536,87 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>74.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>23.7</v>
+        <v>23.3</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>23.7</v>
+        <v>23.3</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>75</v>
+        <v>74.8</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>74.95</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>23.5</v>
+        <v>23.05</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="G6" s="9" t="n">
         <v>52</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>74.8</v>
-      </c>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n"/>
       <c r="C7" s="7" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="D7" s="8" t="n">
-        <v>22.8</v>
-      </c>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="7" t="n">
-        <v>23.27</v>
+        <v>23.05</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>7.1</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
@@ -3629,146 +3625,146 @@
       </c>
       <c r="D8" s="8" t="n"/>
       <c r="E8" s="7" t="n">
-        <v>23.27</v>
+        <v>23.05</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>6.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n"/>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>75.7</v>
+      </c>
       <c r="C9" s="7" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="D9" s="8" t="n"/>
+        <v>75.17</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>22.3</v>
+      </c>
       <c r="E9" s="7" t="n">
-        <v>23.27</v>
+        <v>22.8</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n">
-        <v>75.7</v>
-      </c>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n"/>
       <c r="C10" s="7" t="n">
-        <v>75.09999999999999</v>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>22.3</v>
-      </c>
+        <v>75.17</v>
+      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="7" t="n">
-        <v>23.02</v>
+        <v>22.8</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
       <c r="C11" s="7" t="n">
-        <v>75.09999999999999</v>
+        <v>75.17</v>
       </c>
       <c r="D11" s="8" t="n"/>
       <c r="E11" s="7" t="n">
-        <v>23.02</v>
+        <v>22.8</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>6.5</v>
+        <v>-1.4</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>6.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="7" t="n">
-        <v>75.17</v>
+        <v>75.25</v>
       </c>
       <c r="D12" s="8" t="n"/>
       <c r="E12" s="7" t="n">
-        <v>22.8</v>
+        <v>22.55</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>-1.4</v>
+        <v>-1.3</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="7" t="n">
-        <v>75.25</v>
+        <v>75.7</v>
       </c>
       <c r="D13" s="8" t="n"/>
       <c r="E13" s="7" t="n">
-        <v>22.55</v>
+        <v>22.3</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-1.3</v>
+        <v>-7.7</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
@@ -3780,19 +3776,19 @@
         <v>22.3</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.6</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B15" s="8" t="n"/>
@@ -3804,43 +3800,39 @@
         <v>22.3</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-8.6</v>
+        <v>-16.4</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B16" s="8" t="n"/>
-      <c r="C16" s="7" t="n">
-        <v>75.7</v>
-      </c>
+      <c r="C16" s="7" t="n"/>
       <c r="D16" s="8" t="n"/>
-      <c r="E16" s="7" t="n">
-        <v>22.3</v>
-      </c>
+      <c r="E16" s="7" t="n"/>
       <c r="F16" s="8" t="n">
         <v>-16.4</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B17" s="8" t="n"/>
@@ -3848,19 +3840,19 @@
       <c r="D17" s="8" t="n"/>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="8" t="n">
-        <v>-16.4</v>
+        <v>-14.3</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B18" s="8" t="n"/>
@@ -3868,19 +3860,19 @@
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="8" t="n">
-        <v>-14.3</v>
+        <v>-9.1</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B19" s="8" t="n"/>
@@ -3888,19 +3880,19 @@
       <c r="D19" s="8" t="n"/>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="8" t="n">
-        <v>-9.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B20" s="8" t="n"/>
@@ -3908,39 +3900,47 @@
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="8" t="n">
-        <v>-8.300000000000001</v>
+        <v>-5</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="7" t="n"/>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>22</v>
+      </c>
       <c r="F21" s="8" t="n">
-        <v>-5</v>
+        <v>-1.8</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B22" s="8" t="n">
@@ -3950,103 +3950,99 @@
         <v>74.5</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-1.8</v>
+        <v>-13.8</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="n">
-        <v>74.5</v>
-      </c>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n"/>
       <c r="C23" s="7" t="n">
         <v>74.5</v>
       </c>
-      <c r="D23" s="8" t="n">
-        <v>23</v>
-      </c>
+      <c r="D23" s="8" t="n"/>
       <c r="E23" s="7" t="n">
         <v>22.5</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-13.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="H23" s="10" t="n">
-        <v>8.1</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="n"/>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>74.40000000000001</v>
+      </c>
       <c r="C24" s="7" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="D24" s="8" t="n"/>
+        <v>74.47</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>23.3</v>
+      </c>
       <c r="E24" s="7" t="n">
-        <v>22.5</v>
+        <v>22.77</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>-15.7</v>
+        <v>-10.5</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="H24" s="10" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="H24" s="10" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="n">
-        <v>74.40000000000001</v>
-      </c>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D25" s="8" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="D25" s="8" t="n"/>
       <c r="E25" s="7" t="n">
         <v>22.77</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-10.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B26" s="8" t="n"/>
@@ -4058,90 +4054,94 @@
         <v>22.77</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-9.4</v>
+        <v>-7.5</v>
       </c>
       <c r="G26" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="n"/>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>74.5</v>
+      </c>
       <c r="C27" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D27" s="8" t="n"/>
+      <c r="D27" s="8" t="n">
+        <v>22.9</v>
+      </c>
       <c r="E27" s="7" t="n">
-        <v>22.77</v>
+        <v>22.8</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-7.5</v>
+        <v>-4.5</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>74.47</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.2</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>23</v>
+        <v>22.93</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-2.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H29" s="10" t="n">
         <v>8</v>
@@ -4150,291 +4150,283 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C30" s="7" t="n">
         <v>74.7</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>22.93</v>
+        <v>22.78</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>74.7</v>
+        <v>74.64</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>22.78</v>
+        <v>22.6</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-11.9</v>
+        <v>-10.3</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>22.6</v>
+        <v>22.55</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-10.3</v>
+        <v>-13.7</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>74.65000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>22.55</v>
+        <v>22.57</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-13.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="n">
-        <v>74.2</v>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="n"/>
       <c r="C34" s="7" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="D34" s="8" t="n">
-        <v>22.7</v>
-      </c>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D34" s="8" t="n"/>
       <c r="E34" s="7" t="n">
-        <v>22.57</v>
+        <v>22.52</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-15.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.52</v>
       </c>
       <c r="D35" s="8" t="n"/>
       <c r="E35" s="7" t="n">
-        <v>22.52</v>
+        <v>22.46</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B36" s="8" t="n"/>
       <c r="C36" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D36" s="8" t="n"/>
       <c r="E36" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>-18.2</v>
+        <v>-23.1</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="7" t="n">
-        <v>74.42</v>
+        <v>74.33</v>
       </c>
       <c r="D37" s="8" t="n"/>
       <c r="E37" s="7" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="7" t="n">
-        <v>74.33</v>
+        <v>74.45</v>
       </c>
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="7" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>-18.2</v>
+        <v>-19.5</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B39" s="8" t="n"/>
       <c r="C39" s="7" t="n">
-        <v>74.45</v>
+        <v>74.2</v>
       </c>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-19.5</v>
+        <v>-26.4</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B40" s="8" t="n"/>
-      <c r="C40" s="7" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="C40" s="7" t="n"/>
       <c r="D40" s="8" t="n"/>
-      <c r="E40" s="7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="E40" s="7" t="n"/>
       <c r="F40" s="8" t="n">
-        <v>-26.4</v>
+        <v>-19.9</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B41" s="8" t="n"/>
@@ -4442,807 +4434,811 @@
       <c r="D41" s="8" t="n"/>
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="8" t="n">
-        <v>-19.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="n"/>
-      <c r="C42" s="7" t="n"/>
-      <c r="D42" s="8" t="n"/>
-      <c r="E42" s="7" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>21.7</v>
+      </c>
       <c r="F42" s="8" t="n">
-        <v>-15.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>21.7</v>
+        <v>22.05</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-9.4</v>
+        <v>-12</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>73.2</v>
+        <v>73.33</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>-12</v>
+        <v>-12.4</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-12.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>73.31999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>-7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D49" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>22.26</v>
+        <v>22.4</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>73.16</v>
+        <v>73.2</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>-10.9</v>
+        <v>-16</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-16</v>
+        <v>-10.1</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D52" s="8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>22.3</v>
+        <v>22.31</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>-10.1</v>
+        <v>-5.9</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>73.16</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>22.31</v>
+        <v>22.43</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-5.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B54" s="8" t="n">
         <v>72.8</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>73.06999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>22.43</v>
+        <v>22.41</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>-9.9</v>
+        <v>-13.3</v>
       </c>
       <c r="G54" s="9" t="n">
         <v>68</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>73.11</v>
+        <v>73.06</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>-13.3</v>
+        <v>-16.6</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B56" s="8" t="n">
         <v>72.5</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>73.06</v>
+        <v>72.97</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>-16.6</v>
+        <v>-11.8</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>72.97</v>
+        <v>72.86</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>22.26</v>
+        <v>22.21</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>-11.8</v>
+        <v>-21.1</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C58" s="7" t="n">
-        <v>72.86</v>
+        <v>72.8</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>-21.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>72.8</v>
+        <v>72.69</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>22.24</v>
+        <v>22.19</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>-25.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B60" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C60" s="7" t="n">
-        <v>72.69</v>
+        <v>72.61</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>-18.3</v>
+        <v>-16</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>-16</v>
+        <v>-10.4</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B62" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="n"/>
       <c r="C62" s="7" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="D62" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="D62" s="8" t="n"/>
       <c r="E62" s="7" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>-10.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B63" s="8" t="n"/>
       <c r="C63" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="7" t="n">
-        <v>21.85</v>
+        <v>21.7</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B64" s="8" t="n"/>
       <c r="C64" s="7" t="n">
-        <v>72.58</v>
+        <v>72.5</v>
       </c>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>-12.3</v>
+        <v>-6.6</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B65" s="8" t="n"/>
       <c r="C65" s="7" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="7" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B66" s="8" t="n"/>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C66" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D66" s="8" t="n"/>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="D66" s="8" t="n">
+        <v>21.2</v>
+      </c>
       <c r="E66" s="7" t="n">
-        <v>21.73</v>
+        <v>21.63</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B67" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>21.63</v>
+        <v>21.57</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B68" s="8" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="C68" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E68" s="7" t="n">
         <v>21.57</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>-7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B69" s="8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>72.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D69" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E69" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E69" s="7" t="n">
-        <v>21.57</v>
-      </c>
       <c r="F69" s="8" t="n">
-        <v>-10.9</v>
+        <v>-7.7</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="n"/>
       <c r="C70" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D70" s="8" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D70" s="8" t="n"/>
       <c r="E70" s="7" t="n">
         <v>21.8</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.9</v>
       </c>
       <c r="G70" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B71" s="8" t="n"/>
@@ -5254,19 +5250,19 @@
         <v>21.8</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>-8.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B72" s="8" t="n"/>
@@ -5278,274 +5274,278 @@
         <v>21.8</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>-12.5</v>
+        <v>-11.2</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B73" s="8" t="n"/>
       <c r="C73" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>-11.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G73" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B74" s="8" t="n"/>
       <c r="C74" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="7" t="n">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>-13.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B75" s="8" t="n"/>
       <c r="C75" s="7" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="7" t="n">
-        <v>22.15</v>
+        <v>22.5</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="G75" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B76" s="8" t="n"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="C76" s="7" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="D76" s="8" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D76" s="8" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E76" s="7" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>-12.4</v>
+        <v>-7.8</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B77" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C77" s="7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>20.5</v>
+        <v>20.95</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>-7.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C78" s="7" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D78" s="8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>20.95</v>
+        <v>21.13</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>-3.1</v>
+        <v>-11.8</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D79" s="8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>-11.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="C80" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>72.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>-8.6</v>
+        <v>-13.5</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B82" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>21.33</v>
+        <v>21.43</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H82" s="10" t="n">
         <v>7.7</v>
@@ -5554,333 +5554,329 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B83" s="8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>72.23</v>
+        <v>72.39</v>
       </c>
       <c r="D83" s="8" t="n">
         <v>22</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>21.43</v>
+        <v>21.64</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>-7.1</v>
+        <v>-12.5</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B84" s="8" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C84" s="7" t="n">
         <v>72.39</v>
       </c>
       <c r="D84" s="8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>21.64</v>
+        <v>21.69</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>-12.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B85" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>72.39</v>
+        <v>72.36</v>
       </c>
       <c r="D85" s="8" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>21.69</v>
+        <v>21.56</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>-6.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B86" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="n"/>
       <c r="C86" s="7" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="D86" s="8" t="n">
-        <v>20.6</v>
-      </c>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="D86" s="8" t="n"/>
       <c r="E86" s="7" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B87" s="8" t="n"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="C87" s="7" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="D87" s="8" t="n"/>
+        <v>72.45</v>
+      </c>
+      <c r="D87" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E87" s="7" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B88" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C88" s="7" t="n">
-        <v>72.45</v>
+        <v>72.47</v>
       </c>
       <c r="D88" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>21.67</v>
+        <v>21.53</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B89" s="8" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>72.47</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D89" s="8" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>21.53</v>
+        <v>21.47</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B90" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C90" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D90" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B91" s="8" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>72.31999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="D91" s="8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>-4.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B92" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="C92" s="7" t="n">
-        <v>72.23</v>
+        <v>72.3</v>
       </c>
       <c r="D92" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>21.4</v>
+        <v>21.55</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>-1.6</v>
+        <v>-15.1</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B93" s="8" t="n">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>72.3</v>
+        <v>72.37</v>
       </c>
       <c r="D93" s="8" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>21.55</v>
+        <v>21.69</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>-15.1</v>
+        <v>-10.3</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B94" s="8" t="n">
-        <v>72.8</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="n"/>
       <c r="C94" s="7" t="n">
-        <v>72.37</v>
-      </c>
-      <c r="D94" s="8" t="n">
-        <v>22.5</v>
-      </c>
+        <v>72.28</v>
+      </c>
+      <c r="D94" s="8" t="n"/>
       <c r="E94" s="7" t="n">
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>-10.3</v>
+        <v>-12.6</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H94" s="10" t="n">
-        <v>5.7</v>
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>
@@ -6280,7 +6276,9 @@
       <c r="D15" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="E15" s="8" t="n"/>
+      <c r="E15" s="8" t="n">
+        <v>53.8</v>
+      </c>
       <c r="F15" s="4" t="n">
         <v>500</v>
       </c>

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>53.8</v>
+        <v>58.4</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -3536,211 +3536,207 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>75</v>
+        <v>74.8</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>75</v>
+        <v>74.8</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="G5" s="9" t="n">
         <v>52</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n">
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="7" t="n">
         <v>74.8</v>
       </c>
-      <c r="C6" s="7" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="7" t="n">
         <v>22.8</v>
       </c>
-      <c r="E6" s="7" t="n">
-        <v>23.05</v>
-      </c>
       <c r="F6" s="8" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>7.1</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="7" t="n">
-        <v>74.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D7" s="8" t="n"/>
       <c r="E7" s="7" t="n">
-        <v>23.05</v>
+        <v>22.8</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>6.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n"/>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>75.7</v>
+      </c>
       <c r="C8" s="7" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="D8" s="8" t="n"/>
+        <v>75.25</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>22.3</v>
+      </c>
       <c r="E8" s="7" t="n">
-        <v>23.05</v>
+        <v>22.55</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n">
-        <v>75.7</v>
-      </c>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n"/>
       <c r="C9" s="7" t="n">
-        <v>75.17</v>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>22.3</v>
-      </c>
+        <v>75.25</v>
+      </c>
+      <c r="D9" s="8" t="n"/>
       <c r="E9" s="7" t="n">
-        <v>22.8</v>
+        <v>22.55</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
       <c r="C10" s="7" t="n">
-        <v>75.17</v>
+        <v>75.25</v>
       </c>
       <c r="D10" s="8" t="n"/>
       <c r="E10" s="7" t="n">
-        <v>22.8</v>
+        <v>22.55</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>6.5</v>
+        <v>-1.4</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>6.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
       <c r="C11" s="7" t="n">
-        <v>75.17</v>
+        <v>75.25</v>
       </c>
       <c r="D11" s="8" t="n"/>
       <c r="E11" s="7" t="n">
-        <v>22.8</v>
+        <v>22.55</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-1.4</v>
+        <v>-1.3</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="7" t="n">
-        <v>75.25</v>
+        <v>75.7</v>
       </c>
       <c r="D12" s="8" t="n"/>
       <c r="E12" s="7" t="n">
-        <v>22.55</v>
+        <v>22.3</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>-1.3</v>
+        <v>-7.7</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
@@ -3752,19 +3748,19 @@
         <v>22.3</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.6</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
@@ -3776,43 +3772,39 @@
         <v>22.3</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>-8.6</v>
+        <v>-16.4</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B15" s="8" t="n"/>
-      <c r="C15" s="7" t="n">
-        <v>75.7</v>
-      </c>
+      <c r="C15" s="7" t="n"/>
       <c r="D15" s="8" t="n"/>
-      <c r="E15" s="7" t="n">
-        <v>22.3</v>
-      </c>
+      <c r="E15" s="7" t="n"/>
       <c r="F15" s="8" t="n">
         <v>-16.4</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B16" s="8" t="n"/>
@@ -3820,19 +3812,19 @@
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="8" t="n">
-        <v>-16.4</v>
+        <v>-14.3</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B17" s="8" t="n"/>
@@ -3840,19 +3832,19 @@
       <c r="D17" s="8" t="n"/>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="8" t="n">
-        <v>-14.3</v>
+        <v>-9.1</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B18" s="8" t="n"/>
@@ -3860,19 +3852,19 @@
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="8" t="n">
-        <v>-9.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B19" s="8" t="n"/>
@@ -3880,39 +3872,47 @@
       <c r="D19" s="8" t="n"/>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="8" t="n">
-        <v>-8.300000000000001</v>
+        <v>-5</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="7" t="n"/>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>22</v>
+      </c>
       <c r="F20" s="8" t="n">
-        <v>-5</v>
+        <v>-1.8</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
@@ -3922,103 +3922,99 @@
         <v>74.5</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-1.8</v>
+        <v>-13.8</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="n">
-        <v>74.5</v>
-      </c>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n"/>
       <c r="C22" s="7" t="n">
         <v>74.5</v>
       </c>
-      <c r="D22" s="8" t="n">
-        <v>23</v>
-      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="7" t="n">
         <v>22.5</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-13.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="H22" s="10" t="n">
-        <v>8.1</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="n"/>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>74.40000000000001</v>
+      </c>
       <c r="C23" s="7" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="D23" s="8" t="n"/>
+        <v>74.47</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>23.3</v>
+      </c>
       <c r="E23" s="7" t="n">
-        <v>22.5</v>
+        <v>22.77</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-15.7</v>
+        <v>-10.5</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="H23" s="10" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="H23" s="10" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="n">
-        <v>74.40000000000001</v>
-      </c>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D24" s="8" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="7" t="n">
         <v>22.77</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>-10.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B25" s="8" t="n"/>
@@ -4030,90 +4026,94 @@
         <v>22.77</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-9.4</v>
+        <v>-7.5</v>
       </c>
       <c r="G25" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="n"/>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n">
+        <v>74.5</v>
+      </c>
       <c r="C26" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D26" s="8" t="n"/>
+      <c r="D26" s="8" t="n">
+        <v>22.9</v>
+      </c>
       <c r="E26" s="7" t="n">
-        <v>22.77</v>
+        <v>22.8</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-7.5</v>
+        <v>-4.5</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>74.47</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.2</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>23</v>
+        <v>22.93</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-2.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H28" s="10" t="n">
         <v>8</v>
@@ -4122,291 +4122,283 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C29" s="7" t="n">
         <v>74.7</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>22.93</v>
+        <v>22.78</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>74.7</v>
+        <v>74.64</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>22.78</v>
+        <v>22.6</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-11.9</v>
+        <v>-10.3</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>22.6</v>
+        <v>22.55</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-10.3</v>
+        <v>-13.7</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>74.65000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>22.55</v>
+        <v>22.57</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-13.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="n">
-        <v>74.2</v>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n"/>
       <c r="C33" s="7" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="D33" s="8" t="n">
-        <v>22.7</v>
-      </c>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D33" s="8" t="n"/>
       <c r="E33" s="7" t="n">
-        <v>22.57</v>
+        <v>22.52</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-15.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.52</v>
       </c>
       <c r="D34" s="8" t="n"/>
       <c r="E34" s="7" t="n">
-        <v>22.52</v>
+        <v>22.46</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D35" s="8" t="n"/>
       <c r="E35" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-18.2</v>
+        <v>-23.1</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B36" s="8" t="n"/>
       <c r="C36" s="7" t="n">
-        <v>74.42</v>
+        <v>74.33</v>
       </c>
       <c r="D36" s="8" t="n"/>
       <c r="E36" s="7" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="7" t="n">
-        <v>74.33</v>
+        <v>74.45</v>
       </c>
       <c r="D37" s="8" t="n"/>
       <c r="E37" s="7" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-18.2</v>
+        <v>-19.5</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="7" t="n">
-        <v>74.45</v>
+        <v>74.2</v>
       </c>
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>-19.5</v>
+        <v>-26.4</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B39" s="8" t="n"/>
-      <c r="C39" s="7" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="C39" s="7" t="n"/>
       <c r="D39" s="8" t="n"/>
-      <c r="E39" s="7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="E39" s="7" t="n"/>
       <c r="F39" s="8" t="n">
-        <v>-26.4</v>
+        <v>-19.9</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B40" s="8" t="n"/>
@@ -4414,807 +4406,811 @@
       <c r="D40" s="8" t="n"/>
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="8" t="n">
-        <v>-19.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B41" s="8" t="n"/>
-      <c r="C41" s="7" t="n"/>
-      <c r="D41" s="8" t="n"/>
-      <c r="E41" s="7" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E41" s="7" t="n">
+        <v>21.7</v>
+      </c>
       <c r="F41" s="8" t="n">
-        <v>-15.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>21.7</v>
+        <v>22.05</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>-9.4</v>
+        <v>-12</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>73.2</v>
+        <v>73.33</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-12</v>
+        <v>-12.4</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>-12.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>73.31999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D48" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>22.26</v>
+        <v>22.4</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>73.16</v>
+        <v>73.2</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-10.9</v>
+        <v>-16</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>-16</v>
+        <v>-10.1</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>22.3</v>
+        <v>22.31</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-10.1</v>
+        <v>-5.9</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>73.16</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D52" s="8" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>22.31</v>
+        <v>22.43</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>-5.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
         <v>72.8</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>73.06999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>22.43</v>
+        <v>22.41</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-9.9</v>
+        <v>-13.3</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>68</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>73.11</v>
+        <v>73.06</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>-13.3</v>
+        <v>-16.6</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
         <v>72.5</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>73.06</v>
+        <v>72.97</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>-16.6</v>
+        <v>-11.8</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>72.97</v>
+        <v>72.86</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>22.26</v>
+        <v>22.21</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>-11.8</v>
+        <v>-21.1</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>72.86</v>
+        <v>72.8</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>-21.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C58" s="7" t="n">
-        <v>72.8</v>
+        <v>72.69</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>22.24</v>
+        <v>22.19</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>-25.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>72.69</v>
+        <v>72.61</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>-18.3</v>
+        <v>-16</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B60" s="8" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C60" s="7" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>-16</v>
+        <v>-10.4</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n"/>
       <c r="C61" s="7" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="D61" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="D61" s="8" t="n"/>
       <c r="E61" s="7" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>-10.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B62" s="8" t="n"/>
       <c r="C62" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="7" t="n">
-        <v>21.85</v>
+        <v>21.7</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B63" s="8" t="n"/>
       <c r="C63" s="7" t="n">
-        <v>72.58</v>
+        <v>72.5</v>
       </c>
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>-12.3</v>
+        <v>-6.6</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B64" s="8" t="n"/>
       <c r="C64" s="7" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="7" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B65" s="8" t="n"/>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C65" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D65" s="8" t="n"/>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="D65" s="8" t="n">
+        <v>21.2</v>
+      </c>
       <c r="E65" s="7" t="n">
-        <v>21.73</v>
+        <v>21.63</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B66" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>21.63</v>
+        <v>21.57</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B67" s="8" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E67" s="7" t="n">
         <v>21.57</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>-7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B68" s="8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C68" s="7" t="n">
-        <v>72.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D68" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E68" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E68" s="7" t="n">
-        <v>21.57</v>
-      </c>
       <c r="F68" s="8" t="n">
-        <v>-10.9</v>
+        <v>-7.7</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B69" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="n"/>
       <c r="C69" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D69" s="8" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D69" s="8" t="n"/>
       <c r="E69" s="7" t="n">
         <v>21.8</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.9</v>
       </c>
       <c r="G69" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B70" s="8" t="n"/>
@@ -5226,19 +5222,19 @@
         <v>21.8</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>-8.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B71" s="8" t="n"/>
@@ -5250,274 +5246,278 @@
         <v>21.8</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>-12.5</v>
+        <v>-11.2</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B72" s="8" t="n"/>
       <c r="C72" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="D72" s="8" t="n"/>
       <c r="E72" s="7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>-11.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G72" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B73" s="8" t="n"/>
       <c r="C73" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="7" t="n">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>-13.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B74" s="8" t="n"/>
       <c r="C74" s="7" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="7" t="n">
-        <v>22.15</v>
+        <v>22.5</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="G74" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B75" s="8" t="n"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="C75" s="7" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="D75" s="8" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D75" s="8" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E75" s="7" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>-12.4</v>
+        <v>-7.8</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B76" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>20.5</v>
+        <v>20.95</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>-7.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B77" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C77" s="7" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>20.95</v>
+        <v>21.13</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>-3.1</v>
+        <v>-11.8</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C78" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D78" s="8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>-11.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D79" s="8" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C80" s="7" t="n">
-        <v>72.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>-8.6</v>
+        <v>-13.5</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>21.33</v>
+        <v>21.43</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H81" s="10" t="n">
         <v>7.7</v>
@@ -5526,357 +5526,353 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B82" s="8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>72.23</v>
+        <v>72.39</v>
       </c>
       <c r="D82" s="8" t="n">
         <v>22</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>21.43</v>
+        <v>21.64</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>-7.1</v>
+        <v>-12.5</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B83" s="8" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C83" s="7" t="n">
         <v>72.39</v>
       </c>
       <c r="D83" s="8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>21.64</v>
+        <v>21.69</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>-12.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B84" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C84" s="7" t="n">
-        <v>72.39</v>
+        <v>72.36</v>
       </c>
       <c r="D84" s="8" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>21.69</v>
+        <v>21.56</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>-6.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B85" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="n"/>
       <c r="C85" s="7" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="D85" s="8" t="n">
-        <v>20.6</v>
-      </c>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="D85" s="8" t="n"/>
       <c r="E85" s="7" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B86" s="8" t="n"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="C86" s="7" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="D86" s="8" t="n"/>
+        <v>72.45</v>
+      </c>
+      <c r="D86" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E86" s="7" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B87" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>72.45</v>
+        <v>72.47</v>
       </c>
       <c r="D87" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>21.67</v>
+        <v>21.53</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B88" s="8" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C88" s="7" t="n">
-        <v>72.47</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D88" s="8" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>21.53</v>
+        <v>21.47</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B89" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D89" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B90" s="8" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C90" s="7" t="n">
-        <v>72.31999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="D90" s="8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>-4.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B91" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>72.23</v>
+        <v>72.3</v>
       </c>
       <c r="D91" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>21.4</v>
+        <v>21.55</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>-1.6</v>
+        <v>-15.1</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B92" s="8" t="n">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="C92" s="7" t="n">
-        <v>72.3</v>
+        <v>72.37</v>
       </c>
       <c r="D92" s="8" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>21.55</v>
+        <v>21.69</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>-15.1</v>
+        <v>-10.3</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B93" s="8" t="n">
-        <v>72.8</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="n"/>
       <c r="C93" s="7" t="n">
-        <v>72.37</v>
-      </c>
-      <c r="D93" s="8" t="n">
-        <v>22.5</v>
-      </c>
+        <v>72.28</v>
+      </c>
+      <c r="D93" s="8" t="n"/>
       <c r="E93" s="7" t="n">
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>-10.3</v>
+        <v>-14.8</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>5.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B94" s="8" t="n"/>
       <c r="C94" s="7" t="n">
-        <v>72.28</v>
+        <v>72.3</v>
       </c>
       <c r="D94" s="8" t="n"/>
       <c r="E94" s="7" t="n">
-        <v>21.67</v>
+        <v>21.78</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>-12.6</v>
+        <v>-32.1</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H94" s="10" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -6277,13 +6273,17 @@
         <v>53</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>53.8</v>
+        <v>58.4</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="11" t="n"/>
+      <c r="G15" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>-393</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>58.4</v>
+        <v>62.2</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -3536,183 +3536,171 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>22.8</v>
-      </c>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="7" t="n"/>
       <c r="F5" s="8" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>7.1</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
-      <c r="C6" s="7" t="n">
-        <v>74.8</v>
-      </c>
+      <c r="C6" s="7" t="n"/>
       <c r="D6" s="8" t="n"/>
-      <c r="E6" s="7" t="n">
-        <v>22.8</v>
-      </c>
+      <c r="E6" s="7" t="n"/>
       <c r="F6" s="8" t="n">
-        <v>6.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n"/>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>75.7</v>
+      </c>
       <c r="C7" s="7" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="D7" s="8" t="n"/>
+        <v>75.7</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>22.3</v>
+      </c>
       <c r="E7" s="7" t="n">
-        <v>22.8</v>
+        <v>22.3</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n">
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="7" t="n">
         <v>75.7</v>
       </c>
-      <c r="C8" s="7" t="n">
-        <v>75.25</v>
-      </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="7" t="n">
         <v>22.3</v>
       </c>
-      <c r="E8" s="7" t="n">
-        <v>22.55</v>
-      </c>
       <c r="F8" s="8" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B9" s="8" t="n"/>
       <c r="C9" s="7" t="n">
-        <v>75.25</v>
+        <v>75.7</v>
       </c>
       <c r="D9" s="8" t="n"/>
       <c r="E9" s="7" t="n">
-        <v>22.55</v>
+        <v>22.3</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>6.5</v>
+        <v>-1.4</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>6.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
       <c r="C10" s="7" t="n">
-        <v>75.25</v>
+        <v>75.7</v>
       </c>
       <c r="D10" s="8" t="n"/>
       <c r="E10" s="7" t="n">
-        <v>22.55</v>
+        <v>22.3</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>-1.4</v>
+        <v>-1.3</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
       <c r="C11" s="7" t="n">
-        <v>75.25</v>
+        <v>75.7</v>
       </c>
       <c r="D11" s="8" t="n"/>
       <c r="E11" s="7" t="n">
-        <v>22.55</v>
+        <v>22.3</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-1.3</v>
+        <v>-7.7</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
@@ -3724,19 +3712,19 @@
         <v>22.3</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.6</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
@@ -3748,43 +3736,39 @@
         <v>22.3</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-8.6</v>
+        <v>-16.4</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
-      <c r="C14" s="7" t="n">
-        <v>75.7</v>
-      </c>
+      <c r="C14" s="7" t="n"/>
       <c r="D14" s="8" t="n"/>
-      <c r="E14" s="7" t="n">
-        <v>22.3</v>
-      </c>
+      <c r="E14" s="7" t="n"/>
       <c r="F14" s="8" t="n">
         <v>-16.4</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B15" s="8" t="n"/>
@@ -3792,19 +3776,19 @@
       <c r="D15" s="8" t="n"/>
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="8" t="n">
-        <v>-16.4</v>
+        <v>-14.3</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B16" s="8" t="n"/>
@@ -3812,19 +3796,19 @@
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="8" t="n">
-        <v>-14.3</v>
+        <v>-9.1</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B17" s="8" t="n"/>
@@ -3832,19 +3816,19 @@
       <c r="D17" s="8" t="n"/>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="8" t="n">
-        <v>-9.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B18" s="8" t="n"/>
@@ -3852,39 +3836,47 @@
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="8" t="n">
-        <v>-8.300000000000001</v>
+        <v>-5</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="7" t="n"/>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>22</v>
+      </c>
       <c r="F19" s="8" t="n">
-        <v>-5</v>
+        <v>-1.8</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
@@ -3894,103 +3886,99 @@
         <v>74.5</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>-1.8</v>
+        <v>-13.8</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="n">
-        <v>74.5</v>
-      </c>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n"/>
       <c r="C21" s="7" t="n">
         <v>74.5</v>
       </c>
-      <c r="D21" s="8" t="n">
-        <v>23</v>
-      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="7" t="n">
         <v>22.5</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-13.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="H21" s="10" t="n">
-        <v>8.1</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="n"/>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>74.40000000000001</v>
+      </c>
       <c r="C22" s="7" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="D22" s="8" t="n"/>
+        <v>74.47</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>23.3</v>
+      </c>
       <c r="E22" s="7" t="n">
-        <v>22.5</v>
+        <v>22.77</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-15.7</v>
+        <v>-10.5</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="H22" s="10" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="H22" s="10" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="n">
-        <v>74.40000000000001</v>
-      </c>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n"/>
       <c r="C23" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D23" s="8" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="D23" s="8" t="n"/>
       <c r="E23" s="7" t="n">
         <v>22.77</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-10.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
@@ -4002,90 +3990,94 @@
         <v>22.77</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>-9.4</v>
+        <v>-7.5</v>
       </c>
       <c r="G24" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="n"/>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>74.5</v>
+      </c>
       <c r="C25" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D25" s="8" t="n"/>
+      <c r="D25" s="8" t="n">
+        <v>22.9</v>
+      </c>
       <c r="E25" s="7" t="n">
-        <v>22.77</v>
+        <v>22.8</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-7.5</v>
+        <v>-4.5</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>74.47</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.2</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>23</v>
+        <v>22.93</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-2.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H27" s="10" t="n">
         <v>8</v>
@@ -4094,291 +4086,283 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C28" s="7" t="n">
         <v>74.7</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>22.93</v>
+        <v>22.78</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>74.7</v>
+        <v>74.64</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>22.78</v>
+        <v>22.6</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-11.9</v>
+        <v>-10.3</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>22.6</v>
+        <v>22.55</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-10.3</v>
+        <v>-13.7</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>74.65000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>22.55</v>
+        <v>22.57</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-13.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="n">
-        <v>74.2</v>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="n"/>
       <c r="C32" s="7" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="D32" s="8" t="n">
-        <v>22.7</v>
-      </c>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D32" s="8" t="n"/>
       <c r="E32" s="7" t="n">
-        <v>22.57</v>
+        <v>22.52</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-15.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B33" s="8" t="n"/>
       <c r="C33" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.52</v>
       </c>
       <c r="D33" s="8" t="n"/>
       <c r="E33" s="7" t="n">
-        <v>22.52</v>
+        <v>22.46</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D34" s="8" t="n"/>
       <c r="E34" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-18.2</v>
+        <v>-23.1</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="7" t="n">
-        <v>74.42</v>
+        <v>74.33</v>
       </c>
       <c r="D35" s="8" t="n"/>
       <c r="E35" s="7" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B36" s="8" t="n"/>
       <c r="C36" s="7" t="n">
-        <v>74.33</v>
+        <v>74.45</v>
       </c>
       <c r="D36" s="8" t="n"/>
       <c r="E36" s="7" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>-18.2</v>
+        <v>-19.5</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B37" s="8" t="n"/>
       <c r="C37" s="7" t="n">
-        <v>74.45</v>
+        <v>74.2</v>
       </c>
       <c r="D37" s="8" t="n"/>
       <c r="E37" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-19.5</v>
+        <v>-26.4</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B38" s="8" t="n"/>
-      <c r="C38" s="7" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="C38" s="7" t="n"/>
       <c r="D38" s="8" t="n"/>
-      <c r="E38" s="7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="E38" s="7" t="n"/>
       <c r="F38" s="8" t="n">
-        <v>-26.4</v>
+        <v>-19.9</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B39" s="8" t="n"/>
@@ -4386,807 +4370,811 @@
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="7" t="n"/>
       <c r="F39" s="8" t="n">
-        <v>-19.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="n"/>
-      <c r="C40" s="7" t="n"/>
-      <c r="D40" s="8" t="n"/>
-      <c r="E40" s="7" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>21.7</v>
+      </c>
       <c r="F40" s="8" t="n">
-        <v>-15.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>21.7</v>
+        <v>22.05</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-9.4</v>
+        <v>-12</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>73.2</v>
+        <v>73.33</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>-12</v>
+        <v>-12.4</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-12.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>73.31999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>-7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D47" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>22.26</v>
+        <v>22.4</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>73.16</v>
+        <v>73.2</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>-10.9</v>
+        <v>-16</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-16</v>
+        <v>-10.1</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>22.3</v>
+        <v>22.31</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>-10.1</v>
+        <v>-5.9</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>73.16</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>22.31</v>
+        <v>22.43</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-5.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B52" s="8" t="n">
         <v>72.8</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>73.06999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="D52" s="8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>22.43</v>
+        <v>22.41</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>-9.9</v>
+        <v>-13.3</v>
       </c>
       <c r="G52" s="9" t="n">
         <v>68</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>73.11</v>
+        <v>73.06</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-13.3</v>
+        <v>-16.6</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B54" s="8" t="n">
         <v>72.5</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>73.06</v>
+        <v>72.97</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>-16.6</v>
+        <v>-11.8</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>72.97</v>
+        <v>72.86</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>22.26</v>
+        <v>22.21</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>-11.8</v>
+        <v>-21.1</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>72.86</v>
+        <v>72.8</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>-21.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>72.8</v>
+        <v>72.69</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>22.24</v>
+        <v>22.19</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>-25.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C58" s="7" t="n">
-        <v>72.69</v>
+        <v>72.61</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>-18.3</v>
+        <v>-16</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>-16</v>
+        <v>-10.4</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B60" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="n"/>
       <c r="C60" s="7" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="D60" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="D60" s="8" t="n"/>
       <c r="E60" s="7" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>-10.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B61" s="8" t="n"/>
       <c r="C61" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="7" t="n">
-        <v>21.85</v>
+        <v>21.7</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B62" s="8" t="n"/>
       <c r="C62" s="7" t="n">
-        <v>72.58</v>
+        <v>72.5</v>
       </c>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>-12.3</v>
+        <v>-6.6</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B63" s="8" t="n"/>
       <c r="C63" s="7" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="7" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="n"/>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C64" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D64" s="8" t="n"/>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="D64" s="8" t="n">
+        <v>21.2</v>
+      </c>
       <c r="E64" s="7" t="n">
-        <v>21.73</v>
+        <v>21.63</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B65" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D65" s="8" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>21.63</v>
+        <v>21.57</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B66" s="8" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E66" s="7" t="n">
         <v>21.57</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>-7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B67" s="8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>72.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D67" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E67" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E67" s="7" t="n">
-        <v>21.57</v>
-      </c>
       <c r="F67" s="8" t="n">
-        <v>-10.9</v>
+        <v>-7.7</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="n"/>
       <c r="C68" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D68" s="8" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D68" s="8" t="n"/>
       <c r="E68" s="7" t="n">
         <v>21.8</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.9</v>
       </c>
       <c r="G68" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B69" s="8" t="n"/>
@@ -5198,19 +5186,19 @@
         <v>21.8</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>-8.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B70" s="8" t="n"/>
@@ -5222,274 +5210,278 @@
         <v>21.8</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>-12.5</v>
+        <v>-11.2</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B71" s="8" t="n"/>
       <c r="C71" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="D71" s="8" t="n"/>
       <c r="E71" s="7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>-11.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G71" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B72" s="8" t="n"/>
       <c r="C72" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D72" s="8" t="n"/>
       <c r="E72" s="7" t="n">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>-13.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B73" s="8" t="n"/>
       <c r="C73" s="7" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="7" t="n">
-        <v>22.15</v>
+        <v>22.5</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="G73" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B74" s="8" t="n"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="C74" s="7" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="D74" s="8" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D74" s="8" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E74" s="7" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>-12.4</v>
+        <v>-7.8</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B75" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C75" s="7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>20.5</v>
+        <v>20.95</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>-7.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B76" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>20.95</v>
+        <v>21.13</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>-3.1</v>
+        <v>-11.8</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B77" s="8" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C77" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>-11.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="C78" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D78" s="8" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>72.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D79" s="8" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>-8.6</v>
+        <v>-13.5</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C80" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>21.33</v>
+        <v>21.43</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H80" s="10" t="n">
         <v>7.7</v>
@@ -5498,381 +5490,377 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>72.23</v>
+        <v>72.39</v>
       </c>
       <c r="D81" s="8" t="n">
         <v>22</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>21.43</v>
+        <v>21.64</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>-7.1</v>
+        <v>-12.5</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B82" s="8" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C82" s="7" t="n">
         <v>72.39</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>21.64</v>
+        <v>21.69</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>-12.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B83" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>72.39</v>
+        <v>72.36</v>
       </c>
       <c r="D83" s="8" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>21.69</v>
+        <v>21.56</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>-6.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B84" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="n"/>
       <c r="C84" s="7" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="D84" s="8" t="n">
-        <v>20.6</v>
-      </c>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="D84" s="8" t="n"/>
       <c r="E84" s="7" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B85" s="8" t="n"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="C85" s="7" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="D85" s="8" t="n"/>
+        <v>72.45</v>
+      </c>
+      <c r="D85" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E85" s="7" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B86" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C86" s="7" t="n">
-        <v>72.45</v>
+        <v>72.47</v>
       </c>
       <c r="D86" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>21.67</v>
+        <v>21.53</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B87" s="8" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>72.47</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D87" s="8" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>21.53</v>
+        <v>21.47</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B88" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C88" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D88" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B89" s="8" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>72.31999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="D89" s="8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>-4.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B90" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="C90" s="7" t="n">
-        <v>72.23</v>
+        <v>72.3</v>
       </c>
       <c r="D90" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>21.4</v>
+        <v>21.55</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>-1.6</v>
+        <v>-15.1</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B91" s="8" t="n">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>72.3</v>
+        <v>72.37</v>
       </c>
       <c r="D91" s="8" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>21.55</v>
+        <v>21.69</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>-15.1</v>
+        <v>-10.3</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B92" s="8" t="n">
-        <v>72.8</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="n"/>
       <c r="C92" s="7" t="n">
-        <v>72.37</v>
-      </c>
-      <c r="D92" s="8" t="n">
-        <v>22.5</v>
-      </c>
+        <v>72.28</v>
+      </c>
+      <c r="D92" s="8" t="n"/>
       <c r="E92" s="7" t="n">
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>-10.3</v>
+        <v>-14.8</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>5.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B93" s="8" t="n"/>
       <c r="C93" s="7" t="n">
-        <v>72.28</v>
+        <v>72.3</v>
       </c>
       <c r="D93" s="8" t="n"/>
       <c r="E93" s="7" t="n">
-        <v>21.67</v>
+        <v>21.78</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>-14.8</v>
+        <v>-40.9</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B94" s="8" t="n"/>
       <c r="C94" s="7" t="n">
-        <v>72.3</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="D94" s="8" t="n"/>
       <c r="E94" s="7" t="n">
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>-32.1</v>
+        <v>-44</v>
       </c>
       <c r="G94" s="9" t="n">
         <v>60</v>
       </c>
       <c r="H94" s="10" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -6273,16 +6261,16 @@
         <v>53</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>58.4</v>
+        <v>62.2</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>500</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>107</v>
+        <v>187</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>-393</v>
+        <v>-313</v>
       </c>
     </row>
     <row r="16">

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>62.2</v>
+        <v>55.9</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -5830,7 +5830,7 @@
         <v>21.78</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>-40.9</v>
+        <v>-15.7</v>
       </c>
       <c r="G93" s="9" t="n">
         <v>60</v>
@@ -5854,7 +5854,7 @@
         <v>21.82</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>-44</v>
+        <v>-18.2</v>
       </c>
       <c r="G94" s="9" t="n">
         <v>60</v>
@@ -6261,16 +6261,16 @@
         <v>53</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>62.2</v>
+        <v>55.9</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>500</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>187</v>
+        <v>259</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>-313</v>
+        <v>-241</v>
       </c>
     </row>
     <row r="16">

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>55.9</v>
+        <v>55.8</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -3536,7 +3536,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
@@ -3544,67 +3544,71 @@
       <c r="D5" s="8" t="n"/>
       <c r="E5" s="7" t="n"/>
       <c r="F5" s="8" t="n">
-        <v>6.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="7" t="n"/>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>22.3</v>
+      </c>
       <c r="F6" s="8" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>75.7</v>
-      </c>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n"/>
       <c r="C7" s="7" t="n">
         <v>75.7</v>
       </c>
-      <c r="D7" s="8" t="n">
-        <v>22.3</v>
-      </c>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="7" t="n">
         <v>22.3</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
@@ -3616,19 +3620,19 @@
         <v>22.3</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>6.5</v>
+        <v>-1.4</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>6.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B9" s="8" t="n"/>
@@ -3640,19 +3644,19 @@
         <v>22.3</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-1.4</v>
+        <v>-1.3</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
@@ -3664,19 +3668,19 @@
         <v>22.3</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>-1.3</v>
+        <v>-7.7</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
@@ -3688,19 +3692,19 @@
         <v>22.3</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.6</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
@@ -3712,43 +3716,39 @@
         <v>22.3</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>-8.6</v>
+        <v>-16.4</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
-      <c r="C13" s="7" t="n">
-        <v>75.7</v>
-      </c>
+      <c r="C13" s="7" t="n"/>
       <c r="D13" s="8" t="n"/>
-      <c r="E13" s="7" t="n">
-        <v>22.3</v>
-      </c>
+      <c r="E13" s="7" t="n"/>
       <c r="F13" s="8" t="n">
         <v>-16.4</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
@@ -3756,19 +3756,19 @@
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="8" t="n">
-        <v>-16.4</v>
+        <v>-14.3</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B15" s="8" t="n"/>
@@ -3776,19 +3776,19 @@
       <c r="D15" s="8" t="n"/>
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="8" t="n">
-        <v>-14.3</v>
+        <v>-9.1</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B16" s="8" t="n"/>
@@ -3796,19 +3796,19 @@
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="8" t="n">
-        <v>-9.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B17" s="8" t="n"/>
@@ -3816,39 +3816,47 @@
       <c r="D17" s="8" t="n"/>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="8" t="n">
-        <v>-8.300000000000001</v>
+        <v>-5</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="7" t="n"/>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>22</v>
+      </c>
       <c r="F18" s="8" t="n">
-        <v>-5</v>
+        <v>-1.8</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
@@ -3858,103 +3866,99 @@
         <v>74.5</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-1.8</v>
+        <v>-13.8</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n">
-        <v>74.5</v>
-      </c>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n"/>
       <c r="C20" s="7" t="n">
         <v>74.5</v>
       </c>
-      <c r="D20" s="8" t="n">
-        <v>23</v>
-      </c>
+      <c r="D20" s="8" t="n"/>
       <c r="E20" s="7" t="n">
         <v>22.5</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>-13.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="H20" s="10" t="n">
-        <v>8.1</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H20" s="10" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="n"/>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>74.40000000000001</v>
+      </c>
       <c r="C21" s="7" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="D21" s="8" t="n"/>
+        <v>74.47</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>23.3</v>
+      </c>
       <c r="E21" s="7" t="n">
-        <v>22.5</v>
+        <v>22.77</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-15.7</v>
+        <v>-10.5</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="H21" s="10" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="n">
-        <v>74.40000000000001</v>
-      </c>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n"/>
       <c r="C22" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D22" s="8" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="7" t="n">
         <v>22.77</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-10.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
@@ -3966,90 +3970,94 @@
         <v>22.77</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-9.4</v>
+        <v>-7.5</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="n"/>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>74.5</v>
+      </c>
       <c r="C24" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D24" s="8" t="n"/>
+      <c r="D24" s="8" t="n">
+        <v>22.9</v>
+      </c>
       <c r="E24" s="7" t="n">
-        <v>22.77</v>
+        <v>22.8</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>-7.5</v>
+        <v>-4.5</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>74.47</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.2</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>23</v>
+        <v>22.93</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-2.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H26" s="10" t="n">
         <v>8</v>
@@ -4058,291 +4066,283 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C27" s="7" t="n">
         <v>74.7</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>22.93</v>
+        <v>22.78</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>74.7</v>
+        <v>74.64</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>22.78</v>
+        <v>22.6</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-11.9</v>
+        <v>-10.3</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>22.6</v>
+        <v>22.55</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-10.3</v>
+        <v>-13.7</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>74.65000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>22.55</v>
+        <v>22.57</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-13.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="n">
-        <v>74.2</v>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n"/>
       <c r="C31" s="7" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="D31" s="8" t="n">
-        <v>22.7</v>
-      </c>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D31" s="8" t="n"/>
       <c r="E31" s="7" t="n">
-        <v>22.57</v>
+        <v>22.52</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-15.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.52</v>
       </c>
       <c r="D32" s="8" t="n"/>
       <c r="E32" s="7" t="n">
-        <v>22.52</v>
+        <v>22.46</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B33" s="8" t="n"/>
       <c r="C33" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D33" s="8" t="n"/>
       <c r="E33" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-18.2</v>
+        <v>-23.1</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="7" t="n">
-        <v>74.42</v>
+        <v>74.33</v>
       </c>
       <c r="D34" s="8" t="n"/>
       <c r="E34" s="7" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="7" t="n">
-        <v>74.33</v>
+        <v>74.45</v>
       </c>
       <c r="D35" s="8" t="n"/>
       <c r="E35" s="7" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-18.2</v>
+        <v>-19.5</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B36" s="8" t="n"/>
       <c r="C36" s="7" t="n">
-        <v>74.45</v>
+        <v>74.2</v>
       </c>
       <c r="D36" s="8" t="n"/>
       <c r="E36" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>-19.5</v>
+        <v>-26.4</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B37" s="8" t="n"/>
-      <c r="C37" s="7" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="C37" s="7" t="n"/>
       <c r="D37" s="8" t="n"/>
-      <c r="E37" s="7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="E37" s="7" t="n"/>
       <c r="F37" s="8" t="n">
-        <v>-26.4</v>
+        <v>-19.9</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B38" s="8" t="n"/>
@@ -4350,807 +4350,811 @@
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="7" t="n"/>
       <c r="F38" s="8" t="n">
-        <v>-19.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="n"/>
-      <c r="C39" s="7" t="n"/>
-      <c r="D39" s="8" t="n"/>
-      <c r="E39" s="7" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E39" s="7" t="n">
+        <v>21.7</v>
+      </c>
       <c r="F39" s="8" t="n">
-        <v>-15.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>21.7</v>
+        <v>22.05</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>-9.4</v>
+        <v>-12</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>73.2</v>
+        <v>73.33</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-12</v>
+        <v>-12.4</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>-12.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>73.31999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D46" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>22.26</v>
+        <v>22.4</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>73.16</v>
+        <v>73.2</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-10.9</v>
+        <v>-16</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>-16</v>
+        <v>-10.1</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>22.3</v>
+        <v>22.31</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-10.1</v>
+        <v>-5.9</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>73.16</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>22.31</v>
+        <v>22.43</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>-5.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
         <v>72.8</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>73.06999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>22.43</v>
+        <v>22.41</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-9.9</v>
+        <v>-13.3</v>
       </c>
       <c r="G51" s="9" t="n">
         <v>68</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>73.11</v>
+        <v>73.06</v>
       </c>
       <c r="D52" s="8" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>-13.3</v>
+        <v>-16.6</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
         <v>72.5</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>73.06</v>
+        <v>72.97</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-16.6</v>
+        <v>-11.8</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>72.97</v>
+        <v>72.86</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>22.26</v>
+        <v>22.21</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>-11.8</v>
+        <v>-21.1</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>72.86</v>
+        <v>72.8</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>-21.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>72.8</v>
+        <v>72.69</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>22.24</v>
+        <v>22.19</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>-25.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>72.69</v>
+        <v>72.61</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>-18.3</v>
+        <v>-16</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C58" s="7" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>-16</v>
+        <v>-10.4</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B59" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n"/>
       <c r="C59" s="7" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="D59" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="D59" s="8" t="n"/>
       <c r="E59" s="7" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>-10.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B60" s="8" t="n"/>
       <c r="C60" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="7" t="n">
-        <v>21.85</v>
+        <v>21.7</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B61" s="8" t="n"/>
       <c r="C61" s="7" t="n">
-        <v>72.58</v>
+        <v>72.5</v>
       </c>
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>-12.3</v>
+        <v>-6.6</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B62" s="8" t="n"/>
       <c r="C62" s="7" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="7" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B63" s="8" t="n"/>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C63" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D63" s="8" t="n"/>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="D63" s="8" t="n">
+        <v>21.2</v>
+      </c>
       <c r="E63" s="7" t="n">
-        <v>21.73</v>
+        <v>21.63</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B64" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C64" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D64" s="8" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>21.63</v>
+        <v>21.57</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B65" s="8" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="D65" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E65" s="7" t="n">
         <v>21.57</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>-7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B66" s="8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>72.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D66" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E66" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E66" s="7" t="n">
-        <v>21.57</v>
-      </c>
       <c r="F66" s="8" t="n">
-        <v>-10.9</v>
+        <v>-7.7</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="n"/>
       <c r="C67" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D67" s="8" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D67" s="8" t="n"/>
       <c r="E67" s="7" t="n">
         <v>21.8</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.9</v>
       </c>
       <c r="G67" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B68" s="8" t="n"/>
@@ -5162,19 +5166,19 @@
         <v>21.8</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>-8.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B69" s="8" t="n"/>
@@ -5186,274 +5190,278 @@
         <v>21.8</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>-12.5</v>
+        <v>-11.2</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B70" s="8" t="n"/>
       <c r="C70" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="D70" s="8" t="n"/>
       <c r="E70" s="7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>-11.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G70" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B71" s="8" t="n"/>
       <c r="C71" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D71" s="8" t="n"/>
       <c r="E71" s="7" t="n">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>-13.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B72" s="8" t="n"/>
       <c r="C72" s="7" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D72" s="8" t="n"/>
       <c r="E72" s="7" t="n">
-        <v>22.15</v>
+        <v>22.5</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="G72" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="n"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="C73" s="7" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="D73" s="8" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D73" s="8" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E73" s="7" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>-12.4</v>
+        <v>-7.8</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B74" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C74" s="7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>20.5</v>
+        <v>20.95</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>-7.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B75" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C75" s="7" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>20.95</v>
+        <v>21.13</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>-3.1</v>
+        <v>-11.8</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B76" s="8" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>-11.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B77" s="8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="C77" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C78" s="7" t="n">
-        <v>72.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D78" s="8" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>-8.6</v>
+        <v>-13.5</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="D79" s="8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>21.33</v>
+        <v>21.43</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H79" s="10" t="n">
         <v>7.7</v>
@@ -5462,406 +5470,398 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="C80" s="7" t="n">
-        <v>72.23</v>
+        <v>72.39</v>
       </c>
       <c r="D80" s="8" t="n">
         <v>22</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>21.43</v>
+        <v>21.64</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>-7.1</v>
+        <v>-12.5</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C81" s="7" t="n">
         <v>72.39</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>21.64</v>
+        <v>21.69</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>-12.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B82" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>72.39</v>
+        <v>72.36</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>21.69</v>
+        <v>21.56</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>-6.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B83" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="n"/>
       <c r="C83" s="7" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="D83" s="8" t="n">
-        <v>20.6</v>
-      </c>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="D83" s="8" t="n"/>
       <c r="E83" s="7" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B84" s="8" t="n"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="C84" s="7" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="D84" s="8" t="n"/>
+        <v>72.45</v>
+      </c>
+      <c r="D84" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E84" s="7" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B85" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>72.45</v>
+        <v>72.47</v>
       </c>
       <c r="D85" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>21.67</v>
+        <v>21.53</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B86" s="8" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C86" s="7" t="n">
-        <v>72.47</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D86" s="8" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>21.53</v>
+        <v>21.47</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B87" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D87" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B88" s="8" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C88" s="7" t="n">
-        <v>72.31999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="D88" s="8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>-4.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B89" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>72.23</v>
+        <v>72.3</v>
       </c>
       <c r="D89" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>21.4</v>
+        <v>21.55</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>-1.6</v>
+        <v>-15.1</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B90" s="8" t="n">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="C90" s="7" t="n">
-        <v>72.3</v>
+        <v>72.37</v>
       </c>
       <c r="D90" s="8" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>21.55</v>
+        <v>21.69</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>-15.1</v>
+        <v>-10.3</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B91" s="8" t="n">
-        <v>72.8</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="n"/>
       <c r="C91" s="7" t="n">
-        <v>72.37</v>
-      </c>
-      <c r="D91" s="8" t="n">
-        <v>22.5</v>
-      </c>
+        <v>72.28</v>
+      </c>
+      <c r="D91" s="8" t="n"/>
       <c r="E91" s="7" t="n">
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>-10.3</v>
+        <v>-14.8</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>5.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B92" s="8" t="n"/>
       <c r="C92" s="7" t="n">
-        <v>72.28</v>
+        <v>72.3</v>
       </c>
       <c r="D92" s="8" t="n"/>
       <c r="E92" s="7" t="n">
-        <v>21.67</v>
+        <v>21.78</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>-14.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B93" s="8" t="n"/>
       <c r="C93" s="7" t="n">
-        <v>72.3</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="D93" s="8" t="n"/>
       <c r="E93" s="7" t="n">
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>-15.7</v>
+        <v>-15.4</v>
       </c>
       <c r="G93" s="9" t="n">
         <v>60</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B94" s="8" t="n"/>
       <c r="C94" s="7" t="n">
-        <v>72.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D94" s="8" t="n"/>
       <c r="E94" s="7" t="n">
-        <v>21.82</v>
+        <v>21.83</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>-18.2</v>
-      </c>
-      <c r="G94" s="9" t="n">
-        <v>60</v>
-      </c>
-      <c r="H94" s="10" t="n">
-        <v>7.8</v>
-      </c>
+        <v>-15.7</v>
+      </c>
+      <c r="G94" s="9" t="n"/>
+      <c r="H94" s="10" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6261,7 +6261,7 @@
         <v>53</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>55.9</v>
+        <v>55.8</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>500</v>

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>55.8</v>
+        <v>54.1</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -3536,55 +3536,59 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="7" t="n"/>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>22.3</v>
+      </c>
       <c r="F5" s="8" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n">
-        <v>75.7</v>
-      </c>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n"/>
       <c r="C6" s="7" t="n">
         <v>75.7</v>
       </c>
-      <c r="D6" s="8" t="n">
-        <v>22.3</v>
-      </c>
+      <c r="D6" s="8" t="n"/>
       <c r="E6" s="7" t="n">
         <v>22.3</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="G6" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
@@ -3596,19 +3600,19 @@
         <v>22.3</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>6.5</v>
+        <v>-1.4</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>6.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
@@ -3620,19 +3624,19 @@
         <v>22.3</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>-1.4</v>
+        <v>-1.3</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B9" s="8" t="n"/>
@@ -3644,19 +3648,19 @@
         <v>22.3</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-1.3</v>
+        <v>-7.7</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
@@ -3668,19 +3672,19 @@
         <v>22.3</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.6</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
@@ -3692,43 +3696,39 @@
         <v>22.3</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-8.6</v>
+        <v>-16.4</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
-      <c r="C12" s="7" t="n">
-        <v>75.7</v>
-      </c>
+      <c r="C12" s="7" t="n"/>
       <c r="D12" s="8" t="n"/>
-      <c r="E12" s="7" t="n">
-        <v>22.3</v>
-      </c>
+      <c r="E12" s="7" t="n"/>
       <c r="F12" s="8" t="n">
         <v>-16.4</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
@@ -3736,19 +3736,19 @@
       <c r="D13" s="8" t="n"/>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="8" t="n">
-        <v>-16.4</v>
+        <v>-14.3</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
@@ -3756,19 +3756,19 @@
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="8" t="n">
-        <v>-14.3</v>
+        <v>-9.1</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B15" s="8" t="n"/>
@@ -3776,19 +3776,19 @@
       <c r="D15" s="8" t="n"/>
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="8" t="n">
-        <v>-9.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B16" s="8" t="n"/>
@@ -3796,39 +3796,47 @@
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="8" t="n">
-        <v>-8.300000000000001</v>
+        <v>-5</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="7" t="n"/>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>22</v>
+      </c>
       <c r="F17" s="8" t="n">
-        <v>-5</v>
+        <v>-1.8</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
@@ -3838,103 +3846,99 @@
         <v>74.5</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>-1.8</v>
+        <v>-13.8</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n">
-        <v>74.5</v>
-      </c>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n"/>
       <c r="C19" s="7" t="n">
         <v>74.5</v>
       </c>
-      <c r="D19" s="8" t="n">
-        <v>23</v>
-      </c>
+      <c r="D19" s="8" t="n"/>
       <c r="E19" s="7" t="n">
         <v>22.5</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-13.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="H19" s="10" t="n">
-        <v>8.1</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n"/>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>74.40000000000001</v>
+      </c>
       <c r="C20" s="7" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="D20" s="8" t="n"/>
+        <v>74.47</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>23.3</v>
+      </c>
       <c r="E20" s="7" t="n">
-        <v>22.5</v>
+        <v>22.77</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>-15.7</v>
+        <v>-10.5</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="H20" s="10" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="n">
-        <v>74.40000000000001</v>
-      </c>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n"/>
       <c r="C21" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D21" s="8" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="7" t="n">
         <v>22.77</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-10.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
@@ -3946,90 +3950,94 @@
         <v>22.77</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-9.4</v>
+        <v>-7.5</v>
       </c>
       <c r="G22" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="n"/>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>74.5</v>
+      </c>
       <c r="C23" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D23" s="8" t="n"/>
+      <c r="D23" s="8" t="n">
+        <v>22.9</v>
+      </c>
       <c r="E23" s="7" t="n">
-        <v>22.77</v>
+        <v>22.8</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-7.5</v>
+        <v>-4.5</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>74.47</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.2</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>23</v>
+        <v>22.93</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-2.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H25" s="10" t="n">
         <v>8</v>
@@ -4038,291 +4046,283 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C26" s="7" t="n">
         <v>74.7</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>22.93</v>
+        <v>22.78</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>74.7</v>
+        <v>74.64</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>22.78</v>
+        <v>22.6</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-11.9</v>
+        <v>-10.3</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>22.6</v>
+        <v>22.55</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-10.3</v>
+        <v>-13.7</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>74.65000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>22.55</v>
+        <v>22.57</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-13.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="n">
-        <v>74.2</v>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="n"/>
       <c r="C30" s="7" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="D30" s="8" t="n">
-        <v>22.7</v>
-      </c>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D30" s="8" t="n"/>
       <c r="E30" s="7" t="n">
-        <v>22.57</v>
+        <v>22.52</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-15.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.52</v>
       </c>
       <c r="D31" s="8" t="n"/>
       <c r="E31" s="7" t="n">
-        <v>22.52</v>
+        <v>22.46</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D32" s="8" t="n"/>
       <c r="E32" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-18.2</v>
+        <v>-23.1</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B33" s="8" t="n"/>
       <c r="C33" s="7" t="n">
-        <v>74.42</v>
+        <v>74.33</v>
       </c>
       <c r="D33" s="8" t="n"/>
       <c r="E33" s="7" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="7" t="n">
-        <v>74.33</v>
+        <v>74.45</v>
       </c>
       <c r="D34" s="8" t="n"/>
       <c r="E34" s="7" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-18.2</v>
+        <v>-19.5</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="7" t="n">
-        <v>74.45</v>
+        <v>74.2</v>
       </c>
       <c r="D35" s="8" t="n"/>
       <c r="E35" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-19.5</v>
+        <v>-26.4</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B36" s="8" t="n"/>
-      <c r="C36" s="7" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="C36" s="7" t="n"/>
       <c r="D36" s="8" t="n"/>
-      <c r="E36" s="7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="E36" s="7" t="n"/>
       <c r="F36" s="8" t="n">
-        <v>-26.4</v>
+        <v>-19.9</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B37" s="8" t="n"/>
@@ -4330,807 +4330,811 @@
       <c r="D37" s="8" t="n"/>
       <c r="E37" s="7" t="n"/>
       <c r="F37" s="8" t="n">
-        <v>-19.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="n"/>
-      <c r="C38" s="7" t="n"/>
-      <c r="D38" s="8" t="n"/>
-      <c r="E38" s="7" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>21.7</v>
+      </c>
       <c r="F38" s="8" t="n">
-        <v>-15.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>21.7</v>
+        <v>22.05</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-9.4</v>
+        <v>-12</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>73.2</v>
+        <v>73.33</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>-12</v>
+        <v>-12.4</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-12.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>73.31999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>-7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D45" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>22.26</v>
+        <v>22.4</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>73.16</v>
+        <v>73.2</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>-10.9</v>
+        <v>-16</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-16</v>
+        <v>-10.1</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>22.3</v>
+        <v>22.31</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>-10.1</v>
+        <v>-5.9</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>73.16</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>22.31</v>
+        <v>22.43</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-5.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B50" s="8" t="n">
         <v>72.8</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>73.06999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>22.43</v>
+        <v>22.41</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>-9.9</v>
+        <v>-13.3</v>
       </c>
       <c r="G50" s="9" t="n">
         <v>68</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>73.11</v>
+        <v>73.06</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-13.3</v>
+        <v>-16.6</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B52" s="8" t="n">
         <v>72.5</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>73.06</v>
+        <v>72.97</v>
       </c>
       <c r="D52" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>-16.6</v>
+        <v>-11.8</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>72.97</v>
+        <v>72.86</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>22.26</v>
+        <v>22.21</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-11.8</v>
+        <v>-21.1</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>72.86</v>
+        <v>72.8</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>-21.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>72.8</v>
+        <v>72.69</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>22.24</v>
+        <v>22.19</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>-25.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>72.69</v>
+        <v>72.61</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>-18.3</v>
+        <v>-16</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>-16</v>
+        <v>-10.4</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B58" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="n"/>
       <c r="C58" s="7" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="D58" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="D58" s="8" t="n"/>
       <c r="E58" s="7" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>-10.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B59" s="8" t="n"/>
       <c r="C59" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="7" t="n">
-        <v>21.85</v>
+        <v>21.7</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B60" s="8" t="n"/>
       <c r="C60" s="7" t="n">
-        <v>72.58</v>
+        <v>72.5</v>
       </c>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>-12.3</v>
+        <v>-6.6</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B61" s="8" t="n"/>
       <c r="C61" s="7" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="7" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B62" s="8" t="n"/>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C62" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D62" s="8" t="n"/>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="D62" s="8" t="n">
+        <v>21.2</v>
+      </c>
       <c r="E62" s="7" t="n">
-        <v>21.73</v>
+        <v>21.63</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B63" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>21.63</v>
+        <v>21.57</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B64" s="8" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="C64" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="D64" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E64" s="7" t="n">
         <v>21.57</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>-7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B65" s="8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>72.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D65" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E65" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E65" s="7" t="n">
-        <v>21.57</v>
-      </c>
       <c r="F65" s="8" t="n">
-        <v>-10.9</v>
+        <v>-7.7</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B66" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="n"/>
       <c r="C66" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D66" s="8" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D66" s="8" t="n"/>
       <c r="E66" s="7" t="n">
         <v>21.8</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.9</v>
       </c>
       <c r="G66" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B67" s="8" t="n"/>
@@ -5142,19 +5146,19 @@
         <v>21.8</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>-8.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B68" s="8" t="n"/>
@@ -5166,274 +5170,278 @@
         <v>21.8</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>-12.5</v>
+        <v>-11.2</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B69" s="8" t="n"/>
       <c r="C69" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>-11.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G69" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B70" s="8" t="n"/>
       <c r="C70" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D70" s="8" t="n"/>
       <c r="E70" s="7" t="n">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>-13.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B71" s="8" t="n"/>
       <c r="C71" s="7" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D71" s="8" t="n"/>
       <c r="E71" s="7" t="n">
-        <v>22.15</v>
+        <v>22.5</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="G71" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B72" s="8" t="n"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="C72" s="7" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="D72" s="8" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D72" s="8" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E72" s="7" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>-12.4</v>
+        <v>-7.8</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B73" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C73" s="7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D73" s="8" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>20.5</v>
+        <v>20.95</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>-7.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B74" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C74" s="7" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>20.95</v>
+        <v>21.13</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>-3.1</v>
+        <v>-11.8</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B75" s="8" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C75" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>-11.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B76" s="8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B77" s="8" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C77" s="7" t="n">
-        <v>72.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>-8.6</v>
+        <v>-13.5</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C78" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="D78" s="8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>21.33</v>
+        <v>21.43</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H78" s="10" t="n">
         <v>7.7</v>
@@ -5442,426 +5450,426 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>72.23</v>
+        <v>72.39</v>
       </c>
       <c r="D79" s="8" t="n">
         <v>22</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>21.43</v>
+        <v>21.64</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>-7.1</v>
+        <v>-12.5</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C80" s="7" t="n">
         <v>72.39</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>21.64</v>
+        <v>21.69</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>-12.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>72.39</v>
+        <v>72.36</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>21.69</v>
+        <v>21.56</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>-6.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B82" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="n"/>
       <c r="C82" s="7" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="D82" s="8" t="n">
-        <v>20.6</v>
-      </c>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="D82" s="8" t="n"/>
       <c r="E82" s="7" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B83" s="8" t="n"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="C83" s="7" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="D83" s="8" t="n"/>
+        <v>72.45</v>
+      </c>
+      <c r="D83" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E83" s="7" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B84" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C84" s="7" t="n">
-        <v>72.45</v>
+        <v>72.47</v>
       </c>
       <c r="D84" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>21.67</v>
+        <v>21.53</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B85" s="8" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>72.47</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D85" s="8" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>21.53</v>
+        <v>21.47</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B86" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C86" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D86" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B87" s="8" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>72.31999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="D87" s="8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>-4.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B88" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="C88" s="7" t="n">
-        <v>72.23</v>
+        <v>72.3</v>
       </c>
       <c r="D88" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>21.4</v>
+        <v>21.55</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>-1.6</v>
+        <v>-15.1</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B89" s="8" t="n">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>72.3</v>
+        <v>72.37</v>
       </c>
       <c r="D89" s="8" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>21.55</v>
+        <v>21.69</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>-15.1</v>
+        <v>-10.3</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B90" s="8" t="n">
-        <v>72.8</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="n"/>
       <c r="C90" s="7" t="n">
-        <v>72.37</v>
-      </c>
-      <c r="D90" s="8" t="n">
-        <v>22.5</v>
-      </c>
+        <v>72.28</v>
+      </c>
+      <c r="D90" s="8" t="n"/>
       <c r="E90" s="7" t="n">
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>-10.3</v>
+        <v>-14.8</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>5.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B91" s="8" t="n"/>
       <c r="C91" s="7" t="n">
-        <v>72.28</v>
+        <v>72.3</v>
       </c>
       <c r="D91" s="8" t="n"/>
       <c r="E91" s="7" t="n">
-        <v>21.67</v>
+        <v>21.78</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>-14.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B92" s="8" t="n"/>
       <c r="C92" s="7" t="n">
-        <v>72.3</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="D92" s="8" t="n"/>
       <c r="E92" s="7" t="n">
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>-15.7</v>
+        <v>-15.4</v>
       </c>
       <c r="G92" s="9" t="n">
         <v>60</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B93" s="8" t="n"/>
       <c r="C93" s="7" t="n">
-        <v>72.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D93" s="8" t="n"/>
       <c r="E93" s="7" t="n">
-        <v>21.82</v>
+        <v>21.83</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>-15.4</v>
+        <v>-8.9</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B94" s="8" t="n"/>
       <c r="C94" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D94" s="8" t="n"/>
       <c r="E94" s="7" t="n">
-        <v>21.83</v>
+        <v>22</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>-15.7</v>
-      </c>
-      <c r="G94" s="9" t="n"/>
-      <c r="H94" s="10" t="n"/>
+        <v>-6.7</v>
+      </c>
+      <c r="G94" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="H94" s="10" t="n">
+        <v>6.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6261,16 +6269,16 @@
         <v>53</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>55.8</v>
+        <v>54.1</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>500</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>259</v>
+        <v>318</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>-241</v>
+        <v>-182</v>
       </c>
     </row>
     <row r="16">

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>54.1</v>
+        <v>54.4</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -3536,179 +3536,147 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>22.3</v>
-      </c>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="7" t="n"/>
       <c r="F5" s="8" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="G5" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
-      <c r="C6" s="7" t="n">
-        <v>75.7</v>
-      </c>
+      <c r="C6" s="7" t="n"/>
       <c r="D6" s="8" t="n"/>
-      <c r="E6" s="7" t="n">
-        <v>22.3</v>
-      </c>
+      <c r="E6" s="7" t="n"/>
       <c r="F6" s="8" t="n">
-        <v>6.5</v>
+        <v>-1.4</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>6.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
-      <c r="C7" s="7" t="n">
-        <v>75.7</v>
-      </c>
+      <c r="C7" s="7" t="n"/>
       <c r="D7" s="8" t="n"/>
-      <c r="E7" s="7" t="n">
-        <v>22.3</v>
-      </c>
+      <c r="E7" s="7" t="n"/>
       <c r="F7" s="8" t="n">
-        <v>-1.4</v>
+        <v>-1.3</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
-      <c r="C8" s="7" t="n">
-        <v>75.7</v>
-      </c>
+      <c r="C8" s="7" t="n"/>
       <c r="D8" s="8" t="n"/>
-      <c r="E8" s="7" t="n">
-        <v>22.3</v>
-      </c>
+      <c r="E8" s="7" t="n"/>
       <c r="F8" s="8" t="n">
-        <v>-1.3</v>
+        <v>-7.7</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B9" s="8" t="n"/>
-      <c r="C9" s="7" t="n">
-        <v>75.7</v>
-      </c>
+      <c r="C9" s="7" t="n"/>
       <c r="D9" s="8" t="n"/>
-      <c r="E9" s="7" t="n">
-        <v>22.3</v>
-      </c>
+      <c r="E9" s="7" t="n"/>
       <c r="F9" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.6</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
-      <c r="C10" s="7" t="n">
-        <v>75.7</v>
-      </c>
+      <c r="C10" s="7" t="n"/>
       <c r="D10" s="8" t="n"/>
-      <c r="E10" s="7" t="n">
-        <v>22.3</v>
-      </c>
+      <c r="E10" s="7" t="n"/>
       <c r="F10" s="8" t="n">
-        <v>-8.6</v>
+        <v>-16.4</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
-      <c r="C11" s="7" t="n">
-        <v>75.7</v>
-      </c>
+      <c r="C11" s="7" t="n"/>
       <c r="D11" s="8" t="n"/>
-      <c r="E11" s="7" t="n">
-        <v>22.3</v>
-      </c>
+      <c r="E11" s="7" t="n"/>
       <c r="F11" s="8" t="n">
         <v>-16.4</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
@@ -3716,19 +3684,19 @@
       <c r="D12" s="8" t="n"/>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="8" t="n">
-        <v>-16.4</v>
+        <v>-14.3</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
@@ -3736,19 +3704,19 @@
       <c r="D13" s="8" t="n"/>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="8" t="n">
-        <v>-14.3</v>
+        <v>-9.1</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
@@ -3756,19 +3724,19 @@
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="8" t="n">
-        <v>-9.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B15" s="8" t="n"/>
@@ -3776,39 +3744,47 @@
       <c r="D15" s="8" t="n"/>
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="8" t="n">
-        <v>-8.300000000000001</v>
+        <v>-5</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="7" t="n"/>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>22</v>
+      </c>
       <c r="F16" s="8" t="n">
-        <v>-5</v>
+        <v>-1.8</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
@@ -3818,103 +3794,99 @@
         <v>74.5</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-1.8</v>
+        <v>-13.8</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="n">
-        <v>74.5</v>
-      </c>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n"/>
       <c r="C18" s="7" t="n">
         <v>74.5</v>
       </c>
-      <c r="D18" s="8" t="n">
-        <v>23</v>
-      </c>
+      <c r="D18" s="8" t="n"/>
       <c r="E18" s="7" t="n">
         <v>22.5</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>-13.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="H18" s="10" t="n">
-        <v>8.1</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n"/>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>74.40000000000001</v>
+      </c>
       <c r="C19" s="7" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="D19" s="8" t="n"/>
+        <v>74.47</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>23.3</v>
+      </c>
       <c r="E19" s="7" t="n">
-        <v>22.5</v>
+        <v>22.77</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-15.7</v>
+        <v>-10.5</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="H19" s="10" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n">
-        <v>74.40000000000001</v>
-      </c>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n"/>
       <c r="C20" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D20" s="8" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="D20" s="8" t="n"/>
       <c r="E20" s="7" t="n">
         <v>22.77</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>-10.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
@@ -3926,90 +3898,94 @@
         <v>22.77</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-9.4</v>
+        <v>-7.5</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="n"/>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>74.5</v>
+      </c>
       <c r="C22" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D22" s="8" t="n"/>
+      <c r="D22" s="8" t="n">
+        <v>22.9</v>
+      </c>
       <c r="E22" s="7" t="n">
-        <v>22.77</v>
+        <v>22.8</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-7.5</v>
+        <v>-4.5</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>74.47</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.2</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>23</v>
+        <v>22.93</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>-2.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H24" s="10" t="n">
         <v>8</v>
@@ -4018,291 +3994,283 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C25" s="7" t="n">
         <v>74.7</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>22.93</v>
+        <v>22.78</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>74.7</v>
+        <v>74.64</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>22.78</v>
+        <v>22.6</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-11.9</v>
+        <v>-10.3</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>22.6</v>
+        <v>22.55</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-10.3</v>
+        <v>-13.7</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>74.65000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>22.55</v>
+        <v>22.57</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-13.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="n">
-        <v>74.2</v>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n"/>
       <c r="C29" s="7" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="D29" s="8" t="n">
-        <v>22.7</v>
-      </c>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D29" s="8" t="n"/>
       <c r="E29" s="7" t="n">
-        <v>22.57</v>
+        <v>22.52</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-15.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B30" s="8" t="n"/>
       <c r="C30" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.52</v>
       </c>
       <c r="D30" s="8" t="n"/>
       <c r="E30" s="7" t="n">
-        <v>22.52</v>
+        <v>22.46</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D31" s="8" t="n"/>
       <c r="E31" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-18.2</v>
+        <v>-23.1</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="7" t="n">
-        <v>74.42</v>
+        <v>74.33</v>
       </c>
       <c r="D32" s="8" t="n"/>
       <c r="E32" s="7" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B33" s="8" t="n"/>
       <c r="C33" s="7" t="n">
-        <v>74.33</v>
+        <v>74.45</v>
       </c>
       <c r="D33" s="8" t="n"/>
       <c r="E33" s="7" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-18.2</v>
+        <v>-19.5</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="7" t="n">
-        <v>74.45</v>
+        <v>74.2</v>
       </c>
       <c r="D34" s="8" t="n"/>
       <c r="E34" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-19.5</v>
+        <v>-26.4</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B35" s="8" t="n"/>
-      <c r="C35" s="7" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="C35" s="7" t="n"/>
       <c r="D35" s="8" t="n"/>
-      <c r="E35" s="7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="E35" s="7" t="n"/>
       <c r="F35" s="8" t="n">
-        <v>-26.4</v>
+        <v>-19.9</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B36" s="8" t="n"/>
@@ -4310,807 +4278,811 @@
       <c r="D36" s="8" t="n"/>
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="8" t="n">
-        <v>-19.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="n"/>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="8" t="n"/>
-      <c r="E37" s="7" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E37" s="7" t="n">
+        <v>21.7</v>
+      </c>
       <c r="F37" s="8" t="n">
-        <v>-15.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>21.7</v>
+        <v>22.05</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>-9.4</v>
+        <v>-12</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>73.2</v>
+        <v>73.33</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-12</v>
+        <v>-12.4</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>-12.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>73.31999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D44" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>22.26</v>
+        <v>22.4</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>73.16</v>
+        <v>73.2</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-10.9</v>
+        <v>-16</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>-16</v>
+        <v>-10.1</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>22.3</v>
+        <v>22.31</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-10.1</v>
+        <v>-5.9</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>73.16</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>22.31</v>
+        <v>22.43</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>-5.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
         <v>72.8</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>73.06999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>22.43</v>
+        <v>22.41</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-9.9</v>
+        <v>-13.3</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>68</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>73.11</v>
+        <v>73.06</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>-13.3</v>
+        <v>-16.6</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
         <v>72.5</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>73.06</v>
+        <v>72.97</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-16.6</v>
+        <v>-11.8</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>72.97</v>
+        <v>72.86</v>
       </c>
       <c r="D52" s="8" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>22.26</v>
+        <v>22.21</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>-11.8</v>
+        <v>-21.1</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>72.86</v>
+        <v>72.8</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-21.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>72.8</v>
+        <v>72.69</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>22.24</v>
+        <v>22.19</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>-25.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>72.69</v>
+        <v>72.61</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>-18.3</v>
+        <v>-16</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>-16</v>
+        <v>-10.4</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n"/>
       <c r="C57" s="7" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="D57" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="D57" s="8" t="n"/>
       <c r="E57" s="7" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>-10.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B58" s="8" t="n"/>
       <c r="C58" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="7" t="n">
-        <v>21.85</v>
+        <v>21.7</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B59" s="8" t="n"/>
       <c r="C59" s="7" t="n">
-        <v>72.58</v>
+        <v>72.5</v>
       </c>
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>-12.3</v>
+        <v>-6.6</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B60" s="8" t="n"/>
       <c r="C60" s="7" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="7" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="n"/>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C61" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D61" s="8" t="n"/>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>21.2</v>
+      </c>
       <c r="E61" s="7" t="n">
-        <v>21.73</v>
+        <v>21.63</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B62" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C62" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>21.63</v>
+        <v>21.57</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B63" s="8" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E63" s="7" t="n">
         <v>21.57</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>-7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B64" s="8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C64" s="7" t="n">
-        <v>72.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D64" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E64" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E64" s="7" t="n">
-        <v>21.57</v>
-      </c>
       <c r="F64" s="8" t="n">
-        <v>-10.9</v>
+        <v>-7.7</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B65" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="n"/>
       <c r="C65" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D65" s="8" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D65" s="8" t="n"/>
       <c r="E65" s="7" t="n">
         <v>21.8</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.9</v>
       </c>
       <c r="G65" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B66" s="8" t="n"/>
@@ -5122,19 +5094,19 @@
         <v>21.8</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>-8.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B67" s="8" t="n"/>
@@ -5146,274 +5118,278 @@
         <v>21.8</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>-12.5</v>
+        <v>-11.2</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B68" s="8" t="n"/>
       <c r="C68" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>-11.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G68" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B69" s="8" t="n"/>
       <c r="C69" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="7" t="n">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>-13.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B70" s="8" t="n"/>
       <c r="C70" s="7" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D70" s="8" t="n"/>
       <c r="E70" s="7" t="n">
-        <v>22.15</v>
+        <v>22.5</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="G70" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B71" s="8" t="n"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="C71" s="7" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="D71" s="8" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D71" s="8" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E71" s="7" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>-12.4</v>
+        <v>-7.8</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B72" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C72" s="7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>20.5</v>
+        <v>20.95</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>-7.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B73" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C73" s="7" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D73" s="8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>20.95</v>
+        <v>21.13</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>-3.1</v>
+        <v>-11.8</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B74" s="8" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C74" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>-11.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B75" s="8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="C75" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B76" s="8" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>72.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>-8.6</v>
+        <v>-13.5</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B77" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C77" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>21.33</v>
+        <v>21.43</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H77" s="10" t="n">
         <v>7.7</v>
@@ -5422,453 +5398,449 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="C78" s="7" t="n">
-        <v>72.23</v>
+        <v>72.39</v>
       </c>
       <c r="D78" s="8" t="n">
         <v>22</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>21.43</v>
+        <v>21.64</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>-7.1</v>
+        <v>-12.5</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C79" s="7" t="n">
         <v>72.39</v>
       </c>
       <c r="D79" s="8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>21.64</v>
+        <v>21.69</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>-12.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C80" s="7" t="n">
-        <v>72.39</v>
+        <v>72.36</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>21.69</v>
+        <v>21.56</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>-6.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B81" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="n"/>
       <c r="C81" s="7" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="D81" s="8" t="n">
-        <v>20.6</v>
-      </c>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="D81" s="8" t="n"/>
       <c r="E81" s="7" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B82" s="8" t="n"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="C82" s="7" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="D82" s="8" t="n"/>
+        <v>72.45</v>
+      </c>
+      <c r="D82" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E82" s="7" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B83" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>72.45</v>
+        <v>72.47</v>
       </c>
       <c r="D83" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>21.67</v>
+        <v>21.53</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B84" s="8" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C84" s="7" t="n">
-        <v>72.47</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D84" s="8" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>21.53</v>
+        <v>21.47</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B85" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D85" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B86" s="8" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C86" s="7" t="n">
-        <v>72.31999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="D86" s="8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>-4.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B87" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>72.23</v>
+        <v>72.3</v>
       </c>
       <c r="D87" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>21.4</v>
+        <v>21.55</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>-1.6</v>
+        <v>-15.1</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B88" s="8" t="n">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="C88" s="7" t="n">
-        <v>72.3</v>
+        <v>72.37</v>
       </c>
       <c r="D88" s="8" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>21.55</v>
+        <v>21.69</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>-15.1</v>
+        <v>-10.3</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B89" s="8" t="n">
-        <v>72.8</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="n"/>
       <c r="C89" s="7" t="n">
-        <v>72.37</v>
-      </c>
-      <c r="D89" s="8" t="n">
-        <v>22.5</v>
-      </c>
+        <v>72.28</v>
+      </c>
+      <c r="D89" s="8" t="n"/>
       <c r="E89" s="7" t="n">
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>-10.3</v>
+        <v>-14.8</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>5.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B90" s="8" t="n"/>
       <c r="C90" s="7" t="n">
-        <v>72.28</v>
+        <v>72.3</v>
       </c>
       <c r="D90" s="8" t="n"/>
       <c r="E90" s="7" t="n">
-        <v>21.67</v>
+        <v>21.78</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>-14.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B91" s="8" t="n"/>
       <c r="C91" s="7" t="n">
-        <v>72.3</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="D91" s="8" t="n"/>
       <c r="E91" s="7" t="n">
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>-15.7</v>
+        <v>-15.4</v>
       </c>
       <c r="G91" s="9" t="n">
         <v>60</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B92" s="8" t="n"/>
       <c r="C92" s="7" t="n">
-        <v>72.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D92" s="8" t="n"/>
       <c r="E92" s="7" t="n">
-        <v>21.82</v>
+        <v>21.83</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>-15.4</v>
+        <v>-8.9</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B93" s="8" t="n"/>
       <c r="C93" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D93" s="8" t="n"/>
       <c r="E93" s="7" t="n">
-        <v>21.83</v>
+        <v>22</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>-8.9</v>
+        <v>-6.7</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B94" s="8" t="n"/>
       <c r="C94" s="7" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D94" s="8" t="n"/>
       <c r="E94" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>-6.7</v>
+        <v>-7.3</v>
       </c>
       <c r="G94" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H94" s="10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -6269,7 +6241,7 @@
         <v>53</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>54.1</v>
+        <v>54.4</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>500</v>

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>54.4</v>
+        <v>54.2</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -3536,7 +3536,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
@@ -3544,19 +3544,19 @@
       <c r="D5" s="8" t="n"/>
       <c r="E5" s="7" t="n"/>
       <c r="F5" s="8" t="n">
-        <v>6.5</v>
+        <v>-1.4</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>6.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
@@ -3564,19 +3564,19 @@
       <c r="D6" s="8" t="n"/>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="8" t="n">
-        <v>-1.4</v>
+        <v>-1.3</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
@@ -3584,19 +3584,19 @@
       <c r="D7" s="8" t="n"/>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="8" t="n">
-        <v>-1.3</v>
+        <v>-7.7</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
@@ -3604,19 +3604,19 @@
       <c r="D8" s="8" t="n"/>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.6</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B9" s="8" t="n"/>
@@ -3624,19 +3624,19 @@
       <c r="D9" s="8" t="n"/>
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="8" t="n">
-        <v>-8.6</v>
+        <v>-16.4</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
@@ -3647,16 +3647,16 @@
         <v>-16.4</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
@@ -3664,19 +3664,19 @@
       <c r="D11" s="8" t="n"/>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="8" t="n">
-        <v>-16.4</v>
+        <v>-14.3</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
@@ -3684,19 +3684,19 @@
       <c r="D12" s="8" t="n"/>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="8" t="n">
-        <v>-14.3</v>
+        <v>-9.1</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
@@ -3704,19 +3704,19 @@
       <c r="D13" s="8" t="n"/>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="8" t="n">
-        <v>-9.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
@@ -3724,39 +3724,47 @@
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="8" t="n">
-        <v>-8.300000000000001</v>
+        <v>-5</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="7" t="n"/>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>22</v>
+      </c>
       <c r="F15" s="8" t="n">
-        <v>-5</v>
+        <v>-1.8</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
@@ -3766,103 +3774,99 @@
         <v>74.5</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>-1.8</v>
+        <v>-13.8</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="n">
-        <v>74.5</v>
-      </c>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n"/>
       <c r="C17" s="7" t="n">
         <v>74.5</v>
       </c>
-      <c r="D17" s="8" t="n">
-        <v>23</v>
-      </c>
+      <c r="D17" s="8" t="n"/>
       <c r="E17" s="7" t="n">
         <v>22.5</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-13.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="H17" s="10" t="n">
-        <v>8.1</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="n"/>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>74.40000000000001</v>
+      </c>
       <c r="C18" s="7" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="D18" s="8" t="n"/>
+        <v>74.47</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>23.3</v>
+      </c>
       <c r="E18" s="7" t="n">
-        <v>22.5</v>
+        <v>22.77</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>-15.7</v>
+        <v>-10.5</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="H18" s="10" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n">
-        <v>74.40000000000001</v>
-      </c>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n"/>
       <c r="C19" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D19" s="8" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="D19" s="8" t="n"/>
       <c r="E19" s="7" t="n">
         <v>22.77</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-10.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B20" s="8" t="n"/>
@@ -3874,90 +3878,94 @@
         <v>22.77</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>-9.4</v>
+        <v>-7.5</v>
       </c>
       <c r="G20" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="n"/>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>74.5</v>
+      </c>
       <c r="C21" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D21" s="8" t="n"/>
+      <c r="D21" s="8" t="n">
+        <v>22.9</v>
+      </c>
       <c r="E21" s="7" t="n">
-        <v>22.77</v>
+        <v>22.8</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-7.5</v>
+        <v>-4.5</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>74.47</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.2</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>23</v>
+        <v>22.93</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-2.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H23" s="10" t="n">
         <v>8</v>
@@ -3966,291 +3974,283 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C24" s="7" t="n">
         <v>74.7</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>22.93</v>
+        <v>22.78</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>74.7</v>
+        <v>74.64</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>22.78</v>
+        <v>22.6</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-11.9</v>
+        <v>-10.3</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>22.6</v>
+        <v>22.55</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-10.3</v>
+        <v>-13.7</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>74.65000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>22.55</v>
+        <v>22.57</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-13.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="n">
-        <v>74.2</v>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n"/>
       <c r="C28" s="7" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="D28" s="8" t="n">
-        <v>22.7</v>
-      </c>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D28" s="8" t="n"/>
       <c r="E28" s="7" t="n">
-        <v>22.57</v>
+        <v>22.52</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-15.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B29" s="8" t="n"/>
       <c r="C29" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.52</v>
       </c>
       <c r="D29" s="8" t="n"/>
       <c r="E29" s="7" t="n">
-        <v>22.52</v>
+        <v>22.46</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B30" s="8" t="n"/>
       <c r="C30" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D30" s="8" t="n"/>
       <c r="E30" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-18.2</v>
+        <v>-23.1</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="7" t="n">
-        <v>74.42</v>
+        <v>74.33</v>
       </c>
       <c r="D31" s="8" t="n"/>
       <c r="E31" s="7" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="7" t="n">
-        <v>74.33</v>
+        <v>74.45</v>
       </c>
       <c r="D32" s="8" t="n"/>
       <c r="E32" s="7" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-18.2</v>
+        <v>-19.5</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B33" s="8" t="n"/>
       <c r="C33" s="7" t="n">
-        <v>74.45</v>
+        <v>74.2</v>
       </c>
       <c r="D33" s="8" t="n"/>
       <c r="E33" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-19.5</v>
+        <v>-26.4</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B34" s="8" t="n"/>
-      <c r="C34" s="7" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="C34" s="7" t="n"/>
       <c r="D34" s="8" t="n"/>
-      <c r="E34" s="7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="E34" s="7" t="n"/>
       <c r="F34" s="8" t="n">
-        <v>-26.4</v>
+        <v>-19.9</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B35" s="8" t="n"/>
@@ -4258,807 +4258,811 @@
       <c r="D35" s="8" t="n"/>
       <c r="E35" s="7" t="n"/>
       <c r="F35" s="8" t="n">
-        <v>-19.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="n"/>
-      <c r="C36" s="7" t="n"/>
-      <c r="D36" s="8" t="n"/>
-      <c r="E36" s="7" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>21.7</v>
+      </c>
       <c r="F36" s="8" t="n">
-        <v>-15.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>21.7</v>
+        <v>22.05</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-9.4</v>
+        <v>-12</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>73.2</v>
+        <v>73.33</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>-12</v>
+        <v>-12.4</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-12.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>73.31999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>-7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D43" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>22.26</v>
+        <v>22.4</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>73.16</v>
+        <v>73.2</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>-10.9</v>
+        <v>-16</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-16</v>
+        <v>-10.1</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>22.3</v>
+        <v>22.31</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>-10.1</v>
+        <v>-5.9</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>73.16</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>22.31</v>
+        <v>22.43</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-5.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
         <v>72.8</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>73.06999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>22.43</v>
+        <v>22.41</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>-9.9</v>
+        <v>-13.3</v>
       </c>
       <c r="G48" s="9" t="n">
         <v>68</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>73.11</v>
+        <v>73.06</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-13.3</v>
+        <v>-16.6</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B50" s="8" t="n">
         <v>72.5</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>73.06</v>
+        <v>72.97</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>-16.6</v>
+        <v>-11.8</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>72.97</v>
+        <v>72.86</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>22.26</v>
+        <v>22.21</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-11.8</v>
+        <v>-21.1</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>72.86</v>
+        <v>72.8</v>
       </c>
       <c r="D52" s="8" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>-21.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>72.8</v>
+        <v>72.69</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>22.24</v>
+        <v>22.19</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-25.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>72.69</v>
+        <v>72.61</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>-18.3</v>
+        <v>-16</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>-16</v>
+        <v>-10.4</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="n"/>
       <c r="C56" s="7" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="D56" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="D56" s="8" t="n"/>
       <c r="E56" s="7" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>-10.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B57" s="8" t="n"/>
       <c r="C57" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="7" t="n">
-        <v>21.85</v>
+        <v>21.7</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B58" s="8" t="n"/>
       <c r="C58" s="7" t="n">
-        <v>72.58</v>
+        <v>72.5</v>
       </c>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>-12.3</v>
+        <v>-6.6</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B59" s="8" t="n"/>
       <c r="C59" s="7" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="7" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B60" s="8" t="n"/>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C60" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D60" s="8" t="n"/>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="D60" s="8" t="n">
+        <v>21.2</v>
+      </c>
       <c r="E60" s="7" t="n">
-        <v>21.73</v>
+        <v>21.63</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>21.63</v>
+        <v>21.57</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B62" s="8" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="C62" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E62" s="7" t="n">
         <v>21.57</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>-7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B63" s="8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>72.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D63" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E63" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E63" s="7" t="n">
-        <v>21.57</v>
-      </c>
       <c r="F63" s="8" t="n">
-        <v>-10.9</v>
+        <v>-7.7</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="n"/>
       <c r="C64" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D64" s="8" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D64" s="8" t="n"/>
       <c r="E64" s="7" t="n">
         <v>21.8</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.9</v>
       </c>
       <c r="G64" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B65" s="8" t="n"/>
@@ -5070,19 +5074,19 @@
         <v>21.8</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>-8.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B66" s="8" t="n"/>
@@ -5094,274 +5098,278 @@
         <v>21.8</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>-12.5</v>
+        <v>-11.2</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B67" s="8" t="n"/>
       <c r="C67" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>-11.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G67" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B68" s="8" t="n"/>
       <c r="C68" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="7" t="n">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>-13.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B69" s="8" t="n"/>
       <c r="C69" s="7" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="7" t="n">
-        <v>22.15</v>
+        <v>22.5</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="G69" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="n"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="C70" s="7" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="D70" s="8" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D70" s="8" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E70" s="7" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>-12.4</v>
+        <v>-7.8</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>20.5</v>
+        <v>20.95</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>-7.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B72" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C72" s="7" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>20.95</v>
+        <v>21.13</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>-3.1</v>
+        <v>-11.8</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B73" s="8" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C73" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D73" s="8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>-11.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B74" s="8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="C74" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B75" s="8" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C75" s="7" t="n">
-        <v>72.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>-8.6</v>
+        <v>-13.5</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B76" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>21.33</v>
+        <v>21.43</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H76" s="10" t="n">
         <v>7.7</v>
@@ -5370,477 +5378,469 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B77" s="8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="C77" s="7" t="n">
-        <v>72.23</v>
+        <v>72.39</v>
       </c>
       <c r="D77" s="8" t="n">
         <v>22</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>21.43</v>
+        <v>21.64</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>-7.1</v>
+        <v>-12.5</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C78" s="7" t="n">
         <v>72.39</v>
       </c>
       <c r="D78" s="8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>21.64</v>
+        <v>21.69</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>-12.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>72.39</v>
+        <v>72.36</v>
       </c>
       <c r="D79" s="8" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>21.69</v>
+        <v>21.56</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>-6.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B80" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="n"/>
       <c r="C80" s="7" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="D80" s="8" t="n">
-        <v>20.6</v>
-      </c>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="D80" s="8" t="n"/>
       <c r="E80" s="7" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B81" s="8" t="n"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="C81" s="7" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="D81" s="8" t="n"/>
+        <v>72.45</v>
+      </c>
+      <c r="D81" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E81" s="7" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B82" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>72.45</v>
+        <v>72.47</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>21.67</v>
+        <v>21.53</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B83" s="8" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>72.47</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D83" s="8" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>21.53</v>
+        <v>21.47</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B84" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C84" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D84" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B85" s="8" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>72.31999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="D85" s="8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>-4.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B86" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="C86" s="7" t="n">
-        <v>72.23</v>
+        <v>72.3</v>
       </c>
       <c r="D86" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>21.4</v>
+        <v>21.55</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>-1.6</v>
+        <v>-15.1</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B87" s="8" t="n">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>72.3</v>
+        <v>72.37</v>
       </c>
       <c r="D87" s="8" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>21.55</v>
+        <v>21.69</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>-15.1</v>
+        <v>-10.3</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B88" s="8" t="n">
-        <v>72.8</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="n"/>
       <c r="C88" s="7" t="n">
-        <v>72.37</v>
-      </c>
-      <c r="D88" s="8" t="n">
-        <v>22.5</v>
-      </c>
+        <v>72.28</v>
+      </c>
+      <c r="D88" s="8" t="n"/>
       <c r="E88" s="7" t="n">
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>-10.3</v>
+        <v>-14.8</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>5.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B89" s="8" t="n"/>
       <c r="C89" s="7" t="n">
-        <v>72.28</v>
+        <v>72.3</v>
       </c>
       <c r="D89" s="8" t="n"/>
       <c r="E89" s="7" t="n">
-        <v>21.67</v>
+        <v>21.78</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>-14.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B90" s="8" t="n"/>
       <c r="C90" s="7" t="n">
-        <v>72.3</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="D90" s="8" t="n"/>
       <c r="E90" s="7" t="n">
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>-15.7</v>
+        <v>-15.4</v>
       </c>
       <c r="G90" s="9" t="n">
         <v>60</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B91" s="8" t="n"/>
       <c r="C91" s="7" t="n">
-        <v>72.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D91" s="8" t="n"/>
       <c r="E91" s="7" t="n">
-        <v>21.82</v>
+        <v>21.83</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>-15.4</v>
+        <v>-8.9</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B92" s="8" t="n"/>
       <c r="C92" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D92" s="8" t="n"/>
       <c r="E92" s="7" t="n">
-        <v>21.83</v>
+        <v>22</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>-8.9</v>
+        <v>-6.7</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B93" s="8" t="n"/>
       <c r="C93" s="7" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D93" s="8" t="n"/>
       <c r="E93" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>-6.7</v>
+        <v>-12.2</v>
       </c>
       <c r="G93" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B94" s="8" t="n"/>
-      <c r="C94" s="7" t="n">
-        <v>72.8</v>
-      </c>
+      <c r="C94" s="7" t="n"/>
       <c r="D94" s="8" t="n"/>
-      <c r="E94" s="7" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="E94" s="7" t="n"/>
       <c r="F94" s="8" t="n">
-        <v>-7.3</v>
+        <v>-4.5</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H94" s="10" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -6241,16 +6241,16 @@
         <v>53</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>54.4</v>
+        <v>54.2</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>500</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>318</v>
+        <v>363</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>-182</v>
+        <v>-137</v>
       </c>
     </row>
     <row r="16">

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -1291,7 +1291,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Norge → hjem man. RACE lør</t>
+          <t>Gentofte (hjem fra Norge søn 23.). RACE lør</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>54.2</v>
+        <v>52.9</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -5814,7 +5814,7 @@
         <v>22.5</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>-12.2</v>
+        <v>-4.8</v>
       </c>
       <c r="G93" s="9" t="n">
         <v>47</v>
@@ -5834,7 +5834,7 @@
       <c r="D94" s="8" t="n"/>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="8" t="n">
-        <v>-4.5</v>
+        <v>0.6</v>
       </c>
       <c r="G94" s="9" t="n">
         <v>56</v>
@@ -6241,16 +6241,16 @@
         <v>53</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>54.2</v>
+        <v>52.9</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>500</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>-137</v>
+        <v>-126</v>
       </c>
     </row>
     <row r="16">

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>72.8</v>
+        <v>73.2</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>68</v>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>22.5</v>
+        <v>21.9</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>16</v>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>4.71</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>52.9</v>
+        <v>51.7</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -3536,7 +3536,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
@@ -3544,19 +3544,19 @@
       <c r="D5" s="8" t="n"/>
       <c r="E5" s="7" t="n"/>
       <c r="F5" s="8" t="n">
-        <v>-1.4</v>
+        <v>-1.3</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
@@ -3564,19 +3564,19 @@
       <c r="D6" s="8" t="n"/>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="8" t="n">
-        <v>-1.3</v>
+        <v>-7.7</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
@@ -3584,19 +3584,19 @@
       <c r="D7" s="8" t="n"/>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.6</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
@@ -3604,19 +3604,19 @@
       <c r="D8" s="8" t="n"/>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="8" t="n">
-        <v>-8.6</v>
+        <v>-16.4</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B9" s="8" t="n"/>
@@ -3627,16 +3627,16 @@
         <v>-16.4</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
@@ -3644,19 +3644,19 @@
       <c r="D10" s="8" t="n"/>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="8" t="n">
-        <v>-16.4</v>
+        <v>-14.3</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
@@ -3664,19 +3664,19 @@
       <c r="D11" s="8" t="n"/>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="8" t="n">
-        <v>-14.3</v>
+        <v>-9.1</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
@@ -3684,19 +3684,19 @@
       <c r="D12" s="8" t="n"/>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="8" t="n">
-        <v>-9.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
@@ -3704,39 +3704,47 @@
       <c r="D13" s="8" t="n"/>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="8" t="n">
-        <v>-8.300000000000001</v>
+        <v>-5</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="7" t="n"/>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>22</v>
+      </c>
       <c r="F14" s="8" t="n">
-        <v>-5</v>
+        <v>-1.8</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
@@ -3746,103 +3754,99 @@
         <v>74.5</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-1.8</v>
+        <v>-13.8</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="n">
-        <v>74.5</v>
-      </c>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n"/>
       <c r="C16" s="7" t="n">
         <v>74.5</v>
       </c>
-      <c r="D16" s="8" t="n">
-        <v>23</v>
-      </c>
+      <c r="D16" s="8" t="n"/>
       <c r="E16" s="7" t="n">
         <v>22.5</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>-13.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="H16" s="10" t="n">
-        <v>8.1</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="n"/>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>74.40000000000001</v>
+      </c>
       <c r="C17" s="7" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="D17" s="8" t="n"/>
+        <v>74.47</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>23.3</v>
+      </c>
       <c r="E17" s="7" t="n">
-        <v>22.5</v>
+        <v>22.77</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-15.7</v>
+        <v>-10.5</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="H17" s="10" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="n">
-        <v>74.40000000000001</v>
-      </c>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n"/>
       <c r="C18" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D18" s="8" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="D18" s="8" t="n"/>
       <c r="E18" s="7" t="n">
         <v>22.77</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>-10.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B19" s="8" t="n"/>
@@ -3854,90 +3858,94 @@
         <v>22.77</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-9.4</v>
+        <v>-7.5</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n"/>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>74.5</v>
+      </c>
       <c r="C20" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D20" s="8" t="n"/>
+      <c r="D20" s="8" t="n">
+        <v>22.9</v>
+      </c>
       <c r="E20" s="7" t="n">
-        <v>22.77</v>
+        <v>22.8</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>-7.5</v>
+        <v>-4.5</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>74.47</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.2</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>23</v>
+        <v>22.93</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-2.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H22" s="10" t="n">
         <v>8</v>
@@ -3946,291 +3954,283 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C23" s="7" t="n">
         <v>74.7</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>22.93</v>
+        <v>22.78</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>74.7</v>
+        <v>74.64</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>22.78</v>
+        <v>22.6</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>-11.9</v>
+        <v>-10.3</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>22.6</v>
+        <v>22.55</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-10.3</v>
+        <v>-13.7</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>74.65000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>22.55</v>
+        <v>22.57</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-13.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="n">
-        <v>74.2</v>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n"/>
       <c r="C27" s="7" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="D27" s="8" t="n">
-        <v>22.7</v>
-      </c>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D27" s="8" t="n"/>
       <c r="E27" s="7" t="n">
-        <v>22.57</v>
+        <v>22.52</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-15.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B28" s="8" t="n"/>
       <c r="C28" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.52</v>
       </c>
       <c r="D28" s="8" t="n"/>
       <c r="E28" s="7" t="n">
-        <v>22.52</v>
+        <v>22.46</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B29" s="8" t="n"/>
       <c r="C29" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D29" s="8" t="n"/>
       <c r="E29" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-18.2</v>
+        <v>-23.1</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B30" s="8" t="n"/>
       <c r="C30" s="7" t="n">
-        <v>74.42</v>
+        <v>74.33</v>
       </c>
       <c r="D30" s="8" t="n"/>
       <c r="E30" s="7" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="7" t="n">
-        <v>74.33</v>
+        <v>74.45</v>
       </c>
       <c r="D31" s="8" t="n"/>
       <c r="E31" s="7" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-18.2</v>
+        <v>-19.5</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B32" s="8" t="n"/>
       <c r="C32" s="7" t="n">
-        <v>74.45</v>
+        <v>74.2</v>
       </c>
       <c r="D32" s="8" t="n"/>
       <c r="E32" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-19.5</v>
+        <v>-26.4</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B33" s="8" t="n"/>
-      <c r="C33" s="7" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="C33" s="7" t="n"/>
       <c r="D33" s="8" t="n"/>
-      <c r="E33" s="7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="E33" s="7" t="n"/>
       <c r="F33" s="8" t="n">
-        <v>-26.4</v>
+        <v>-19.9</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B34" s="8" t="n"/>
@@ -4238,807 +4238,811 @@
       <c r="D34" s="8" t="n"/>
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="8" t="n">
-        <v>-19.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="n"/>
-      <c r="C35" s="7" t="n"/>
-      <c r="D35" s="8" t="n"/>
-      <c r="E35" s="7" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E35" s="7" t="n">
+        <v>21.7</v>
+      </c>
       <c r="F35" s="8" t="n">
-        <v>-15.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>21.7</v>
+        <v>22.05</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>-9.4</v>
+        <v>-12</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>73.2</v>
+        <v>73.33</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-12</v>
+        <v>-12.4</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>-12.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>73.31999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D42" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>22.26</v>
+        <v>22.4</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>73.16</v>
+        <v>73.2</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-10.9</v>
+        <v>-16</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>-16</v>
+        <v>-10.1</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>22.3</v>
+        <v>22.31</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-10.1</v>
+        <v>-5.9</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>73.16</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>22.31</v>
+        <v>22.43</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>-5.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
         <v>72.8</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>73.06999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>22.43</v>
+        <v>22.41</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-9.9</v>
+        <v>-13.3</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>68</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>73.11</v>
+        <v>73.06</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>-13.3</v>
+        <v>-16.6</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
         <v>72.5</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>73.06</v>
+        <v>72.97</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-16.6</v>
+        <v>-11.8</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>72.97</v>
+        <v>72.86</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>22.26</v>
+        <v>22.21</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>-11.8</v>
+        <v>-21.1</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>72.86</v>
+        <v>72.8</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-21.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>72.8</v>
+        <v>72.69</v>
       </c>
       <c r="D52" s="8" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>22.24</v>
+        <v>22.19</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>-25.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>72.69</v>
+        <v>72.61</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-18.3</v>
+        <v>-16</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>-16</v>
+        <v>-10.4</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n"/>
       <c r="C55" s="7" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="D55" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="D55" s="8" t="n"/>
       <c r="E55" s="7" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>-10.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B56" s="8" t="n"/>
       <c r="C56" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="7" t="n">
-        <v>21.85</v>
+        <v>21.7</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B57" s="8" t="n"/>
       <c r="C57" s="7" t="n">
-        <v>72.58</v>
+        <v>72.5</v>
       </c>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>-12.3</v>
+        <v>-6.6</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B58" s="8" t="n"/>
       <c r="C58" s="7" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="7" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B59" s="8" t="n"/>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C59" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D59" s="8" t="n"/>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="D59" s="8" t="n">
+        <v>21.2</v>
+      </c>
       <c r="E59" s="7" t="n">
-        <v>21.73</v>
+        <v>21.63</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B60" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C60" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>21.63</v>
+        <v>21.57</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E61" s="7" t="n">
         <v>21.57</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>-7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B62" s="8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C62" s="7" t="n">
-        <v>72.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D62" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E62" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E62" s="7" t="n">
-        <v>21.57</v>
-      </c>
       <c r="F62" s="8" t="n">
-        <v>-10.9</v>
+        <v>-7.7</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B63" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="n"/>
       <c r="C63" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D63" s="8" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D63" s="8" t="n"/>
       <c r="E63" s="7" t="n">
         <v>21.8</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.9</v>
       </c>
       <c r="G63" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B64" s="8" t="n"/>
@@ -5050,19 +5054,19 @@
         <v>21.8</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>-8.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B65" s="8" t="n"/>
@@ -5074,274 +5078,278 @@
         <v>21.8</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>-12.5</v>
+        <v>-11.2</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B66" s="8" t="n"/>
       <c r="C66" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>-11.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G66" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B67" s="8" t="n"/>
       <c r="C67" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="7" t="n">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>-13.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B68" s="8" t="n"/>
       <c r="C68" s="7" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="7" t="n">
-        <v>22.15</v>
+        <v>22.5</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="G68" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B69" s="8" t="n"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="C69" s="7" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="D69" s="8" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D69" s="8" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E69" s="7" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>-12.4</v>
+        <v>-7.8</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C70" s="7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>20.5</v>
+        <v>20.95</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>-7.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>20.95</v>
+        <v>21.13</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>-3.1</v>
+        <v>-11.8</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B72" s="8" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C72" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>-11.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B73" s="8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="C73" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D73" s="8" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B74" s="8" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C74" s="7" t="n">
-        <v>72.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>-8.6</v>
+        <v>-13.5</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B75" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C75" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>21.33</v>
+        <v>21.43</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H75" s="10" t="n">
         <v>7.7</v>
@@ -5350,497 +5358,497 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B76" s="8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>72.23</v>
+        <v>72.39</v>
       </c>
       <c r="D76" s="8" t="n">
         <v>22</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>21.43</v>
+        <v>21.64</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>-7.1</v>
+        <v>-12.5</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B77" s="8" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C77" s="7" t="n">
         <v>72.39</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>21.64</v>
+        <v>21.69</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>-12.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C78" s="7" t="n">
-        <v>72.39</v>
+        <v>72.36</v>
       </c>
       <c r="D78" s="8" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>21.69</v>
+        <v>21.56</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>-6.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B79" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="n"/>
       <c r="C79" s="7" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="D79" s="8" t="n">
-        <v>20.6</v>
-      </c>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="D79" s="8" t="n"/>
       <c r="E79" s="7" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B80" s="8" t="n"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="C80" s="7" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="D80" s="8" t="n"/>
+        <v>72.45</v>
+      </c>
+      <c r="D80" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E80" s="7" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>72.45</v>
+        <v>72.47</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>21.67</v>
+        <v>21.53</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B82" s="8" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>72.47</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>21.53</v>
+        <v>21.47</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B83" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D83" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B84" s="8" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C84" s="7" t="n">
-        <v>72.31999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="D84" s="8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>-4.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B85" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>72.23</v>
+        <v>72.3</v>
       </c>
       <c r="D85" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>21.4</v>
+        <v>21.55</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>-1.6</v>
+        <v>-15.1</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B86" s="8" t="n">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="C86" s="7" t="n">
-        <v>72.3</v>
+        <v>72.37</v>
       </c>
       <c r="D86" s="8" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>21.55</v>
+        <v>21.69</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>-15.1</v>
+        <v>-10.3</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B87" s="8" t="n">
-        <v>72.8</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="n"/>
       <c r="C87" s="7" t="n">
-        <v>72.37</v>
-      </c>
-      <c r="D87" s="8" t="n">
-        <v>22.5</v>
-      </c>
+        <v>72.28</v>
+      </c>
+      <c r="D87" s="8" t="n"/>
       <c r="E87" s="7" t="n">
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>-10.3</v>
+        <v>-14.8</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>5.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B88" s="8" t="n"/>
       <c r="C88" s="7" t="n">
-        <v>72.28</v>
+        <v>72.3</v>
       </c>
       <c r="D88" s="8" t="n"/>
       <c r="E88" s="7" t="n">
-        <v>21.67</v>
+        <v>21.78</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>-14.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B89" s="8" t="n"/>
       <c r="C89" s="7" t="n">
-        <v>72.3</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="D89" s="8" t="n"/>
       <c r="E89" s="7" t="n">
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>-15.7</v>
+        <v>-15.4</v>
       </c>
       <c r="G89" s="9" t="n">
         <v>60</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B90" s="8" t="n"/>
       <c r="C90" s="7" t="n">
-        <v>72.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D90" s="8" t="n"/>
       <c r="E90" s="7" t="n">
-        <v>21.82</v>
+        <v>21.83</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>-15.4</v>
+        <v>-8.9</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B91" s="8" t="n"/>
       <c r="C91" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D91" s="8" t="n"/>
       <c r="E91" s="7" t="n">
-        <v>21.83</v>
+        <v>22</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>-8.9</v>
+        <v>-6.7</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B92" s="8" t="n"/>
       <c r="C92" s="7" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D92" s="8" t="n"/>
       <c r="E92" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>-6.7</v>
+        <v>-4.8</v>
       </c>
       <c r="G92" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B93" s="8" t="n"/>
-      <c r="C93" s="7" t="n">
-        <v>72.8</v>
-      </c>
+      <c r="C93" s="7" t="n"/>
       <c r="D93" s="8" t="n"/>
-      <c r="E93" s="7" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="E93" s="7" t="n"/>
       <c r="F93" s="8" t="n">
-        <v>-4.8</v>
+        <v>0.6</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B94" s="8" t="n"/>
-      <c r="C94" s="7" t="n"/>
-      <c r="D94" s="8" t="n"/>
-      <c r="E94" s="7" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="C94" s="7" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="D94" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E94" s="7" t="n">
+        <v>21.9</v>
+      </c>
       <c r="F94" s="8" t="n">
-        <v>0.6</v>
+        <v>6.3</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="H94" s="10" t="n">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -6270,7 +6278,9 @@
       <c r="D16" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="E16" s="8" t="n"/>
+      <c r="E16" s="8" t="n">
+        <v>51.7</v>
+      </c>
       <c r="F16" s="4" t="n">
         <v>300</v>
       </c>

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>73.2</v>
+        <v>72.8</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>68</v>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>21.9</v>
+        <v>22.2</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>16</v>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>4.71</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>51.7</v>
+        <v>53.7</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -3536,7 +3536,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
@@ -3544,19 +3544,19 @@
       <c r="D5" s="8" t="n"/>
       <c r="E5" s="7" t="n"/>
       <c r="F5" s="8" t="n">
-        <v>-1.3</v>
+        <v>-7.7</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
@@ -3564,19 +3564,19 @@
       <c r="D6" s="8" t="n"/>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.6</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
@@ -3584,19 +3584,19 @@
       <c r="D7" s="8" t="n"/>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="8" t="n">
-        <v>-8.6</v>
+        <v>-16.4</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
@@ -3607,16 +3607,16 @@
         <v>-16.4</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B9" s="8" t="n"/>
@@ -3624,19 +3624,19 @@
       <c r="D9" s="8" t="n"/>
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="8" t="n">
-        <v>-16.4</v>
+        <v>-14.3</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
@@ -3644,19 +3644,19 @@
       <c r="D10" s="8" t="n"/>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="8" t="n">
-        <v>-14.3</v>
+        <v>-9.1</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
@@ -3664,19 +3664,19 @@
       <c r="D11" s="8" t="n"/>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="8" t="n">
-        <v>-9.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
@@ -3684,39 +3684,47 @@
       <c r="D12" s="8" t="n"/>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="8" t="n">
-        <v>-8.300000000000001</v>
+        <v>-5</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="7" t="n"/>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>22</v>
+      </c>
       <c r="F13" s="8" t="n">
-        <v>-5</v>
+        <v>-1.8</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
@@ -3726,103 +3734,99 @@
         <v>74.5</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>-1.8</v>
+        <v>-13.8</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="n">
-        <v>74.5</v>
-      </c>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n"/>
       <c r="C15" s="7" t="n">
         <v>74.5</v>
       </c>
-      <c r="D15" s="8" t="n">
-        <v>23</v>
-      </c>
+      <c r="D15" s="8" t="n"/>
       <c r="E15" s="7" t="n">
         <v>22.5</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-13.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="H15" s="10" t="n">
-        <v>8.1</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="n"/>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>74.40000000000001</v>
+      </c>
       <c r="C16" s="7" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="D16" s="8" t="n"/>
+        <v>74.47</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>23.3</v>
+      </c>
       <c r="E16" s="7" t="n">
-        <v>22.5</v>
+        <v>22.77</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>-15.7</v>
+        <v>-10.5</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="H16" s="10" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="n">
-        <v>74.40000000000001</v>
-      </c>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n"/>
       <c r="C17" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D17" s="8" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="D17" s="8" t="n"/>
       <c r="E17" s="7" t="n">
         <v>22.77</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-10.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B18" s="8" t="n"/>
@@ -3834,90 +3838,94 @@
         <v>22.77</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>-9.4</v>
+        <v>-7.5</v>
       </c>
       <c r="G18" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n"/>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>74.5</v>
+      </c>
       <c r="C19" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D19" s="8" t="n"/>
+      <c r="D19" s="8" t="n">
+        <v>22.9</v>
+      </c>
       <c r="E19" s="7" t="n">
-        <v>22.77</v>
+        <v>22.8</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-7.5</v>
+        <v>-4.5</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>74.47</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.2</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>23</v>
+        <v>22.93</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-2.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H21" s="10" t="n">
         <v>8</v>
@@ -3926,291 +3934,283 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>74.7</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>22.93</v>
+        <v>22.78</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>74.7</v>
+        <v>74.64</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>22.78</v>
+        <v>22.6</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-11.9</v>
+        <v>-10.3</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>22.6</v>
+        <v>22.55</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>-10.3</v>
+        <v>-13.7</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>74.65000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>22.55</v>
+        <v>22.57</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-13.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="n">
-        <v>74.2</v>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n"/>
       <c r="C26" s="7" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>22.7</v>
-      </c>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="7" t="n">
-        <v>22.57</v>
+        <v>22.52</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-15.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.52</v>
       </c>
       <c r="D27" s="8" t="n"/>
       <c r="E27" s="7" t="n">
-        <v>22.52</v>
+        <v>22.46</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B28" s="8" t="n"/>
       <c r="C28" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D28" s="8" t="n"/>
       <c r="E28" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-18.2</v>
+        <v>-23.1</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B29" s="8" t="n"/>
       <c r="C29" s="7" t="n">
-        <v>74.42</v>
+        <v>74.33</v>
       </c>
       <c r="D29" s="8" t="n"/>
       <c r="E29" s="7" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B30" s="8" t="n"/>
       <c r="C30" s="7" t="n">
-        <v>74.33</v>
+        <v>74.45</v>
       </c>
       <c r="D30" s="8" t="n"/>
       <c r="E30" s="7" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-18.2</v>
+        <v>-19.5</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B31" s="8" t="n"/>
       <c r="C31" s="7" t="n">
-        <v>74.45</v>
+        <v>74.2</v>
       </c>
       <c r="D31" s="8" t="n"/>
       <c r="E31" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-19.5</v>
+        <v>-26.4</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B32" s="8" t="n"/>
-      <c r="C32" s="7" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="C32" s="7" t="n"/>
       <c r="D32" s="8" t="n"/>
-      <c r="E32" s="7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="E32" s="7" t="n"/>
       <c r="F32" s="8" t="n">
-        <v>-26.4</v>
+        <v>-19.9</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B33" s="8" t="n"/>
@@ -4218,807 +4218,811 @@
       <c r="D33" s="8" t="n"/>
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="8" t="n">
-        <v>-19.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="7" t="n"/>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="7" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>21.7</v>
+      </c>
       <c r="F34" s="8" t="n">
-        <v>-15.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>21.7</v>
+        <v>22.05</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-9.4</v>
+        <v>-12</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>73.2</v>
+        <v>73.33</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>-12</v>
+        <v>-12.4</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-12.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>73.31999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>-7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D41" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>22.26</v>
+        <v>22.4</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>73.16</v>
+        <v>73.2</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>-10.9</v>
+        <v>-16</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-16</v>
+        <v>-10.1</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>22.3</v>
+        <v>22.31</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>-10.1</v>
+        <v>-5.9</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>73.16</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>22.31</v>
+        <v>22.43</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-5.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
         <v>72.8</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>73.06999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>22.43</v>
+        <v>22.41</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>-9.9</v>
+        <v>-13.3</v>
       </c>
       <c r="G46" s="9" t="n">
         <v>68</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>73.11</v>
+        <v>73.06</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-13.3</v>
+        <v>-16.6</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
         <v>72.5</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>73.06</v>
+        <v>72.97</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>-16.6</v>
+        <v>-11.8</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>72.97</v>
+        <v>72.86</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>22.26</v>
+        <v>22.21</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-11.8</v>
+        <v>-21.1</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>72.86</v>
+        <v>72.8</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>-21.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>72.8</v>
+        <v>72.69</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>22.24</v>
+        <v>22.19</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-25.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>72.69</v>
+        <v>72.61</v>
       </c>
       <c r="D52" s="8" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>-18.3</v>
+        <v>-16</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-16</v>
+        <v>-10.4</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="n"/>
       <c r="C54" s="7" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="D54" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="D54" s="8" t="n"/>
       <c r="E54" s="7" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>-10.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B55" s="8" t="n"/>
       <c r="C55" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="7" t="n">
-        <v>21.85</v>
+        <v>21.7</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B56" s="8" t="n"/>
       <c r="C56" s="7" t="n">
-        <v>72.58</v>
+        <v>72.5</v>
       </c>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>-12.3</v>
+        <v>-6.6</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B57" s="8" t="n"/>
       <c r="C57" s="7" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="7" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B58" s="8" t="n"/>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C58" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D58" s="8" t="n"/>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="D58" s="8" t="n">
+        <v>21.2</v>
+      </c>
       <c r="E58" s="7" t="n">
-        <v>21.73</v>
+        <v>21.63</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>21.63</v>
+        <v>21.57</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B60" s="8" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="C60" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E60" s="7" t="n">
         <v>21.57</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>-7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>72.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D61" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E61" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E61" s="7" t="n">
-        <v>21.57</v>
-      </c>
       <c r="F61" s="8" t="n">
-        <v>-10.9</v>
+        <v>-7.7</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B62" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="n"/>
       <c r="C62" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D62" s="8" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D62" s="8" t="n"/>
       <c r="E62" s="7" t="n">
         <v>21.8</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.9</v>
       </c>
       <c r="G62" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B63" s="8" t="n"/>
@@ -5030,19 +5034,19 @@
         <v>21.8</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>-8.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B64" s="8" t="n"/>
@@ -5054,274 +5058,278 @@
         <v>21.8</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>-12.5</v>
+        <v>-11.2</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B65" s="8" t="n"/>
       <c r="C65" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>-11.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G65" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B66" s="8" t="n"/>
       <c r="C66" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="7" t="n">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>-13.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B67" s="8" t="n"/>
       <c r="C67" s="7" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="7" t="n">
-        <v>22.15</v>
+        <v>22.5</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="G67" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="n"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="C68" s="7" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="D68" s="8" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D68" s="8" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E68" s="7" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>-12.4</v>
+        <v>-7.8</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B69" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>20.5</v>
+        <v>20.95</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>-7.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C70" s="7" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>20.95</v>
+        <v>21.13</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>-3.1</v>
+        <v>-11.8</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>-11.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B72" s="8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="C72" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B73" s="8" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C73" s="7" t="n">
-        <v>72.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D73" s="8" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>-8.6</v>
+        <v>-13.5</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B74" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C74" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>21.33</v>
+        <v>21.43</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H74" s="10" t="n">
         <v>7.7</v>
@@ -5330,525 +5338,525 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B75" s="8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="C75" s="7" t="n">
-        <v>72.23</v>
+        <v>72.39</v>
       </c>
       <c r="D75" s="8" t="n">
         <v>22</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>21.43</v>
+        <v>21.64</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>-7.1</v>
+        <v>-12.5</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B76" s="8" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C76" s="7" t="n">
         <v>72.39</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>21.64</v>
+        <v>21.69</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>-12.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B77" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C77" s="7" t="n">
-        <v>72.39</v>
+        <v>72.36</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>21.69</v>
+        <v>21.56</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>-6.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B78" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="n"/>
       <c r="C78" s="7" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="D78" s="8" t="n">
-        <v>20.6</v>
-      </c>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="D78" s="8" t="n"/>
       <c r="E78" s="7" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B79" s="8" t="n"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="C79" s="7" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="D79" s="8" t="n"/>
+        <v>72.45</v>
+      </c>
+      <c r="D79" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E79" s="7" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C80" s="7" t="n">
-        <v>72.45</v>
+        <v>72.47</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>21.67</v>
+        <v>21.53</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>72.47</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>21.53</v>
+        <v>21.47</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B82" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B83" s="8" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>72.31999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="D83" s="8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>-4.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B84" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="C84" s="7" t="n">
-        <v>72.23</v>
+        <v>72.3</v>
       </c>
       <c r="D84" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>21.4</v>
+        <v>21.55</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>-1.6</v>
+        <v>-15.1</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B85" s="8" t="n">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>72.3</v>
+        <v>72.37</v>
       </c>
       <c r="D85" s="8" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>21.55</v>
+        <v>21.69</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>-15.1</v>
+        <v>-10.3</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B86" s="8" t="n">
-        <v>72.8</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="n"/>
       <c r="C86" s="7" t="n">
-        <v>72.37</v>
-      </c>
-      <c r="D86" s="8" t="n">
-        <v>22.5</v>
-      </c>
+        <v>72.28</v>
+      </c>
+      <c r="D86" s="8" t="n"/>
       <c r="E86" s="7" t="n">
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>-10.3</v>
+        <v>-14.8</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>5.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B87" s="8" t="n"/>
       <c r="C87" s="7" t="n">
-        <v>72.28</v>
+        <v>72.3</v>
       </c>
       <c r="D87" s="8" t="n"/>
       <c r="E87" s="7" t="n">
-        <v>21.67</v>
+        <v>21.78</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>-14.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B88" s="8" t="n"/>
       <c r="C88" s="7" t="n">
-        <v>72.3</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="D88" s="8" t="n"/>
       <c r="E88" s="7" t="n">
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>-15.7</v>
+        <v>-15.4</v>
       </c>
       <c r="G88" s="9" t="n">
         <v>60</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B89" s="8" t="n"/>
       <c r="C89" s="7" t="n">
-        <v>72.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D89" s="8" t="n"/>
       <c r="E89" s="7" t="n">
-        <v>21.82</v>
+        <v>21.83</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>-15.4</v>
+        <v>-8.9</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B90" s="8" t="n"/>
       <c r="C90" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D90" s="8" t="n"/>
       <c r="E90" s="7" t="n">
-        <v>21.83</v>
+        <v>22</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>-8.9</v>
+        <v>-6.7</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B91" s="8" t="n"/>
       <c r="C91" s="7" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D91" s="8" t="n"/>
       <c r="E91" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>-6.7</v>
+        <v>-4.8</v>
       </c>
       <c r="G91" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B92" s="8" t="n"/>
-      <c r="C92" s="7" t="n">
-        <v>72.8</v>
-      </c>
+      <c r="C92" s="7" t="n"/>
       <c r="D92" s="8" t="n"/>
-      <c r="E92" s="7" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="E92" s="7" t="n"/>
       <c r="F92" s="8" t="n">
-        <v>-4.8</v>
+        <v>0.6</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B93" s="8" t="n"/>
-      <c r="C93" s="7" t="n"/>
-      <c r="D93" s="8" t="n"/>
-      <c r="E93" s="7" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="C93" s="7" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="D93" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E93" s="7" t="n">
+        <v>21.9</v>
+      </c>
       <c r="F93" s="8" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B94" s="8" t="n">
-        <v>73.2</v>
+        <v>72.8</v>
       </c>
       <c r="C94" s="7" t="n">
-        <v>73.2</v>
+        <v>73</v>
       </c>
       <c r="D94" s="8" t="n">
-        <v>21.9</v>
+        <v>22.2</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>21.9</v>
+        <v>22.05</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>6.3</v>
+        <v>-5.3</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H94" s="10" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -6279,13 +6287,17 @@
         <v>51</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>51.7</v>
+        <v>53.7</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>300</v>
       </c>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="11" t="n"/>
+      <c r="G16" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="H16" s="11" t="n">
+        <v>-277</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>68</v>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>22.2</v>
+        <v>21.6</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>16</v>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>4.71</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>53.7</v>
+        <v>54.2</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -3536,7 +3536,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
@@ -3544,19 +3544,19 @@
       <c r="D5" s="8" t="n"/>
       <c r="E5" s="7" t="n"/>
       <c r="F5" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.6</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
@@ -3564,19 +3564,19 @@
       <c r="D6" s="8" t="n"/>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="8" t="n">
-        <v>-8.6</v>
+        <v>-16.4</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
@@ -3587,16 +3587,16 @@
         <v>-16.4</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
@@ -3604,19 +3604,19 @@
       <c r="D8" s="8" t="n"/>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="8" t="n">
-        <v>-16.4</v>
+        <v>-14.3</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B9" s="8" t="n"/>
@@ -3624,19 +3624,19 @@
       <c r="D9" s="8" t="n"/>
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="8" t="n">
-        <v>-14.3</v>
+        <v>-9.1</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
@@ -3644,19 +3644,19 @@
       <c r="D10" s="8" t="n"/>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="8" t="n">
-        <v>-9.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
@@ -3664,39 +3664,47 @@
       <c r="D11" s="8" t="n"/>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="8" t="n">
-        <v>-8.300000000000001</v>
+        <v>-5</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="7" t="n"/>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>22</v>
+      </c>
       <c r="F12" s="8" t="n">
-        <v>-5</v>
+        <v>-1.8</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
@@ -3706,103 +3714,99 @@
         <v>74.5</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-1.8</v>
+        <v>-13.8</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n">
-        <v>74.5</v>
-      </c>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n"/>
       <c r="C14" s="7" t="n">
         <v>74.5</v>
       </c>
-      <c r="D14" s="8" t="n">
-        <v>23</v>
-      </c>
+      <c r="D14" s="8" t="n"/>
       <c r="E14" s="7" t="n">
         <v>22.5</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>-13.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="H14" s="10" t="n">
-        <v>8.1</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="n"/>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>74.40000000000001</v>
+      </c>
       <c r="C15" s="7" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="D15" s="8" t="n"/>
+        <v>74.47</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>23.3</v>
+      </c>
       <c r="E15" s="7" t="n">
-        <v>22.5</v>
+        <v>22.77</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-15.7</v>
+        <v>-10.5</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="H15" s="10" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="n">
-        <v>74.40000000000001</v>
-      </c>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n"/>
       <c r="C16" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D16" s="8" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="D16" s="8" t="n"/>
       <c r="E16" s="7" t="n">
         <v>22.77</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>-10.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B17" s="8" t="n"/>
@@ -3814,90 +3818,94 @@
         <v>22.77</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-9.4</v>
+        <v>-7.5</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="n"/>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>74.5</v>
+      </c>
       <c r="C18" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D18" s="8" t="n"/>
+      <c r="D18" s="8" t="n">
+        <v>22.9</v>
+      </c>
       <c r="E18" s="7" t="n">
-        <v>22.77</v>
+        <v>22.8</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>-7.5</v>
+        <v>-4.5</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>74.47</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.2</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>23</v>
+        <v>22.93</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>-2.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H20" s="10" t="n">
         <v>8</v>
@@ -3906,291 +3914,283 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>74.7</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>22.93</v>
+        <v>22.78</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>74.7</v>
+        <v>74.64</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>22.78</v>
+        <v>22.6</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-11.9</v>
+        <v>-10.3</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>22.6</v>
+        <v>22.55</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-10.3</v>
+        <v>-13.7</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>74.65000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>22.55</v>
+        <v>22.57</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>-13.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="n">
-        <v>74.2</v>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="7" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="D25" s="8" t="n">
-        <v>22.7</v>
-      </c>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D25" s="8" t="n"/>
       <c r="E25" s="7" t="n">
-        <v>22.57</v>
+        <v>22.52</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-15.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.52</v>
       </c>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="7" t="n">
-        <v>22.52</v>
+        <v>22.46</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D27" s="8" t="n"/>
       <c r="E27" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-18.2</v>
+        <v>-23.1</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B28" s="8" t="n"/>
       <c r="C28" s="7" t="n">
-        <v>74.42</v>
+        <v>74.33</v>
       </c>
       <c r="D28" s="8" t="n"/>
       <c r="E28" s="7" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B29" s="8" t="n"/>
       <c r="C29" s="7" t="n">
-        <v>74.33</v>
+        <v>74.45</v>
       </c>
       <c r="D29" s="8" t="n"/>
       <c r="E29" s="7" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-18.2</v>
+        <v>-19.5</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B30" s="8" t="n"/>
       <c r="C30" s="7" t="n">
-        <v>74.45</v>
+        <v>74.2</v>
       </c>
       <c r="D30" s="8" t="n"/>
       <c r="E30" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-19.5</v>
+        <v>-26.4</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B31" s="8" t="n"/>
-      <c r="C31" s="7" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="C31" s="7" t="n"/>
       <c r="D31" s="8" t="n"/>
-      <c r="E31" s="7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="E31" s="7" t="n"/>
       <c r="F31" s="8" t="n">
-        <v>-26.4</v>
+        <v>-19.9</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B32" s="8" t="n"/>
@@ -4198,807 +4198,811 @@
       <c r="D32" s="8" t="n"/>
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="8" t="n">
-        <v>-19.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="n"/>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="7" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <v>21.7</v>
+      </c>
       <c r="F33" s="8" t="n">
-        <v>-15.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>21.7</v>
+        <v>22.05</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-9.4</v>
+        <v>-12</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>73.2</v>
+        <v>73.33</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-12</v>
+        <v>-12.4</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>-12.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>73.31999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D40" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>22.26</v>
+        <v>22.4</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>73.16</v>
+        <v>73.2</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-10.9</v>
+        <v>-16</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>-16</v>
+        <v>-10.1</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>22.3</v>
+        <v>22.31</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-10.1</v>
+        <v>-5.9</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>73.16</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>22.31</v>
+        <v>22.43</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>-5.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
         <v>72.8</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>73.06999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>22.43</v>
+        <v>22.41</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-9.9</v>
+        <v>-13.3</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>68</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>73.11</v>
+        <v>73.06</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>-13.3</v>
+        <v>-16.6</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
         <v>72.5</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>73.06</v>
+        <v>72.97</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-16.6</v>
+        <v>-11.8</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>72.97</v>
+        <v>72.86</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>22.26</v>
+        <v>22.21</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>-11.8</v>
+        <v>-21.1</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>72.86</v>
+        <v>72.8</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-21.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>72.8</v>
+        <v>72.69</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>22.24</v>
+        <v>22.19</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>-25.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>72.69</v>
+        <v>72.61</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-18.3</v>
+        <v>-16</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="D52" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>-16</v>
+        <v>-10.4</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B53" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="n"/>
       <c r="C53" s="7" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="D53" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="D53" s="8" t="n"/>
       <c r="E53" s="7" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-10.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B54" s="8" t="n"/>
       <c r="C54" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="D54" s="8" t="n"/>
       <c r="E54" s="7" t="n">
-        <v>21.85</v>
+        <v>21.7</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B55" s="8" t="n"/>
       <c r="C55" s="7" t="n">
-        <v>72.58</v>
+        <v>72.5</v>
       </c>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>-12.3</v>
+        <v>-6.6</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B56" s="8" t="n"/>
       <c r="C56" s="7" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="7" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="n"/>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C57" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D57" s="8" t="n"/>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>21.2</v>
+      </c>
       <c r="E57" s="7" t="n">
-        <v>21.73</v>
+        <v>21.63</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C58" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>21.63</v>
+        <v>21.57</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E59" s="7" t="n">
         <v>21.57</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>-7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B60" s="8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C60" s="7" t="n">
-        <v>72.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D60" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E60" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E60" s="7" t="n">
-        <v>21.57</v>
-      </c>
       <c r="F60" s="8" t="n">
-        <v>-10.9</v>
+        <v>-7.7</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n"/>
       <c r="C61" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D61" s="8" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D61" s="8" t="n"/>
       <c r="E61" s="7" t="n">
         <v>21.8</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.9</v>
       </c>
       <c r="G61" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B62" s="8" t="n"/>
@@ -5010,19 +5014,19 @@
         <v>21.8</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>-8.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B63" s="8" t="n"/>
@@ -5034,274 +5038,278 @@
         <v>21.8</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>-12.5</v>
+        <v>-11.2</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B64" s="8" t="n"/>
       <c r="C64" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>-11.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G64" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B65" s="8" t="n"/>
       <c r="C65" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="7" t="n">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>-13.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B66" s="8" t="n"/>
       <c r="C66" s="7" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="7" t="n">
-        <v>22.15</v>
+        <v>22.5</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="G66" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="n"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="C67" s="7" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="D67" s="8" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D67" s="8" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E67" s="7" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>-12.4</v>
+        <v>-7.8</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B68" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C68" s="7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>20.5</v>
+        <v>20.95</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>-7.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B69" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>20.95</v>
+        <v>21.13</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>-3.1</v>
+        <v>-11.8</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C70" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>-11.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B72" s="8" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C72" s="7" t="n">
-        <v>72.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>-8.6</v>
+        <v>-13.5</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B73" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C73" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="D73" s="8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>21.33</v>
+        <v>21.43</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H73" s="10" t="n">
         <v>7.7</v>
@@ -5310,510 +5318,510 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B74" s="8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="C74" s="7" t="n">
-        <v>72.23</v>
+        <v>72.39</v>
       </c>
       <c r="D74" s="8" t="n">
         <v>22</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>21.43</v>
+        <v>21.64</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>-7.1</v>
+        <v>-12.5</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B75" s="8" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C75" s="7" t="n">
         <v>72.39</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>21.64</v>
+        <v>21.69</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>-12.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B76" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>72.39</v>
+        <v>72.36</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>21.69</v>
+        <v>21.56</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>-6.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B77" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="n"/>
       <c r="C77" s="7" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="D77" s="8" t="n">
-        <v>20.6</v>
-      </c>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="D77" s="8" t="n"/>
       <c r="E77" s="7" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B78" s="8" t="n"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="C78" s="7" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="D78" s="8" t="n"/>
+        <v>72.45</v>
+      </c>
+      <c r="D78" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E78" s="7" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>72.45</v>
+        <v>72.47</v>
       </c>
       <c r="D79" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>21.67</v>
+        <v>21.53</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C80" s="7" t="n">
-        <v>72.47</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>21.53</v>
+        <v>21.47</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B82" s="8" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>72.31999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>-4.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B83" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>72.23</v>
+        <v>72.3</v>
       </c>
       <c r="D83" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>21.4</v>
+        <v>21.55</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>-1.6</v>
+        <v>-15.1</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B84" s="8" t="n">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="C84" s="7" t="n">
-        <v>72.3</v>
+        <v>72.37</v>
       </c>
       <c r="D84" s="8" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>21.55</v>
+        <v>21.69</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>-15.1</v>
+        <v>-10.3</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B85" s="8" t="n">
-        <v>72.8</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="n"/>
       <c r="C85" s="7" t="n">
-        <v>72.37</v>
-      </c>
-      <c r="D85" s="8" t="n">
-        <v>22.5</v>
-      </c>
+        <v>72.28</v>
+      </c>
+      <c r="D85" s="8" t="n"/>
       <c r="E85" s="7" t="n">
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>-10.3</v>
+        <v>-14.8</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>5.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B86" s="8" t="n"/>
       <c r="C86" s="7" t="n">
-        <v>72.28</v>
+        <v>72.3</v>
       </c>
       <c r="D86" s="8" t="n"/>
       <c r="E86" s="7" t="n">
-        <v>21.67</v>
+        <v>21.78</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>-14.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B87" s="8" t="n"/>
       <c r="C87" s="7" t="n">
-        <v>72.3</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="D87" s="8" t="n"/>
       <c r="E87" s="7" t="n">
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>-15.7</v>
+        <v>-15.4</v>
       </c>
       <c r="G87" s="9" t="n">
         <v>60</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B88" s="8" t="n"/>
       <c r="C88" s="7" t="n">
-        <v>72.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D88" s="8" t="n"/>
       <c r="E88" s="7" t="n">
-        <v>21.82</v>
+        <v>21.83</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>-15.4</v>
+        <v>-8.9</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B89" s="8" t="n"/>
       <c r="C89" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D89" s="8" t="n"/>
       <c r="E89" s="7" t="n">
-        <v>21.83</v>
+        <v>22</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>-8.9</v>
+        <v>-6.7</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B90" s="8" t="n"/>
       <c r="C90" s="7" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D90" s="8" t="n"/>
       <c r="E90" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>-6.7</v>
+        <v>-4.8</v>
       </c>
       <c r="G90" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B91" s="8" t="n"/>
-      <c r="C91" s="7" t="n">
-        <v>72.8</v>
-      </c>
+      <c r="C91" s="7" t="n"/>
       <c r="D91" s="8" t="n"/>
-      <c r="E91" s="7" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="E91" s="7" t="n"/>
       <c r="F91" s="8" t="n">
-        <v>-4.8</v>
+        <v>0.6</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B92" s="8" t="n"/>
-      <c r="C92" s="7" t="n"/>
-      <c r="D92" s="8" t="n"/>
-      <c r="E92" s="7" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="C92" s="7" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="D92" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E92" s="7" t="n">
+        <v>21.9</v>
+      </c>
       <c r="F92" s="8" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B93" s="8" t="n">
-        <v>73.2</v>
+        <v>72.8</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>73.2</v>
+        <v>73</v>
       </c>
       <c r="D93" s="8" t="n">
         <v>21.9</v>
@@ -5822,41 +5830,41 @@
         <v>21.9</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>3.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B94" s="8" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C94" s="7" t="n">
-        <v>73</v>
+        <v>72.97</v>
       </c>
       <c r="D94" s="8" t="n">
-        <v>22.2</v>
+        <v>21.6</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>22.05</v>
+        <v>21.8</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>-5.3</v>
+        <v>-6.3</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="H94" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>9.6</v>
       </c>
     </row>
   </sheetData>
@@ -6287,16 +6295,16 @@
         <v>51</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>53.7</v>
+        <v>54.2</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>300</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>23</v>
+        <v>188</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>-277</v>
+        <v>-112</v>
       </c>
     </row>
     <row r="17">

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>72.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>68</v>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>21.6</v>
+        <v>20.9</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>16</v>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3.81</v>
+        <v>3.83</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>4.71</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>54.2</v>
+        <v>53.4</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -3536,7 +3536,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
@@ -3544,19 +3544,19 @@
       <c r="D5" s="8" t="n"/>
       <c r="E5" s="7" t="n"/>
       <c r="F5" s="8" t="n">
-        <v>-8.6</v>
+        <v>-16.4</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
@@ -3567,16 +3567,16 @@
         <v>-16.4</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
@@ -3584,19 +3584,19 @@
       <c r="D7" s="8" t="n"/>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="8" t="n">
-        <v>-16.4</v>
+        <v>-14.3</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
@@ -3604,19 +3604,19 @@
       <c r="D8" s="8" t="n"/>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="8" t="n">
-        <v>-14.3</v>
+        <v>-9.1</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B9" s="8" t="n"/>
@@ -3624,19 +3624,19 @@
       <c r="D9" s="8" t="n"/>
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="8" t="n">
-        <v>-9.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
@@ -3644,39 +3644,47 @@
       <c r="D10" s="8" t="n"/>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="8" t="n">
-        <v>-8.300000000000001</v>
+        <v>-5</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="7" t="n"/>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>22</v>
+      </c>
       <c r="F11" s="8" t="n">
-        <v>-5</v>
+        <v>-1.8</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
@@ -3686,103 +3694,99 @@
         <v>74.5</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>-1.8</v>
+        <v>-13.8</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n">
-        <v>74.5</v>
-      </c>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n"/>
       <c r="C13" s="7" t="n">
         <v>74.5</v>
       </c>
-      <c r="D13" s="8" t="n">
-        <v>23</v>
-      </c>
+      <c r="D13" s="8" t="n"/>
       <c r="E13" s="7" t="n">
         <v>22.5</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-13.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="H13" s="10" t="n">
-        <v>8.1</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n"/>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>74.40000000000001</v>
+      </c>
       <c r="C14" s="7" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="D14" s="8" t="n"/>
+        <v>74.47</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>23.3</v>
+      </c>
       <c r="E14" s="7" t="n">
-        <v>22.5</v>
+        <v>22.77</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>-15.7</v>
+        <v>-10.5</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="H14" s="10" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="n">
-        <v>74.40000000000001</v>
-      </c>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n"/>
       <c r="C15" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D15" s="8" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="D15" s="8" t="n"/>
       <c r="E15" s="7" t="n">
         <v>22.77</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-10.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B16" s="8" t="n"/>
@@ -3794,90 +3798,94 @@
         <v>22.77</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>-9.4</v>
+        <v>-7.5</v>
       </c>
       <c r="G16" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="n"/>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>74.5</v>
+      </c>
       <c r="C17" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D17" s="8" t="n"/>
+      <c r="D17" s="8" t="n">
+        <v>22.9</v>
+      </c>
       <c r="E17" s="7" t="n">
-        <v>22.77</v>
+        <v>22.8</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-7.5</v>
+        <v>-4.5</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>74.47</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.2</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>23</v>
+        <v>22.93</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-2.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H19" s="10" t="n">
         <v>8</v>
@@ -3886,291 +3894,283 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C20" s="7" t="n">
         <v>74.7</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>22.93</v>
+        <v>22.78</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>74.7</v>
+        <v>74.64</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>22.78</v>
+        <v>22.6</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-11.9</v>
+        <v>-10.3</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>22.6</v>
+        <v>22.55</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-10.3</v>
+        <v>-13.7</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>74.65000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>22.55</v>
+        <v>22.57</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-13.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="n">
-        <v>74.2</v>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="7" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="D24" s="8" t="n">
-        <v>22.7</v>
-      </c>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="7" t="n">
-        <v>22.57</v>
+        <v>22.52</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>-15.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B25" s="8" t="n"/>
       <c r="C25" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.52</v>
       </c>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="7" t="n">
-        <v>22.52</v>
+        <v>22.46</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-18.2</v>
+        <v>-23.1</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="7" t="n">
-        <v>74.42</v>
+        <v>74.33</v>
       </c>
       <c r="D27" s="8" t="n"/>
       <c r="E27" s="7" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B28" s="8" t="n"/>
       <c r="C28" s="7" t="n">
-        <v>74.33</v>
+        <v>74.45</v>
       </c>
       <c r="D28" s="8" t="n"/>
       <c r="E28" s="7" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-18.2</v>
+        <v>-19.5</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B29" s="8" t="n"/>
       <c r="C29" s="7" t="n">
-        <v>74.45</v>
+        <v>74.2</v>
       </c>
       <c r="D29" s="8" t="n"/>
       <c r="E29" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-19.5</v>
+        <v>-26.4</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B30" s="8" t="n"/>
-      <c r="C30" s="7" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="C30" s="7" t="n"/>
       <c r="D30" s="8" t="n"/>
-      <c r="E30" s="7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="E30" s="7" t="n"/>
       <c r="F30" s="8" t="n">
-        <v>-26.4</v>
+        <v>-19.9</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B31" s="8" t="n"/>
@@ -4178,807 +4178,811 @@
       <c r="D31" s="8" t="n"/>
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="8" t="n">
-        <v>-19.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="n"/>
-      <c r="C32" s="7" t="n"/>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="7" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>21.7</v>
+      </c>
       <c r="F32" s="8" t="n">
-        <v>-15.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>21.7</v>
+        <v>22.05</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-9.4</v>
+        <v>-12</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>73.2</v>
+        <v>73.33</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-12</v>
+        <v>-12.4</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-12.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>73.31999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>-7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D39" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>22.26</v>
+        <v>22.4</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>73.16</v>
+        <v>73.2</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>-10.9</v>
+        <v>-16</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-16</v>
+        <v>-10.1</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>22.3</v>
+        <v>22.31</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>-10.1</v>
+        <v>-5.9</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>73.16</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>22.31</v>
+        <v>22.43</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-5.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
         <v>72.8</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>73.06999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>22.43</v>
+        <v>22.41</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>-9.9</v>
+        <v>-13.3</v>
       </c>
       <c r="G44" s="9" t="n">
         <v>68</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>73.11</v>
+        <v>73.06</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-13.3</v>
+        <v>-16.6</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
         <v>72.5</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>73.06</v>
+        <v>72.97</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>-16.6</v>
+        <v>-11.8</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>72.97</v>
+        <v>72.86</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>22.26</v>
+        <v>22.21</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-11.8</v>
+        <v>-21.1</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>72.86</v>
+        <v>72.8</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>-21.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>72.8</v>
+        <v>72.69</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>22.24</v>
+        <v>22.19</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-25.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>72.69</v>
+        <v>72.61</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>-18.3</v>
+        <v>-16</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-16</v>
+        <v>-10.4</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="n"/>
       <c r="C52" s="7" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="D52" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="D52" s="8" t="n"/>
       <c r="E52" s="7" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>-10.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B53" s="8" t="n"/>
       <c r="C53" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="D53" s="8" t="n"/>
       <c r="E53" s="7" t="n">
-        <v>21.85</v>
+        <v>21.7</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B54" s="8" t="n"/>
       <c r="C54" s="7" t="n">
-        <v>72.58</v>
+        <v>72.5</v>
       </c>
       <c r="D54" s="8" t="n"/>
       <c r="E54" s="7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>-12.3</v>
+        <v>-6.6</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B55" s="8" t="n"/>
       <c r="C55" s="7" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="7" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="n"/>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C56" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D56" s="8" t="n"/>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="D56" s="8" t="n">
+        <v>21.2</v>
+      </c>
       <c r="E56" s="7" t="n">
-        <v>21.73</v>
+        <v>21.63</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>21.63</v>
+        <v>21.57</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="C58" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E58" s="7" t="n">
         <v>21.57</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>-7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>72.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D59" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E59" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E59" s="7" t="n">
-        <v>21.57</v>
-      </c>
       <c r="F59" s="8" t="n">
-        <v>-10.9</v>
+        <v>-7.7</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B60" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="n"/>
       <c r="C60" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D60" s="8" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D60" s="8" t="n"/>
       <c r="E60" s="7" t="n">
         <v>21.8</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.9</v>
       </c>
       <c r="G60" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B61" s="8" t="n"/>
@@ -4990,19 +4994,19 @@
         <v>21.8</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>-8.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B62" s="8" t="n"/>
@@ -5014,274 +5018,278 @@
         <v>21.8</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>-12.5</v>
+        <v>-11.2</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B63" s="8" t="n"/>
       <c r="C63" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>-11.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G63" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B64" s="8" t="n"/>
       <c r="C64" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="7" t="n">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>-13.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B65" s="8" t="n"/>
       <c r="C65" s="7" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="7" t="n">
-        <v>22.15</v>
+        <v>22.5</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="G65" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B66" s="8" t="n"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="C66" s="7" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="D66" s="8" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D66" s="8" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E66" s="7" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>-12.4</v>
+        <v>-7.8</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B67" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>20.5</v>
+        <v>20.95</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>-7.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B68" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C68" s="7" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>20.95</v>
+        <v>21.13</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>-3.1</v>
+        <v>-11.8</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B69" s="8" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>-11.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="C70" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>72.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>-8.6</v>
+        <v>-13.5</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B72" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C72" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>21.33</v>
+        <v>21.43</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H72" s="10" t="n">
         <v>7.7</v>
@@ -5290,510 +5298,510 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B73" s="8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="C73" s="7" t="n">
-        <v>72.23</v>
+        <v>72.39</v>
       </c>
       <c r="D73" s="8" t="n">
         <v>22</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>21.43</v>
+        <v>21.64</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>-7.1</v>
+        <v>-12.5</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B74" s="8" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C74" s="7" t="n">
         <v>72.39</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>21.64</v>
+        <v>21.69</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>-12.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B75" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C75" s="7" t="n">
-        <v>72.39</v>
+        <v>72.36</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>21.69</v>
+        <v>21.56</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>-6.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B76" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="n"/>
       <c r="C76" s="7" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="D76" s="8" t="n">
-        <v>20.6</v>
-      </c>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="D76" s="8" t="n"/>
       <c r="E76" s="7" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B77" s="8" t="n"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="C77" s="7" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="D77" s="8" t="n"/>
+        <v>72.45</v>
+      </c>
+      <c r="D77" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E77" s="7" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C78" s="7" t="n">
-        <v>72.45</v>
+        <v>72.47</v>
       </c>
       <c r="D78" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>21.67</v>
+        <v>21.53</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>72.47</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D79" s="8" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>21.53</v>
+        <v>21.47</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C80" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>72.31999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>-4.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B82" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>72.23</v>
+        <v>72.3</v>
       </c>
       <c r="D82" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>21.4</v>
+        <v>21.55</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>-1.6</v>
+        <v>-15.1</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B83" s="8" t="n">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>72.3</v>
+        <v>72.37</v>
       </c>
       <c r="D83" s="8" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>21.55</v>
+        <v>21.69</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>-15.1</v>
+        <v>-10.3</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B84" s="8" t="n">
-        <v>72.8</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="n"/>
       <c r="C84" s="7" t="n">
-        <v>72.37</v>
-      </c>
-      <c r="D84" s="8" t="n">
-        <v>22.5</v>
-      </c>
+        <v>72.28</v>
+      </c>
+      <c r="D84" s="8" t="n"/>
       <c r="E84" s="7" t="n">
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>-10.3</v>
+        <v>-14.8</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>5.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B85" s="8" t="n"/>
       <c r="C85" s="7" t="n">
-        <v>72.28</v>
+        <v>72.3</v>
       </c>
       <c r="D85" s="8" t="n"/>
       <c r="E85" s="7" t="n">
-        <v>21.67</v>
+        <v>21.78</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>-14.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B86" s="8" t="n"/>
       <c r="C86" s="7" t="n">
-        <v>72.3</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="D86" s="8" t="n"/>
       <c r="E86" s="7" t="n">
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>-15.7</v>
+        <v>-15.4</v>
       </c>
       <c r="G86" s="9" t="n">
         <v>60</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B87" s="8" t="n"/>
       <c r="C87" s="7" t="n">
-        <v>72.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D87" s="8" t="n"/>
       <c r="E87" s="7" t="n">
-        <v>21.82</v>
+        <v>21.83</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>-15.4</v>
+        <v>-8.9</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B88" s="8" t="n"/>
       <c r="C88" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D88" s="8" t="n"/>
       <c r="E88" s="7" t="n">
-        <v>21.83</v>
+        <v>22</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>-8.9</v>
+        <v>-6.7</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B89" s="8" t="n"/>
       <c r="C89" s="7" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D89" s="8" t="n"/>
       <c r="E89" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>-6.7</v>
+        <v>-4.8</v>
       </c>
       <c r="G89" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B90" s="8" t="n"/>
-      <c r="C90" s="7" t="n">
-        <v>72.8</v>
-      </c>
+      <c r="C90" s="7" t="n"/>
       <c r="D90" s="8" t="n"/>
-      <c r="E90" s="7" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="E90" s="7" t="n"/>
       <c r="F90" s="8" t="n">
-        <v>-4.8</v>
+        <v>0.6</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B91" s="8" t="n"/>
-      <c r="C91" s="7" t="n"/>
-      <c r="D91" s="8" t="n"/>
-      <c r="E91" s="7" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="C91" s="7" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="D91" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E91" s="7" t="n">
+        <v>21.9</v>
+      </c>
       <c r="F91" s="8" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B92" s="8" t="n">
-        <v>73.2</v>
+        <v>72.8</v>
       </c>
       <c r="C92" s="7" t="n">
-        <v>73.2</v>
+        <v>73</v>
       </c>
       <c r="D92" s="8" t="n">
         <v>21.9</v>
@@ -5802,69 +5810,69 @@
         <v>21.9</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>3.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B93" s="8" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>73</v>
+        <v>72.97</v>
       </c>
       <c r="D93" s="8" t="n">
-        <v>21.9</v>
+        <v>21.3</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>-9.4</v>
+        <v>-6.9</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B94" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C94" s="7" t="n">
-        <v>72.97</v>
+        <v>72.88</v>
       </c>
       <c r="D94" s="8" t="n">
-        <v>21.6</v>
+        <v>20.9</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>-6.3</v>
+        <v>-2.3</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H94" s="10" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -6295,16 +6303,16 @@
         <v>51</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>54.2</v>
+        <v>53.4</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>300</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>188</v>
+        <v>231</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>-112</v>
+        <v>-69</v>
       </c>
     </row>
     <row r="17">

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>72.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>68</v>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3.83</v>
+        <v>3.76</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>4.71</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>53.4</v>
+        <v>53.1</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -3536,7 +3536,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
@@ -3547,16 +3547,16 @@
         <v>-16.4</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
@@ -3564,19 +3564,19 @@
       <c r="D6" s="8" t="n"/>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="8" t="n">
-        <v>-16.4</v>
+        <v>-14.3</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
@@ -3584,19 +3584,19 @@
       <c r="D7" s="8" t="n"/>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="8" t="n">
-        <v>-14.3</v>
+        <v>-9.1</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
@@ -3604,19 +3604,19 @@
       <c r="D8" s="8" t="n"/>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="8" t="n">
-        <v>-9.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B9" s="8" t="n"/>
@@ -3624,39 +3624,47 @@
       <c r="D9" s="8" t="n"/>
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="8" t="n">
-        <v>-8.300000000000001</v>
+        <v>-5</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="7" t="n"/>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>22</v>
+      </c>
       <c r="F10" s="8" t="n">
-        <v>-5</v>
+        <v>-1.8</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
@@ -3666,103 +3674,99 @@
         <v>74.5</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-1.8</v>
+        <v>-13.8</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n">
-        <v>74.5</v>
-      </c>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n"/>
       <c r="C12" s="7" t="n">
         <v>74.5</v>
       </c>
-      <c r="D12" s="8" t="n">
-        <v>23</v>
-      </c>
+      <c r="D12" s="8" t="n"/>
       <c r="E12" s="7" t="n">
         <v>22.5</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>-13.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="H12" s="10" t="n">
-        <v>8.1</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n"/>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>74.40000000000001</v>
+      </c>
       <c r="C13" s="7" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="D13" s="8" t="n"/>
+        <v>74.47</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>23.3</v>
+      </c>
       <c r="E13" s="7" t="n">
-        <v>22.5</v>
+        <v>22.77</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-15.7</v>
+        <v>-10.5</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="H13" s="10" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n">
-        <v>74.40000000000001</v>
-      </c>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n"/>
       <c r="C14" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D14" s="8" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="D14" s="8" t="n"/>
       <c r="E14" s="7" t="n">
         <v>22.77</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>-10.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B15" s="8" t="n"/>
@@ -3774,90 +3778,94 @@
         <v>22.77</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-9.4</v>
+        <v>-7.5</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="n"/>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>74.5</v>
+      </c>
       <c r="C16" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D16" s="8" t="n"/>
+      <c r="D16" s="8" t="n">
+        <v>22.9</v>
+      </c>
       <c r="E16" s="7" t="n">
-        <v>22.77</v>
+        <v>22.8</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>-7.5</v>
+        <v>-4.5</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>74.47</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.2</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>23</v>
+        <v>22.93</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>-2.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H18" s="10" t="n">
         <v>8</v>
@@ -3866,291 +3874,283 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C19" s="7" t="n">
         <v>74.7</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>22.93</v>
+        <v>22.78</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>74.7</v>
+        <v>74.64</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>22.78</v>
+        <v>22.6</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>-11.9</v>
+        <v>-10.3</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>22.6</v>
+        <v>22.55</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-10.3</v>
+        <v>-13.7</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>74.65000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>22.55</v>
+        <v>22.57</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-13.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="n">
-        <v>74.2</v>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n"/>
       <c r="C23" s="7" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="D23" s="8" t="n">
-        <v>22.7</v>
-      </c>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D23" s="8" t="n"/>
       <c r="E23" s="7" t="n">
-        <v>22.57</v>
+        <v>22.52</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-15.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.52</v>
       </c>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="7" t="n">
-        <v>22.52</v>
+        <v>22.46</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B25" s="8" t="n"/>
       <c r="C25" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-18.2</v>
+        <v>-23.1</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="7" t="n">
-        <v>74.42</v>
+        <v>74.33</v>
       </c>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="7" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="7" t="n">
-        <v>74.33</v>
+        <v>74.45</v>
       </c>
       <c r="D27" s="8" t="n"/>
       <c r="E27" s="7" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-18.2</v>
+        <v>-19.5</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B28" s="8" t="n"/>
       <c r="C28" s="7" t="n">
-        <v>74.45</v>
+        <v>74.2</v>
       </c>
       <c r="D28" s="8" t="n"/>
       <c r="E28" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-19.5</v>
+        <v>-26.4</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B29" s="8" t="n"/>
-      <c r="C29" s="7" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="C29" s="7" t="n"/>
       <c r="D29" s="8" t="n"/>
-      <c r="E29" s="7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="E29" s="7" t="n"/>
       <c r="F29" s="8" t="n">
-        <v>-26.4</v>
+        <v>-19.9</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B30" s="8" t="n"/>
@@ -4158,807 +4158,811 @@
       <c r="D30" s="8" t="n"/>
       <c r="E30" s="7" t="n"/>
       <c r="F30" s="8" t="n">
-        <v>-19.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="n"/>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="7" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>21.7</v>
+      </c>
       <c r="F31" s="8" t="n">
-        <v>-15.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>21.7</v>
+        <v>22.05</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-9.4</v>
+        <v>-12</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>73.2</v>
+        <v>73.33</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-12</v>
+        <v>-12.4</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-12.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>73.31999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D38" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>22.26</v>
+        <v>22.4</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>73.16</v>
+        <v>73.2</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-10.9</v>
+        <v>-16</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>-16</v>
+        <v>-10.1</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>22.3</v>
+        <v>22.31</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-10.1</v>
+        <v>-5.9</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>73.16</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>22.31</v>
+        <v>22.43</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>-5.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
         <v>72.8</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>73.06999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>22.43</v>
+        <v>22.41</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-9.9</v>
+        <v>-13.3</v>
       </c>
       <c r="G43" s="9" t="n">
         <v>68</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>73.11</v>
+        <v>73.06</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>-13.3</v>
+        <v>-16.6</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
         <v>72.5</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>73.06</v>
+        <v>72.97</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-16.6</v>
+        <v>-11.8</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>72.97</v>
+        <v>72.86</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>22.26</v>
+        <v>22.21</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>-11.8</v>
+        <v>-21.1</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>72.86</v>
+        <v>72.8</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-21.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>72.8</v>
+        <v>72.69</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>22.24</v>
+        <v>22.19</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>-25.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>72.69</v>
+        <v>72.61</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-18.3</v>
+        <v>-16</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>-16</v>
+        <v>-10.4</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B51" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n"/>
       <c r="C51" s="7" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="D51" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="D51" s="8" t="n"/>
       <c r="E51" s="7" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-10.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B52" s="8" t="n"/>
       <c r="C52" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="D52" s="8" t="n"/>
       <c r="E52" s="7" t="n">
-        <v>21.85</v>
+        <v>21.7</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B53" s="8" t="n"/>
       <c r="C53" s="7" t="n">
-        <v>72.58</v>
+        <v>72.5</v>
       </c>
       <c r="D53" s="8" t="n"/>
       <c r="E53" s="7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-12.3</v>
+        <v>-6.6</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B54" s="8" t="n"/>
       <c r="C54" s="7" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D54" s="8" t="n"/>
       <c r="E54" s="7" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="n"/>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C55" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D55" s="8" t="n"/>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>21.2</v>
+      </c>
       <c r="E55" s="7" t="n">
-        <v>21.73</v>
+        <v>21.63</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>21.63</v>
+        <v>21.57</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E57" s="7" t="n">
         <v>21.57</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>-7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C58" s="7" t="n">
-        <v>72.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D58" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E58" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E58" s="7" t="n">
-        <v>21.57</v>
-      </c>
       <c r="F58" s="8" t="n">
-        <v>-10.9</v>
+        <v>-7.7</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B59" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n"/>
       <c r="C59" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D59" s="8" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D59" s="8" t="n"/>
       <c r="E59" s="7" t="n">
         <v>21.8</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.9</v>
       </c>
       <c r="G59" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B60" s="8" t="n"/>
@@ -4970,19 +4974,19 @@
         <v>21.8</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>-8.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B61" s="8" t="n"/>
@@ -4994,274 +4998,278 @@
         <v>21.8</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>-12.5</v>
+        <v>-11.2</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B62" s="8" t="n"/>
       <c r="C62" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>-11.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G62" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B63" s="8" t="n"/>
       <c r="C63" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="7" t="n">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>-13.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B64" s="8" t="n"/>
       <c r="C64" s="7" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="7" t="n">
-        <v>22.15</v>
+        <v>22.5</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="G64" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B65" s="8" t="n"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="C65" s="7" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="D65" s="8" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D65" s="8" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E65" s="7" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>-12.4</v>
+        <v>-7.8</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B66" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>20.5</v>
+        <v>20.95</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>-7.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B67" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>20.95</v>
+        <v>21.13</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>-3.1</v>
+        <v>-11.8</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B68" s="8" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C68" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>-11.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B69" s="8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C70" s="7" t="n">
-        <v>72.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>-8.6</v>
+        <v>-13.5</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>21.33</v>
+        <v>21.43</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H71" s="10" t="n">
         <v>7.7</v>
@@ -5270,510 +5278,510 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B72" s="8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="C72" s="7" t="n">
-        <v>72.23</v>
+        <v>72.39</v>
       </c>
       <c r="D72" s="8" t="n">
         <v>22</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>21.43</v>
+        <v>21.64</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>-7.1</v>
+        <v>-12.5</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B73" s="8" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C73" s="7" t="n">
         <v>72.39</v>
       </c>
       <c r="D73" s="8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>21.64</v>
+        <v>21.69</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>-12.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B74" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C74" s="7" t="n">
-        <v>72.39</v>
+        <v>72.36</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>21.69</v>
+        <v>21.56</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>-6.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B75" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="n"/>
       <c r="C75" s="7" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="D75" s="8" t="n">
-        <v>20.6</v>
-      </c>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="D75" s="8" t="n"/>
       <c r="E75" s="7" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B76" s="8" t="n"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="C76" s="7" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="D76" s="8" t="n"/>
+        <v>72.45</v>
+      </c>
+      <c r="D76" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E76" s="7" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B77" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C77" s="7" t="n">
-        <v>72.45</v>
+        <v>72.47</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>21.67</v>
+        <v>21.53</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C78" s="7" t="n">
-        <v>72.47</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D78" s="8" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>21.53</v>
+        <v>21.47</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D79" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C80" s="7" t="n">
-        <v>72.31999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>-4.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>72.23</v>
+        <v>72.3</v>
       </c>
       <c r="D81" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>21.4</v>
+        <v>21.55</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>-1.6</v>
+        <v>-15.1</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B82" s="8" t="n">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>72.3</v>
+        <v>72.37</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>21.55</v>
+        <v>21.69</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>-15.1</v>
+        <v>-10.3</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B83" s="8" t="n">
-        <v>72.8</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="n"/>
       <c r="C83" s="7" t="n">
-        <v>72.37</v>
-      </c>
-      <c r="D83" s="8" t="n">
-        <v>22.5</v>
-      </c>
+        <v>72.28</v>
+      </c>
+      <c r="D83" s="8" t="n"/>
       <c r="E83" s="7" t="n">
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>-10.3</v>
+        <v>-14.8</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>5.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B84" s="8" t="n"/>
       <c r="C84" s="7" t="n">
-        <v>72.28</v>
+        <v>72.3</v>
       </c>
       <c r="D84" s="8" t="n"/>
       <c r="E84" s="7" t="n">
-        <v>21.67</v>
+        <v>21.78</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>-14.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B85" s="8" t="n"/>
       <c r="C85" s="7" t="n">
-        <v>72.3</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="D85" s="8" t="n"/>
       <c r="E85" s="7" t="n">
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>-15.7</v>
+        <v>-15.4</v>
       </c>
       <c r="G85" s="9" t="n">
         <v>60</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B86" s="8" t="n"/>
       <c r="C86" s="7" t="n">
-        <v>72.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D86" s="8" t="n"/>
       <c r="E86" s="7" t="n">
-        <v>21.82</v>
+        <v>21.83</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>-15.4</v>
+        <v>-8.9</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B87" s="8" t="n"/>
       <c r="C87" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D87" s="8" t="n"/>
       <c r="E87" s="7" t="n">
-        <v>21.83</v>
+        <v>22</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>-8.9</v>
+        <v>-6.7</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B88" s="8" t="n"/>
       <c r="C88" s="7" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D88" s="8" t="n"/>
       <c r="E88" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>-6.7</v>
+        <v>-4.8</v>
       </c>
       <c r="G88" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B89" s="8" t="n"/>
-      <c r="C89" s="7" t="n">
-        <v>72.8</v>
-      </c>
+      <c r="C89" s="7" t="n"/>
       <c r="D89" s="8" t="n"/>
-      <c r="E89" s="7" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="E89" s="7" t="n"/>
       <c r="F89" s="8" t="n">
-        <v>-4.8</v>
+        <v>0.6</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B90" s="8" t="n"/>
-      <c r="C90" s="7" t="n"/>
-      <c r="D90" s="8" t="n"/>
-      <c r="E90" s="7" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="C90" s="7" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="D90" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E90" s="7" t="n">
+        <v>21.9</v>
+      </c>
       <c r="F90" s="8" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B91" s="8" t="n">
-        <v>73.2</v>
+        <v>72.8</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>73.2</v>
+        <v>73</v>
       </c>
       <c r="D91" s="8" t="n">
         <v>21.9</v>
@@ -5782,97 +5790,97 @@
         <v>21.9</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>3.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B92" s="8" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C92" s="7" t="n">
-        <v>73</v>
+        <v>72.97</v>
       </c>
       <c r="D92" s="8" t="n">
-        <v>21.9</v>
+        <v>21.3</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>-9.4</v>
+        <v>-6.9</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B93" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>72.97</v>
+        <v>72.88</v>
       </c>
       <c r="D93" s="8" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>-6.9</v>
+        <v>-3.2</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B94" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="C94" s="7" t="n">
-        <v>72.88</v>
+        <v>73.08</v>
       </c>
       <c r="D94" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>21.5</v>
+        <v>21.38</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>-2.3</v>
+        <v>-0.2</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H94" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -6303,16 +6311,16 @@
         <v>51</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>53.4</v>
+        <v>53.1</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>300</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>231</v>
+        <v>260</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>-69</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="17">

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>53.1</v>
+        <v>52.4</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -3536,7 +3536,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
@@ -3544,19 +3544,19 @@
       <c r="D5" s="8" t="n"/>
       <c r="E5" s="7" t="n"/>
       <c r="F5" s="8" t="n">
-        <v>-16.4</v>
+        <v>-14.3</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
@@ -3564,19 +3564,19 @@
       <c r="D6" s="8" t="n"/>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="8" t="n">
-        <v>-14.3</v>
+        <v>-9.1</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
@@ -3584,19 +3584,19 @@
       <c r="D7" s="8" t="n"/>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="8" t="n">
-        <v>-9.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
@@ -3604,39 +3604,47 @@
       <c r="D8" s="8" t="n"/>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="8" t="n">
-        <v>-8.300000000000001</v>
+        <v>-5</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="7" t="n"/>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>22</v>
+      </c>
       <c r="F9" s="8" t="n">
-        <v>-5</v>
+        <v>-1.8</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
@@ -3646,103 +3654,99 @@
         <v>74.5</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>-1.8</v>
+        <v>-13.8</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n">
-        <v>74.5</v>
-      </c>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n"/>
       <c r="C11" s="7" t="n">
         <v>74.5</v>
       </c>
-      <c r="D11" s="8" t="n">
-        <v>23</v>
-      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="7" t="n">
         <v>22.5</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-13.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="H11" s="10" t="n">
-        <v>8.1</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n"/>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>74.40000000000001</v>
+      </c>
       <c r="C12" s="7" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="D12" s="8" t="n"/>
+        <v>74.47</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>23.3</v>
+      </c>
       <c r="E12" s="7" t="n">
-        <v>22.5</v>
+        <v>22.77</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>-15.7</v>
+        <v>-10.5</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="H12" s="10" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n">
-        <v>74.40000000000001</v>
-      </c>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n"/>
       <c r="C13" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D13" s="8" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="D13" s="8" t="n"/>
       <c r="E13" s="7" t="n">
         <v>22.77</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-10.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
@@ -3754,90 +3758,94 @@
         <v>22.77</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>-9.4</v>
+        <v>-7.5</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="n"/>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>74.5</v>
+      </c>
       <c r="C15" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D15" s="8" t="n"/>
+      <c r="D15" s="8" t="n">
+        <v>22.9</v>
+      </c>
       <c r="E15" s="7" t="n">
-        <v>22.77</v>
+        <v>22.8</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-7.5</v>
+        <v>-4.5</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>74.47</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.2</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>23</v>
+        <v>22.93</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-2.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H17" s="10" t="n">
         <v>8</v>
@@ -3846,291 +3854,283 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>74.7</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>22.93</v>
+        <v>22.78</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>74.7</v>
+        <v>74.64</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>22.78</v>
+        <v>22.6</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-11.9</v>
+        <v>-10.3</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>22.6</v>
+        <v>22.55</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>-10.3</v>
+        <v>-13.7</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>74.65000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>22.55</v>
+        <v>22.57</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-13.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="n">
-        <v>74.2</v>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n"/>
       <c r="C22" s="7" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>22.7</v>
-      </c>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="7" t="n">
-        <v>22.57</v>
+        <v>22.52</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-15.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.52</v>
       </c>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="7" t="n">
-        <v>22.52</v>
+        <v>22.46</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>-18.2</v>
+        <v>-23.1</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B25" s="8" t="n"/>
       <c r="C25" s="7" t="n">
-        <v>74.42</v>
+        <v>74.33</v>
       </c>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="7" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="7" t="n">
-        <v>74.33</v>
+        <v>74.45</v>
       </c>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="7" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-18.2</v>
+        <v>-19.5</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B27" s="8" t="n"/>
       <c r="C27" s="7" t="n">
-        <v>74.45</v>
+        <v>74.2</v>
       </c>
       <c r="D27" s="8" t="n"/>
       <c r="E27" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-19.5</v>
+        <v>-26.4</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B28" s="8" t="n"/>
-      <c r="C28" s="7" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="C28" s="7" t="n"/>
       <c r="D28" s="8" t="n"/>
-      <c r="E28" s="7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="E28" s="7" t="n"/>
       <c r="F28" s="8" t="n">
-        <v>-26.4</v>
+        <v>-19.9</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B29" s="8" t="n"/>
@@ -4138,807 +4138,811 @@
       <c r="D29" s="8" t="n"/>
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="8" t="n">
-        <v>-19.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="n"/>
-      <c r="C30" s="7" t="n"/>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="7" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>21.7</v>
+      </c>
       <c r="F30" s="8" t="n">
-        <v>-15.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>21.7</v>
+        <v>22.05</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-9.4</v>
+        <v>-12</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>73.2</v>
+        <v>73.33</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-12</v>
+        <v>-12.4</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-12.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>73.31999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>-7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D37" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>22.26</v>
+        <v>22.4</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>73.16</v>
+        <v>73.2</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>-10.9</v>
+        <v>-16</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-16</v>
+        <v>-10.1</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>22.3</v>
+        <v>22.31</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>-10.1</v>
+        <v>-5.9</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>73.16</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>22.31</v>
+        <v>22.43</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-5.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B42" s="8" t="n">
         <v>72.8</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>73.06999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>22.43</v>
+        <v>22.41</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>-9.9</v>
+        <v>-13.3</v>
       </c>
       <c r="G42" s="9" t="n">
         <v>68</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>73.11</v>
+        <v>73.06</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-13.3</v>
+        <v>-16.6</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
         <v>72.5</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>73.06</v>
+        <v>72.97</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>-16.6</v>
+        <v>-11.8</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>72.97</v>
+        <v>72.86</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>22.26</v>
+        <v>22.21</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-11.8</v>
+        <v>-21.1</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>72.86</v>
+        <v>72.8</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>-21.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>72.8</v>
+        <v>72.69</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>22.24</v>
+        <v>22.19</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-25.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>72.69</v>
+        <v>72.61</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>-18.3</v>
+        <v>-16</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-16</v>
+        <v>-10.4</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B50" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="n"/>
       <c r="C50" s="7" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="D50" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="D50" s="8" t="n"/>
       <c r="E50" s="7" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>-10.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B51" s="8" t="n"/>
       <c r="C51" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="D51" s="8" t="n"/>
       <c r="E51" s="7" t="n">
-        <v>21.85</v>
+        <v>21.7</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B52" s="8" t="n"/>
       <c r="C52" s="7" t="n">
-        <v>72.58</v>
+        <v>72.5</v>
       </c>
       <c r="D52" s="8" t="n"/>
       <c r="E52" s="7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>-12.3</v>
+        <v>-6.6</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B53" s="8" t="n"/>
       <c r="C53" s="7" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D53" s="8" t="n"/>
       <c r="E53" s="7" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="n"/>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C54" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D54" s="8" t="n"/>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="D54" s="8" t="n">
+        <v>21.2</v>
+      </c>
       <c r="E54" s="7" t="n">
-        <v>21.73</v>
+        <v>21.63</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>21.63</v>
+        <v>21.57</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E56" s="7" t="n">
         <v>21.57</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>-7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>72.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D57" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E57" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E57" s="7" t="n">
-        <v>21.57</v>
-      </c>
       <c r="F57" s="8" t="n">
-        <v>-10.9</v>
+        <v>-7.7</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B58" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="n"/>
       <c r="C58" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D58" s="8" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D58" s="8" t="n"/>
       <c r="E58" s="7" t="n">
         <v>21.8</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.9</v>
       </c>
       <c r="G58" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B59" s="8" t="n"/>
@@ -4950,19 +4954,19 @@
         <v>21.8</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>-8.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B60" s="8" t="n"/>
@@ -4974,274 +4978,278 @@
         <v>21.8</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>-12.5</v>
+        <v>-11.2</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B61" s="8" t="n"/>
       <c r="C61" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>-11.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G61" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B62" s="8" t="n"/>
       <c r="C62" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="7" t="n">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>-13.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B63" s="8" t="n"/>
       <c r="C63" s="7" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="7" t="n">
-        <v>22.15</v>
+        <v>22.5</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="G63" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="n"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="C64" s="7" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="D64" s="8" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D64" s="8" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E64" s="7" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>-12.4</v>
+        <v>-7.8</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B65" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D65" s="8" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>20.5</v>
+        <v>20.95</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>-7.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B66" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>20.95</v>
+        <v>21.13</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>-3.1</v>
+        <v>-11.8</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B67" s="8" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>-11.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B68" s="8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="C68" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B69" s="8" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>72.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>-8.6</v>
+        <v>-13.5</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C70" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>21.33</v>
+        <v>21.43</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H70" s="10" t="n">
         <v>7.7</v>
@@ -5250,510 +5258,510 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>72.23</v>
+        <v>72.39</v>
       </c>
       <c r="D71" s="8" t="n">
         <v>22</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>21.43</v>
+        <v>21.64</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>-7.1</v>
+        <v>-12.5</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B72" s="8" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C72" s="7" t="n">
         <v>72.39</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>21.64</v>
+        <v>21.69</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>-12.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B73" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C73" s="7" t="n">
-        <v>72.39</v>
+        <v>72.36</v>
       </c>
       <c r="D73" s="8" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>21.69</v>
+        <v>21.56</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>-6.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B74" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="n"/>
       <c r="C74" s="7" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="D74" s="8" t="n">
-        <v>20.6</v>
-      </c>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="D74" s="8" t="n"/>
       <c r="E74" s="7" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B75" s="8" t="n"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="C75" s="7" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="D75" s="8" t="n"/>
+        <v>72.45</v>
+      </c>
+      <c r="D75" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E75" s="7" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B76" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>72.45</v>
+        <v>72.47</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>21.67</v>
+        <v>21.53</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B77" s="8" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C77" s="7" t="n">
-        <v>72.47</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>21.53</v>
+        <v>21.47</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C78" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D78" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>72.31999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="D79" s="8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>-4.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="C80" s="7" t="n">
-        <v>72.23</v>
+        <v>72.3</v>
       </c>
       <c r="D80" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>21.4</v>
+        <v>21.55</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>-1.6</v>
+        <v>-15.1</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>72.3</v>
+        <v>72.37</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>21.55</v>
+        <v>21.69</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>-15.1</v>
+        <v>-10.3</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B82" s="8" t="n">
-        <v>72.8</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="n"/>
       <c r="C82" s="7" t="n">
-        <v>72.37</v>
-      </c>
-      <c r="D82" s="8" t="n">
-        <v>22.5</v>
-      </c>
+        <v>72.28</v>
+      </c>
+      <c r="D82" s="8" t="n"/>
       <c r="E82" s="7" t="n">
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>-10.3</v>
+        <v>-14.8</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>5.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B83" s="8" t="n"/>
       <c r="C83" s="7" t="n">
-        <v>72.28</v>
+        <v>72.3</v>
       </c>
       <c r="D83" s="8" t="n"/>
       <c r="E83" s="7" t="n">
-        <v>21.67</v>
+        <v>21.78</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>-14.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B84" s="8" t="n"/>
       <c r="C84" s="7" t="n">
-        <v>72.3</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="D84" s="8" t="n"/>
       <c r="E84" s="7" t="n">
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>-15.7</v>
+        <v>-15.4</v>
       </c>
       <c r="G84" s="9" t="n">
         <v>60</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B85" s="8" t="n"/>
       <c r="C85" s="7" t="n">
-        <v>72.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D85" s="8" t="n"/>
       <c r="E85" s="7" t="n">
-        <v>21.82</v>
+        <v>21.83</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>-15.4</v>
+        <v>-8.9</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B86" s="8" t="n"/>
       <c r="C86" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D86" s="8" t="n"/>
       <c r="E86" s="7" t="n">
-        <v>21.83</v>
+        <v>22</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>-8.9</v>
+        <v>-6.7</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B87" s="8" t="n"/>
       <c r="C87" s="7" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D87" s="8" t="n"/>
       <c r="E87" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>-6.7</v>
+        <v>-4.8</v>
       </c>
       <c r="G87" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B88" s="8" t="n"/>
-      <c r="C88" s="7" t="n">
-        <v>72.8</v>
-      </c>
+      <c r="C88" s="7" t="n"/>
       <c r="D88" s="8" t="n"/>
-      <c r="E88" s="7" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="E88" s="7" t="n"/>
       <c r="F88" s="8" t="n">
-        <v>-4.8</v>
+        <v>0.6</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B89" s="8" t="n"/>
-      <c r="C89" s="7" t="n"/>
-      <c r="D89" s="8" t="n"/>
-      <c r="E89" s="7" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="C89" s="7" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="D89" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E89" s="7" t="n">
+        <v>21.9</v>
+      </c>
       <c r="F89" s="8" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B90" s="8" t="n">
-        <v>73.2</v>
+        <v>72.8</v>
       </c>
       <c r="C90" s="7" t="n">
-        <v>73.2</v>
+        <v>73</v>
       </c>
       <c r="D90" s="8" t="n">
         <v>21.9</v>
@@ -5762,125 +5770,121 @@
         <v>21.9</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>3.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B91" s="8" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>73</v>
+        <v>72.97</v>
       </c>
       <c r="D91" s="8" t="n">
-        <v>21.9</v>
+        <v>21.3</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>-9.4</v>
+        <v>-6.9</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B92" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C92" s="7" t="n">
-        <v>72.97</v>
+        <v>72.88</v>
       </c>
       <c r="D92" s="8" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>-6.9</v>
+        <v>-3.2</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B93" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>72.88</v>
+        <v>73.08</v>
       </c>
       <c r="D93" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>21.5</v>
+        <v>21.38</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>-3.2</v>
+        <v>0.9</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B94" s="8" t="n">
-        <v>73.90000000000001</v>
-      </c>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="n"/>
       <c r="C94" s="7" t="n">
         <v>73.08</v>
       </c>
-      <c r="D94" s="8" t="n">
-        <v>20.9</v>
-      </c>
+      <c r="D94" s="8" t="n"/>
       <c r="E94" s="7" t="n">
         <v>21.38</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>-0.2</v>
+        <v>2.8</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H94" s="10" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -6311,16 +6315,16 @@
         <v>51</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>53.1</v>
+        <v>52.4</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>300</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>-40</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="17">

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>73.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>68</v>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>20.9</v>
+        <v>21.8</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>16</v>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3.76</v>
+        <v>3.83</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>4.71</v>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Christiansborg Rundt lør 29. aug — svømmes UTAPERET (2000 m, bevidst valg). Marathon-vedligehold: 19 km ons.</t>
+          <t>Christiansborg Rundt lør 29. aug — svømmes UTAPERET (2000 m, bevidst valg). Médoc-simulation 19 km tir. Svøm 2.000 m i træk ons. Médoc løbes med Eva.</t>
         </is>
       </c>
     </row>
@@ -5869,16 +5869,20 @@
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="B94" s="8" t="n"/>
+      <c r="B94" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C94" s="7" t="n">
-        <v>73.08</v>
-      </c>
-      <c r="D94" s="8" t="n"/>
+        <v>73</v>
+      </c>
+      <c r="D94" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E94" s="7" t="n">
-        <v>21.38</v>
+        <v>21.45</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="G94" s="9" t="n">
         <v>53</v>
@@ -6321,10 +6325,10 @@
         <v>300</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>280</v>
+        <v>315</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>-20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -3536,7 +3536,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
@@ -3544,19 +3544,19 @@
       <c r="D5" s="8" t="n"/>
       <c r="E5" s="7" t="n"/>
       <c r="F5" s="8" t="n">
-        <v>-14.3</v>
+        <v>-9.1</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
@@ -3564,19 +3564,19 @@
       <c r="D6" s="8" t="n"/>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="8" t="n">
-        <v>-9.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
@@ -3584,39 +3584,47 @@
       <c r="D7" s="8" t="n"/>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="8" t="n">
-        <v>-8.300000000000001</v>
+        <v>-5</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="7" t="n"/>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>22</v>
+      </c>
       <c r="F8" s="8" t="n">
-        <v>-5</v>
+        <v>-1.8</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
@@ -3626,103 +3634,99 @@
         <v>74.5</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-1.8</v>
+        <v>-13.8</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n">
-        <v>74.5</v>
-      </c>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n"/>
       <c r="C10" s="7" t="n">
         <v>74.5</v>
       </c>
-      <c r="D10" s="8" t="n">
-        <v>23</v>
-      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="7" t="n">
         <v>22.5</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>-13.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="H10" s="10" t="n">
-        <v>8.1</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n"/>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>74.40000000000001</v>
+      </c>
       <c r="C11" s="7" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="D11" s="8" t="n"/>
+        <v>74.47</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>23.3</v>
+      </c>
       <c r="E11" s="7" t="n">
-        <v>22.5</v>
+        <v>22.77</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-15.7</v>
+        <v>-10.5</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="H11" s="10" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n">
-        <v>74.40000000000001</v>
-      </c>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n"/>
       <c r="C12" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D12" s="8" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="D12" s="8" t="n"/>
       <c r="E12" s="7" t="n">
         <v>22.77</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>-10.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
@@ -3734,90 +3738,94 @@
         <v>22.77</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-9.4</v>
+        <v>-7.5</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n"/>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>74.5</v>
+      </c>
       <c r="C14" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D14" s="8" t="n"/>
+      <c r="D14" s="8" t="n">
+        <v>22.9</v>
+      </c>
       <c r="E14" s="7" t="n">
-        <v>22.77</v>
+        <v>22.8</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>-7.5</v>
+        <v>-4.5</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>74.47</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.2</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>23</v>
+        <v>22.93</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>-2.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H16" s="10" t="n">
         <v>8</v>
@@ -3826,291 +3834,283 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>74.7</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>22.93</v>
+        <v>22.78</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>74.7</v>
+        <v>74.64</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>22.78</v>
+        <v>22.6</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>-11.9</v>
+        <v>-10.3</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>22.6</v>
+        <v>22.55</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-10.3</v>
+        <v>-13.7</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>74.65000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>22.55</v>
+        <v>22.57</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>-13.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="n">
-        <v>74.2</v>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n"/>
       <c r="C21" s="7" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="D21" s="8" t="n">
-        <v>22.7</v>
-      </c>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="7" t="n">
-        <v>22.57</v>
+        <v>22.52</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-15.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.52</v>
       </c>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="7" t="n">
-        <v>22.52</v>
+        <v>22.46</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-18.2</v>
+        <v>-23.1</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="7" t="n">
-        <v>74.42</v>
+        <v>74.33</v>
       </c>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="7" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B25" s="8" t="n"/>
       <c r="C25" s="7" t="n">
-        <v>74.33</v>
+        <v>74.45</v>
       </c>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="7" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-18.2</v>
+        <v>-19.5</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="7" t="n">
-        <v>74.45</v>
+        <v>74.2</v>
       </c>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-19.5</v>
+        <v>-26.4</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B27" s="8" t="n"/>
-      <c r="C27" s="7" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="C27" s="7" t="n"/>
       <c r="D27" s="8" t="n"/>
-      <c r="E27" s="7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="E27" s="7" t="n"/>
       <c r="F27" s="8" t="n">
-        <v>-26.4</v>
+        <v>-19.9</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B28" s="8" t="n"/>
@@ -4118,807 +4118,811 @@
       <c r="D28" s="8" t="n"/>
       <c r="E28" s="7" t="n"/>
       <c r="F28" s="8" t="n">
-        <v>-19.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="7" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>21.7</v>
+      </c>
       <c r="F29" s="8" t="n">
-        <v>-15.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>21.7</v>
+        <v>22.05</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-9.4</v>
+        <v>-12</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>73.2</v>
+        <v>73.33</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-12</v>
+        <v>-12.4</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-12.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>73.31999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D36" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>22.26</v>
+        <v>22.4</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>73.16</v>
+        <v>73.2</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-10.9</v>
+        <v>-16</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>-16</v>
+        <v>-10.1</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>22.3</v>
+        <v>22.31</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-10.1</v>
+        <v>-5.9</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>73.16</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>22.31</v>
+        <v>22.43</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>-5.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
         <v>72.8</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>73.06999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>22.43</v>
+        <v>22.41</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-9.9</v>
+        <v>-13.3</v>
       </c>
       <c r="G41" s="9" t="n">
         <v>68</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>73.11</v>
+        <v>73.06</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>-13.3</v>
+        <v>-16.6</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
         <v>72.5</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>73.06</v>
+        <v>72.97</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-16.6</v>
+        <v>-11.8</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>72.97</v>
+        <v>72.86</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>22.26</v>
+        <v>22.21</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>-11.8</v>
+        <v>-21.1</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>72.86</v>
+        <v>72.8</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-21.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>72.8</v>
+        <v>72.69</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>22.24</v>
+        <v>22.19</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>-25.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>72.69</v>
+        <v>72.61</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-18.3</v>
+        <v>-16</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>-16</v>
+        <v>-10.4</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B49" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n"/>
       <c r="C49" s="7" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="D49" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="D49" s="8" t="n"/>
       <c r="E49" s="7" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-10.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B50" s="8" t="n"/>
       <c r="C50" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="D50" s="8" t="n"/>
       <c r="E50" s="7" t="n">
-        <v>21.85</v>
+        <v>21.7</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B51" s="8" t="n"/>
       <c r="C51" s="7" t="n">
-        <v>72.58</v>
+        <v>72.5</v>
       </c>
       <c r="D51" s="8" t="n"/>
       <c r="E51" s="7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-12.3</v>
+        <v>-6.6</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B52" s="8" t="n"/>
       <c r="C52" s="7" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D52" s="8" t="n"/>
       <c r="E52" s="7" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B53" s="8" t="n"/>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C53" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D53" s="8" t="n"/>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="D53" s="8" t="n">
+        <v>21.2</v>
+      </c>
       <c r="E53" s="7" t="n">
-        <v>21.73</v>
+        <v>21.63</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>21.63</v>
+        <v>21.57</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E55" s="7" t="n">
         <v>21.57</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>-7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>72.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D56" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E56" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E56" s="7" t="n">
-        <v>21.57</v>
-      </c>
       <c r="F56" s="8" t="n">
-        <v>-10.9</v>
+        <v>-7.7</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n"/>
       <c r="C57" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D57" s="8" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D57" s="8" t="n"/>
       <c r="E57" s="7" t="n">
         <v>21.8</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.9</v>
       </c>
       <c r="G57" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B58" s="8" t="n"/>
@@ -4930,19 +4934,19 @@
         <v>21.8</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>-8.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B59" s="8" t="n"/>
@@ -4954,274 +4958,278 @@
         <v>21.8</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>-12.5</v>
+        <v>-11.2</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B60" s="8" t="n"/>
       <c r="C60" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>-11.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G60" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B61" s="8" t="n"/>
       <c r="C61" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="7" t="n">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>-13.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B62" s="8" t="n"/>
       <c r="C62" s="7" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="7" t="n">
-        <v>22.15</v>
+        <v>22.5</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="G62" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B63" s="8" t="n"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="C63" s="7" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="D63" s="8" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D63" s="8" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E63" s="7" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>-12.4</v>
+        <v>-7.8</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B64" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C64" s="7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D64" s="8" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>20.5</v>
+        <v>20.95</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>-7.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B65" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D65" s="8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>20.95</v>
+        <v>21.13</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>-3.1</v>
+        <v>-11.8</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B66" s="8" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>-11.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B67" s="8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B68" s="8" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C68" s="7" t="n">
-        <v>72.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>-8.6</v>
+        <v>-13.5</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B69" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>21.33</v>
+        <v>21.43</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H69" s="10" t="n">
         <v>7.7</v>
@@ -5230,510 +5238,510 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="C70" s="7" t="n">
-        <v>72.23</v>
+        <v>72.39</v>
       </c>
       <c r="D70" s="8" t="n">
         <v>22</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>21.43</v>
+        <v>21.64</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>-7.1</v>
+        <v>-12.5</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C71" s="7" t="n">
         <v>72.39</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>21.64</v>
+        <v>21.69</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>-12.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B72" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C72" s="7" t="n">
-        <v>72.39</v>
+        <v>72.36</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>21.69</v>
+        <v>21.56</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>-6.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="n"/>
       <c r="C73" s="7" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="D73" s="8" t="n">
-        <v>20.6</v>
-      </c>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="D73" s="8" t="n"/>
       <c r="E73" s="7" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B74" s="8" t="n"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="C74" s="7" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="D74" s="8" t="n"/>
+        <v>72.45</v>
+      </c>
+      <c r="D74" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E74" s="7" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B75" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C75" s="7" t="n">
-        <v>72.45</v>
+        <v>72.47</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>21.67</v>
+        <v>21.53</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B76" s="8" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>72.47</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>21.53</v>
+        <v>21.47</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B77" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C77" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C78" s="7" t="n">
-        <v>72.31999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="D78" s="8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>-4.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>72.23</v>
+        <v>72.3</v>
       </c>
       <c r="D79" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>21.4</v>
+        <v>21.55</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>-1.6</v>
+        <v>-15.1</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="C80" s="7" t="n">
-        <v>72.3</v>
+        <v>72.37</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>21.55</v>
+        <v>21.69</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>-15.1</v>
+        <v>-10.3</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B81" s="8" t="n">
-        <v>72.8</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="n"/>
       <c r="C81" s="7" t="n">
-        <v>72.37</v>
-      </c>
-      <c r="D81" s="8" t="n">
-        <v>22.5</v>
-      </c>
+        <v>72.28</v>
+      </c>
+      <c r="D81" s="8" t="n"/>
       <c r="E81" s="7" t="n">
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>-10.3</v>
+        <v>-14.8</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>5.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B82" s="8" t="n"/>
       <c r="C82" s="7" t="n">
-        <v>72.28</v>
+        <v>72.3</v>
       </c>
       <c r="D82" s="8" t="n"/>
       <c r="E82" s="7" t="n">
-        <v>21.67</v>
+        <v>21.78</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>-14.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B83" s="8" t="n"/>
       <c r="C83" s="7" t="n">
-        <v>72.3</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="D83" s="8" t="n"/>
       <c r="E83" s="7" t="n">
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>-15.7</v>
+        <v>-15.4</v>
       </c>
       <c r="G83" s="9" t="n">
         <v>60</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B84" s="8" t="n"/>
       <c r="C84" s="7" t="n">
-        <v>72.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D84" s="8" t="n"/>
       <c r="E84" s="7" t="n">
-        <v>21.82</v>
+        <v>21.83</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>-15.4</v>
+        <v>-8.9</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B85" s="8" t="n"/>
       <c r="C85" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D85" s="8" t="n"/>
       <c r="E85" s="7" t="n">
-        <v>21.83</v>
+        <v>22</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>-8.9</v>
+        <v>-6.7</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B86" s="8" t="n"/>
       <c r="C86" s="7" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D86" s="8" t="n"/>
       <c r="E86" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>-6.7</v>
+        <v>-4.8</v>
       </c>
       <c r="G86" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B87" s="8" t="n"/>
-      <c r="C87" s="7" t="n">
-        <v>72.8</v>
-      </c>
+      <c r="C87" s="7" t="n"/>
       <c r="D87" s="8" t="n"/>
-      <c r="E87" s="7" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="E87" s="7" t="n"/>
       <c r="F87" s="8" t="n">
-        <v>-4.8</v>
+        <v>0.6</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B88" s="8" t="n"/>
-      <c r="C88" s="7" t="n"/>
-      <c r="D88" s="8" t="n"/>
-      <c r="E88" s="7" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="C88" s="7" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="D88" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E88" s="7" t="n">
+        <v>21.9</v>
+      </c>
       <c r="F88" s="8" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B89" s="8" t="n">
-        <v>73.2</v>
+        <v>72.8</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>73.2</v>
+        <v>73</v>
       </c>
       <c r="D89" s="8" t="n">
         <v>21.9</v>
@@ -5742,153 +5750,149 @@
         <v>21.9</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>3.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B90" s="8" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C90" s="7" t="n">
-        <v>73</v>
+        <v>72.97</v>
       </c>
       <c r="D90" s="8" t="n">
-        <v>21.9</v>
+        <v>21.3</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>-9.4</v>
+        <v>-6.9</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B91" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>72.97</v>
+        <v>72.88</v>
       </c>
       <c r="D91" s="8" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>-6.9</v>
+        <v>-3.2</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B92" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="C92" s="7" t="n">
-        <v>72.88</v>
+        <v>73.08</v>
       </c>
       <c r="D92" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>21.5</v>
+        <v>21.38</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>-3.2</v>
+        <v>0.9</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B93" s="8" t="n">
-        <v>73.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>73.08</v>
+        <v>73</v>
       </c>
       <c r="D93" s="8" t="n">
-        <v>20.9</v>
+        <v>21.8</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>21.38</v>
+        <v>21.45</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="B94" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="n"/>
       <c r="C94" s="7" t="n">
         <v>73</v>
       </c>
-      <c r="D94" s="8" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="D94" s="8" t="n"/>
       <c r="E94" s="7" t="n">
         <v>21.45</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H94" s="10" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -6319,7 +6323,7 @@
         <v>51</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>300</v>

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -5886,7 +5886,7 @@
         <v>21.45</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="G94" s="9" t="n">
         <v>61</v>
@@ -6323,16 +6323,16 @@
         <v>51</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>300</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>315</v>
+        <v>367</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>15</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>52.4</v>
+        <v>51.2</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -3536,7 +3536,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
@@ -3544,19 +3544,19 @@
       <c r="D5" s="8" t="n"/>
       <c r="E5" s="7" t="n"/>
       <c r="F5" s="8" t="n">
-        <v>-9.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
@@ -3564,39 +3564,47 @@
       <c r="D6" s="8" t="n"/>
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="8" t="n">
-        <v>-8.300000000000001</v>
+        <v>-5</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="7" t="n"/>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>22</v>
+      </c>
       <c r="F7" s="8" t="n">
-        <v>-5</v>
+        <v>-1.8</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
@@ -3606,103 +3614,99 @@
         <v>74.5</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>-1.8</v>
+        <v>-13.8</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n">
-        <v>74.5</v>
-      </c>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n"/>
       <c r="C9" s="7" t="n">
         <v>74.5</v>
       </c>
-      <c r="D9" s="8" t="n">
-        <v>23</v>
-      </c>
+      <c r="D9" s="8" t="n"/>
       <c r="E9" s="7" t="n">
         <v>22.5</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-13.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="H9" s="10" t="n">
-        <v>8.1</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n"/>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>74.40000000000001</v>
+      </c>
       <c r="C10" s="7" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="D10" s="8" t="n"/>
+        <v>74.47</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>23.3</v>
+      </c>
       <c r="E10" s="7" t="n">
-        <v>22.5</v>
+        <v>22.77</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>-15.7</v>
+        <v>-10.5</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="H10" s="10" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n">
-        <v>74.40000000000001</v>
-      </c>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n"/>
       <c r="C11" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D11" s="8" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="7" t="n">
         <v>22.77</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-10.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
@@ -3714,90 +3718,94 @@
         <v>22.77</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>-9.4</v>
+        <v>-7.5</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n"/>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>74.5</v>
+      </c>
       <c r="C13" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D13" s="8" t="n"/>
+      <c r="D13" s="8" t="n">
+        <v>22.9</v>
+      </c>
       <c r="E13" s="7" t="n">
-        <v>22.77</v>
+        <v>22.8</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-7.5</v>
+        <v>-4.5</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>74.47</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.2</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>23</v>
+        <v>22.93</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-2.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H15" s="10" t="n">
         <v>8</v>
@@ -3806,291 +3814,283 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>74.7</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>22.93</v>
+        <v>22.78</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>74.7</v>
+        <v>74.64</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>22.78</v>
+        <v>22.6</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-11.9</v>
+        <v>-10.3</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>22.6</v>
+        <v>22.55</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>-10.3</v>
+        <v>-13.7</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>74.65000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>22.55</v>
+        <v>22.57</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-13.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n">
-        <v>74.2</v>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n"/>
       <c r="C20" s="7" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>22.7</v>
-      </c>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D20" s="8" t="n"/>
       <c r="E20" s="7" t="n">
-        <v>22.57</v>
+        <v>22.52</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>-15.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.52</v>
       </c>
       <c r="D21" s="8" t="n"/>
       <c r="E21" s="7" t="n">
-        <v>22.52</v>
+        <v>22.46</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-18.2</v>
+        <v>-23.1</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="7" t="n">
-        <v>74.42</v>
+        <v>74.33</v>
       </c>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="7" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="7" t="n">
-        <v>74.33</v>
+        <v>74.45</v>
       </c>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="7" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>-18.2</v>
+        <v>-19.5</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B25" s="8" t="n"/>
       <c r="C25" s="7" t="n">
-        <v>74.45</v>
+        <v>74.2</v>
       </c>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-19.5</v>
+        <v>-26.4</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B26" s="8" t="n"/>
-      <c r="C26" s="7" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="C26" s="7" t="n"/>
       <c r="D26" s="8" t="n"/>
-      <c r="E26" s="7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="E26" s="7" t="n"/>
       <c r="F26" s="8" t="n">
-        <v>-26.4</v>
+        <v>-19.9</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B27" s="8" t="n"/>
@@ -4098,807 +4098,811 @@
       <c r="D27" s="8" t="n"/>
       <c r="E27" s="7" t="n"/>
       <c r="F27" s="8" t="n">
-        <v>-19.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="n"/>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="7" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>21.7</v>
+      </c>
       <c r="F28" s="8" t="n">
-        <v>-15.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>21.7</v>
+        <v>22.05</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-9.4</v>
+        <v>-12</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>73.2</v>
+        <v>73.33</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-12</v>
+        <v>-12.4</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-12.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>73.31999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D35" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>22.26</v>
+        <v>22.4</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>73.16</v>
+        <v>73.2</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>-10.9</v>
+        <v>-16</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-16</v>
+        <v>-10.1</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>22.3</v>
+        <v>22.31</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>-10.1</v>
+        <v>-5.9</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>73.16</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>22.31</v>
+        <v>22.43</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-5.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
         <v>72.8</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>73.06999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>22.43</v>
+        <v>22.41</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>-9.9</v>
+        <v>-13.3</v>
       </c>
       <c r="G40" s="9" t="n">
         <v>68</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>73.11</v>
+        <v>73.06</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-13.3</v>
+        <v>-16.6</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B42" s="8" t="n">
         <v>72.5</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>73.06</v>
+        <v>72.97</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>-16.6</v>
+        <v>-11.8</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>72.97</v>
+        <v>72.86</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>22.26</v>
+        <v>22.21</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-11.8</v>
+        <v>-21.1</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>72.86</v>
+        <v>72.8</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>-21.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>72.8</v>
+        <v>72.69</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>22.24</v>
+        <v>22.19</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-25.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>72.69</v>
+        <v>72.61</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>-18.3</v>
+        <v>-16</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-16</v>
+        <v>-10.4</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B48" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="n"/>
       <c r="C48" s="7" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="D48" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="D48" s="8" t="n"/>
       <c r="E48" s="7" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>-10.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B49" s="8" t="n"/>
       <c r="C49" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="D49" s="8" t="n"/>
       <c r="E49" s="7" t="n">
-        <v>21.85</v>
+        <v>21.7</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B50" s="8" t="n"/>
       <c r="C50" s="7" t="n">
-        <v>72.58</v>
+        <v>72.5</v>
       </c>
       <c r="D50" s="8" t="n"/>
       <c r="E50" s="7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>-12.3</v>
+        <v>-6.6</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B51" s="8" t="n"/>
       <c r="C51" s="7" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D51" s="8" t="n"/>
       <c r="E51" s="7" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="n"/>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C52" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D52" s="8" t="n"/>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="D52" s="8" t="n">
+        <v>21.2</v>
+      </c>
       <c r="E52" s="7" t="n">
-        <v>21.73</v>
+        <v>21.63</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>21.63</v>
+        <v>21.57</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E54" s="7" t="n">
         <v>21.57</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>-7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>72.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D55" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E55" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E55" s="7" t="n">
-        <v>21.57</v>
-      </c>
       <c r="F55" s="8" t="n">
-        <v>-10.9</v>
+        <v>-7.7</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="n"/>
       <c r="C56" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D56" s="8" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D56" s="8" t="n"/>
       <c r="E56" s="7" t="n">
         <v>21.8</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.9</v>
       </c>
       <c r="G56" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B57" s="8" t="n"/>
@@ -4910,19 +4914,19 @@
         <v>21.8</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>-8.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B58" s="8" t="n"/>
@@ -4934,274 +4938,278 @@
         <v>21.8</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>-12.5</v>
+        <v>-11.2</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B59" s="8" t="n"/>
       <c r="C59" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>-11.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G59" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B60" s="8" t="n"/>
       <c r="C60" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="7" t="n">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>-13.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B61" s="8" t="n"/>
       <c r="C61" s="7" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="7" t="n">
-        <v>22.15</v>
+        <v>22.5</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="G61" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B62" s="8" t="n"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="C62" s="7" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="D62" s="8" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D62" s="8" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E62" s="7" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>-12.4</v>
+        <v>-7.8</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B63" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>20.5</v>
+        <v>20.95</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>-7.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B64" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C64" s="7" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D64" s="8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>20.95</v>
+        <v>21.13</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>-3.1</v>
+        <v>-11.8</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B65" s="8" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D65" s="8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>-11.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B66" s="8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B67" s="8" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>72.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>-8.6</v>
+        <v>-13.5</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B68" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C68" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>21.33</v>
+        <v>21.43</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H68" s="10" t="n">
         <v>7.7</v>
@@ -5210,510 +5218,510 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B69" s="8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>72.23</v>
+        <v>72.39</v>
       </c>
       <c r="D69" s="8" t="n">
         <v>22</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>21.43</v>
+        <v>21.64</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>-7.1</v>
+        <v>-12.5</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C70" s="7" t="n">
         <v>72.39</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>21.64</v>
+        <v>21.69</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>-12.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>72.39</v>
+        <v>72.36</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>21.69</v>
+        <v>21.56</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>-6.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B72" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="n"/>
       <c r="C72" s="7" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="D72" s="8" t="n">
-        <v>20.6</v>
-      </c>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="D72" s="8" t="n"/>
       <c r="E72" s="7" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="n"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="C73" s="7" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="D73" s="8" t="n"/>
+        <v>72.45</v>
+      </c>
+      <c r="D73" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E73" s="7" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B74" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C74" s="7" t="n">
-        <v>72.45</v>
+        <v>72.47</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>21.67</v>
+        <v>21.53</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B75" s="8" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C75" s="7" t="n">
-        <v>72.47</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>21.53</v>
+        <v>21.47</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B76" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B77" s="8" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C77" s="7" t="n">
-        <v>72.31999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>-4.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="C78" s="7" t="n">
-        <v>72.23</v>
+        <v>72.3</v>
       </c>
       <c r="D78" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>21.4</v>
+        <v>21.55</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>-1.6</v>
+        <v>-15.1</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>72.3</v>
+        <v>72.37</v>
       </c>
       <c r="D79" s="8" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>21.55</v>
+        <v>21.69</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>-15.1</v>
+        <v>-10.3</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B80" s="8" t="n">
-        <v>72.8</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="n"/>
       <c r="C80" s="7" t="n">
-        <v>72.37</v>
-      </c>
-      <c r="D80" s="8" t="n">
-        <v>22.5</v>
-      </c>
+        <v>72.28</v>
+      </c>
+      <c r="D80" s="8" t="n"/>
       <c r="E80" s="7" t="n">
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>-10.3</v>
+        <v>-14.8</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>5.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B81" s="8" t="n"/>
       <c r="C81" s="7" t="n">
-        <v>72.28</v>
+        <v>72.3</v>
       </c>
       <c r="D81" s="8" t="n"/>
       <c r="E81" s="7" t="n">
-        <v>21.67</v>
+        <v>21.78</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>-14.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B82" s="8" t="n"/>
       <c r="C82" s="7" t="n">
-        <v>72.3</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="D82" s="8" t="n"/>
       <c r="E82" s="7" t="n">
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>-15.7</v>
+        <v>-15.4</v>
       </c>
       <c r="G82" s="9" t="n">
         <v>60</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B83" s="8" t="n"/>
       <c r="C83" s="7" t="n">
-        <v>72.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D83" s="8" t="n"/>
       <c r="E83" s="7" t="n">
-        <v>21.82</v>
+        <v>21.83</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>-15.4</v>
+        <v>-8.9</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B84" s="8" t="n"/>
       <c r="C84" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D84" s="8" t="n"/>
       <c r="E84" s="7" t="n">
-        <v>21.83</v>
+        <v>22</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>-8.9</v>
+        <v>-6.7</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B85" s="8" t="n"/>
       <c r="C85" s="7" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D85" s="8" t="n"/>
       <c r="E85" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>-6.7</v>
+        <v>-4.8</v>
       </c>
       <c r="G85" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B86" s="8" t="n"/>
-      <c r="C86" s="7" t="n">
-        <v>72.8</v>
-      </c>
+      <c r="C86" s="7" t="n"/>
       <c r="D86" s="8" t="n"/>
-      <c r="E86" s="7" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="E86" s="7" t="n"/>
       <c r="F86" s="8" t="n">
-        <v>-4.8</v>
+        <v>0.6</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B87" s="8" t="n"/>
-      <c r="C87" s="7" t="n"/>
-      <c r="D87" s="8" t="n"/>
-      <c r="E87" s="7" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="C87" s="7" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="D87" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E87" s="7" t="n">
+        <v>21.9</v>
+      </c>
       <c r="F87" s="8" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B88" s="8" t="n">
-        <v>73.2</v>
+        <v>72.8</v>
       </c>
       <c r="C88" s="7" t="n">
-        <v>73.2</v>
+        <v>73</v>
       </c>
       <c r="D88" s="8" t="n">
         <v>21.9</v>
@@ -5722,177 +5730,173 @@
         <v>21.9</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>3.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B89" s="8" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>73</v>
+        <v>72.97</v>
       </c>
       <c r="D89" s="8" t="n">
-        <v>21.9</v>
+        <v>21.3</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>-9.4</v>
+        <v>-6.9</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B90" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C90" s="7" t="n">
-        <v>72.97</v>
+        <v>72.88</v>
       </c>
       <c r="D90" s="8" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>-6.9</v>
+        <v>-3.2</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B91" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>72.88</v>
+        <v>73.08</v>
       </c>
       <c r="D91" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>21.5</v>
+        <v>21.38</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>-3.2</v>
+        <v>0.9</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B92" s="8" t="n">
-        <v>73.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C92" s="7" t="n">
-        <v>73.08</v>
+        <v>73</v>
       </c>
       <c r="D92" s="8" t="n">
-        <v>20.9</v>
+        <v>21.8</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>21.38</v>
+        <v>21.45</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="B93" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="n"/>
       <c r="C93" s="7" t="n">
         <v>73</v>
       </c>
-      <c r="D93" s="8" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="D93" s="8" t="n"/>
       <c r="E93" s="7" t="n">
         <v>21.45</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B94" s="8" t="n"/>
       <c r="C94" s="7" t="n">
-        <v>73</v>
+        <v>72.95999999999999</v>
       </c>
       <c r="D94" s="8" t="n"/>
       <c r="E94" s="7" t="n">
-        <v>21.45</v>
+        <v>21.36</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>2.4</v>
+        <v>7.8</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H94" s="10" t="n">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -6352,7 +6356,9 @@
       <c r="D17" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="E17" s="8" t="n"/>
+      <c r="E17" s="8" t="n">
+        <v>51.2</v>
+      </c>
       <c r="F17" s="4" t="n">
         <v>180</v>
       </c>

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>72.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>68</v>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>21.8</v>
+        <v>20.7</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>16</v>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3.83</v>
+        <v>3.87</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>4.71</v>
@@ -5881,16 +5881,20 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B94" s="8" t="n"/>
+      <c r="B94" s="8" t="n">
+        <v>71.90000000000001</v>
+      </c>
       <c r="C94" s="7" t="n">
-        <v>72.95999999999999</v>
-      </c>
-      <c r="D94" s="8" t="n"/>
+        <v>72.78</v>
+      </c>
+      <c r="D94" s="8" t="n">
+        <v>20.7</v>
+      </c>
       <c r="E94" s="7" t="n">
-        <v>21.36</v>
+        <v>21.25</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="G94" s="9" t="n">
         <v>59</v>
@@ -6362,8 +6366,12 @@
       <c r="F17" s="4" t="n">
         <v>180</v>
       </c>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="11" t="n"/>
+      <c r="G17" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H17" s="11" t="n">
+        <v>-166</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>51.2</v>
+        <v>51.6</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Christiansborg Rundt lør 29. aug — svømmes UTAPERET (2000 m, bevidst valg). Médoc-simulation 19 km tir. Svøm 2.000 m i træk ons. Médoc løbes med Eva.</t>
+          <t>Christiansborg Rundt lør 29. aug — svømmes UTAPERET (2000 m, bevidst valg). Løb Z2 18 km tir (simulation udgået efter aftale). Svøm 2.000 m i træk ons. Søn: cykel indendørs i stedet for løb (ingen løb to dage i streg). Médoc løbes med Eva.</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
         <v>21.25</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G94" s="9" t="n">
         <v>59</v>
@@ -6361,16 +6361,16 @@
         <v>47</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>51.2</v>
+        <v>51.6</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>180</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>-166</v>
+        <v>-148</v>
       </c>
     </row>
     <row r="18">

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -1327,7 +1327,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Marathon du Médoc lør 5. sep. Ren taper + race-ernæringsplan.</t>
+          <t>Marathon du Médoc lør 5. sep. Ren taper + race-ernæringsplan. Tir: cykel i stedet for løb (ingen løb to dage i streg). Ons: 25 min styrke overkrop/core, ingen benbelastning.</t>
         </is>
       </c>
     </row>

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>51.6</v>
+        <v>52.4</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -3536,7 +3536,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
@@ -3544,39 +3544,47 @@
       <c r="D5" s="8" t="n"/>
       <c r="E5" s="7" t="n"/>
       <c r="F5" s="8" t="n">
-        <v>-8.300000000000001</v>
+        <v>-5</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="7" t="n"/>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>22</v>
+      </c>
       <c r="F6" s="8" t="n">
-        <v>-5</v>
+        <v>-1.8</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
@@ -3586,103 +3594,99 @@
         <v>74.5</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-1.8</v>
+        <v>-13.8</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n">
-        <v>74.5</v>
-      </c>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n"/>
       <c r="C8" s="7" t="n">
         <v>74.5</v>
       </c>
-      <c r="D8" s="8" t="n">
-        <v>23</v>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="7" t="n">
         <v>22.5</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>-13.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>8.1</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n"/>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>74.40000000000001</v>
+      </c>
       <c r="C9" s="7" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="D9" s="8" t="n"/>
+        <v>74.47</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>23.3</v>
+      </c>
       <c r="E9" s="7" t="n">
-        <v>22.5</v>
+        <v>22.77</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-15.7</v>
+        <v>-10.5</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="H9" s="10" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n">
-        <v>74.40000000000001</v>
-      </c>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n"/>
       <c r="C10" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D10" s="8" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="7" t="n">
         <v>22.77</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>-10.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
@@ -3694,90 +3698,94 @@
         <v>22.77</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-9.4</v>
+        <v>-7.5</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n"/>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>74.5</v>
+      </c>
       <c r="C12" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D12" s="8" t="n"/>
+      <c r="D12" s="8" t="n">
+        <v>22.9</v>
+      </c>
       <c r="E12" s="7" t="n">
-        <v>22.77</v>
+        <v>22.8</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>-7.5</v>
+        <v>-4.5</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>74.47</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.2</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>23</v>
+        <v>22.93</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>-2.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H14" s="10" t="n">
         <v>8</v>
@@ -3786,291 +3794,283 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>74.7</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>22.93</v>
+        <v>22.78</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>74.7</v>
+        <v>74.64</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>22.78</v>
+        <v>22.6</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>-11.9</v>
+        <v>-10.3</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>22.6</v>
+        <v>22.55</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-10.3</v>
+        <v>-13.7</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>74.65000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>22.55</v>
+        <v>22.57</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>-13.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n">
-        <v>74.2</v>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n"/>
       <c r="C19" s="7" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="D19" s="8" t="n">
-        <v>22.7</v>
-      </c>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D19" s="8" t="n"/>
       <c r="E19" s="7" t="n">
-        <v>22.57</v>
+        <v>22.52</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-15.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.52</v>
       </c>
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="7" t="n">
-        <v>22.52</v>
+        <v>22.46</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D21" s="8" t="n"/>
       <c r="E21" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-18.2</v>
+        <v>-23.1</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="7" t="n">
-        <v>74.42</v>
+        <v>74.33</v>
       </c>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="7" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="7" t="n">
-        <v>74.33</v>
+        <v>74.45</v>
       </c>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="7" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-18.2</v>
+        <v>-19.5</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="7" t="n">
-        <v>74.45</v>
+        <v>74.2</v>
       </c>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>-19.5</v>
+        <v>-26.4</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B25" s="8" t="n"/>
-      <c r="C25" s="7" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="C25" s="7" t="n"/>
       <c r="D25" s="8" t="n"/>
-      <c r="E25" s="7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="E25" s="7" t="n"/>
       <c r="F25" s="8" t="n">
-        <v>-26.4</v>
+        <v>-19.9</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B26" s="8" t="n"/>
@@ -4078,807 +4078,811 @@
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="8" t="n">
-        <v>-19.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="7" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>21.7</v>
+      </c>
       <c r="F27" s="8" t="n">
-        <v>-15.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>21.7</v>
+        <v>22.05</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-9.4</v>
+        <v>-12</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>73.2</v>
+        <v>73.33</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-12</v>
+        <v>-12.4</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-12.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>73.31999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D34" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>22.26</v>
+        <v>22.4</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>73.16</v>
+        <v>73.2</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-10.9</v>
+        <v>-16</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>-16</v>
+        <v>-10.1</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>22.3</v>
+        <v>22.31</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-10.1</v>
+        <v>-5.9</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>73.16</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>22.31</v>
+        <v>22.43</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>-5.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
         <v>72.8</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>73.06999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>22.43</v>
+        <v>22.41</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-9.9</v>
+        <v>-13.3</v>
       </c>
       <c r="G39" s="9" t="n">
         <v>68</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>73.11</v>
+        <v>73.06</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>-13.3</v>
+        <v>-16.6</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
         <v>72.5</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>73.06</v>
+        <v>72.97</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-16.6</v>
+        <v>-11.8</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>72.97</v>
+        <v>72.86</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>22.26</v>
+        <v>22.21</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>-11.8</v>
+        <v>-21.1</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>72.86</v>
+        <v>72.8</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-21.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>72.8</v>
+        <v>72.69</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>22.24</v>
+        <v>22.19</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>-25.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>72.69</v>
+        <v>72.61</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-18.3</v>
+        <v>-16</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>-16</v>
+        <v>-10.4</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B47" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n"/>
       <c r="C47" s="7" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="D47" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="D47" s="8" t="n"/>
       <c r="E47" s="7" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-10.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B48" s="8" t="n"/>
       <c r="C48" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="D48" s="8" t="n"/>
       <c r="E48" s="7" t="n">
-        <v>21.85</v>
+        <v>21.7</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B49" s="8" t="n"/>
       <c r="C49" s="7" t="n">
-        <v>72.58</v>
+        <v>72.5</v>
       </c>
       <c r="D49" s="8" t="n"/>
       <c r="E49" s="7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-12.3</v>
+        <v>-6.6</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B50" s="8" t="n"/>
       <c r="C50" s="7" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D50" s="8" t="n"/>
       <c r="E50" s="7" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B51" s="8" t="n"/>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C51" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D51" s="8" t="n"/>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>21.2</v>
+      </c>
       <c r="E51" s="7" t="n">
-        <v>21.73</v>
+        <v>21.63</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D52" s="8" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>21.63</v>
+        <v>21.57</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E53" s="7" t="n">
         <v>21.57</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>72.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D54" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E54" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E54" s="7" t="n">
-        <v>21.57</v>
-      </c>
       <c r="F54" s="8" t="n">
-        <v>-10.9</v>
+        <v>-7.7</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n"/>
       <c r="C55" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D55" s="8" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D55" s="8" t="n"/>
       <c r="E55" s="7" t="n">
         <v>21.8</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.9</v>
       </c>
       <c r="G55" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B56" s="8" t="n"/>
@@ -4890,19 +4894,19 @@
         <v>21.8</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>-8.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B57" s="8" t="n"/>
@@ -4914,274 +4918,278 @@
         <v>21.8</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>-12.5</v>
+        <v>-11.2</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B58" s="8" t="n"/>
       <c r="C58" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>-11.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G58" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B59" s="8" t="n"/>
       <c r="C59" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="7" t="n">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>-13.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B60" s="8" t="n"/>
       <c r="C60" s="7" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="7" t="n">
-        <v>22.15</v>
+        <v>22.5</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="G60" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="n"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="C61" s="7" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="D61" s="8" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E61" s="7" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>-12.4</v>
+        <v>-7.8</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B62" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C62" s="7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>20.5</v>
+        <v>20.95</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>-7.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B63" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>20.95</v>
+        <v>21.13</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>-3.1</v>
+        <v>-11.8</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B64" s="8" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C64" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D64" s="8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>-11.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B65" s="8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D65" s="8" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B66" s="8" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>72.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>-8.6</v>
+        <v>-13.5</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B67" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>21.33</v>
+        <v>21.43</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H67" s="10" t="n">
         <v>7.7</v>
@@ -5190,510 +5198,510 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B68" s="8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="C68" s="7" t="n">
-        <v>72.23</v>
+        <v>72.39</v>
       </c>
       <c r="D68" s="8" t="n">
         <v>22</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>21.43</v>
+        <v>21.64</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>-7.1</v>
+        <v>-12.5</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B69" s="8" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C69" s="7" t="n">
         <v>72.39</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>21.64</v>
+        <v>21.69</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>-12.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C70" s="7" t="n">
-        <v>72.39</v>
+        <v>72.36</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>21.69</v>
+        <v>21.56</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>-6.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B71" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="n"/>
       <c r="C71" s="7" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="D71" s="8" t="n">
-        <v>20.6</v>
-      </c>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="D71" s="8" t="n"/>
       <c r="E71" s="7" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B72" s="8" t="n"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="C72" s="7" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="D72" s="8" t="n"/>
+        <v>72.45</v>
+      </c>
+      <c r="D72" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E72" s="7" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B73" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C73" s="7" t="n">
-        <v>72.45</v>
+        <v>72.47</v>
       </c>
       <c r="D73" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>21.67</v>
+        <v>21.53</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B74" s="8" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C74" s="7" t="n">
-        <v>72.47</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>21.53</v>
+        <v>21.47</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B75" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C75" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B76" s="8" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>72.31999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>-4.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B77" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="C77" s="7" t="n">
-        <v>72.23</v>
+        <v>72.3</v>
       </c>
       <c r="D77" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>21.4</v>
+        <v>21.55</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>-1.6</v>
+        <v>-15.1</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="C78" s="7" t="n">
-        <v>72.3</v>
+        <v>72.37</v>
       </c>
       <c r="D78" s="8" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>21.55</v>
+        <v>21.69</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>-15.1</v>
+        <v>-10.3</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B79" s="8" t="n">
-        <v>72.8</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="n"/>
       <c r="C79" s="7" t="n">
-        <v>72.37</v>
-      </c>
-      <c r="D79" s="8" t="n">
-        <v>22.5</v>
-      </c>
+        <v>72.28</v>
+      </c>
+      <c r="D79" s="8" t="n"/>
       <c r="E79" s="7" t="n">
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>-10.3</v>
+        <v>-14.8</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>5.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B80" s="8" t="n"/>
       <c r="C80" s="7" t="n">
-        <v>72.28</v>
+        <v>72.3</v>
       </c>
       <c r="D80" s="8" t="n"/>
       <c r="E80" s="7" t="n">
-        <v>21.67</v>
+        <v>21.78</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>-14.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B81" s="8" t="n"/>
       <c r="C81" s="7" t="n">
-        <v>72.3</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="D81" s="8" t="n"/>
       <c r="E81" s="7" t="n">
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>-15.7</v>
+        <v>-15.4</v>
       </c>
       <c r="G81" s="9" t="n">
         <v>60</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B82" s="8" t="n"/>
       <c r="C82" s="7" t="n">
-        <v>72.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D82" s="8" t="n"/>
       <c r="E82" s="7" t="n">
-        <v>21.82</v>
+        <v>21.83</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>-15.4</v>
+        <v>-8.9</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B83" s="8" t="n"/>
       <c r="C83" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D83" s="8" t="n"/>
       <c r="E83" s="7" t="n">
-        <v>21.83</v>
+        <v>22</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>-8.9</v>
+        <v>-6.7</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B84" s="8" t="n"/>
       <c r="C84" s="7" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D84" s="8" t="n"/>
       <c r="E84" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>-6.7</v>
+        <v>-4.8</v>
       </c>
       <c r="G84" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B85" s="8" t="n"/>
-      <c r="C85" s="7" t="n">
-        <v>72.8</v>
-      </c>
+      <c r="C85" s="7" t="n"/>
       <c r="D85" s="8" t="n"/>
-      <c r="E85" s="7" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="E85" s="7" t="n"/>
       <c r="F85" s="8" t="n">
-        <v>-4.8</v>
+        <v>0.6</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B86" s="8" t="n"/>
-      <c r="C86" s="7" t="n"/>
-      <c r="D86" s="8" t="n"/>
-      <c r="E86" s="7" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="C86" s="7" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="D86" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E86" s="7" t="n">
+        <v>21.9</v>
+      </c>
       <c r="F86" s="8" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B87" s="8" t="n">
-        <v>73.2</v>
+        <v>72.8</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>73.2</v>
+        <v>73</v>
       </c>
       <c r="D87" s="8" t="n">
         <v>21.9</v>
@@ -5702,206 +5710,198 @@
         <v>21.9</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>3.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B88" s="8" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C88" s="7" t="n">
-        <v>73</v>
+        <v>72.97</v>
       </c>
       <c r="D88" s="8" t="n">
-        <v>21.9</v>
+        <v>21.3</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>-9.4</v>
+        <v>-6.9</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B89" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>72.97</v>
+        <v>72.88</v>
       </c>
       <c r="D89" s="8" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>-6.9</v>
+        <v>-3.2</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B90" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="C90" s="7" t="n">
-        <v>72.88</v>
+        <v>73.08</v>
       </c>
       <c r="D90" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>21.5</v>
+        <v>21.38</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>-3.2</v>
+        <v>0.9</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B91" s="8" t="n">
-        <v>73.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>73.08</v>
+        <v>73</v>
       </c>
       <c r="D91" s="8" t="n">
-        <v>20.9</v>
+        <v>21.8</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>21.38</v>
+        <v>21.45</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="B92" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="n"/>
       <c r="C92" s="7" t="n">
         <v>73</v>
       </c>
-      <c r="D92" s="8" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="D92" s="8" t="n"/>
       <c r="E92" s="7" t="n">
         <v>21.45</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="B93" s="8" t="n"/>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="n">
+        <v>71.90000000000001</v>
+      </c>
       <c r="C93" s="7" t="n">
-        <v>73</v>
-      </c>
-      <c r="D93" s="8" t="n"/>
+        <v>72.78</v>
+      </c>
+      <c r="D93" s="8" t="n">
+        <v>20.7</v>
+      </c>
       <c r="E93" s="7" t="n">
-        <v>21.45</v>
+        <v>21.25</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="B94" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="n"/>
       <c r="C94" s="7" t="n">
         <v>72.78</v>
       </c>
-      <c r="D94" s="8" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="D94" s="8" t="n"/>
       <c r="E94" s="7" t="n">
-        <v>21.25</v>
+        <v>21.12</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G94" s="9" t="n">
-        <v>59</v>
-      </c>
-      <c r="H94" s="10" t="n">
-        <v>6.7</v>
-      </c>
+        <v>-0.4</v>
+      </c>
+      <c r="G94" s="9" t="n"/>
+      <c r="H94" s="10" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6361,7 +6361,7 @@
         <v>47</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>51.6</v>
+        <v>52.4</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>180</v>

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>71.90000000000001</v>
+        <v>71</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>68</v>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>20.7</v>
+        <v>21.5</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>16</v>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3.87</v>
+        <v>3.92</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>4.71</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>52.4</v>
+        <v>52.7</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -3536,27 +3536,35 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="7" t="n"/>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>22</v>
+      </c>
       <c r="F5" s="8" t="n">
-        <v>-5</v>
+        <v>-1.8</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
@@ -3566,103 +3574,99 @@
         <v>74.5</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>-1.8</v>
+        <v>-13.8</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>74.5</v>
-      </c>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n"/>
       <c r="C7" s="7" t="n">
         <v>74.5</v>
       </c>
-      <c r="D7" s="8" t="n">
-        <v>23</v>
-      </c>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="7" t="n">
         <v>22.5</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-13.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="H7" s="10" t="n">
-        <v>8.1</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n"/>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>74.40000000000001</v>
+      </c>
       <c r="C8" s="7" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="D8" s="8" t="n"/>
+        <v>74.47</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>23.3</v>
+      </c>
       <c r="E8" s="7" t="n">
-        <v>22.5</v>
+        <v>22.77</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>-15.7</v>
+        <v>-10.5</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="H8" s="10" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n">
-        <v>74.40000000000001</v>
-      </c>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n"/>
       <c r="C9" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D9" s="8" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="D9" s="8" t="n"/>
       <c r="E9" s="7" t="n">
         <v>22.77</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-10.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
@@ -3674,90 +3678,94 @@
         <v>22.77</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>-9.4</v>
+        <v>-7.5</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n"/>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>74.5</v>
+      </c>
       <c r="C11" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D11" s="8" t="n"/>
+      <c r="D11" s="8" t="n">
+        <v>22.9</v>
+      </c>
       <c r="E11" s="7" t="n">
-        <v>22.77</v>
+        <v>22.8</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-7.5</v>
+        <v>-4.5</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>74.47</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.2</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>23</v>
+        <v>22.93</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-2.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H13" s="10" t="n">
         <v>8</v>
@@ -3766,291 +3774,283 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>74.7</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>22.93</v>
+        <v>22.78</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>74.7</v>
+        <v>74.64</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>22.78</v>
+        <v>22.6</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-11.9</v>
+        <v>-10.3</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>22.6</v>
+        <v>22.55</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>-10.3</v>
+        <v>-13.7</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>74.65000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>22.55</v>
+        <v>22.57</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-13.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="n">
-        <v>74.2</v>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n"/>
       <c r="C18" s="7" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>22.7</v>
-      </c>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D18" s="8" t="n"/>
       <c r="E18" s="7" t="n">
-        <v>22.57</v>
+        <v>22.52</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>-15.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B19" s="8" t="n"/>
       <c r="C19" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.52</v>
       </c>
       <c r="D19" s="8" t="n"/>
       <c r="E19" s="7" t="n">
-        <v>22.52</v>
+        <v>22.46</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>-18.2</v>
+        <v>-23.1</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="7" t="n">
-        <v>74.42</v>
+        <v>74.33</v>
       </c>
       <c r="D21" s="8" t="n"/>
       <c r="E21" s="7" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="7" t="n">
-        <v>74.33</v>
+        <v>74.45</v>
       </c>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="7" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-18.2</v>
+        <v>-19.5</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="7" t="n">
-        <v>74.45</v>
+        <v>74.2</v>
       </c>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-19.5</v>
+        <v>-26.4</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
-      <c r="C24" s="7" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="C24" s="7" t="n"/>
       <c r="D24" s="8" t="n"/>
-      <c r="E24" s="7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="E24" s="7" t="n"/>
       <c r="F24" s="8" t="n">
-        <v>-26.4</v>
+        <v>-19.9</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B25" s="8" t="n"/>
@@ -4058,807 +4058,811 @@
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="8" t="n">
-        <v>-19.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="7" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>21.7</v>
+      </c>
       <c r="F26" s="8" t="n">
-        <v>-15.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>21.7</v>
+        <v>22.05</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-9.4</v>
+        <v>-12</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>73.2</v>
+        <v>73.33</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-12</v>
+        <v>-12.4</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-12.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>73.31999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D33" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>22.26</v>
+        <v>22.4</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>73.16</v>
+        <v>73.2</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-10.9</v>
+        <v>-16</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-16</v>
+        <v>-10.1</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>22.3</v>
+        <v>22.31</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>-10.1</v>
+        <v>-5.9</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>73.16</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>22.31</v>
+        <v>22.43</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-5.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
         <v>72.8</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>73.06999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>22.43</v>
+        <v>22.41</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>-9.9</v>
+        <v>-13.3</v>
       </c>
       <c r="G38" s="9" t="n">
         <v>68</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>73.11</v>
+        <v>73.06</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-13.3</v>
+        <v>-16.6</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
         <v>72.5</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>73.06</v>
+        <v>72.97</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>-16.6</v>
+        <v>-11.8</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>72.97</v>
+        <v>72.86</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>22.26</v>
+        <v>22.21</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-11.8</v>
+        <v>-21.1</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>72.86</v>
+        <v>72.8</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>-21.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>72.8</v>
+        <v>72.69</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>22.24</v>
+        <v>22.19</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-25.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>72.69</v>
+        <v>72.61</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>-18.3</v>
+        <v>-16</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-16</v>
+        <v>-10.4</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="n"/>
       <c r="C46" s="7" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="D46" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="D46" s="8" t="n"/>
       <c r="E46" s="7" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>-10.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B47" s="8" t="n"/>
       <c r="C47" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="D47" s="8" t="n"/>
       <c r="E47" s="7" t="n">
-        <v>21.85</v>
+        <v>21.7</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B48" s="8" t="n"/>
       <c r="C48" s="7" t="n">
-        <v>72.58</v>
+        <v>72.5</v>
       </c>
       <c r="D48" s="8" t="n"/>
       <c r="E48" s="7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>-12.3</v>
+        <v>-6.6</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B49" s="8" t="n"/>
       <c r="C49" s="7" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D49" s="8" t="n"/>
       <c r="E49" s="7" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B50" s="8" t="n"/>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C50" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D50" s="8" t="n"/>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="D50" s="8" t="n">
+        <v>21.2</v>
+      </c>
       <c r="E50" s="7" t="n">
-        <v>21.73</v>
+        <v>21.63</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>21.63</v>
+        <v>21.57</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="D52" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E52" s="7" t="n">
         <v>21.57</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>-7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>72.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D53" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E53" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E53" s="7" t="n">
-        <v>21.57</v>
-      </c>
       <c r="F53" s="8" t="n">
-        <v>-10.9</v>
+        <v>-7.7</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="n"/>
       <c r="C54" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D54" s="8" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D54" s="8" t="n"/>
       <c r="E54" s="7" t="n">
         <v>21.8</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.9</v>
       </c>
       <c r="G54" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B55" s="8" t="n"/>
@@ -4870,19 +4874,19 @@
         <v>21.8</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>-8.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B56" s="8" t="n"/>
@@ -4894,274 +4898,278 @@
         <v>21.8</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>-12.5</v>
+        <v>-11.2</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B57" s="8" t="n"/>
       <c r="C57" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>-11.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G57" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B58" s="8" t="n"/>
       <c r="C58" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="7" t="n">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>-13.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B59" s="8" t="n"/>
       <c r="C59" s="7" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="7" t="n">
-        <v>22.15</v>
+        <v>22.5</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="G59" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B60" s="8" t="n"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="C60" s="7" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="D60" s="8" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D60" s="8" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E60" s="7" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>-12.4</v>
+        <v>-7.8</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>20.5</v>
+        <v>20.95</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>-7.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B62" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C62" s="7" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>20.95</v>
+        <v>21.13</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>-3.1</v>
+        <v>-11.8</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B63" s="8" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>-11.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B64" s="8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="C64" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D64" s="8" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B65" s="8" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>72.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D65" s="8" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>-8.6</v>
+        <v>-13.5</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B66" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>21.33</v>
+        <v>21.43</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H66" s="10" t="n">
         <v>7.7</v>
@@ -5170,510 +5178,510 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B67" s="8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>72.23</v>
+        <v>72.39</v>
       </c>
       <c r="D67" s="8" t="n">
         <v>22</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>21.43</v>
+        <v>21.64</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>-7.1</v>
+        <v>-12.5</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B68" s="8" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C68" s="7" t="n">
         <v>72.39</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>21.64</v>
+        <v>21.69</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>-12.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B69" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>72.39</v>
+        <v>72.36</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>21.69</v>
+        <v>21.56</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>-6.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="n"/>
       <c r="C70" s="7" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="D70" s="8" t="n">
-        <v>20.6</v>
-      </c>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="D70" s="8" t="n"/>
       <c r="E70" s="7" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B71" s="8" t="n"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="C71" s="7" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="D71" s="8" t="n"/>
+        <v>72.45</v>
+      </c>
+      <c r="D71" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E71" s="7" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B72" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C72" s="7" t="n">
-        <v>72.45</v>
+        <v>72.47</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>21.67</v>
+        <v>21.53</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B73" s="8" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C73" s="7" t="n">
-        <v>72.47</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D73" s="8" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>21.53</v>
+        <v>21.47</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B74" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C74" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B75" s="8" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C75" s="7" t="n">
-        <v>72.31999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>-4.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B76" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>72.23</v>
+        <v>72.3</v>
       </c>
       <c r="D76" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>21.4</v>
+        <v>21.55</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>-1.6</v>
+        <v>-15.1</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B77" s="8" t="n">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="C77" s="7" t="n">
-        <v>72.3</v>
+        <v>72.37</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>21.55</v>
+        <v>21.69</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>-15.1</v>
+        <v>-10.3</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B78" s="8" t="n">
-        <v>72.8</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="n"/>
       <c r="C78" s="7" t="n">
-        <v>72.37</v>
-      </c>
-      <c r="D78" s="8" t="n">
-        <v>22.5</v>
-      </c>
+        <v>72.28</v>
+      </c>
+      <c r="D78" s="8" t="n"/>
       <c r="E78" s="7" t="n">
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>-10.3</v>
+        <v>-14.8</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>5.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B79" s="8" t="n"/>
       <c r="C79" s="7" t="n">
-        <v>72.28</v>
+        <v>72.3</v>
       </c>
       <c r="D79" s="8" t="n"/>
       <c r="E79" s="7" t="n">
-        <v>21.67</v>
+        <v>21.78</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>-14.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B80" s="8" t="n"/>
       <c r="C80" s="7" t="n">
-        <v>72.3</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="D80" s="8" t="n"/>
       <c r="E80" s="7" t="n">
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>-15.7</v>
+        <v>-15.4</v>
       </c>
       <c r="G80" s="9" t="n">
         <v>60</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B81" s="8" t="n"/>
       <c r="C81" s="7" t="n">
-        <v>72.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D81" s="8" t="n"/>
       <c r="E81" s="7" t="n">
-        <v>21.82</v>
+        <v>21.83</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>-15.4</v>
+        <v>-8.9</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B82" s="8" t="n"/>
       <c r="C82" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D82" s="8" t="n"/>
       <c r="E82" s="7" t="n">
-        <v>21.83</v>
+        <v>22</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>-8.9</v>
+        <v>-6.7</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B83" s="8" t="n"/>
       <c r="C83" s="7" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D83" s="8" t="n"/>
       <c r="E83" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>-6.7</v>
+        <v>-4.8</v>
       </c>
       <c r="G83" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B84" s="8" t="n"/>
-      <c r="C84" s="7" t="n">
-        <v>72.8</v>
-      </c>
+      <c r="C84" s="7" t="n"/>
       <c r="D84" s="8" t="n"/>
-      <c r="E84" s="7" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="E84" s="7" t="n"/>
       <c r="F84" s="8" t="n">
-        <v>-4.8</v>
+        <v>0.6</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B85" s="8" t="n"/>
-      <c r="C85" s="7" t="n"/>
-      <c r="D85" s="8" t="n"/>
-      <c r="E85" s="7" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="C85" s="7" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="D85" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E85" s="7" t="n">
+        <v>21.9</v>
+      </c>
       <c r="F85" s="8" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B86" s="8" t="n">
-        <v>73.2</v>
+        <v>72.8</v>
       </c>
       <c r="C86" s="7" t="n">
-        <v>73.2</v>
+        <v>73</v>
       </c>
       <c r="D86" s="8" t="n">
         <v>21.9</v>
@@ -5682,226 +5690,234 @@
         <v>21.9</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>3.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B87" s="8" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>73</v>
+        <v>72.97</v>
       </c>
       <c r="D87" s="8" t="n">
-        <v>21.9</v>
+        <v>21.3</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>-9.4</v>
+        <v>-6.9</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B88" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C88" s="7" t="n">
-        <v>72.97</v>
+        <v>72.88</v>
       </c>
       <c r="D88" s="8" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>-6.9</v>
+        <v>-3.2</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B89" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>72.88</v>
+        <v>73.08</v>
       </c>
       <c r="D89" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>21.5</v>
+        <v>21.38</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>-3.2</v>
+        <v>0.9</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B90" s="8" t="n">
-        <v>73.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C90" s="7" t="n">
-        <v>73.08</v>
+        <v>73</v>
       </c>
       <c r="D90" s="8" t="n">
-        <v>20.9</v>
+        <v>21.8</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>21.38</v>
+        <v>21.45</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="B91" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="n"/>
       <c r="C91" s="7" t="n">
         <v>73</v>
       </c>
-      <c r="D91" s="8" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="D91" s="8" t="n"/>
       <c r="E91" s="7" t="n">
         <v>21.45</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="B92" s="8" t="n"/>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="n">
+        <v>71.90000000000001</v>
+      </c>
       <c r="C92" s="7" t="n">
-        <v>73</v>
-      </c>
-      <c r="D92" s="8" t="n"/>
+        <v>72.78</v>
+      </c>
+      <c r="D92" s="8" t="n">
+        <v>20.7</v>
+      </c>
       <c r="E92" s="7" t="n">
-        <v>21.45</v>
+        <v>21.25</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B93" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>72.78</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="D93" s="8" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>21.25</v>
+        <v>21.2</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>4</v>
+        <v>-3.6</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>6.7</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="B94" s="8" t="n"/>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="n">
+        <v>71</v>
+      </c>
       <c r="C94" s="7" t="n">
-        <v>72.78</v>
-      </c>
-      <c r="D94" s="8" t="n"/>
+        <v>72.25</v>
+      </c>
+      <c r="D94" s="8" t="n">
+        <v>21.5</v>
+      </c>
       <c r="E94" s="7" t="n">
-        <v>21.12</v>
+        <v>21.23</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="G94" s="9" t="n"/>
-      <c r="H94" s="10" t="n"/>
+        <v>-1.7</v>
+      </c>
+      <c r="G94" s="9" t="n">
+        <v>62</v>
+      </c>
+      <c r="H94" s="10" t="n">
+        <v>8.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6361,16 +6377,16 @@
         <v>47</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>52.4</v>
+        <v>52.7</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>180</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>32</v>
+        <v>147</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>-148</v>
+        <v>-33</v>
       </c>
     </row>
     <row r="18">

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>71</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>68</v>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>16</v>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>4.71</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>52.7</v>
+        <v>50.9</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -3536,7 +3536,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B5" s="8" t="n">
@@ -3546,198 +3546,198 @@
         <v>74.5</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-1.8</v>
+        <v>-13.8</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n">
-        <v>74.5</v>
-      </c>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n"/>
       <c r="C6" s="7" t="n">
         <v>74.5</v>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="E6" s="7" t="n">
-        <v>22.5</v>
-      </c>
       <c r="F6" s="8" t="n">
-        <v>-13.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="H6" s="10" t="n">
-        <v>8.1</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n"/>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>74.40000000000001</v>
+      </c>
       <c r="C7" s="7" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="D7" s="8" t="n"/>
+        <v>74.45</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>23.3</v>
+      </c>
       <c r="E7" s="7" t="n">
-        <v>22.5</v>
+        <v>23.15</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-15.7</v>
+        <v>-10.5</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="H7" s="10" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n">
-        <v>74.40000000000001</v>
-      </c>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n"/>
       <c r="C8" s="7" t="n">
-        <v>74.47</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>23.3</v>
-      </c>
+        <v>74.45</v>
+      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="7" t="n">
-        <v>22.77</v>
+        <v>23.15</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>-10.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B9" s="8" t="n"/>
       <c r="C9" s="7" t="n">
-        <v>74.47</v>
+        <v>74.45</v>
       </c>
       <c r="D9" s="8" t="n"/>
       <c r="E9" s="7" t="n">
-        <v>22.77</v>
+        <v>23.15</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-9.4</v>
+        <v>-7.5</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n"/>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>74.5</v>
+      </c>
       <c r="C10" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="D10" s="8" t="n"/>
+      <c r="D10" s="8" t="n">
+        <v>22.9</v>
+      </c>
       <c r="E10" s="7" t="n">
-        <v>22.77</v>
+        <v>23.07</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>-7.5</v>
+        <v>-4.5</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>74.47</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.2</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>23</v>
+        <v>22.93</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>-2.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H12" s="10" t="n">
         <v>8</v>
@@ -3746,291 +3746,283 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>74.7</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>22.93</v>
+        <v>22.78</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>74.7</v>
+        <v>74.64</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>22.78</v>
+        <v>22.6</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>-11.9</v>
+        <v>-10.3</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>22.6</v>
+        <v>22.55</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-10.3</v>
+        <v>-13.7</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>74.65000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>22.55</v>
+        <v>22.57</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>-13.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="n">
-        <v>74.2</v>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n"/>
       <c r="C17" s="7" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>22.7</v>
-      </c>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D17" s="8" t="n"/>
       <c r="E17" s="7" t="n">
-        <v>22.57</v>
+        <v>22.52</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-15.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B18" s="8" t="n"/>
       <c r="C18" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.52</v>
       </c>
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="7" t="n">
-        <v>22.52</v>
+        <v>22.46</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B19" s="8" t="n"/>
       <c r="C19" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D19" s="8" t="n"/>
       <c r="E19" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-18.2</v>
+        <v>-23.1</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="7" t="n">
-        <v>74.42</v>
+        <v>74.33</v>
       </c>
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="7" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="7" t="n">
-        <v>74.33</v>
+        <v>74.45</v>
       </c>
       <c r="D21" s="8" t="n"/>
       <c r="E21" s="7" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-18.2</v>
+        <v>-19.5</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="7" t="n">
-        <v>74.45</v>
+        <v>74.2</v>
       </c>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-19.5</v>
+        <v>-26.4</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
-      <c r="C23" s="7" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="C23" s="7" t="n"/>
       <c r="D23" s="8" t="n"/>
-      <c r="E23" s="7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="E23" s="7" t="n"/>
       <c r="F23" s="8" t="n">
-        <v>-26.4</v>
+        <v>-19.9</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
@@ -4038,807 +4030,811 @@
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="8" t="n">
-        <v>-19.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="7" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>21.7</v>
+      </c>
       <c r="F25" s="8" t="n">
-        <v>-15.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>21.7</v>
+        <v>22.05</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-9.4</v>
+        <v>-12</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>73.2</v>
+        <v>73.33</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-12</v>
+        <v>-12.4</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-12.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>73.31999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D32" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>22.26</v>
+        <v>22.4</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>73.16</v>
+        <v>73.2</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-10.9</v>
+        <v>-16</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-16</v>
+        <v>-10.1</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>22.3</v>
+        <v>22.31</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-10.1</v>
+        <v>-5.9</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>73.16</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>22.31</v>
+        <v>22.43</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>-5.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
         <v>72.8</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>73.06999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>22.43</v>
+        <v>22.41</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-9.9</v>
+        <v>-13.3</v>
       </c>
       <c r="G37" s="9" t="n">
         <v>68</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>73.11</v>
+        <v>73.06</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>-13.3</v>
+        <v>-16.6</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
         <v>72.5</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>73.06</v>
+        <v>72.97</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-16.6</v>
+        <v>-11.8</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>72.97</v>
+        <v>72.86</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>22.26</v>
+        <v>22.21</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>-11.8</v>
+        <v>-21.1</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>72.86</v>
+        <v>72.8</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-21.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>72.8</v>
+        <v>72.69</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>22.24</v>
+        <v>22.19</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>-25.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>72.69</v>
+        <v>72.61</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-18.3</v>
+        <v>-16</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>-16</v>
+        <v>-10.4</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B45" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n"/>
       <c r="C45" s="7" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="D45" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="D45" s="8" t="n"/>
       <c r="E45" s="7" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-10.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B46" s="8" t="n"/>
       <c r="C46" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="D46" s="8" t="n"/>
       <c r="E46" s="7" t="n">
-        <v>21.85</v>
+        <v>21.7</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B47" s="8" t="n"/>
       <c r="C47" s="7" t="n">
-        <v>72.58</v>
+        <v>72.5</v>
       </c>
       <c r="D47" s="8" t="n"/>
       <c r="E47" s="7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-12.3</v>
+        <v>-6.6</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B48" s="8" t="n"/>
       <c r="C48" s="7" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D48" s="8" t="n"/>
       <c r="E48" s="7" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B49" s="8" t="n"/>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C49" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D49" s="8" t="n"/>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>21.2</v>
+      </c>
       <c r="E49" s="7" t="n">
-        <v>21.73</v>
+        <v>21.63</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>21.63</v>
+        <v>21.57</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E51" s="7" t="n">
         <v>21.57</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>72.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D52" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E52" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E52" s="7" t="n">
-        <v>21.57</v>
-      </c>
       <c r="F52" s="8" t="n">
-        <v>-10.9</v>
+        <v>-7.7</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B53" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="n"/>
       <c r="C53" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D53" s="8" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D53" s="8" t="n"/>
       <c r="E53" s="7" t="n">
         <v>21.8</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.9</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B54" s="8" t="n"/>
@@ -4850,19 +4846,19 @@
         <v>21.8</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>-8.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B55" s="8" t="n"/>
@@ -4874,274 +4870,278 @@
         <v>21.8</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>-12.5</v>
+        <v>-11.2</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B56" s="8" t="n"/>
       <c r="C56" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>-11.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G56" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B57" s="8" t="n"/>
       <c r="C57" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="7" t="n">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>-13.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B58" s="8" t="n"/>
       <c r="C58" s="7" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="7" t="n">
-        <v>22.15</v>
+        <v>22.5</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="G58" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B59" s="8" t="n"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="C59" s="7" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="D59" s="8" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D59" s="8" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E59" s="7" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>-12.4</v>
+        <v>-7.8</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B60" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C60" s="7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>20.5</v>
+        <v>20.95</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>-7.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>20.95</v>
+        <v>21.13</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>-3.1</v>
+        <v>-11.8</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B62" s="8" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C62" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>-11.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B63" s="8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B64" s="8" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C64" s="7" t="n">
-        <v>72.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D64" s="8" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>-8.6</v>
+        <v>-13.5</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B65" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="D65" s="8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>21.33</v>
+        <v>21.43</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H65" s="10" t="n">
         <v>7.7</v>
@@ -5150,510 +5150,510 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B66" s="8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>72.23</v>
+        <v>72.39</v>
       </c>
       <c r="D66" s="8" t="n">
         <v>22</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>21.43</v>
+        <v>21.64</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>-7.1</v>
+        <v>-12.5</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B67" s="8" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C67" s="7" t="n">
         <v>72.39</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>21.64</v>
+        <v>21.69</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>-12.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B68" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C68" s="7" t="n">
-        <v>72.39</v>
+        <v>72.36</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>21.69</v>
+        <v>21.56</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>-6.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B69" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="n"/>
       <c r="C69" s="7" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="D69" s="8" t="n">
-        <v>20.6</v>
-      </c>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="D69" s="8" t="n"/>
       <c r="E69" s="7" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="n"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="C70" s="7" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="D70" s="8" t="n"/>
+        <v>72.45</v>
+      </c>
+      <c r="D70" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E70" s="7" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>72.45</v>
+        <v>72.47</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>21.67</v>
+        <v>21.53</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B72" s="8" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C72" s="7" t="n">
-        <v>72.47</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>21.53</v>
+        <v>21.47</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B73" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C73" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D73" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B74" s="8" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C74" s="7" t="n">
-        <v>72.31999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>-4.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B75" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="C75" s="7" t="n">
-        <v>72.23</v>
+        <v>72.3</v>
       </c>
       <c r="D75" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>21.4</v>
+        <v>21.55</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>-1.6</v>
+        <v>-15.1</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B76" s="8" t="n">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>72.3</v>
+        <v>72.37</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>21.55</v>
+        <v>21.69</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>-15.1</v>
+        <v>-10.3</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B77" s="8" t="n">
-        <v>72.8</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="n"/>
       <c r="C77" s="7" t="n">
-        <v>72.37</v>
-      </c>
-      <c r="D77" s="8" t="n">
-        <v>22.5</v>
-      </c>
+        <v>72.28</v>
+      </c>
+      <c r="D77" s="8" t="n"/>
       <c r="E77" s="7" t="n">
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>-10.3</v>
+        <v>-14.8</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>5.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B78" s="8" t="n"/>
       <c r="C78" s="7" t="n">
-        <v>72.28</v>
+        <v>72.3</v>
       </c>
       <c r="D78" s="8" t="n"/>
       <c r="E78" s="7" t="n">
-        <v>21.67</v>
+        <v>21.78</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>-14.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B79" s="8" t="n"/>
       <c r="C79" s="7" t="n">
-        <v>72.3</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="D79" s="8" t="n"/>
       <c r="E79" s="7" t="n">
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>-15.7</v>
+        <v>-15.4</v>
       </c>
       <c r="G79" s="9" t="n">
         <v>60</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B80" s="8" t="n"/>
       <c r="C80" s="7" t="n">
-        <v>72.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D80" s="8" t="n"/>
       <c r="E80" s="7" t="n">
-        <v>21.82</v>
+        <v>21.83</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>-15.4</v>
+        <v>-8.9</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B81" s="8" t="n"/>
       <c r="C81" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D81" s="8" t="n"/>
       <c r="E81" s="7" t="n">
-        <v>21.83</v>
+        <v>22</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>-8.9</v>
+        <v>-6.7</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B82" s="8" t="n"/>
       <c r="C82" s="7" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D82" s="8" t="n"/>
       <c r="E82" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>-6.7</v>
+        <v>-4.8</v>
       </c>
       <c r="G82" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B83" s="8" t="n"/>
-      <c r="C83" s="7" t="n">
-        <v>72.8</v>
-      </c>
+      <c r="C83" s="7" t="n"/>
       <c r="D83" s="8" t="n"/>
-      <c r="E83" s="7" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="E83" s="7" t="n"/>
       <c r="F83" s="8" t="n">
-        <v>-4.8</v>
+        <v>0.6</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B84" s="8" t="n"/>
-      <c r="C84" s="7" t="n"/>
-      <c r="D84" s="8" t="n"/>
-      <c r="E84" s="7" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="C84" s="7" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="D84" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E84" s="7" t="n">
+        <v>21.9</v>
+      </c>
       <c r="F84" s="8" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B85" s="8" t="n">
-        <v>73.2</v>
+        <v>72.8</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>73.2</v>
+        <v>73</v>
       </c>
       <c r="D85" s="8" t="n">
         <v>21.9</v>
@@ -5662,261 +5662,261 @@
         <v>21.9</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>3.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B86" s="8" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C86" s="7" t="n">
-        <v>73</v>
+        <v>72.97</v>
       </c>
       <c r="D86" s="8" t="n">
-        <v>21.9</v>
+        <v>21.3</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>-9.4</v>
+        <v>-6.9</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B87" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>72.97</v>
+        <v>72.88</v>
       </c>
       <c r="D87" s="8" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>-6.9</v>
+        <v>-3.2</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B88" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="C88" s="7" t="n">
-        <v>72.88</v>
+        <v>73.08</v>
       </c>
       <c r="D88" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>21.5</v>
+        <v>21.38</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>-3.2</v>
+        <v>0.9</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B89" s="8" t="n">
-        <v>73.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>73.08</v>
+        <v>73</v>
       </c>
       <c r="D89" s="8" t="n">
-        <v>20.9</v>
+        <v>21.8</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>21.38</v>
+        <v>21.45</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="B90" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="n"/>
       <c r="C90" s="7" t="n">
         <v>73</v>
       </c>
-      <c r="D90" s="8" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="D90" s="8" t="n"/>
       <c r="E90" s="7" t="n">
         <v>21.45</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="B91" s="8" t="n"/>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="n">
+        <v>71.90000000000001</v>
+      </c>
       <c r="C91" s="7" t="n">
-        <v>73</v>
-      </c>
-      <c r="D91" s="8" t="n"/>
+        <v>72.78</v>
+      </c>
+      <c r="D91" s="8" t="n">
+        <v>20.7</v>
+      </c>
       <c r="E91" s="7" t="n">
-        <v>21.45</v>
+        <v>21.25</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B92" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="C92" s="7" t="n">
-        <v>72.78</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="D92" s="8" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>21.25</v>
+        <v>21.2</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>4</v>
+        <v>-3.6</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>6.7</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B93" s="8" t="n">
-        <v>71.5</v>
+        <v>71</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.25</v>
       </c>
       <c r="D93" s="8" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>-3.6</v>
+        <v>1</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B94" s="8" t="n">
-        <v>71</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="C94" s="7" t="n">
-        <v>72.25</v>
+        <v>72.08</v>
       </c>
       <c r="D94" s="8" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>21.23</v>
+        <v>21.38</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>-1.7</v>
+        <v>6.6</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="H94" s="10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -6377,16 +6377,16 @@
         <v>47</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>52.7</v>
+        <v>50.9</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>180</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>-33</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="18">

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>71.59999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>68</v>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>21.4</v>
+        <v>21.8</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>16</v>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3.88</v>
+        <v>3.83</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>4.71</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>50.9</v>
+        <v>50.2</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -782,12 +782,12 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Santini Stelvio Gran Fondo (lang rute)</t>
+          <t>CPH Half</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>2027-06-06</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -797,47 +797,71 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>130km / 4500hm</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Ja (2026-07-16)</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>B-løb. TILMELDT 16/7-2026 (med Eva). Hyggeløb + form-check mod TdS.</t>
-        </is>
-      </c>
+          <t>21.1km</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>Santini Stelvio Gran Fondo (lang rute)</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>2027-06-06</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>130km / 4500hm</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Ja (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>B-løb. TILMELDT 16/7-2026 (med Eva). Hyggeløb + form-check mod TdS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
           <t>Tour des Stations Ultrafondo</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>2027-08-28</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>242km / 8848hm</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Nej</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>A-løb. IKKE TILMELDT — 2027 åbner først ca. sep-26. Tjek 20/9. Cutoff 20:30 Croix-de-Cœur. Start 02:30 (18 t margin).</t>
         </is>
@@ -854,7 +878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -876,7 +900,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>14 uger fra 2026-06-01</t>
+          <t>16 uger fra 2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1328,6 +1352,68 @@
       <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Marathon du Médoc lør 5. sep. Ren taper + race-ernæringsplan. Tir: cykel i stedet for løb (ingen løb to dage i streg). Ons: 25 min styrke overkrop/core, ingen benbelastning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>RECOVERY</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>225</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Gentofte</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Restitution efter Marathon du Médoc. Intet løb før tidligst lør 12/9 — 42 km excentrisk belastning kræver 10-14 dage. Cykel bærer den aerobe base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>RACE</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>255</v>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Gentofte. RACE søn</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>CPH Half søn 20/9 — B-løb, mål sub 1:30 (4:16/km). Max 3 løb, ingen løb to dage i streg. Cut starter man 21/9, ikke før.</t>
         </is>
       </c>
     </row>
@@ -3536,180 +3622,176 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>23</v>
-      </c>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="7" t="n"/>
       <c r="F5" s="8" t="n">
-        <v>-13.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="H5" s="10" t="n">
-        <v>8.1</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n"/>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>74.40000000000001</v>
+      </c>
       <c r="C6" s="7" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="D6" s="8" t="n"/>
+        <v>74.40000000000001</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>23.3</v>
+      </c>
       <c r="E6" s="7" t="n">
-        <v>23</v>
+        <v>23.3</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>-15.7</v>
+        <v>-10.5</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="H6" s="10" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n">
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="7" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="C7" s="7" t="n">
-        <v>74.45</v>
-      </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="7" t="n">
         <v>23.3</v>
       </c>
-      <c r="E7" s="7" t="n">
-        <v>23.15</v>
-      </c>
       <c r="F7" s="8" t="n">
-        <v>-10.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
       <c r="C8" s="7" t="n">
-        <v>74.45</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D8" s="8" t="n"/>
       <c r="E8" s="7" t="n">
-        <v>23.15</v>
+        <v>23.3</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>-9.4</v>
+        <v>-7.5</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n"/>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>74.5</v>
+      </c>
       <c r="C9" s="7" t="n">
         <v>74.45</v>
       </c>
-      <c r="D9" s="8" t="n"/>
+      <c r="D9" s="8" t="n">
+        <v>22.9</v>
+      </c>
       <c r="E9" s="7" t="n">
-        <v>23.15</v>
+        <v>23.1</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-7.5</v>
+        <v>-4.5</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>74.47</v>
+        <v>74.63</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>23.07</v>
+        <v>23</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.2</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>23</v>
+        <v>22.93</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-2.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H11" s="10" t="n">
         <v>8</v>
@@ -3718,291 +3800,283 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>74.7</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>22.93</v>
+        <v>22.78</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>74.7</v>
+        <v>74.64</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>22.78</v>
+        <v>22.6</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-11.9</v>
+        <v>-10.3</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>22.6</v>
+        <v>22.55</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>-10.3</v>
+        <v>-13.7</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>74.65000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>22.55</v>
+        <v>22.57</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-13.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="n">
-        <v>74.2</v>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n"/>
       <c r="C16" s="7" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>22.7</v>
-      </c>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D16" s="8" t="n"/>
       <c r="E16" s="7" t="n">
-        <v>22.57</v>
+        <v>22.52</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>-15.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B17" s="8" t="n"/>
       <c r="C17" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.52</v>
       </c>
       <c r="D17" s="8" t="n"/>
       <c r="E17" s="7" t="n">
-        <v>22.52</v>
+        <v>22.46</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B18" s="8" t="n"/>
       <c r="C18" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>-18.2</v>
+        <v>-23.1</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B19" s="8" t="n"/>
       <c r="C19" s="7" t="n">
-        <v>74.42</v>
+        <v>74.33</v>
       </c>
       <c r="D19" s="8" t="n"/>
       <c r="E19" s="7" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="7" t="n">
-        <v>74.33</v>
+        <v>74.45</v>
       </c>
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="7" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>-18.2</v>
+        <v>-19.5</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="7" t="n">
-        <v>74.45</v>
+        <v>74.2</v>
       </c>
       <c r="D21" s="8" t="n"/>
       <c r="E21" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-19.5</v>
+        <v>-26.4</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
-      <c r="C22" s="7" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="C22" s="7" t="n"/>
       <c r="D22" s="8" t="n"/>
-      <c r="E22" s="7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="E22" s="7" t="n"/>
       <c r="F22" s="8" t="n">
-        <v>-26.4</v>
+        <v>-19.9</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
@@ -4010,807 +4084,811 @@
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="8" t="n">
-        <v>-19.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="7" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>21.7</v>
+      </c>
       <c r="F24" s="8" t="n">
-        <v>-15.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>21.7</v>
+        <v>22.05</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-9.4</v>
+        <v>-12</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>73.2</v>
+        <v>73.33</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-12</v>
+        <v>-12.4</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-12.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>73.31999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D31" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>22.26</v>
+        <v>22.4</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>73.16</v>
+        <v>73.2</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-10.9</v>
+        <v>-16</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-16</v>
+        <v>-10.1</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>22.3</v>
+        <v>22.31</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-10.1</v>
+        <v>-5.9</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>73.16</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>22.31</v>
+        <v>22.43</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-5.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
         <v>72.8</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>73.06999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>22.43</v>
+        <v>22.41</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>-9.9</v>
+        <v>-13.3</v>
       </c>
       <c r="G36" s="9" t="n">
         <v>68</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>73.11</v>
+        <v>73.06</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-13.3</v>
+        <v>-16.6</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
         <v>72.5</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>73.06</v>
+        <v>72.97</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>-16.6</v>
+        <v>-11.8</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>72.97</v>
+        <v>72.86</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>22.26</v>
+        <v>22.21</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-11.8</v>
+        <v>-21.1</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>72.86</v>
+        <v>72.8</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>-21.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>72.8</v>
+        <v>72.69</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>22.24</v>
+        <v>22.19</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-25.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>72.69</v>
+        <v>72.61</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>-18.3</v>
+        <v>-16</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-16</v>
+        <v>-10.4</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="n"/>
       <c r="C44" s="7" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="D44" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="D44" s="8" t="n"/>
       <c r="E44" s="7" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>-10.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B45" s="8" t="n"/>
       <c r="C45" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="D45" s="8" t="n"/>
       <c r="E45" s="7" t="n">
-        <v>21.85</v>
+        <v>21.7</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B46" s="8" t="n"/>
       <c r="C46" s="7" t="n">
-        <v>72.58</v>
+        <v>72.5</v>
       </c>
       <c r="D46" s="8" t="n"/>
       <c r="E46" s="7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>-12.3</v>
+        <v>-6.6</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B47" s="8" t="n"/>
       <c r="C47" s="7" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D47" s="8" t="n"/>
       <c r="E47" s="7" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B48" s="8" t="n"/>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C48" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D48" s="8" t="n"/>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>21.2</v>
+      </c>
       <c r="E48" s="7" t="n">
-        <v>21.73</v>
+        <v>21.63</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>21.63</v>
+        <v>21.57</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E50" s="7" t="n">
         <v>21.57</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>-7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>72.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D51" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E51" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E51" s="7" t="n">
-        <v>21.57</v>
-      </c>
       <c r="F51" s="8" t="n">
-        <v>-10.9</v>
+        <v>-7.7</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="n"/>
       <c r="C52" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D52" s="8" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D52" s="8" t="n"/>
       <c r="E52" s="7" t="n">
         <v>21.8</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.9</v>
       </c>
       <c r="G52" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B53" s="8" t="n"/>
@@ -4822,19 +4900,19 @@
         <v>21.8</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-8.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B54" s="8" t="n"/>
@@ -4846,274 +4924,278 @@
         <v>21.8</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>-12.5</v>
+        <v>-11.2</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B55" s="8" t="n"/>
       <c r="C55" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>-11.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G55" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B56" s="8" t="n"/>
       <c r="C56" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="7" t="n">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>-13.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B57" s="8" t="n"/>
       <c r="C57" s="7" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="7" t="n">
-        <v>22.15</v>
+        <v>22.5</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="G57" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B58" s="8" t="n"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="C58" s="7" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="D58" s="8" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D58" s="8" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E58" s="7" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>-12.4</v>
+        <v>-7.8</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>20.5</v>
+        <v>20.95</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>-7.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B60" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C60" s="7" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>20.95</v>
+        <v>21.13</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>-3.1</v>
+        <v>-11.8</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>-11.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B62" s="8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="C62" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B63" s="8" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>72.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>-8.6</v>
+        <v>-13.5</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B64" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C64" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="D64" s="8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>21.33</v>
+        <v>21.43</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H64" s="10" t="n">
         <v>7.7</v>
@@ -5122,510 +5204,510 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B65" s="8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>72.23</v>
+        <v>72.39</v>
       </c>
       <c r="D65" s="8" t="n">
         <v>22</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>21.43</v>
+        <v>21.64</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>-7.1</v>
+        <v>-12.5</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B66" s="8" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C66" s="7" t="n">
         <v>72.39</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>21.64</v>
+        <v>21.69</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>-12.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B67" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>72.39</v>
+        <v>72.36</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>21.69</v>
+        <v>21.56</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>-6.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="n"/>
       <c r="C68" s="7" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="D68" s="8" t="n">
-        <v>20.6</v>
-      </c>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="D68" s="8" t="n"/>
       <c r="E68" s="7" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B69" s="8" t="n"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="C69" s="7" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="D69" s="8" t="n"/>
+        <v>72.45</v>
+      </c>
+      <c r="D69" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E69" s="7" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C70" s="7" t="n">
-        <v>72.45</v>
+        <v>72.47</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>21.67</v>
+        <v>21.53</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>72.47</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>21.53</v>
+        <v>21.47</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B72" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C72" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B73" s="8" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C73" s="7" t="n">
-        <v>72.31999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="D73" s="8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>-4.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B74" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="C74" s="7" t="n">
-        <v>72.23</v>
+        <v>72.3</v>
       </c>
       <c r="D74" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>21.4</v>
+        <v>21.55</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>-1.6</v>
+        <v>-15.1</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B75" s="8" t="n">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="C75" s="7" t="n">
-        <v>72.3</v>
+        <v>72.37</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>21.55</v>
+        <v>21.69</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>-15.1</v>
+        <v>-10.3</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B76" s="8" t="n">
-        <v>72.8</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="n"/>
       <c r="C76" s="7" t="n">
-        <v>72.37</v>
-      </c>
-      <c r="D76" s="8" t="n">
-        <v>22.5</v>
-      </c>
+        <v>72.28</v>
+      </c>
+      <c r="D76" s="8" t="n"/>
       <c r="E76" s="7" t="n">
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>-10.3</v>
+        <v>-14.8</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>5.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B77" s="8" t="n"/>
       <c r="C77" s="7" t="n">
-        <v>72.28</v>
+        <v>72.3</v>
       </c>
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="7" t="n">
-        <v>21.67</v>
+        <v>21.78</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>-14.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B78" s="8" t="n"/>
       <c r="C78" s="7" t="n">
-        <v>72.3</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="D78" s="8" t="n"/>
       <c r="E78" s="7" t="n">
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>-15.7</v>
+        <v>-15.4</v>
       </c>
       <c r="G78" s="9" t="n">
         <v>60</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B79" s="8" t="n"/>
       <c r="C79" s="7" t="n">
-        <v>72.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D79" s="8" t="n"/>
       <c r="E79" s="7" t="n">
-        <v>21.82</v>
+        <v>21.83</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>-15.4</v>
+        <v>-8.9</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B80" s="8" t="n"/>
       <c r="C80" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D80" s="8" t="n"/>
       <c r="E80" s="7" t="n">
-        <v>21.83</v>
+        <v>22</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>-8.9</v>
+        <v>-6.7</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B81" s="8" t="n"/>
       <c r="C81" s="7" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D81" s="8" t="n"/>
       <c r="E81" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>-6.7</v>
+        <v>-4.8</v>
       </c>
       <c r="G81" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B82" s="8" t="n"/>
-      <c r="C82" s="7" t="n">
-        <v>72.8</v>
-      </c>
+      <c r="C82" s="7" t="n"/>
       <c r="D82" s="8" t="n"/>
-      <c r="E82" s="7" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="E82" s="7" t="n"/>
       <c r="F82" s="8" t="n">
-        <v>-4.8</v>
+        <v>0.6</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B83" s="8" t="n"/>
-      <c r="C83" s="7" t="n"/>
-      <c r="D83" s="8" t="n"/>
-      <c r="E83" s="7" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="C83" s="7" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="D83" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E83" s="7" t="n">
+        <v>21.9</v>
+      </c>
       <c r="F83" s="8" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B84" s="8" t="n">
-        <v>73.2</v>
+        <v>72.8</v>
       </c>
       <c r="C84" s="7" t="n">
-        <v>73.2</v>
+        <v>73</v>
       </c>
       <c r="D84" s="8" t="n">
         <v>21.9</v>
@@ -5634,289 +5716,289 @@
         <v>21.9</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>3.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B85" s="8" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>73</v>
+        <v>72.97</v>
       </c>
       <c r="D85" s="8" t="n">
-        <v>21.9</v>
+        <v>21.3</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>-9.4</v>
+        <v>-6.9</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B86" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C86" s="7" t="n">
-        <v>72.97</v>
+        <v>72.88</v>
       </c>
       <c r="D86" s="8" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>-6.9</v>
+        <v>-3.2</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B87" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>72.88</v>
+        <v>73.08</v>
       </c>
       <c r="D87" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>21.5</v>
+        <v>21.38</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>-3.2</v>
+        <v>0.9</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B88" s="8" t="n">
-        <v>73.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C88" s="7" t="n">
-        <v>73.08</v>
+        <v>73</v>
       </c>
       <c r="D88" s="8" t="n">
-        <v>20.9</v>
+        <v>21.8</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>21.38</v>
+        <v>21.45</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="B89" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="n"/>
       <c r="C89" s="7" t="n">
         <v>73</v>
       </c>
-      <c r="D89" s="8" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="D89" s="8" t="n"/>
       <c r="E89" s="7" t="n">
         <v>21.45</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="B90" s="8" t="n"/>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="n">
+        <v>71.90000000000001</v>
+      </c>
       <c r="C90" s="7" t="n">
-        <v>73</v>
-      </c>
-      <c r="D90" s="8" t="n"/>
+        <v>72.78</v>
+      </c>
+      <c r="D90" s="8" t="n">
+        <v>20.7</v>
+      </c>
       <c r="E90" s="7" t="n">
-        <v>21.45</v>
+        <v>21.25</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B91" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>72.78</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="D91" s="8" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>21.25</v>
+        <v>21.2</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>4</v>
+        <v>-3.6</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>6.7</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B92" s="8" t="n">
-        <v>71.5</v>
+        <v>71</v>
       </c>
       <c r="C92" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.25</v>
       </c>
       <c r="D92" s="8" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>-3.6</v>
+        <v>1</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B93" s="8" t="n">
-        <v>71</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>72.25</v>
+        <v>72.08</v>
       </c>
       <c r="D93" s="8" t="n">
-        <v>21.9</v>
+        <v>21.4</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>21.3</v>
+        <v>21.38</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>1</v>
+        <v>5.9</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B94" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C94" s="7" t="n">
-        <v>72.08</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="D94" s="8" t="n">
-        <v>21.4</v>
+        <v>21.8</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>21.38</v>
+        <v>21.53</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>6.6</v>
+        <v>7.7</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="H94" s="10" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -5930,7 +6012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6377,16 +6459,16 @@
         <v>47</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>50.9</v>
+        <v>50.2</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>180</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>-18</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="18">
@@ -6412,6 +6494,54 @@
       </c>
       <c r="G18" s="4" t="n"/>
       <c r="H18" s="11" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>RECOVERY</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="4" t="n">
+        <v>225</v>
+      </c>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="11" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>RACE</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="4" t="n">
+        <v>255</v>
+      </c>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -1342,7 +1342,7 @@
         <v>43</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>40</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>225</v>
+        <v>265</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>41</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>255</v>
+        <v>336</v>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="4" t="n">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="G18" s="4" t="n"/>
       <c r="H18" s="11" t="n"/>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="4" t="n">
-        <v>225</v>
+        <v>265</v>
       </c>
       <c r="G19" s="4" t="n"/>
       <c r="H19" s="11" t="n"/>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="4" t="n">
-        <v>255</v>
+        <v>336</v>
       </c>
       <c r="G20" s="4" t="n"/>
       <c r="H20" s="11" t="n"/>

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>68</v>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>21.8</v>
+        <v>20.8</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>16</v>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>4.71</v>
@@ -5980,16 +5980,16 @@
         </is>
       </c>
       <c r="B94" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C94" s="7" t="n">
-        <v>71.84999999999999</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="D94" s="8" t="n">
-        <v>21.8</v>
+        <v>20.8</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>21.53</v>
+        <v>21.37</v>
       </c>
       <c r="F94" s="8" t="n">
         <v>7.7</v>

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>72.3</v>
+        <v>72.5</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>68</v>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>20.8</v>
+        <v>21.6</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>16</v>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>4.71</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -3622,53 +3622,59 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="7" t="n"/>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>23.3</v>
+      </c>
       <c r="F5" s="8" t="n">
-        <v>-15.7</v>
+        <v>-10.5</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="H5" s="10" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n">
-        <v>74.40000000000001</v>
-      </c>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n"/>
       <c r="C6" s="7" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="D6" s="8" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="D6" s="8" t="n"/>
       <c r="E6" s="7" t="n">
         <v>23.3</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>-10.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
@@ -3680,90 +3686,94 @@
         <v>23.3</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-9.4</v>
+        <v>-7.5</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n"/>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>74.5</v>
+      </c>
       <c r="C8" s="7" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="D8" s="8" t="n"/>
+        <v>74.45</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>22.9</v>
+      </c>
       <c r="E8" s="7" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>-7.5</v>
+        <v>-4.5</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>74.45</v>
+        <v>74.63</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.2</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>74.63</v>
+        <v>74.7</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>23</v>
+        <v>22.93</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>-2.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H10" s="10" t="n">
         <v>8</v>
@@ -3772,291 +3782,283 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>74.7</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>22.93</v>
+        <v>22.78</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>74.7</v>
+        <v>74.64</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>22.78</v>
+        <v>22.6</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>-11.9</v>
+        <v>-10.3</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>22.6</v>
+        <v>22.55</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-10.3</v>
+        <v>-13.7</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>74.65000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>22.55</v>
+        <v>22.57</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>-13.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="n">
-        <v>74.2</v>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n"/>
       <c r="C15" s="7" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>22.7</v>
-      </c>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D15" s="8" t="n"/>
       <c r="E15" s="7" t="n">
-        <v>22.57</v>
+        <v>22.52</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-15.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B16" s="8" t="n"/>
       <c r="C16" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.52</v>
       </c>
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="7" t="n">
-        <v>22.52</v>
+        <v>22.46</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B17" s="8" t="n"/>
       <c r="C17" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D17" s="8" t="n"/>
       <c r="E17" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-18.2</v>
+        <v>-23.1</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B18" s="8" t="n"/>
       <c r="C18" s="7" t="n">
-        <v>74.42</v>
+        <v>74.33</v>
       </c>
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="7" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B19" s="8" t="n"/>
       <c r="C19" s="7" t="n">
-        <v>74.33</v>
+        <v>74.45</v>
       </c>
       <c r="D19" s="8" t="n"/>
       <c r="E19" s="7" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-18.2</v>
+        <v>-19.5</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="7" t="n">
-        <v>74.45</v>
+        <v>74.2</v>
       </c>
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>-19.5</v>
+        <v>-26.4</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="7" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="C21" s="7" t="n"/>
       <c r="D21" s="8" t="n"/>
-      <c r="E21" s="7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="E21" s="7" t="n"/>
       <c r="F21" s="8" t="n">
-        <v>-26.4</v>
+        <v>-19.9</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
@@ -4064,807 +4066,811 @@
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="8" t="n">
-        <v>-19.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="7" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>21.7</v>
+      </c>
       <c r="F23" s="8" t="n">
-        <v>-15.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>21.7</v>
+        <v>22.05</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>-9.4</v>
+        <v>-12</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>73.2</v>
+        <v>73.33</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-12</v>
+        <v>-12.4</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-12.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>73.31999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D30" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>22.26</v>
+        <v>22.4</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>73.16</v>
+        <v>73.2</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-10.9</v>
+        <v>-16</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-16</v>
+        <v>-10.1</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>22.3</v>
+        <v>22.31</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-10.1</v>
+        <v>-5.9</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>73.16</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>22.31</v>
+        <v>22.43</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-5.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
         <v>72.8</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>73.06999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>22.43</v>
+        <v>22.41</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-9.9</v>
+        <v>-13.3</v>
       </c>
       <c r="G35" s="9" t="n">
         <v>68</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>73.11</v>
+        <v>73.06</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>-13.3</v>
+        <v>-16.6</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
         <v>72.5</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>73.06</v>
+        <v>72.97</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-16.6</v>
+        <v>-11.8</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>72.97</v>
+        <v>72.86</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>22.26</v>
+        <v>22.21</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>-11.8</v>
+        <v>-21.1</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>72.86</v>
+        <v>72.8</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-21.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>72.8</v>
+        <v>72.69</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>22.24</v>
+        <v>22.19</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>-25.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>72.69</v>
+        <v>72.61</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-18.3</v>
+        <v>-16</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>-16</v>
+        <v>-10.4</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B43" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n"/>
       <c r="C43" s="7" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="D43" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="D43" s="8" t="n"/>
       <c r="E43" s="7" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-10.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B44" s="8" t="n"/>
       <c r="C44" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="D44" s="8" t="n"/>
       <c r="E44" s="7" t="n">
-        <v>21.85</v>
+        <v>21.7</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B45" s="8" t="n"/>
       <c r="C45" s="7" t="n">
-        <v>72.58</v>
+        <v>72.5</v>
       </c>
       <c r="D45" s="8" t="n"/>
       <c r="E45" s="7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-12.3</v>
+        <v>-6.6</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B46" s="8" t="n"/>
       <c r="C46" s="7" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D46" s="8" t="n"/>
       <c r="E46" s="7" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B47" s="8" t="n"/>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C47" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D47" s="8" t="n"/>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>21.2</v>
+      </c>
       <c r="E47" s="7" t="n">
-        <v>21.73</v>
+        <v>21.63</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>21.63</v>
+        <v>21.57</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E49" s="7" t="n">
         <v>21.57</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>72.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D50" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E50" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E50" s="7" t="n">
-        <v>21.57</v>
-      </c>
       <c r="F50" s="8" t="n">
-        <v>-10.9</v>
+        <v>-7.7</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B51" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n"/>
       <c r="C51" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D51" s="8" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D51" s="8" t="n"/>
       <c r="E51" s="7" t="n">
         <v>21.8</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.9</v>
       </c>
       <c r="G51" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B52" s="8" t="n"/>
@@ -4876,19 +4882,19 @@
         <v>21.8</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>-8.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B53" s="8" t="n"/>
@@ -4900,274 +4906,278 @@
         <v>21.8</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-12.5</v>
+        <v>-11.2</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B54" s="8" t="n"/>
       <c r="C54" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="D54" s="8" t="n"/>
       <c r="E54" s="7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>-11.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G54" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B55" s="8" t="n"/>
       <c r="C55" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="7" t="n">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>-13.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B56" s="8" t="n"/>
       <c r="C56" s="7" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="7" t="n">
-        <v>22.15</v>
+        <v>22.5</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="G56" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="n"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="C57" s="7" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="D57" s="8" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E57" s="7" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>-12.4</v>
+        <v>-7.8</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C58" s="7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>20.5</v>
+        <v>20.95</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>-7.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>20.95</v>
+        <v>21.13</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>-3.1</v>
+        <v>-11.8</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B60" s="8" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C60" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>-11.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B62" s="8" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C62" s="7" t="n">
-        <v>72.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>-8.6</v>
+        <v>-13.5</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B63" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>21.33</v>
+        <v>21.43</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H63" s="10" t="n">
         <v>7.7</v>
@@ -5176,510 +5186,510 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B64" s="8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="C64" s="7" t="n">
-        <v>72.23</v>
+        <v>72.39</v>
       </c>
       <c r="D64" s="8" t="n">
         <v>22</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>21.43</v>
+        <v>21.64</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>-7.1</v>
+        <v>-12.5</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B65" s="8" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C65" s="7" t="n">
         <v>72.39</v>
       </c>
       <c r="D65" s="8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>21.64</v>
+        <v>21.69</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>-12.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B66" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>72.39</v>
+        <v>72.36</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>21.69</v>
+        <v>21.56</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>-6.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="n"/>
       <c r="C67" s="7" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="D67" s="8" t="n">
-        <v>20.6</v>
-      </c>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="D67" s="8" t="n"/>
       <c r="E67" s="7" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="n"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="C68" s="7" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="D68" s="8" t="n"/>
+        <v>72.45</v>
+      </c>
+      <c r="D68" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E68" s="7" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B69" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>72.45</v>
+        <v>72.47</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>21.67</v>
+        <v>21.53</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C70" s="7" t="n">
-        <v>72.47</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>21.53</v>
+        <v>21.47</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B72" s="8" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C72" s="7" t="n">
-        <v>72.31999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>-4.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B73" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="C73" s="7" t="n">
-        <v>72.23</v>
+        <v>72.3</v>
       </c>
       <c r="D73" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>21.4</v>
+        <v>21.55</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>-1.6</v>
+        <v>-15.1</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B74" s="8" t="n">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="C74" s="7" t="n">
-        <v>72.3</v>
+        <v>72.37</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>21.55</v>
+        <v>21.69</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>-15.1</v>
+        <v>-10.3</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B75" s="8" t="n">
-        <v>72.8</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="n"/>
       <c r="C75" s="7" t="n">
-        <v>72.37</v>
-      </c>
-      <c r="D75" s="8" t="n">
-        <v>22.5</v>
-      </c>
+        <v>72.28</v>
+      </c>
+      <c r="D75" s="8" t="n"/>
       <c r="E75" s="7" t="n">
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>-10.3</v>
+        <v>-14.8</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>5.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B76" s="8" t="n"/>
       <c r="C76" s="7" t="n">
-        <v>72.28</v>
+        <v>72.3</v>
       </c>
       <c r="D76" s="8" t="n"/>
       <c r="E76" s="7" t="n">
-        <v>21.67</v>
+        <v>21.78</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>-14.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B77" s="8" t="n"/>
       <c r="C77" s="7" t="n">
-        <v>72.3</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="7" t="n">
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>-15.7</v>
+        <v>-15.4</v>
       </c>
       <c r="G77" s="9" t="n">
         <v>60</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B78" s="8" t="n"/>
       <c r="C78" s="7" t="n">
-        <v>72.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D78" s="8" t="n"/>
       <c r="E78" s="7" t="n">
-        <v>21.82</v>
+        <v>21.83</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>-15.4</v>
+        <v>-8.9</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B79" s="8" t="n"/>
       <c r="C79" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D79" s="8" t="n"/>
       <c r="E79" s="7" t="n">
-        <v>21.83</v>
+        <v>22</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>-8.9</v>
+        <v>-6.7</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B80" s="8" t="n"/>
       <c r="C80" s="7" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D80" s="8" t="n"/>
       <c r="E80" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>-6.7</v>
+        <v>-4.8</v>
       </c>
       <c r="G80" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B81" s="8" t="n"/>
-      <c r="C81" s="7" t="n">
-        <v>72.8</v>
-      </c>
+      <c r="C81" s="7" t="n"/>
       <c r="D81" s="8" t="n"/>
-      <c r="E81" s="7" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="E81" s="7" t="n"/>
       <c r="F81" s="8" t="n">
-        <v>-4.8</v>
+        <v>0.6</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B82" s="8" t="n"/>
-      <c r="C82" s="7" t="n"/>
-      <c r="D82" s="8" t="n"/>
-      <c r="E82" s="7" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="C82" s="7" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="D82" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E82" s="7" t="n">
+        <v>21.9</v>
+      </c>
       <c r="F82" s="8" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B83" s="8" t="n">
-        <v>73.2</v>
+        <v>72.8</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>73.2</v>
+        <v>73</v>
       </c>
       <c r="D83" s="8" t="n">
         <v>21.9</v>
@@ -5688,317 +5698,317 @@
         <v>21.9</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>3.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B84" s="8" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C84" s="7" t="n">
-        <v>73</v>
+        <v>72.97</v>
       </c>
       <c r="D84" s="8" t="n">
-        <v>21.9</v>
+        <v>21.3</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>-9.4</v>
+        <v>-6.9</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B85" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>72.97</v>
+        <v>72.88</v>
       </c>
       <c r="D85" s="8" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>-6.9</v>
+        <v>-3.2</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B86" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="C86" s="7" t="n">
-        <v>72.88</v>
+        <v>73.08</v>
       </c>
       <c r="D86" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>21.5</v>
+        <v>21.38</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>-3.2</v>
+        <v>0.9</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B87" s="8" t="n">
-        <v>73.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>73.08</v>
+        <v>73</v>
       </c>
       <c r="D87" s="8" t="n">
-        <v>20.9</v>
+        <v>21.8</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>21.38</v>
+        <v>21.45</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="B88" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="n"/>
       <c r="C88" s="7" t="n">
         <v>73</v>
       </c>
-      <c r="D88" s="8" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="D88" s="8" t="n"/>
       <c r="E88" s="7" t="n">
         <v>21.45</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="B89" s="8" t="n"/>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="n">
+        <v>71.90000000000001</v>
+      </c>
       <c r="C89" s="7" t="n">
-        <v>73</v>
-      </c>
-      <c r="D89" s="8" t="n"/>
+        <v>72.78</v>
+      </c>
+      <c r="D89" s="8" t="n">
+        <v>20.7</v>
+      </c>
       <c r="E89" s="7" t="n">
-        <v>21.45</v>
+        <v>21.25</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B90" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="C90" s="7" t="n">
-        <v>72.78</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="D90" s="8" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>21.25</v>
+        <v>21.2</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>4</v>
+        <v>-3.6</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>6.7</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B91" s="8" t="n">
-        <v>71.5</v>
+        <v>71</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.25</v>
       </c>
       <c r="D91" s="8" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>-3.6</v>
+        <v>1</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B92" s="8" t="n">
-        <v>71</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="C92" s="7" t="n">
-        <v>72.25</v>
+        <v>72.08</v>
       </c>
       <c r="D92" s="8" t="n">
-        <v>21.9</v>
+        <v>21.4</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>21.3</v>
+        <v>21.38</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>1</v>
+        <v>5.9</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B93" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>72.08</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="D93" s="8" t="n">
-        <v>21.4</v>
+        <v>20.8</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>21.38</v>
+        <v>21.37</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>5.9</v>
+        <v>9.5</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B94" s="8" t="n">
-        <v>72.3</v>
+        <v>72.5</v>
       </c>
       <c r="C94" s="7" t="n">
-        <v>71.81999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="D94" s="8" t="n">
-        <v>20.8</v>
+        <v>21.6</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>21.37</v>
+        <v>21.33</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>7.7</v>
+        <v>6</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="H94" s="10" t="n">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -6459,16 +6469,16 @@
         <v>47</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>180</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>177</v>
+        <v>248</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>-3</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18">

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>72.5</v>
+        <v>73</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>68</v>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>21.6</v>
+        <v>22.1</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>16</v>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>4.71</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>50.3</v>
+        <v>50.7</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -3622,130 +3622,122 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>23.3</v>
-      </c>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="7" t="n"/>
       <c r="F5" s="8" t="n">
-        <v>-10.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
-      <c r="C6" s="7" t="n">
-        <v>74.40000000000001</v>
-      </c>
+      <c r="C6" s="7" t="n"/>
       <c r="D6" s="8" t="n"/>
-      <c r="E6" s="7" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="E6" s="7" t="n"/>
       <c r="F6" s="8" t="n">
-        <v>-9.4</v>
+        <v>-7.5</v>
       </c>
       <c r="G6" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n"/>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>74.5</v>
+      </c>
       <c r="C7" s="7" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="D7" s="8" t="n"/>
+        <v>74.5</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>22.9</v>
+      </c>
       <c r="E7" s="7" t="n">
-        <v>23.3</v>
+        <v>22.9</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-7.5</v>
+        <v>-4.5</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>74.45</v>
+        <v>74.75</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>23.1</v>
+        <v>22.85</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.2</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>74.63</v>
+        <v>74.8</v>
       </c>
       <c r="D9" s="8" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="E9" s="7" t="n">
         <v>22.8</v>
       </c>
-      <c r="E9" s="7" t="n">
-        <v>23</v>
-      </c>
       <c r="F9" s="8" t="n">
-        <v>-2.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H9" s="10" t="n">
         <v>8</v>
@@ -3754,291 +3746,283 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>74.7</v>
+        <v>74.78</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>22.93</v>
+        <v>22.65</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>74.7</v>
+        <v>74.64</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>22.78</v>
+        <v>22.6</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-11.9</v>
+        <v>-10.3</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>22.6</v>
+        <v>22.55</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>-10.3</v>
+        <v>-13.7</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>74.65000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>22.55</v>
+        <v>22.57</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-13.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n">
-        <v>74.2</v>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n"/>
       <c r="C14" s="7" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>22.7</v>
-      </c>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D14" s="8" t="n"/>
       <c r="E14" s="7" t="n">
-        <v>22.57</v>
+        <v>22.52</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>-15.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.52</v>
       </c>
       <c r="D15" s="8" t="n"/>
       <c r="E15" s="7" t="n">
-        <v>22.52</v>
+        <v>22.46</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B16" s="8" t="n"/>
       <c r="C16" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>-18.2</v>
+        <v>-23.1</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B17" s="8" t="n"/>
       <c r="C17" s="7" t="n">
-        <v>74.42</v>
+        <v>74.33</v>
       </c>
       <c r="D17" s="8" t="n"/>
       <c r="E17" s="7" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B18" s="8" t="n"/>
       <c r="C18" s="7" t="n">
-        <v>74.33</v>
+        <v>74.45</v>
       </c>
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="7" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>-18.2</v>
+        <v>-19.5</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B19" s="8" t="n"/>
       <c r="C19" s="7" t="n">
-        <v>74.45</v>
+        <v>74.2</v>
       </c>
       <c r="D19" s="8" t="n"/>
       <c r="E19" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-19.5</v>
+        <v>-26.4</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B20" s="8" t="n"/>
-      <c r="C20" s="7" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="C20" s="7" t="n"/>
       <c r="D20" s="8" t="n"/>
-      <c r="E20" s="7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="E20" s="7" t="n"/>
       <c r="F20" s="8" t="n">
-        <v>-26.4</v>
+        <v>-19.9</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
@@ -4046,807 +4030,811 @@
       <c r="D21" s="8" t="n"/>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="8" t="n">
-        <v>-19.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="7" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>21.7</v>
+      </c>
       <c r="F22" s="8" t="n">
-        <v>-15.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>21.7</v>
+        <v>22.05</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-9.4</v>
+        <v>-12</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>73.2</v>
+        <v>73.33</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>-12</v>
+        <v>-12.4</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-12.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>73.31999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D29" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>22.26</v>
+        <v>22.4</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>73.16</v>
+        <v>73.2</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-10.9</v>
+        <v>-16</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-16</v>
+        <v>-10.1</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>22.3</v>
+        <v>22.31</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-10.1</v>
+        <v>-5.9</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>73.16</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>22.31</v>
+        <v>22.43</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-5.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
         <v>72.8</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>73.06999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>22.43</v>
+        <v>22.41</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-9.9</v>
+        <v>-13.3</v>
       </c>
       <c r="G34" s="9" t="n">
         <v>68</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>73.11</v>
+        <v>73.06</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-13.3</v>
+        <v>-16.6</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
         <v>72.5</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>73.06</v>
+        <v>72.97</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>-16.6</v>
+        <v>-11.8</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>72.97</v>
+        <v>72.86</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>22.26</v>
+        <v>22.21</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-11.8</v>
+        <v>-21.1</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>72.86</v>
+        <v>72.8</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>-21.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>72.8</v>
+        <v>72.69</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>22.24</v>
+        <v>22.19</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-25.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>72.69</v>
+        <v>72.61</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>-18.3</v>
+        <v>-16</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-16</v>
+        <v>-10.4</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="n"/>
       <c r="C42" s="7" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="D42" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="D42" s="8" t="n"/>
       <c r="E42" s="7" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>-10.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B43" s="8" t="n"/>
       <c r="C43" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="D43" s="8" t="n"/>
       <c r="E43" s="7" t="n">
-        <v>21.85</v>
+        <v>21.7</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B44" s="8" t="n"/>
       <c r="C44" s="7" t="n">
-        <v>72.58</v>
+        <v>72.5</v>
       </c>
       <c r="D44" s="8" t="n"/>
       <c r="E44" s="7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>-12.3</v>
+        <v>-6.6</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B45" s="8" t="n"/>
       <c r="C45" s="7" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D45" s="8" t="n"/>
       <c r="E45" s="7" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="n"/>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C46" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D46" s="8" t="n"/>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>21.2</v>
+      </c>
       <c r="E46" s="7" t="n">
-        <v>21.73</v>
+        <v>21.63</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>21.63</v>
+        <v>21.57</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E48" s="7" t="n">
         <v>21.57</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>-7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>72.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D49" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E49" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E49" s="7" t="n">
-        <v>21.57</v>
-      </c>
       <c r="F49" s="8" t="n">
-        <v>-10.9</v>
+        <v>-7.7</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B50" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="n"/>
       <c r="C50" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D50" s="8" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D50" s="8" t="n"/>
       <c r="E50" s="7" t="n">
         <v>21.8</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.9</v>
       </c>
       <c r="G50" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B51" s="8" t="n"/>
@@ -4858,19 +4846,19 @@
         <v>21.8</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-8.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B52" s="8" t="n"/>
@@ -4882,274 +4870,278 @@
         <v>21.8</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>-12.5</v>
+        <v>-11.2</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B53" s="8" t="n"/>
       <c r="C53" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="D53" s="8" t="n"/>
       <c r="E53" s="7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-11.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B54" s="8" t="n"/>
       <c r="C54" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D54" s="8" t="n"/>
       <c r="E54" s="7" t="n">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>-13.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B55" s="8" t="n"/>
       <c r="C55" s="7" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="7" t="n">
-        <v>22.15</v>
+        <v>22.5</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="G55" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="n"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="C56" s="7" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="D56" s="8" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D56" s="8" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E56" s="7" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>-12.4</v>
+        <v>-7.8</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>20.5</v>
+        <v>20.95</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>-7.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C58" s="7" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>20.95</v>
+        <v>21.13</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>-3.1</v>
+        <v>-11.8</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>-11.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B60" s="8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="C60" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>72.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>-8.6</v>
+        <v>-13.5</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B62" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C62" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>21.33</v>
+        <v>21.43</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H62" s="10" t="n">
         <v>7.7</v>
@@ -5158,510 +5150,510 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B63" s="8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>72.23</v>
+        <v>72.39</v>
       </c>
       <c r="D63" s="8" t="n">
         <v>22</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>21.43</v>
+        <v>21.64</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>-7.1</v>
+        <v>-12.5</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B64" s="8" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C64" s="7" t="n">
         <v>72.39</v>
       </c>
       <c r="D64" s="8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>21.64</v>
+        <v>21.69</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>-12.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B65" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>72.39</v>
+        <v>72.36</v>
       </c>
       <c r="D65" s="8" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>21.69</v>
+        <v>21.56</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>-6.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B66" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="n"/>
       <c r="C66" s="7" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="D66" s="8" t="n">
-        <v>20.6</v>
-      </c>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="D66" s="8" t="n"/>
       <c r="E66" s="7" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="n"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="C67" s="7" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="D67" s="8" t="n"/>
+        <v>72.45</v>
+      </c>
+      <c r="D67" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E67" s="7" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B68" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C68" s="7" t="n">
-        <v>72.45</v>
+        <v>72.47</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>21.67</v>
+        <v>21.53</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B69" s="8" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>72.47</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>21.53</v>
+        <v>21.47</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C70" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>72.31999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>-4.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B72" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="C72" s="7" t="n">
-        <v>72.23</v>
+        <v>72.3</v>
       </c>
       <c r="D72" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>21.4</v>
+        <v>21.55</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>-1.6</v>
+        <v>-15.1</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B73" s="8" t="n">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="C73" s="7" t="n">
-        <v>72.3</v>
+        <v>72.37</v>
       </c>
       <c r="D73" s="8" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>21.55</v>
+        <v>21.69</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>-15.1</v>
+        <v>-10.3</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B74" s="8" t="n">
-        <v>72.8</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="n"/>
       <c r="C74" s="7" t="n">
-        <v>72.37</v>
-      </c>
-      <c r="D74" s="8" t="n">
-        <v>22.5</v>
-      </c>
+        <v>72.28</v>
+      </c>
+      <c r="D74" s="8" t="n"/>
       <c r="E74" s="7" t="n">
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>-10.3</v>
+        <v>-14.8</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>5.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B75" s="8" t="n"/>
       <c r="C75" s="7" t="n">
-        <v>72.28</v>
+        <v>72.3</v>
       </c>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="7" t="n">
-        <v>21.67</v>
+        <v>21.78</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>-14.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B76" s="8" t="n"/>
       <c r="C76" s="7" t="n">
-        <v>72.3</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="D76" s="8" t="n"/>
       <c r="E76" s="7" t="n">
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>-15.7</v>
+        <v>-15.4</v>
       </c>
       <c r="G76" s="9" t="n">
         <v>60</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B77" s="8" t="n"/>
       <c r="C77" s="7" t="n">
-        <v>72.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="7" t="n">
-        <v>21.82</v>
+        <v>21.83</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>-15.4</v>
+        <v>-8.9</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B78" s="8" t="n"/>
       <c r="C78" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D78" s="8" t="n"/>
       <c r="E78" s="7" t="n">
-        <v>21.83</v>
+        <v>22</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>-8.9</v>
+        <v>-6.7</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B79" s="8" t="n"/>
       <c r="C79" s="7" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D79" s="8" t="n"/>
       <c r="E79" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>-6.7</v>
+        <v>-4.8</v>
       </c>
       <c r="G79" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B80" s="8" t="n"/>
-      <c r="C80" s="7" t="n">
-        <v>72.8</v>
-      </c>
+      <c r="C80" s="7" t="n"/>
       <c r="D80" s="8" t="n"/>
-      <c r="E80" s="7" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="E80" s="7" t="n"/>
       <c r="F80" s="8" t="n">
-        <v>-4.8</v>
+        <v>0.6</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B81" s="8" t="n"/>
-      <c r="C81" s="7" t="n"/>
-      <c r="D81" s="8" t="n"/>
-      <c r="E81" s="7" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="C81" s="7" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="D81" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E81" s="7" t="n">
+        <v>21.9</v>
+      </c>
       <c r="F81" s="8" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B82" s="8" t="n">
-        <v>73.2</v>
+        <v>72.8</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>73.2</v>
+        <v>73</v>
       </c>
       <c r="D82" s="8" t="n">
         <v>21.9</v>
@@ -5670,345 +5662,345 @@
         <v>21.9</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>3.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B83" s="8" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>73</v>
+        <v>72.97</v>
       </c>
       <c r="D83" s="8" t="n">
-        <v>21.9</v>
+        <v>21.3</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>-9.4</v>
+        <v>-6.9</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B84" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C84" s="7" t="n">
-        <v>72.97</v>
+        <v>72.88</v>
       </c>
       <c r="D84" s="8" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>-6.9</v>
+        <v>-3.2</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B85" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>72.88</v>
+        <v>73.08</v>
       </c>
       <c r="D85" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>21.5</v>
+        <v>21.38</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>-3.2</v>
+        <v>0.9</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B86" s="8" t="n">
-        <v>73.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C86" s="7" t="n">
-        <v>73.08</v>
+        <v>73</v>
       </c>
       <c r="D86" s="8" t="n">
-        <v>20.9</v>
+        <v>21.8</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>21.38</v>
+        <v>21.45</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="B87" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="n"/>
       <c r="C87" s="7" t="n">
         <v>73</v>
       </c>
-      <c r="D87" s="8" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="D87" s="8" t="n"/>
       <c r="E87" s="7" t="n">
         <v>21.45</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="B88" s="8" t="n"/>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="n">
+        <v>71.90000000000001</v>
+      </c>
       <c r="C88" s="7" t="n">
-        <v>73</v>
-      </c>
-      <c r="D88" s="8" t="n"/>
+        <v>72.78</v>
+      </c>
+      <c r="D88" s="8" t="n">
+        <v>20.7</v>
+      </c>
       <c r="E88" s="7" t="n">
-        <v>21.45</v>
+        <v>21.25</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B89" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>72.78</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="D89" s="8" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>21.25</v>
+        <v>21.2</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>4</v>
+        <v>-3.6</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>6.7</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B90" s="8" t="n">
-        <v>71.5</v>
+        <v>71</v>
       </c>
       <c r="C90" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.25</v>
       </c>
       <c r="D90" s="8" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>-3.6</v>
+        <v>1</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B91" s="8" t="n">
-        <v>71</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>72.25</v>
+        <v>72.08</v>
       </c>
       <c r="D91" s="8" t="n">
-        <v>21.9</v>
+        <v>21.4</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>21.3</v>
+        <v>21.38</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>1</v>
+        <v>5.9</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B92" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="C92" s="7" t="n">
-        <v>72.08</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="D92" s="8" t="n">
-        <v>21.4</v>
+        <v>20.8</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>21.38</v>
+        <v>21.37</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>5.9</v>
+        <v>9.5</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B93" s="8" t="n">
-        <v>72.3</v>
+        <v>72.5</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>71.81999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="D93" s="8" t="n">
-        <v>20.8</v>
+        <v>21.6</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>21.37</v>
+        <v>21.33</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B94" s="8" t="n">
-        <v>72.5</v>
+        <v>73</v>
       </c>
       <c r="C94" s="7" t="n">
-        <v>71.8</v>
+        <v>71.97</v>
       </c>
       <c r="D94" s="8" t="n">
-        <v>21.6</v>
+        <v>22.1</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>21.33</v>
+        <v>21.44</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H94" s="10" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -6469,16 +6461,16 @@
         <v>47</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>50.3</v>
+        <v>50.7</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>180</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>248</v>
+        <v>320</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>68</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18">

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>50.7</v>
+        <v>52.3</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -5994,7 +5994,7 @@
         <v>21.44</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>2.7</v>
+        <v>-4.7</v>
       </c>
       <c r="G94" s="9" t="n">
         <v>51</v>
@@ -6461,7 +6461,7 @@
         <v>47</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>50.7</v>
+        <v>52.3</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>180</v>

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>73</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>68</v>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>22.1</v>
+        <v>22.6</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>16</v>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>4.71</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>52.3</v>
+        <v>49.5</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -3622,7 +3622,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
@@ -3630,86 +3630,94 @@
       <c r="D5" s="8" t="n"/>
       <c r="E5" s="7" t="n"/>
       <c r="F5" s="8" t="n">
-        <v>-9.4</v>
+        <v>-7.5</v>
       </c>
       <c r="G5" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="7" t="n"/>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>22.9</v>
+      </c>
       <c r="F6" s="8" t="n">
-        <v>-7.5</v>
+        <v>-4.5</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>74.5</v>
+        <v>74.75</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>22.9</v>
+        <v>22.85</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.2</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>74.75</v>
+        <v>74.8</v>
       </c>
       <c r="D8" s="8" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="E8" s="7" t="n">
         <v>22.8</v>
       </c>
-      <c r="E8" s="7" t="n">
-        <v>22.85</v>
-      </c>
       <c r="F8" s="8" t="n">
-        <v>-2.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H8" s="10" t="n">
         <v>8</v>
@@ -3718,291 +3726,283 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>74.8</v>
+        <v>74.78</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>22.8</v>
+        <v>22.65</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>74.78</v>
+        <v>74.64</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>22.65</v>
+        <v>22.6</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>-11.9</v>
+        <v>-10.3</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>22.6</v>
+        <v>22.55</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-10.3</v>
+        <v>-13.7</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>74.65000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>22.55</v>
+        <v>22.57</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>-13.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n">
-        <v>74.2</v>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n"/>
       <c r="C13" s="7" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>22.7</v>
-      </c>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D13" s="8" t="n"/>
       <c r="E13" s="7" t="n">
-        <v>22.57</v>
+        <v>22.52</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-15.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
       <c r="C14" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.52</v>
       </c>
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="7" t="n">
-        <v>22.52</v>
+        <v>22.46</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D15" s="8" t="n"/>
       <c r="E15" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-18.2</v>
+        <v>-23.1</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B16" s="8" t="n"/>
       <c r="C16" s="7" t="n">
-        <v>74.42</v>
+        <v>74.33</v>
       </c>
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="7" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B17" s="8" t="n"/>
       <c r="C17" s="7" t="n">
-        <v>74.33</v>
+        <v>74.45</v>
       </c>
       <c r="D17" s="8" t="n"/>
       <c r="E17" s="7" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-18.2</v>
+        <v>-19.5</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B18" s="8" t="n"/>
       <c r="C18" s="7" t="n">
-        <v>74.45</v>
+        <v>74.2</v>
       </c>
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>-19.5</v>
+        <v>-26.4</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B19" s="8" t="n"/>
-      <c r="C19" s="7" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="C19" s="7" t="n"/>
       <c r="D19" s="8" t="n"/>
-      <c r="E19" s="7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="E19" s="7" t="n"/>
       <c r="F19" s="8" t="n">
-        <v>-26.4</v>
+        <v>-19.9</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B20" s="8" t="n"/>
@@ -4010,807 +4010,811 @@
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="8" t="n">
-        <v>-19.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="7" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>21.7</v>
+      </c>
       <c r="F21" s="8" t="n">
-        <v>-15.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>21.7</v>
+        <v>22.05</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-9.4</v>
+        <v>-12</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>73.2</v>
+        <v>73.33</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-12</v>
+        <v>-12.4</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>-12.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>73.31999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D28" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>22.26</v>
+        <v>22.4</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>73.16</v>
+        <v>73.2</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-10.9</v>
+        <v>-16</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-16</v>
+        <v>-10.1</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>22.3</v>
+        <v>22.31</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-10.1</v>
+        <v>-5.9</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>73.16</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>22.31</v>
+        <v>22.43</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-5.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
         <v>72.8</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>73.06999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>22.43</v>
+        <v>22.41</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-9.9</v>
+        <v>-13.3</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>68</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>73.11</v>
+        <v>73.06</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-13.3</v>
+        <v>-16.6</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
         <v>72.5</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>73.06</v>
+        <v>72.97</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-16.6</v>
+        <v>-11.8</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>72.97</v>
+        <v>72.86</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>22.26</v>
+        <v>22.21</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>-11.8</v>
+        <v>-21.1</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>72.86</v>
+        <v>72.8</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-21.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>72.8</v>
+        <v>72.69</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>22.24</v>
+        <v>22.19</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>-25.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>72.69</v>
+        <v>72.61</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-18.3</v>
+        <v>-16</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>-16</v>
+        <v>-10.4</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B41" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n"/>
       <c r="C41" s="7" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="D41" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="D41" s="8" t="n"/>
       <c r="E41" s="7" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-10.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B42" s="8" t="n"/>
       <c r="C42" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="D42" s="8" t="n"/>
       <c r="E42" s="7" t="n">
-        <v>21.85</v>
+        <v>21.7</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B43" s="8" t="n"/>
       <c r="C43" s="7" t="n">
-        <v>72.58</v>
+        <v>72.5</v>
       </c>
       <c r="D43" s="8" t="n"/>
       <c r="E43" s="7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-12.3</v>
+        <v>-6.6</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B44" s="8" t="n"/>
       <c r="C44" s="7" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D44" s="8" t="n"/>
       <c r="E44" s="7" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B45" s="8" t="n"/>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C45" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D45" s="8" t="n"/>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>21.2</v>
+      </c>
       <c r="E45" s="7" t="n">
-        <v>21.73</v>
+        <v>21.63</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>21.63</v>
+        <v>21.57</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E47" s="7" t="n">
         <v>21.57</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>72.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D48" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E48" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E48" s="7" t="n">
-        <v>21.57</v>
-      </c>
       <c r="F48" s="8" t="n">
-        <v>-10.9</v>
+        <v>-7.7</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B49" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n"/>
       <c r="C49" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D49" s="8" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D49" s="8" t="n"/>
       <c r="E49" s="7" t="n">
         <v>21.8</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.9</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B50" s="8" t="n"/>
@@ -4822,19 +4826,19 @@
         <v>21.8</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>-8.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B51" s="8" t="n"/>
@@ -4846,274 +4850,278 @@
         <v>21.8</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-12.5</v>
+        <v>-11.2</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B52" s="8" t="n"/>
       <c r="C52" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="D52" s="8" t="n"/>
       <c r="E52" s="7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>-11.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G52" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B53" s="8" t="n"/>
       <c r="C53" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D53" s="8" t="n"/>
       <c r="E53" s="7" t="n">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-13.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B54" s="8" t="n"/>
       <c r="C54" s="7" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D54" s="8" t="n"/>
       <c r="E54" s="7" t="n">
-        <v>22.15</v>
+        <v>22.5</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="G54" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="n"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="C55" s="7" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="D55" s="8" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E55" s="7" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>-12.4</v>
+        <v>-7.8</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>20.5</v>
+        <v>20.95</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>-7.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>20.95</v>
+        <v>21.13</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>-3.1</v>
+        <v>-11.8</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C58" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>-11.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B60" s="8" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C60" s="7" t="n">
-        <v>72.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>-8.6</v>
+        <v>-13.5</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>21.33</v>
+        <v>21.43</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H61" s="10" t="n">
         <v>7.7</v>
@@ -5122,510 +5130,510 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B62" s="8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="C62" s="7" t="n">
-        <v>72.23</v>
+        <v>72.39</v>
       </c>
       <c r="D62" s="8" t="n">
         <v>22</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>21.43</v>
+        <v>21.64</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>-7.1</v>
+        <v>-12.5</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B63" s="8" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C63" s="7" t="n">
         <v>72.39</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>21.64</v>
+        <v>21.69</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>-12.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B64" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C64" s="7" t="n">
-        <v>72.39</v>
+        <v>72.36</v>
       </c>
       <c r="D64" s="8" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>21.69</v>
+        <v>21.56</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>-6.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B65" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="n"/>
       <c r="C65" s="7" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="D65" s="8" t="n">
-        <v>20.6</v>
-      </c>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="D65" s="8" t="n"/>
       <c r="E65" s="7" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B66" s="8" t="n"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="C66" s="7" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="D66" s="8" t="n"/>
+        <v>72.45</v>
+      </c>
+      <c r="D66" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E66" s="7" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B67" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>72.45</v>
+        <v>72.47</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>21.67</v>
+        <v>21.53</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B68" s="8" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C68" s="7" t="n">
-        <v>72.47</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>21.53</v>
+        <v>21.47</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B69" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C70" s="7" t="n">
-        <v>72.31999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>-4.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>72.23</v>
+        <v>72.3</v>
       </c>
       <c r="D71" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>21.4</v>
+        <v>21.55</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>-1.6</v>
+        <v>-15.1</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B72" s="8" t="n">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="C72" s="7" t="n">
-        <v>72.3</v>
+        <v>72.37</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>21.55</v>
+        <v>21.69</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>-15.1</v>
+        <v>-10.3</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="n">
-        <v>72.8</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="n"/>
       <c r="C73" s="7" t="n">
-        <v>72.37</v>
-      </c>
-      <c r="D73" s="8" t="n">
-        <v>22.5</v>
-      </c>
+        <v>72.28</v>
+      </c>
+      <c r="D73" s="8" t="n"/>
       <c r="E73" s="7" t="n">
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>-10.3</v>
+        <v>-14.8</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>5.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B74" s="8" t="n"/>
       <c r="C74" s="7" t="n">
-        <v>72.28</v>
+        <v>72.3</v>
       </c>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="7" t="n">
-        <v>21.67</v>
+        <v>21.78</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>-14.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B75" s="8" t="n"/>
       <c r="C75" s="7" t="n">
-        <v>72.3</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="7" t="n">
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>-15.7</v>
+        <v>-15.4</v>
       </c>
       <c r="G75" s="9" t="n">
         <v>60</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B76" s="8" t="n"/>
       <c r="C76" s="7" t="n">
-        <v>72.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D76" s="8" t="n"/>
       <c r="E76" s="7" t="n">
-        <v>21.82</v>
+        <v>21.83</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>-15.4</v>
+        <v>-8.9</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B77" s="8" t="n"/>
       <c r="C77" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="7" t="n">
-        <v>21.83</v>
+        <v>22</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>-8.9</v>
+        <v>-6.7</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B78" s="8" t="n"/>
       <c r="C78" s="7" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D78" s="8" t="n"/>
       <c r="E78" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>-6.7</v>
+        <v>-4.8</v>
       </c>
       <c r="G78" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B79" s="8" t="n"/>
-      <c r="C79" s="7" t="n">
-        <v>72.8</v>
-      </c>
+      <c r="C79" s="7" t="n"/>
       <c r="D79" s="8" t="n"/>
-      <c r="E79" s="7" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="E79" s="7" t="n"/>
       <c r="F79" s="8" t="n">
-        <v>-4.8</v>
+        <v>0.6</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B80" s="8" t="n"/>
-      <c r="C80" s="7" t="n"/>
-      <c r="D80" s="8" t="n"/>
-      <c r="E80" s="7" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="C80" s="7" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="D80" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E80" s="7" t="n">
+        <v>21.9</v>
+      </c>
       <c r="F80" s="8" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>73.2</v>
+        <v>72.8</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>73.2</v>
+        <v>73</v>
       </c>
       <c r="D81" s="8" t="n">
         <v>21.9</v>
@@ -5634,373 +5642,373 @@
         <v>21.9</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>3.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B82" s="8" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>73</v>
+        <v>72.97</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>21.9</v>
+        <v>21.3</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>-9.4</v>
+        <v>-6.9</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B83" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>72.97</v>
+        <v>72.88</v>
       </c>
       <c r="D83" s="8" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>-6.9</v>
+        <v>-3.2</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B84" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="C84" s="7" t="n">
-        <v>72.88</v>
+        <v>73.08</v>
       </c>
       <c r="D84" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>21.5</v>
+        <v>21.38</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>-3.2</v>
+        <v>0.9</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B85" s="8" t="n">
-        <v>73.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>73.08</v>
+        <v>73</v>
       </c>
       <c r="D85" s="8" t="n">
-        <v>20.9</v>
+        <v>21.8</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>21.38</v>
+        <v>21.45</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="B86" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="n"/>
       <c r="C86" s="7" t="n">
         <v>73</v>
       </c>
-      <c r="D86" s="8" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="D86" s="8" t="n"/>
       <c r="E86" s="7" t="n">
         <v>21.45</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="B87" s="8" t="n"/>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="n">
+        <v>71.90000000000001</v>
+      </c>
       <c r="C87" s="7" t="n">
-        <v>73</v>
-      </c>
-      <c r="D87" s="8" t="n"/>
+        <v>72.78</v>
+      </c>
+      <c r="D87" s="8" t="n">
+        <v>20.7</v>
+      </c>
       <c r="E87" s="7" t="n">
-        <v>21.45</v>
+        <v>21.25</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B88" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="C88" s="7" t="n">
-        <v>72.78</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="D88" s="8" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>21.25</v>
+        <v>21.2</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>4</v>
+        <v>-3.6</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>6.7</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B89" s="8" t="n">
-        <v>71.5</v>
+        <v>71</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.25</v>
       </c>
       <c r="D89" s="8" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>-3.6</v>
+        <v>1</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B90" s="8" t="n">
-        <v>71</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="C90" s="7" t="n">
-        <v>72.25</v>
+        <v>72.08</v>
       </c>
       <c r="D90" s="8" t="n">
-        <v>21.9</v>
+        <v>21.4</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>21.3</v>
+        <v>21.38</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>1</v>
+        <v>5.9</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B91" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>72.08</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="D91" s="8" t="n">
-        <v>21.4</v>
+        <v>20.8</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>21.38</v>
+        <v>21.37</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>5.9</v>
+        <v>9.5</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B92" s="8" t="n">
-        <v>72.3</v>
+        <v>72.5</v>
       </c>
       <c r="C92" s="7" t="n">
-        <v>71.81999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="D92" s="8" t="n">
-        <v>20.8</v>
+        <v>21.6</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>21.37</v>
+        <v>21.33</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B93" s="8" t="n">
-        <v>72.5</v>
+        <v>73</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>71.8</v>
+        <v>71.97</v>
       </c>
       <c r="D93" s="8" t="n">
-        <v>21.6</v>
+        <v>22.1</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>21.33</v>
+        <v>21.44</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B94" s="8" t="n">
-        <v>73</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C94" s="7" t="n">
-        <v>71.97</v>
+        <v>72.14</v>
       </c>
       <c r="D94" s="8" t="n">
-        <v>22.1</v>
+        <v>22.6</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>21.44</v>
+        <v>21.71</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>-4.7</v>
+        <v>5</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="H94" s="10" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -6461,7 +6469,7 @@
         <v>47</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>52.3</v>
+        <v>50.7</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>180</v>
@@ -6490,12 +6498,18 @@
       <c r="D18" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="E18" s="8" t="n"/>
+      <c r="E18" s="8" t="n">
+        <v>49.5</v>
+      </c>
       <c r="F18" s="4" t="n">
         <v>93</v>
       </c>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="11" t="n"/>
+      <c r="G18" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" s="11" t="n">
+        <v>-88</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>73.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>68</v>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>22.6</v>
+        <v>20.8</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>16</v>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>4.71</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>49.5</v>
+        <v>49.3</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -3622,74 +3622,82 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="7" t="n"/>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>22.9</v>
+      </c>
       <c r="F5" s="8" t="n">
-        <v>-7.5</v>
+        <v>-4.5</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>74.5</v>
+        <v>74.75</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>22.9</v>
+        <v>22.85</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.2</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>74.75</v>
+        <v>74.8</v>
       </c>
       <c r="D7" s="8" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="E7" s="7" t="n">
         <v>22.8</v>
       </c>
-      <c r="E7" s="7" t="n">
-        <v>22.85</v>
-      </c>
       <c r="F7" s="8" t="n">
-        <v>-2.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H7" s="10" t="n">
         <v>8</v>
@@ -3698,291 +3706,283 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>74.8</v>
+        <v>74.78</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>22.8</v>
+        <v>22.65</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>74.78</v>
+        <v>74.64</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>22.65</v>
+        <v>22.6</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-11.9</v>
+        <v>-10.3</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>22.6</v>
+        <v>22.55</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>-10.3</v>
+        <v>-13.7</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>74.65000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>22.55</v>
+        <v>22.57</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-13.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n">
-        <v>74.2</v>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n"/>
       <c r="C12" s="7" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>22.7</v>
-      </c>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D12" s="8" t="n"/>
       <c r="E12" s="7" t="n">
-        <v>22.57</v>
+        <v>22.52</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>-15.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.52</v>
       </c>
       <c r="D13" s="8" t="n"/>
       <c r="E13" s="7" t="n">
-        <v>22.52</v>
+        <v>22.46</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
       <c r="C14" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>-18.2</v>
+        <v>-23.1</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="7" t="n">
-        <v>74.42</v>
+        <v>74.33</v>
       </c>
       <c r="D15" s="8" t="n"/>
       <c r="E15" s="7" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B16" s="8" t="n"/>
       <c r="C16" s="7" t="n">
-        <v>74.33</v>
+        <v>74.45</v>
       </c>
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="7" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>-18.2</v>
+        <v>-19.5</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B17" s="8" t="n"/>
       <c r="C17" s="7" t="n">
-        <v>74.45</v>
+        <v>74.2</v>
       </c>
       <c r="D17" s="8" t="n"/>
       <c r="E17" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-19.5</v>
+        <v>-26.4</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B18" s="8" t="n"/>
-      <c r="C18" s="7" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="C18" s="7" t="n"/>
       <c r="D18" s="8" t="n"/>
-      <c r="E18" s="7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="E18" s="7" t="n"/>
       <c r="F18" s="8" t="n">
-        <v>-26.4</v>
+        <v>-19.9</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B19" s="8" t="n"/>
@@ -3990,807 +3990,811 @@
       <c r="D19" s="8" t="n"/>
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="8" t="n">
-        <v>-19.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="7" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>21.7</v>
+      </c>
       <c r="F20" s="8" t="n">
-        <v>-15.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>21.7</v>
+        <v>22.05</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-9.4</v>
+        <v>-12</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>73.2</v>
+        <v>73.33</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-12</v>
+        <v>-12.4</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-12.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>73.31999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D27" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>22.26</v>
+        <v>22.4</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>73.16</v>
+        <v>73.2</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-10.9</v>
+        <v>-16</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-16</v>
+        <v>-10.1</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>22.3</v>
+        <v>22.31</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-10.1</v>
+        <v>-5.9</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>73.16</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>22.31</v>
+        <v>22.43</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-5.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
         <v>72.8</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>73.06999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>22.43</v>
+        <v>22.41</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-9.9</v>
+        <v>-13.3</v>
       </c>
       <c r="G32" s="9" t="n">
         <v>68</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>73.11</v>
+        <v>73.06</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-13.3</v>
+        <v>-16.6</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
         <v>72.5</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>73.06</v>
+        <v>72.97</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-16.6</v>
+        <v>-11.8</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>72.97</v>
+        <v>72.86</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>22.26</v>
+        <v>22.21</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-11.8</v>
+        <v>-21.1</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>72.86</v>
+        <v>72.8</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>-21.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>72.8</v>
+        <v>72.69</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>22.24</v>
+        <v>22.19</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-25.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>72.69</v>
+        <v>72.61</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>-18.3</v>
+        <v>-16</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-16</v>
+        <v>-10.4</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="n"/>
       <c r="C40" s="7" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="D40" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="D40" s="8" t="n"/>
       <c r="E40" s="7" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>-10.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="D41" s="8" t="n"/>
       <c r="E41" s="7" t="n">
-        <v>21.85</v>
+        <v>21.7</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B42" s="8" t="n"/>
       <c r="C42" s="7" t="n">
-        <v>72.58</v>
+        <v>72.5</v>
       </c>
       <c r="D42" s="8" t="n"/>
       <c r="E42" s="7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>-12.3</v>
+        <v>-6.6</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B43" s="8" t="n"/>
       <c r="C43" s="7" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D43" s="8" t="n"/>
       <c r="E43" s="7" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="n"/>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C44" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D44" s="8" t="n"/>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>21.2</v>
+      </c>
       <c r="E44" s="7" t="n">
-        <v>21.73</v>
+        <v>21.63</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>21.63</v>
+        <v>21.57</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E46" s="7" t="n">
         <v>21.57</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>-7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>72.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D47" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E47" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E47" s="7" t="n">
-        <v>21.57</v>
-      </c>
       <c r="F47" s="8" t="n">
-        <v>-10.9</v>
+        <v>-7.7</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B48" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="n"/>
       <c r="C48" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D48" s="8" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D48" s="8" t="n"/>
       <c r="E48" s="7" t="n">
         <v>21.8</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.9</v>
       </c>
       <c r="G48" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B49" s="8" t="n"/>
@@ -4802,19 +4806,19 @@
         <v>21.8</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-8.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B50" s="8" t="n"/>
@@ -4826,274 +4830,278 @@
         <v>21.8</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>-12.5</v>
+        <v>-11.2</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B51" s="8" t="n"/>
       <c r="C51" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="D51" s="8" t="n"/>
       <c r="E51" s="7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-11.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G51" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B52" s="8" t="n"/>
       <c r="C52" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D52" s="8" t="n"/>
       <c r="E52" s="7" t="n">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>-13.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B53" s="8" t="n"/>
       <c r="C53" s="7" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D53" s="8" t="n"/>
       <c r="E53" s="7" t="n">
-        <v>22.15</v>
+        <v>22.5</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="n"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="C54" s="7" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="D54" s="8" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D54" s="8" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E54" s="7" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>-12.4</v>
+        <v>-7.8</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>20.5</v>
+        <v>20.95</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>-7.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>20.95</v>
+        <v>21.13</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>-3.1</v>
+        <v>-11.8</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>-11.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="C58" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>72.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>-8.6</v>
+        <v>-13.5</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B60" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C60" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>21.33</v>
+        <v>21.43</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H60" s="10" t="n">
         <v>7.7</v>
@@ -5102,510 +5110,510 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>72.23</v>
+        <v>72.39</v>
       </c>
       <c r="D61" s="8" t="n">
         <v>22</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>21.43</v>
+        <v>21.64</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>-7.1</v>
+        <v>-12.5</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B62" s="8" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C62" s="7" t="n">
         <v>72.39</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>21.64</v>
+        <v>21.69</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>-12.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B63" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>72.39</v>
+        <v>72.36</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>21.69</v>
+        <v>21.56</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>-6.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="n"/>
       <c r="C64" s="7" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="D64" s="8" t="n">
-        <v>20.6</v>
-      </c>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="D64" s="8" t="n"/>
       <c r="E64" s="7" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B65" s="8" t="n"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="C65" s="7" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="D65" s="8" t="n"/>
+        <v>72.45</v>
+      </c>
+      <c r="D65" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E65" s="7" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B66" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>72.45</v>
+        <v>72.47</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>21.67</v>
+        <v>21.53</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B67" s="8" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>72.47</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>21.53</v>
+        <v>21.47</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B68" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C68" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B69" s="8" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>72.31999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>-4.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="C70" s="7" t="n">
-        <v>72.23</v>
+        <v>72.3</v>
       </c>
       <c r="D70" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>21.4</v>
+        <v>21.55</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>-1.6</v>
+        <v>-15.1</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>72.3</v>
+        <v>72.37</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>21.55</v>
+        <v>21.69</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>-15.1</v>
+        <v>-10.3</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B72" s="8" t="n">
-        <v>72.8</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="n"/>
       <c r="C72" s="7" t="n">
-        <v>72.37</v>
-      </c>
-      <c r="D72" s="8" t="n">
-        <v>22.5</v>
-      </c>
+        <v>72.28</v>
+      </c>
+      <c r="D72" s="8" t="n"/>
       <c r="E72" s="7" t="n">
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>-10.3</v>
+        <v>-14.8</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>5.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B73" s="8" t="n"/>
       <c r="C73" s="7" t="n">
-        <v>72.28</v>
+        <v>72.3</v>
       </c>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="7" t="n">
-        <v>21.67</v>
+        <v>21.78</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>-14.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B74" s="8" t="n"/>
       <c r="C74" s="7" t="n">
-        <v>72.3</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="7" t="n">
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>-15.7</v>
+        <v>-15.4</v>
       </c>
       <c r="G74" s="9" t="n">
         <v>60</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B75" s="8" t="n"/>
       <c r="C75" s="7" t="n">
-        <v>72.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="7" t="n">
-        <v>21.82</v>
+        <v>21.83</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>-15.4</v>
+        <v>-8.9</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B76" s="8" t="n"/>
       <c r="C76" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D76" s="8" t="n"/>
       <c r="E76" s="7" t="n">
-        <v>21.83</v>
+        <v>22</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>-8.9</v>
+        <v>-6.7</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B77" s="8" t="n"/>
       <c r="C77" s="7" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>-6.7</v>
+        <v>-4.8</v>
       </c>
       <c r="G77" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B78" s="8" t="n"/>
-      <c r="C78" s="7" t="n">
-        <v>72.8</v>
-      </c>
+      <c r="C78" s="7" t="n"/>
       <c r="D78" s="8" t="n"/>
-      <c r="E78" s="7" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="E78" s="7" t="n"/>
       <c r="F78" s="8" t="n">
-        <v>-4.8</v>
+        <v>0.6</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B79" s="8" t="n"/>
-      <c r="C79" s="7" t="n"/>
-      <c r="D79" s="8" t="n"/>
-      <c r="E79" s="7" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="C79" s="7" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="D79" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E79" s="7" t="n">
+        <v>21.9</v>
+      </c>
       <c r="F79" s="8" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>73.2</v>
+        <v>72.8</v>
       </c>
       <c r="C80" s="7" t="n">
-        <v>73.2</v>
+        <v>73</v>
       </c>
       <c r="D80" s="8" t="n">
         <v>21.9</v>
@@ -5614,395 +5622,395 @@
         <v>21.9</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>3.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>73</v>
+        <v>72.97</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>21.9</v>
+        <v>21.3</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>-9.4</v>
+        <v>-6.9</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B82" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>72.97</v>
+        <v>72.88</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>-6.9</v>
+        <v>-3.2</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B83" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>72.88</v>
+        <v>73.08</v>
       </c>
       <c r="D83" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>21.5</v>
+        <v>21.38</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>-3.2</v>
+        <v>0.9</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B84" s="8" t="n">
-        <v>73.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C84" s="7" t="n">
-        <v>73.08</v>
+        <v>73</v>
       </c>
       <c r="D84" s="8" t="n">
-        <v>20.9</v>
+        <v>21.8</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>21.38</v>
+        <v>21.45</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="B85" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="n"/>
       <c r="C85" s="7" t="n">
         <v>73</v>
       </c>
-      <c r="D85" s="8" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="D85" s="8" t="n"/>
       <c r="E85" s="7" t="n">
         <v>21.45</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="B86" s="8" t="n"/>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="n">
+        <v>71.90000000000001</v>
+      </c>
       <c r="C86" s="7" t="n">
-        <v>73</v>
-      </c>
-      <c r="D86" s="8" t="n"/>
+        <v>72.78</v>
+      </c>
+      <c r="D86" s="8" t="n">
+        <v>20.7</v>
+      </c>
       <c r="E86" s="7" t="n">
-        <v>21.45</v>
+        <v>21.25</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B87" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>72.78</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="D87" s="8" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>21.25</v>
+        <v>21.2</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>4</v>
+        <v>-3.6</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>6.7</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B88" s="8" t="n">
-        <v>71.5</v>
+        <v>71</v>
       </c>
       <c r="C88" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.25</v>
       </c>
       <c r="D88" s="8" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>-3.6</v>
+        <v>1</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B89" s="8" t="n">
-        <v>71</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>72.25</v>
+        <v>72.08</v>
       </c>
       <c r="D89" s="8" t="n">
-        <v>21.9</v>
+        <v>21.4</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>21.3</v>
+        <v>21.38</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>1</v>
+        <v>5.9</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B90" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="C90" s="7" t="n">
-        <v>72.08</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="D90" s="8" t="n">
-        <v>21.4</v>
+        <v>20.8</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>21.38</v>
+        <v>21.37</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>5.9</v>
+        <v>9.5</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B91" s="8" t="n">
-        <v>72.3</v>
+        <v>72.5</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>71.81999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="D91" s="8" t="n">
-        <v>20.8</v>
+        <v>21.6</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>21.37</v>
+        <v>21.33</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B92" s="8" t="n">
-        <v>72.5</v>
+        <v>73</v>
       </c>
       <c r="C92" s="7" t="n">
-        <v>71.8</v>
+        <v>71.97</v>
       </c>
       <c r="D92" s="8" t="n">
-        <v>21.6</v>
+        <v>22.1</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>21.33</v>
+        <v>21.44</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B93" s="8" t="n">
-        <v>73</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>71.97</v>
+        <v>72.14</v>
       </c>
       <c r="D93" s="8" t="n">
-        <v>22.1</v>
+        <v>22.6</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>21.44</v>
+        <v>21.71</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>2.7</v>
+        <v>6.1</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B94" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C94" s="7" t="n">
-        <v>72.14</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="D94" s="8" t="n">
-        <v>22.6</v>
+        <v>20.8</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>21.71</v>
+        <v>21.6</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="G94" s="9" t="n">
         <v>63</v>
@@ -6499,16 +6507,16 @@
         <v>43</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>49.5</v>
+        <v>49.3</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>93</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>-88</v>
+        <v>-47</v>
       </c>
     </row>
     <row r="19">

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>72.2</v>
+        <v>72.3</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>68</v>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>20.8</v>
+        <v>21.3</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>16</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -3622,54 +3622,54 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.2</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>74.75</v>
+        <v>74.95</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>22.85</v>
+        <v>22.75</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>-2.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H6" s="10" t="n">
         <v>8</v>
@@ -3678,291 +3678,283 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>74.8</v>
+        <v>74.87</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>22.8</v>
+        <v>22.57</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>74.78</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>22.65</v>
+        <v>22.52</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>-11.9</v>
+        <v>-10.3</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>74.64</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>22.6</v>
+        <v>22.48</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-10.3</v>
+        <v>-13.7</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>74.65000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>22.55</v>
+        <v>22.52</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>-13.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n">
-        <v>74.2</v>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n"/>
       <c r="C11" s="7" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>22.7</v>
-      </c>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="7" t="n">
-        <v>22.57</v>
+        <v>22.52</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-15.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.52</v>
       </c>
       <c r="D12" s="8" t="n"/>
       <c r="E12" s="7" t="n">
-        <v>22.52</v>
+        <v>22.46</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D13" s="8" t="n"/>
       <c r="E13" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-18.2</v>
+        <v>-23.1</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
       <c r="C14" s="7" t="n">
-        <v>74.42</v>
+        <v>74.33</v>
       </c>
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="7" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="7" t="n">
-        <v>74.33</v>
+        <v>74.45</v>
       </c>
       <c r="D15" s="8" t="n"/>
       <c r="E15" s="7" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-18.2</v>
+        <v>-19.5</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B16" s="8" t="n"/>
       <c r="C16" s="7" t="n">
-        <v>74.45</v>
+        <v>74.2</v>
       </c>
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>-19.5</v>
+        <v>-26.4</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B17" s="8" t="n"/>
-      <c r="C17" s="7" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="C17" s="7" t="n"/>
       <c r="D17" s="8" t="n"/>
-      <c r="E17" s="7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="E17" s="7" t="n"/>
       <c r="F17" s="8" t="n">
-        <v>-26.4</v>
+        <v>-19.9</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B18" s="8" t="n"/>
@@ -3970,807 +3962,811 @@
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="8" t="n">
-        <v>-19.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="7" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>21.7</v>
+      </c>
       <c r="F19" s="8" t="n">
-        <v>-15.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>21.7</v>
+        <v>22.05</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>-9.4</v>
+        <v>-12</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>73.2</v>
+        <v>73.33</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-12</v>
+        <v>-12.4</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-12.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>73.31999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D26" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>22.26</v>
+        <v>22.4</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>73.16</v>
+        <v>73.2</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-10.9</v>
+        <v>-16</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-16</v>
+        <v>-10.1</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>22.3</v>
+        <v>22.31</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-10.1</v>
+        <v>-5.9</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>73.16</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>22.31</v>
+        <v>22.43</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-5.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
         <v>72.8</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>73.06999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>22.43</v>
+        <v>22.41</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-9.9</v>
+        <v>-13.3</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>68</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>73.11</v>
+        <v>73.06</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-13.3</v>
+        <v>-16.6</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
         <v>72.5</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>73.06</v>
+        <v>72.97</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-16.6</v>
+        <v>-11.8</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>72.97</v>
+        <v>72.86</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>22.26</v>
+        <v>22.21</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-11.8</v>
+        <v>-21.1</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>72.86</v>
+        <v>72.8</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-21.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>72.8</v>
+        <v>72.69</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>22.24</v>
+        <v>22.19</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>-25.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>72.69</v>
+        <v>72.61</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-18.3</v>
+        <v>-16</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>-16</v>
+        <v>-10.4</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n"/>
       <c r="C39" s="7" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="D39" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="D39" s="8" t="n"/>
       <c r="E39" s="7" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-10.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B40" s="8" t="n"/>
       <c r="C40" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="D40" s="8" t="n"/>
       <c r="E40" s="7" t="n">
-        <v>21.85</v>
+        <v>21.7</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="7" t="n">
-        <v>72.58</v>
+        <v>72.5</v>
       </c>
       <c r="D41" s="8" t="n"/>
       <c r="E41" s="7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-12.3</v>
+        <v>-6.6</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B42" s="8" t="n"/>
       <c r="C42" s="7" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D42" s="8" t="n"/>
       <c r="E42" s="7" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B43" s="8" t="n"/>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C43" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D43" s="8" t="n"/>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>21.2</v>
+      </c>
       <c r="E43" s="7" t="n">
-        <v>21.73</v>
+        <v>21.63</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>21.63</v>
+        <v>21.57</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E45" s="7" t="n">
         <v>21.57</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>72.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D46" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E46" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E46" s="7" t="n">
-        <v>21.57</v>
-      </c>
       <c r="F46" s="8" t="n">
-        <v>-10.9</v>
+        <v>-7.7</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B47" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n"/>
       <c r="C47" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D47" s="8" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D47" s="8" t="n"/>
       <c r="E47" s="7" t="n">
         <v>21.8</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.9</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B48" s="8" t="n"/>
@@ -4782,19 +4778,19 @@
         <v>21.8</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>-8.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B49" s="8" t="n"/>
@@ -4806,274 +4802,278 @@
         <v>21.8</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-12.5</v>
+        <v>-11.2</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B50" s="8" t="n"/>
       <c r="C50" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="D50" s="8" t="n"/>
       <c r="E50" s="7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>-11.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G50" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B51" s="8" t="n"/>
       <c r="C51" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D51" s="8" t="n"/>
       <c r="E51" s="7" t="n">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-13.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B52" s="8" t="n"/>
       <c r="C52" s="7" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D52" s="8" t="n"/>
       <c r="E52" s="7" t="n">
-        <v>22.15</v>
+        <v>22.5</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="G52" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B53" s="8" t="n"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="C53" s="7" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="D53" s="8" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D53" s="8" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E53" s="7" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-12.4</v>
+        <v>-7.8</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>20.5</v>
+        <v>20.95</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>-7.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>20.95</v>
+        <v>21.13</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>-3.1</v>
+        <v>-11.8</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>-11.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C58" s="7" t="n">
-        <v>72.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>-8.6</v>
+        <v>-13.5</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>21.33</v>
+        <v>21.43</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H59" s="10" t="n">
         <v>7.7</v>
@@ -5082,510 +5082,510 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B60" s="8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="C60" s="7" t="n">
-        <v>72.23</v>
+        <v>72.39</v>
       </c>
       <c r="D60" s="8" t="n">
         <v>22</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>21.43</v>
+        <v>21.64</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>-7.1</v>
+        <v>-12.5</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C61" s="7" t="n">
         <v>72.39</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>21.64</v>
+        <v>21.69</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>-12.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B62" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C62" s="7" t="n">
-        <v>72.39</v>
+        <v>72.36</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>21.69</v>
+        <v>21.56</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>-6.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B63" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="n"/>
       <c r="C63" s="7" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="D63" s="8" t="n">
-        <v>20.6</v>
-      </c>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="D63" s="8" t="n"/>
       <c r="E63" s="7" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="n"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="C64" s="7" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="D64" s="8" t="n"/>
+        <v>72.45</v>
+      </c>
+      <c r="D64" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E64" s="7" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B65" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>72.45</v>
+        <v>72.47</v>
       </c>
       <c r="D65" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>21.67</v>
+        <v>21.53</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B66" s="8" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>72.47</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>21.53</v>
+        <v>21.47</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B67" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B68" s="8" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C68" s="7" t="n">
-        <v>72.31999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>-4.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B69" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>72.23</v>
+        <v>72.3</v>
       </c>
       <c r="D69" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>21.4</v>
+        <v>21.55</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>-1.6</v>
+        <v>-15.1</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="C70" s="7" t="n">
-        <v>72.3</v>
+        <v>72.37</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>21.55</v>
+        <v>21.69</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>-15.1</v>
+        <v>-10.3</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B71" s="8" t="n">
-        <v>72.8</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="n"/>
       <c r="C71" s="7" t="n">
-        <v>72.37</v>
-      </c>
-      <c r="D71" s="8" t="n">
-        <v>22.5</v>
-      </c>
+        <v>72.28</v>
+      </c>
+      <c r="D71" s="8" t="n"/>
       <c r="E71" s="7" t="n">
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>-10.3</v>
+        <v>-14.8</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>5.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B72" s="8" t="n"/>
       <c r="C72" s="7" t="n">
-        <v>72.28</v>
+        <v>72.3</v>
       </c>
       <c r="D72" s="8" t="n"/>
       <c r="E72" s="7" t="n">
-        <v>21.67</v>
+        <v>21.78</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>-14.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B73" s="8" t="n"/>
       <c r="C73" s="7" t="n">
-        <v>72.3</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="7" t="n">
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>-15.7</v>
+        <v>-15.4</v>
       </c>
       <c r="G73" s="9" t="n">
         <v>60</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B74" s="8" t="n"/>
       <c r="C74" s="7" t="n">
-        <v>72.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="7" t="n">
-        <v>21.82</v>
+        <v>21.83</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>-15.4</v>
+        <v>-8.9</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B75" s="8" t="n"/>
       <c r="C75" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="7" t="n">
-        <v>21.83</v>
+        <v>22</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>-8.9</v>
+        <v>-6.7</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B76" s="8" t="n"/>
       <c r="C76" s="7" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D76" s="8" t="n"/>
       <c r="E76" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>-6.7</v>
+        <v>-4.8</v>
       </c>
       <c r="G76" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B77" s="8" t="n"/>
-      <c r="C77" s="7" t="n">
-        <v>72.8</v>
-      </c>
+      <c r="C77" s="7" t="n"/>
       <c r="D77" s="8" t="n"/>
-      <c r="E77" s="7" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="E77" s="7" t="n"/>
       <c r="F77" s="8" t="n">
-        <v>-4.8</v>
+        <v>0.6</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B78" s="8" t="n"/>
-      <c r="C78" s="7" t="n"/>
-      <c r="D78" s="8" t="n"/>
-      <c r="E78" s="7" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="C78" s="7" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="D78" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E78" s="7" t="n">
+        <v>21.9</v>
+      </c>
       <c r="F78" s="8" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>73.2</v>
+        <v>72.8</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>73.2</v>
+        <v>73</v>
       </c>
       <c r="D79" s="8" t="n">
         <v>21.9</v>
@@ -5594,395 +5594,395 @@
         <v>21.9</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>3.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C80" s="7" t="n">
-        <v>73</v>
+        <v>72.97</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>21.9</v>
+        <v>21.3</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>-9.4</v>
+        <v>-6.9</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>72.97</v>
+        <v>72.88</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>-6.9</v>
+        <v>-3.2</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B82" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>72.88</v>
+        <v>73.08</v>
       </c>
       <c r="D82" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>21.5</v>
+        <v>21.38</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>-3.2</v>
+        <v>0.9</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B83" s="8" t="n">
-        <v>73.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>73.08</v>
+        <v>73</v>
       </c>
       <c r="D83" s="8" t="n">
-        <v>20.9</v>
+        <v>21.8</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>21.38</v>
+        <v>21.45</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="B84" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="n"/>
       <c r="C84" s="7" t="n">
         <v>73</v>
       </c>
-      <c r="D84" s="8" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="D84" s="8" t="n"/>
       <c r="E84" s="7" t="n">
         <v>21.45</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="B85" s="8" t="n"/>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="n">
+        <v>71.90000000000001</v>
+      </c>
       <c r="C85" s="7" t="n">
-        <v>73</v>
-      </c>
-      <c r="D85" s="8" t="n"/>
+        <v>72.78</v>
+      </c>
+      <c r="D85" s="8" t="n">
+        <v>20.7</v>
+      </c>
       <c r="E85" s="7" t="n">
-        <v>21.45</v>
+        <v>21.25</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B86" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="C86" s="7" t="n">
-        <v>72.78</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="D86" s="8" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>21.25</v>
+        <v>21.2</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>4</v>
+        <v>-3.6</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>6.7</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B87" s="8" t="n">
-        <v>71.5</v>
+        <v>71</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.25</v>
       </c>
       <c r="D87" s="8" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>-3.6</v>
+        <v>1</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B88" s="8" t="n">
-        <v>71</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="C88" s="7" t="n">
-        <v>72.25</v>
+        <v>72.08</v>
       </c>
       <c r="D88" s="8" t="n">
-        <v>21.9</v>
+        <v>21.4</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>21.3</v>
+        <v>21.38</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>1</v>
+        <v>5.9</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B89" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>72.08</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="D89" s="8" t="n">
-        <v>21.4</v>
+        <v>20.8</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>21.38</v>
+        <v>21.37</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>5.9</v>
+        <v>9.5</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B90" s="8" t="n">
-        <v>72.3</v>
+        <v>72.5</v>
       </c>
       <c r="C90" s="7" t="n">
-        <v>71.81999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="D90" s="8" t="n">
-        <v>20.8</v>
+        <v>21.6</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>21.37</v>
+        <v>21.33</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B91" s="8" t="n">
-        <v>72.5</v>
+        <v>73</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>71.8</v>
+        <v>71.97</v>
       </c>
       <c r="D91" s="8" t="n">
-        <v>21.6</v>
+        <v>22.1</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>21.33</v>
+        <v>21.44</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B92" s="8" t="n">
-        <v>73</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C92" s="7" t="n">
-        <v>71.97</v>
+        <v>72.14</v>
       </c>
       <c r="D92" s="8" t="n">
-        <v>22.1</v>
+        <v>22.6</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>21.44</v>
+        <v>21.71</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>2.7</v>
+        <v>6.1</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="H92" s="10" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B93" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>72.14</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="D93" s="8" t="n">
-        <v>22.6</v>
+        <v>20.8</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>21.71</v>
+        <v>21.6</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>6.1</v>
+        <v>4.8</v>
       </c>
       <c r="G93" s="9" t="n">
         <v>63</v>
@@ -5994,29 +5994,29 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B94" s="8" t="n">
-        <v>72.2</v>
+        <v>72.3</v>
       </c>
       <c r="C94" s="7" t="n">
-        <v>72.23999999999999</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="D94" s="8" t="n">
-        <v>20.8</v>
+        <v>21.3</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>21.6</v>
+        <v>21.51</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="H94" s="10" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -6507,16 +6507,16 @@
         <v>43</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>93</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>-47</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>21.3</v>
+        <v>21.9</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>16</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>49.5</v>
+        <v>49.3</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -3622,26 +3622,26 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-2.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>8</v>
@@ -3650,291 +3650,283 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>74.95</v>
+        <v>74.8</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>22.75</v>
+        <v>22.45</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>74.87</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>22.57</v>
+        <v>22.43</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-11.9</v>
+        <v>-10.3</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>74.68000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D8" s="8" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E8" s="7" t="n">
         <v>22.4</v>
       </c>
-      <c r="E8" s="7" t="n">
-        <v>22.52</v>
-      </c>
       <c r="F8" s="8" t="n">
-        <v>-10.3</v>
+        <v>-13.7</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>74.68000000000001</v>
+        <v>74.52</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>22.48</v>
+        <v>22.46</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-13.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n">
-        <v>74.2</v>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n"/>
       <c r="C10" s="7" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>22.7</v>
-      </c>
+        <v>74.52</v>
+      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="7" t="n">
-        <v>22.52</v>
+        <v>22.46</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>-15.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
       <c r="C11" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.52</v>
       </c>
       <c r="D11" s="8" t="n"/>
       <c r="E11" s="7" t="n">
-        <v>22.52</v>
+        <v>22.46</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D12" s="8" t="n"/>
       <c r="E12" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>-18.2</v>
+        <v>-23.1</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="7" t="n">
-        <v>74.42</v>
+        <v>74.33</v>
       </c>
       <c r="D13" s="8" t="n"/>
       <c r="E13" s="7" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
       <c r="C14" s="7" t="n">
-        <v>74.33</v>
+        <v>74.45</v>
       </c>
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="7" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>-18.2</v>
+        <v>-19.5</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="7" t="n">
-        <v>74.45</v>
+        <v>74.2</v>
       </c>
       <c r="D15" s="8" t="n"/>
       <c r="E15" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>-19.5</v>
+        <v>-26.4</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B16" s="8" t="n"/>
-      <c r="C16" s="7" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="C16" s="7" t="n"/>
       <c r="D16" s="8" t="n"/>
-      <c r="E16" s="7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="E16" s="7" t="n"/>
       <c r="F16" s="8" t="n">
-        <v>-26.4</v>
+        <v>-19.9</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B17" s="8" t="n"/>
@@ -3942,807 +3934,811 @@
       <c r="D17" s="8" t="n"/>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="8" t="n">
-        <v>-19.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="7" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>21.7</v>
+      </c>
       <c r="F18" s="8" t="n">
-        <v>-15.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>21.7</v>
+        <v>22.05</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-9.4</v>
+        <v>-12</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>73.2</v>
+        <v>73.33</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>-12</v>
+        <v>-12.4</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-12.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>73.31999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>-7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D25" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>22.26</v>
+        <v>22.4</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>73.16</v>
+        <v>73.2</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-10.9</v>
+        <v>-16</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-16</v>
+        <v>-10.1</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>22.3</v>
+        <v>22.31</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-10.1</v>
+        <v>-5.9</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>73.16</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>22.31</v>
+        <v>22.43</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-5.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
         <v>72.8</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>73.06999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>22.43</v>
+        <v>22.41</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-9.9</v>
+        <v>-13.3</v>
       </c>
       <c r="G30" s="9" t="n">
         <v>68</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>73.11</v>
+        <v>73.06</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-13.3</v>
+        <v>-16.6</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
         <v>72.5</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>73.06</v>
+        <v>72.97</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-16.6</v>
+        <v>-11.8</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>72.97</v>
+        <v>72.86</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>22.26</v>
+        <v>22.21</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-11.8</v>
+        <v>-21.1</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>72.86</v>
+        <v>72.8</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-21.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>72.8</v>
+        <v>72.69</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>22.24</v>
+        <v>22.19</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-25.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>72.69</v>
+        <v>72.61</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>-18.3</v>
+        <v>-16</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-16</v>
+        <v>-10.4</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="n"/>
       <c r="C38" s="7" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="D38" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="D38" s="8" t="n"/>
       <c r="E38" s="7" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>-10.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B39" s="8" t="n"/>
       <c r="C39" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="7" t="n">
-        <v>21.85</v>
+        <v>21.7</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B40" s="8" t="n"/>
       <c r="C40" s="7" t="n">
-        <v>72.58</v>
+        <v>72.5</v>
       </c>
       <c r="D40" s="8" t="n"/>
       <c r="E40" s="7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>-12.3</v>
+        <v>-6.6</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B41" s="8" t="n"/>
       <c r="C41" s="7" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D41" s="8" t="n"/>
       <c r="E41" s="7" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="n"/>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C42" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D42" s="8" t="n"/>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>21.2</v>
+      </c>
       <c r="E42" s="7" t="n">
-        <v>21.73</v>
+        <v>21.63</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>21.63</v>
+        <v>21.57</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E44" s="7" t="n">
         <v>21.57</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>-7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>72.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D45" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E45" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E45" s="7" t="n">
-        <v>21.57</v>
-      </c>
       <c r="F45" s="8" t="n">
-        <v>-10.9</v>
+        <v>-7.7</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="n"/>
       <c r="C46" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D46" s="8" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D46" s="8" t="n"/>
       <c r="E46" s="7" t="n">
         <v>21.8</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.9</v>
       </c>
       <c r="G46" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B47" s="8" t="n"/>
@@ -4754,19 +4750,19 @@
         <v>21.8</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-8.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B48" s="8" t="n"/>
@@ -4778,274 +4774,278 @@
         <v>21.8</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>-12.5</v>
+        <v>-11.2</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B49" s="8" t="n"/>
       <c r="C49" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="D49" s="8" t="n"/>
       <c r="E49" s="7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-11.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B50" s="8" t="n"/>
       <c r="C50" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D50" s="8" t="n"/>
       <c r="E50" s="7" t="n">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>-13.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B51" s="8" t="n"/>
       <c r="C51" s="7" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D51" s="8" t="n"/>
       <c r="E51" s="7" t="n">
-        <v>22.15</v>
+        <v>22.5</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="G51" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="n"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="C52" s="7" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="D52" s="8" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D52" s="8" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E52" s="7" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>-12.4</v>
+        <v>-7.8</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>20.5</v>
+        <v>20.95</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-7.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>20.95</v>
+        <v>21.13</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>-3.1</v>
+        <v>-11.8</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>-11.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>72.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>-8.6</v>
+        <v>-13.5</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C58" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>21.33</v>
+        <v>21.43</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H58" s="10" t="n">
         <v>7.7</v>
@@ -5054,510 +5054,510 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>72.23</v>
+        <v>72.39</v>
       </c>
       <c r="D59" s="8" t="n">
         <v>22</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>21.43</v>
+        <v>21.64</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>-7.1</v>
+        <v>-12.5</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B60" s="8" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C60" s="7" t="n">
         <v>72.39</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>21.64</v>
+        <v>21.69</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>-12.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>72.39</v>
+        <v>72.36</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>21.69</v>
+        <v>21.56</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>-6.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B62" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="n"/>
       <c r="C62" s="7" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="D62" s="8" t="n">
-        <v>20.6</v>
-      </c>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="D62" s="8" t="n"/>
       <c r="E62" s="7" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B63" s="8" t="n"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="C63" s="7" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="D63" s="8" t="n"/>
+        <v>72.45</v>
+      </c>
+      <c r="D63" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E63" s="7" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B64" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C64" s="7" t="n">
-        <v>72.45</v>
+        <v>72.47</v>
       </c>
       <c r="D64" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>21.67</v>
+        <v>21.53</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B65" s="8" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>72.47</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D65" s="8" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>21.53</v>
+        <v>21.47</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B66" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B67" s="8" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>72.31999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>-4.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B68" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="C68" s="7" t="n">
-        <v>72.23</v>
+        <v>72.3</v>
       </c>
       <c r="D68" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>21.4</v>
+        <v>21.55</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>-1.6</v>
+        <v>-15.1</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B69" s="8" t="n">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>72.3</v>
+        <v>72.37</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>21.55</v>
+        <v>21.69</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>-15.1</v>
+        <v>-10.3</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="n">
-        <v>72.8</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="n"/>
       <c r="C70" s="7" t="n">
-        <v>72.37</v>
-      </c>
-      <c r="D70" s="8" t="n">
-        <v>22.5</v>
-      </c>
+        <v>72.28</v>
+      </c>
+      <c r="D70" s="8" t="n"/>
       <c r="E70" s="7" t="n">
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>-10.3</v>
+        <v>-14.8</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>5.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B71" s="8" t="n"/>
       <c r="C71" s="7" t="n">
-        <v>72.28</v>
+        <v>72.3</v>
       </c>
       <c r="D71" s="8" t="n"/>
       <c r="E71" s="7" t="n">
-        <v>21.67</v>
+        <v>21.78</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>-14.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B72" s="8" t="n"/>
       <c r="C72" s="7" t="n">
-        <v>72.3</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="D72" s="8" t="n"/>
       <c r="E72" s="7" t="n">
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>-15.7</v>
+        <v>-15.4</v>
       </c>
       <c r="G72" s="9" t="n">
         <v>60</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B73" s="8" t="n"/>
       <c r="C73" s="7" t="n">
-        <v>72.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="7" t="n">
-        <v>21.82</v>
+        <v>21.83</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>-15.4</v>
+        <v>-8.9</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B74" s="8" t="n"/>
       <c r="C74" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="7" t="n">
-        <v>21.83</v>
+        <v>22</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>-8.9</v>
+        <v>-6.7</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B75" s="8" t="n"/>
       <c r="C75" s="7" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D75" s="8" t="n"/>
       <c r="E75" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>-6.7</v>
+        <v>-4.8</v>
       </c>
       <c r="G75" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B76" s="8" t="n"/>
-      <c r="C76" s="7" t="n">
-        <v>72.8</v>
-      </c>
+      <c r="C76" s="7" t="n"/>
       <c r="D76" s="8" t="n"/>
-      <c r="E76" s="7" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="E76" s="7" t="n"/>
       <c r="F76" s="8" t="n">
-        <v>-4.8</v>
+        <v>0.6</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B77" s="8" t="n"/>
-      <c r="C77" s="7" t="n"/>
-      <c r="D77" s="8" t="n"/>
-      <c r="E77" s="7" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="C77" s="7" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="D77" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E77" s="7" t="n">
+        <v>21.9</v>
+      </c>
       <c r="F77" s="8" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>73.2</v>
+        <v>72.8</v>
       </c>
       <c r="C78" s="7" t="n">
-        <v>73.2</v>
+        <v>73</v>
       </c>
       <c r="D78" s="8" t="n">
         <v>21.9</v>
@@ -5566,395 +5566,395 @@
         <v>21.9</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>3.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>73</v>
+        <v>72.97</v>
       </c>
       <c r="D79" s="8" t="n">
-        <v>21.9</v>
+        <v>21.3</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>-9.4</v>
+        <v>-6.9</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C80" s="7" t="n">
-        <v>72.97</v>
+        <v>72.88</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>-6.9</v>
+        <v>-3.2</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>72.88</v>
+        <v>73.08</v>
       </c>
       <c r="D81" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>21.5</v>
+        <v>21.38</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>-3.2</v>
+        <v>0.9</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B82" s="8" t="n">
-        <v>73.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>73.08</v>
+        <v>73</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>20.9</v>
+        <v>21.8</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>21.38</v>
+        <v>21.45</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H82" s="10" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="B83" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="n"/>
       <c r="C83" s="7" t="n">
         <v>73</v>
       </c>
-      <c r="D83" s="8" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="D83" s="8" t="n"/>
       <c r="E83" s="7" t="n">
         <v>21.45</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H83" s="10" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="B84" s="8" t="n"/>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="n">
+        <v>71.90000000000001</v>
+      </c>
       <c r="C84" s="7" t="n">
-        <v>73</v>
-      </c>
-      <c r="D84" s="8" t="n"/>
+        <v>72.78</v>
+      </c>
+      <c r="D84" s="8" t="n">
+        <v>20.7</v>
+      </c>
       <c r="E84" s="7" t="n">
-        <v>21.45</v>
+        <v>21.25</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H84" s="10" t="n">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B85" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>72.78</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="D85" s="8" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>21.25</v>
+        <v>21.2</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>4</v>
+        <v>-3.6</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="H85" s="10" t="n">
-        <v>6.7</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B86" s="8" t="n">
-        <v>71.5</v>
+        <v>71</v>
       </c>
       <c r="C86" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.25</v>
       </c>
       <c r="D86" s="8" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="F86" s="8" t="n">
-        <v>-3.6</v>
+        <v>1</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B87" s="8" t="n">
-        <v>71</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>72.25</v>
+        <v>72.08</v>
       </c>
       <c r="D87" s="8" t="n">
-        <v>21.9</v>
+        <v>21.4</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>21.3</v>
+        <v>21.38</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>1</v>
+        <v>5.9</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="H87" s="10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B88" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="C88" s="7" t="n">
-        <v>72.08</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="D88" s="8" t="n">
-        <v>21.4</v>
+        <v>20.8</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>21.38</v>
+        <v>21.37</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>5.9</v>
+        <v>9.5</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="H88" s="10" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B89" s="8" t="n">
-        <v>72.3</v>
+        <v>72.5</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>71.81999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="D89" s="8" t="n">
-        <v>20.8</v>
+        <v>21.6</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>21.37</v>
+        <v>21.33</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="H89" s="10" t="n">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B90" s="8" t="n">
-        <v>72.5</v>
+        <v>73</v>
       </c>
       <c r="C90" s="7" t="n">
-        <v>71.8</v>
+        <v>71.97</v>
       </c>
       <c r="D90" s="8" t="n">
-        <v>21.6</v>
+        <v>22.1</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>21.33</v>
+        <v>21.44</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B91" s="8" t="n">
-        <v>73</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>71.97</v>
+        <v>72.14</v>
       </c>
       <c r="D91" s="8" t="n">
-        <v>22.1</v>
+        <v>22.6</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>21.44</v>
+        <v>21.71</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>2.7</v>
+        <v>6.1</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B92" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C92" s="7" t="n">
-        <v>72.14</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="D92" s="8" t="n">
-        <v>22.6</v>
+        <v>20.8</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>21.71</v>
+        <v>21.6</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>6.1</v>
+        <v>4.8</v>
       </c>
       <c r="G92" s="9" t="n">
         <v>63</v>
@@ -5966,57 +5966,57 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B93" s="8" t="n">
-        <v>72.2</v>
+        <v>72.3</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>72.23999999999999</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="D93" s="8" t="n">
-        <v>20.8</v>
+        <v>21.3</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>21.6</v>
+        <v>21.51</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="H93" s="10" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B94" s="8" t="n">
         <v>72.3</v>
       </c>
       <c r="C94" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.53</v>
       </c>
       <c r="D94" s="8" t="n">
-        <v>21.3</v>
+        <v>21.9</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>21.51</v>
+        <v>21.59</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="H94" s="10" t="n">
-        <v>7.8</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -6507,16 +6507,16 @@
         <v>43</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>49.5</v>
+        <v>49.3</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>93</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>110</v>
+        <v>151</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>17</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Max 0.25 kg/uge. Cut starter 2026-09-07 — intet underskud før Médoc.</t>
+          <t>Max 0.25 kg/uge. Cut starter 2026-09-21.</t>
         </is>
       </c>
     </row>
@@ -878,29 +878,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Plan 2026 — Christiansborg + Marathon du Médoc</t>
+          <t>2026 — Fast as Fifty — Christiansborg + Médoc 2026</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>16 uger fra 2026-06-01</t>
+          <t>14 uger fra 2026-06-01 til 2026-09-06</t>
         </is>
       </c>
     </row>
@@ -917,25 +920,40 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Fase</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Blok</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>CTL-mål</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>FTP-mål</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>W/kg-mål</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>TSS-mål</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Lokation</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -950,23 +968,26 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="E5" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="4" t="n">
         <v>290</v>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>Malmø/Gentofte</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -977,23 +998,26 @@
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>BUILD+</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="E6" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="4" t="n">
         <v>340</v>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>Gentofte → Mallorca</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -1004,23 +1028,26 @@
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>BUILD+</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="E7" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="4" t="n">
         <v>370</v>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>Mallorca → Gentofte</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -1031,23 +1058,26 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>RECOVERY</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="E8" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="4" t="n">
         <v>180</v>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>Gentofte</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -1058,23 +1088,26 @@
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="E9" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="F9" s="4" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="4" t="n">
         <v>385</v>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>Gentofte</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -1085,23 +1118,26 @@
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>RECOVERY</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="E10" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="4" t="n">
         <v>300</v>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>Gentofte → Wales 8.-12.</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Løbefokus — ingen cykel i Wales. Trail Z2 + vandring.</t>
         </is>
@@ -1116,23 +1152,26 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="E11" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="4" t="n">
         <v>430</v>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>Gentofte → Mallorca 16.</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Man-ons Gentofte, tor-søn Mallorca ride-block.</t>
         </is>
@@ -1147,23 +1186,26 @@
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>BUILD+</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="E12" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="4" t="n">
         <v>480</v>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>Mallorca → hjem 22.</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>Store cykeldage man-tir. Langtur 26 km lørdag — ladder starter. TSB-gulv -35.</t>
         </is>
@@ -1178,23 +1220,26 @@
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>RECOVERY</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="E13" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="4" t="n">
         <v>270</v>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>Gentofte</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>Fuld aflastning + FTP- og threshold-retest. Musik i Gentofte fre-søn.</t>
         </is>
@@ -1209,23 +1254,26 @@
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="E14" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="4" t="n">
         <v>420</v>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>Gentofte → fly søn 9.</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>Langtur 28-30 km. Open water-svøm starter.</t>
         </is>
@@ -1240,23 +1288,26 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>BUILD+</t>
         </is>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="E15" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>Mallorca (hjem søn 16.)</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Camp #2. TSB-gulv -35 overvåges dagligt.</t>
         </is>
@@ -1271,23 +1322,26 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="E16" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="4" t="n">
         <v>300</v>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>Gentofte → Norge lør</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>Sidste langtur 32 km tirsdag. OW-svøm x2.</t>
         </is>
@@ -1302,23 +1356,26 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>TAPER</t>
         </is>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="E17" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="4" t="n">
         <v>180</v>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>Gentofte (hjem fra Norge søn 23.). RACE lør</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>Christiansborg Rundt lør 29. aug — svømmes UTAPERET (2000 m, bevidst valg). Løb Z2 18 km tir (simulation udgået efter aftale). Svøm 2.000 m i træk ons. Søn: cykel indendørs i stedet for løb (ingen løb to dage i streg). Médoc løbes med Eva.</t>
         </is>
@@ -1333,87 +1390,28 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>RACE</t>
         </is>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="E18" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="4" t="n">
         <v>93</v>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>Gentofte → Bordeaux tor</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>Marathon du Médoc lør 5. sep. Ren taper + race-ernæringsplan. Tir: cykel i stedet for løb (ingen løb to dage i streg). Ons: 25 min styrke overkrop/core, ingen benbelastning.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>RECOVERY</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>265</v>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Gentofte</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>Restitution efter Marathon du Médoc. Intet løb før tidligst lør 12/9 — 42 km excentrisk belastning kræver 10-14 dage. Cykel bærer den aerobe base.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>RACE</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>336</v>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Gentofte. RACE søn</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>CPH Half søn 20/9 — B-løb, mål sub 1:30 (4:16/km). Max 3 løb, ingen løb to dage i streg. Cut starter man 21/9, ikke før.</t>
         </is>
       </c>
     </row>
@@ -1446,14 +1444,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Plan 2027 — Tour des Stations Ultrafondo</t>
+          <t>2027 — Tour des Stations 2027</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>51 uger fra 2026-09-07 til 2027-08-23 · FTP 278 → 320 W · W/kg 3.85 → 4.71</t>
+          <t>51 uger fra 2026-09-07 til 2027-08-29 · FTP 278 → 320 W · W/kg 3.85 → 4.71</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1527,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>278</v>
@@ -1538,7 +1536,7 @@
         <v>3.97</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>120</v>
+        <v>265</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
@@ -1547,7 +1545,7 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Post-Médoc. Intet struktureret. Gå, spis, sov.</t>
+          <t>Restitution efter Marathon du Médoc. Intet løb før tidligst lør 12/9 — 42 km excentrisk belastning kræver 10-14 dage. Cykel bærer den aerobe base.</t>
         </is>
       </c>
     </row>
@@ -1567,11 +1565,11 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>RECOVERY</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>278</v>
@@ -1580,16 +1578,16 @@
         <v>3.97</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>180</v>
+        <v>336</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Gentofte</t>
+          <t>Gentofte. RACE søn</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>Fri leg. Svøm afvikles permanent efter denne uge.</t>
+          <t>CPH Half søn 20/9 — B-løb, mål sub 1:30 (4:16/km). Max 3 løb, ingen løb to dage i streg. Cut starter man 21/9, ikke før.</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6046,7 +6044,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Ugesummer — planlagt vs. faktisk</t>
+          <t>Ugesummer — planlagt vs. faktisk (medoc-2026)</t>
         </is>
       </c>
     </row>
@@ -6518,54 +6516,6 @@
       <c r="H18" s="11" t="n">
         <v>58</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>RECOVERY</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="4" t="n">
-        <v>265</v>
-      </c>
-      <c r="G19" s="4" t="n"/>
-      <c r="H19" s="11" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>RACE</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="4" t="n">
-        <v>336</v>
-      </c>
-      <c r="G20" s="4" t="n"/>
-      <c r="H20" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>278</v>
@@ -1536,7 +1536,7 @@
         <v>3.97</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>265</v>
+        <v>150</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>278</v>
@@ -1578,7 +1578,7 @@
         <v>3.97</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>336</v>
+        <v>250</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>CPH Half søn 20/9 — B-løb, mål sub 1:30 (4:16/km). Max 3 løb, ingen løb to dage i streg. Cut starter man 21/9, ikke før.</t>
+          <t>CPH Half søn 20/9 — B-løb. Mål sub 1:30 med beslutningsregel ved 5 km. Cut starter IKKE før mandag 21/9.</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Cykel bliver primær. Styrke 2x starter — unilateralt.</t>
+          <t>Cut starter. Kælder starter med FTP-test tor 24/9. Styrke unilateralt 2× starter.</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>FTP-test. Baseline for 2027-sporet — forventet ~278 W (4,0 W/kg). Watt beskyttes under cut, ikke jages.</t>
+          <t>Recovery. Ingen test (kørt 24/9).</t>
         </is>
       </c>
     </row>

--- a/data/Fast_as_Fifty_Masterplan_2026.xlsx
+++ b/data/Fast_as_Fifty_Masterplan_2026.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>49.3</v>
+        <v>48.5</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>88</v>
@@ -3620,291 +3620,283 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>74.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>74.8</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>22.45</v>
+        <v>22.3</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>-11.9</v>
+        <v>-10.3</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>74.56999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>22.43</v>
+        <v>22.3</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-10.3</v>
+        <v>-13.7</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>74.59999999999999</v>
+        <v>74.42</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>22.4</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>-13.7</v>
+        <v>-15.8</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n">
-        <v>74.2</v>
-      </c>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n"/>
       <c r="C9" s="7" t="n">
-        <v>74.52</v>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>22.7</v>
-      </c>
+        <v>74.42</v>
+      </c>
+      <c r="D9" s="8" t="n"/>
       <c r="E9" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-15.8</v>
+        <v>-13.9</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
       <c r="C10" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D10" s="8" t="n"/>
       <c r="E10" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>-13.9</v>
+        <v>-18.2</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
       <c r="C11" s="7" t="n">
-        <v>74.52</v>
+        <v>74.42</v>
       </c>
       <c r="D11" s="8" t="n"/>
       <c r="E11" s="7" t="n">
-        <v>22.46</v>
+        <v>22.4</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-18.2</v>
+        <v>-23.1</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="7" t="n">
-        <v>74.42</v>
+        <v>74.33</v>
       </c>
       <c r="D12" s="8" t="n"/>
       <c r="E12" s="7" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>-23.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="7" t="n">
-        <v>74.33</v>
+        <v>74.45</v>
       </c>
       <c r="D13" s="8" t="n"/>
       <c r="E13" s="7" t="n">
-        <v>22.47</v>
+        <v>22.5</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>-18.2</v>
+        <v>-19.5</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
       <c r="C14" s="7" t="n">
-        <v>74.45</v>
+        <v>74.2</v>
       </c>
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>-19.5</v>
+        <v>-26.4</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B15" s="8" t="n"/>
-      <c r="C15" s="7" t="n">
-        <v>74.2</v>
-      </c>
+      <c r="C15" s="7" t="n"/>
       <c r="D15" s="8" t="n"/>
-      <c r="E15" s="7" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="E15" s="7" t="n"/>
       <c r="F15" s="8" t="n">
-        <v>-26.4</v>
+        <v>-19.9</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B16" s="8" t="n"/>
@@ -3912,807 +3904,811 @@
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="8" t="n">
-        <v>-19.9</v>
+        <v>-15.3</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="7" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>21.7</v>
+      </c>
       <c r="F17" s="8" t="n">
-        <v>-15.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>21.7</v>
+        <v>22.05</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>-9.4</v>
+        <v>-12</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>73.2</v>
+        <v>73.33</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>-12</v>
+        <v>-12.4</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>21.93</v>
+        <v>21.9</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>-12.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>5.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>73.3</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>73.31999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>22</v>
+        <v>22.18</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>22.18</v>
+        <v>22.26</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>-7.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D24" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>22.26</v>
+        <v>22.4</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>-11.1</v>
+        <v>-10.9</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>73.16</v>
+        <v>73.2</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>22.4</v>
+        <v>22.29</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-10.9</v>
+        <v>-16</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>73.2</v>
+        <v>73.14</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>22.29</v>
+        <v>22.3</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-16</v>
+        <v>-10.1</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>73.14</v>
+        <v>73.16</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>22.3</v>
+        <v>22.31</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>-10.1</v>
+        <v>-5.9</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>73.16</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>22.31</v>
+        <v>22.43</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-5.9</v>
+        <v>-9.9</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
         <v>72.8</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>73.06999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>22.43</v>
+        <v>22.41</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>-9.9</v>
+        <v>-13.3</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>68</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>73.11</v>
+        <v>73.06</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>22.41</v>
+        <v>22.27</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-13.3</v>
+        <v>-16.6</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
         <v>72.5</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>73.06</v>
+        <v>72.97</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>22.27</v>
+        <v>22.26</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-16.6</v>
+        <v>-11.8</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>72.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>72.97</v>
+        <v>72.86</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>22.26</v>
+        <v>22.21</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-11.8</v>
+        <v>-21.1</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>72.86</v>
+        <v>72.8</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>22.21</v>
+        <v>22.24</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-21.1</v>
+        <v>-25.6</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>72.8</v>
+        <v>72.69</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>22.24</v>
+        <v>22.19</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-25.6</v>
+        <v>-18.3</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>72.69</v>
+        <v>72.61</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>22.19</v>
+        <v>22</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>-18.3</v>
+        <v>-16</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>-16</v>
+        <v>-10.4</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n"/>
       <c r="C37" s="7" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="D37" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="D37" s="8" t="n"/>
       <c r="E37" s="7" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-10.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B38" s="8" t="n"/>
       <c r="C38" s="7" t="n">
-        <v>72.56999999999999</v>
+        <v>72.58</v>
       </c>
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="7" t="n">
-        <v>21.85</v>
+        <v>21.7</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>-6.2</v>
+        <v>-12.3</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B39" s="8" t="n"/>
       <c r="C39" s="7" t="n">
-        <v>72.58</v>
+        <v>72.5</v>
       </c>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>-12.3</v>
+        <v>-6.6</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B40" s="8" t="n"/>
       <c r="C40" s="7" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D40" s="8" t="n"/>
       <c r="E40" s="7" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B41" s="8" t="n"/>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="C41" s="7" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D41" s="8" t="n"/>
+        <v>72.43000000000001</v>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>21.2</v>
+      </c>
       <c r="E41" s="7" t="n">
-        <v>21.73</v>
+        <v>21.63</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>72.43000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>21.63</v>
+        <v>21.57</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>21.57</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>-7.5</v>
+        <v>-10.9</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>72.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D44" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E44" s="7" t="n">
         <v>21.8</v>
       </c>
-      <c r="E44" s="7" t="n">
-        <v>21.57</v>
-      </c>
       <c r="F44" s="8" t="n">
-        <v>-10.9</v>
+        <v>-7.7</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B45" s="8" t="n">
-        <v>71.90000000000001</v>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n"/>
       <c r="C45" s="7" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D45" s="8" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D45" s="8" t="n"/>
       <c r="E45" s="7" t="n">
         <v>21.8</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>-7.7</v>
+        <v>-8.9</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B46" s="8" t="n"/>
@@ -4724,19 +4720,19 @@
         <v>21.8</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>-8.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B47" s="8" t="n"/>
@@ -4748,274 +4744,278 @@
         <v>21.8</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-12.5</v>
+        <v>-11.2</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B48" s="8" t="n"/>
       <c r="C48" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="D48" s="8" t="n"/>
       <c r="E48" s="7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>-11.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G48" s="9" t="n">
         <v>63</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B49" s="8" t="n"/>
       <c r="C49" s="7" t="n">
-        <v>71.93000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D49" s="8" t="n"/>
       <c r="E49" s="7" t="n">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-13.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>6.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B50" s="8" t="n"/>
       <c r="C50" s="7" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D50" s="8" t="n"/>
       <c r="E50" s="7" t="n">
-        <v>22.15</v>
+        <v>22.5</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.4</v>
       </c>
       <c r="G50" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B51" s="8" t="n"/>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
       <c r="C51" s="7" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="D51" s="8" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>20.5</v>
+      </c>
       <c r="E51" s="7" t="n">
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>-12.4</v>
+        <v>-7.8</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>71.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D52" s="8" t="n">
-        <v>20.5</v>
+        <v>21.4</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>20.5</v>
+        <v>20.95</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>-7.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>20.95</v>
+        <v>21.13</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>-3.1</v>
+        <v>-11.8</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>72.09999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>21.13</v>
+        <v>21.25</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>-11.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>-9.6</v>
+        <v>-8.6</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>72.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>21.22</v>
+        <v>21.33</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>-8.6</v>
+        <v>-13.5</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>72.18000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>21.33</v>
+        <v>21.43</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>-13.5</v>
+        <v>-7.1</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H57" s="10" t="n">
         <v>7.7</v>
@@ -5024,510 +5024,510 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="C58" s="7" t="n">
-        <v>72.23</v>
+        <v>72.39</v>
       </c>
       <c r="D58" s="8" t="n">
         <v>22</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>21.43</v>
+        <v>21.64</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>-7.1</v>
+        <v>-12.5</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C59" s="7" t="n">
         <v>72.39</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>21.64</v>
+        <v>21.69</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>-12.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B60" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C60" s="7" t="n">
-        <v>72.39</v>
+        <v>72.36</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>21.69</v>
+        <v>21.56</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>-6.8</v>
+        <v>-0.2</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n"/>
       <c r="C61" s="7" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="D61" s="8" t="n">
-        <v>20.6</v>
-      </c>
+        <v>72.34999999999999</v>
+      </c>
+      <c r="D61" s="8" t="n"/>
       <c r="E61" s="7" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B62" s="8" t="n"/>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="n">
+        <v>72.90000000000001</v>
+      </c>
       <c r="C62" s="7" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="D62" s="8" t="n"/>
+        <v>72.45</v>
+      </c>
+      <c r="D62" s="8" t="n">
+        <v>21.8</v>
+      </c>
       <c r="E62" s="7" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>4.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B63" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>72.45</v>
+        <v>72.47</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>21.67</v>
+        <v>21.53</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B64" s="8" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C64" s="7" t="n">
-        <v>72.47</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D64" s="8" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>21.53</v>
+        <v>21.47</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>-4.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H64" s="10" t="n">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B65" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="D65" s="8" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>21.47</v>
+        <v>21.43</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B66" s="8" t="n">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>72.31999999999999</v>
+        <v>72.23</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>21.43</v>
+        <v>21.4</v>
       </c>
       <c r="F66" s="8" t="n">
-        <v>-4.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B67" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>72.23</v>
+        <v>72.3</v>
       </c>
       <c r="D67" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>21.4</v>
+        <v>21.55</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>-1.6</v>
+        <v>-15.1</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B68" s="8" t="n">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="C68" s="7" t="n">
-        <v>72.3</v>
+        <v>72.37</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>21.55</v>
+        <v>21.69</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>-15.1</v>
+        <v>-10.3</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="B69" s="8" t="n">
-        <v>72.8</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="n"/>
       <c r="C69" s="7" t="n">
-        <v>72.37</v>
-      </c>
-      <c r="D69" s="8" t="n">
-        <v>22.5</v>
-      </c>
+        <v>72.28</v>
+      </c>
+      <c r="D69" s="8" t="n"/>
       <c r="E69" s="7" t="n">
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>-10.3</v>
+        <v>-14.8</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>5.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B70" s="8" t="n"/>
       <c r="C70" s="7" t="n">
-        <v>72.28</v>
+        <v>72.3</v>
       </c>
       <c r="D70" s="8" t="n"/>
       <c r="E70" s="7" t="n">
-        <v>21.67</v>
+        <v>21.78</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>-14.8</v>
+        <v>-15.7</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B71" s="8" t="n"/>
       <c r="C71" s="7" t="n">
-        <v>72.3</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="D71" s="8" t="n"/>
       <c r="E71" s="7" t="n">
-        <v>21.78</v>
+        <v>21.82</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>-15.7</v>
+        <v>-15.4</v>
       </c>
       <c r="G71" s="9" t="n">
         <v>60</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B72" s="8" t="n"/>
       <c r="C72" s="7" t="n">
-        <v>72.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D72" s="8" t="n"/>
       <c r="E72" s="7" t="n">
-        <v>21.82</v>
+        <v>21.83</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>-15.4</v>
+        <v>-8.9</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H72" s="10" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B73" s="8" t="n"/>
       <c r="C73" s="7" t="n">
-        <v>72.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="7" t="n">
-        <v>21.83</v>
+        <v>22</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>-8.9</v>
+        <v>-6.7</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B74" s="8" t="n"/>
       <c r="C74" s="7" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="7" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>-6.7</v>
+        <v>-4.8</v>
       </c>
       <c r="G74" s="9" t="n">
         <v>47</v>
       </c>
       <c r="H74" s="10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B75" s="8" t="n"/>
-      <c r="C75" s="7" t="n">
-        <v>72.8</v>
-      </c>
+      <c r="C75" s="7" t="n"/>
       <c r="D75" s="8" t="n"/>
-      <c r="E75" s="7" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="E75" s="7" t="n"/>
       <c r="F75" s="8" t="n">
-        <v>-4.8</v>
+        <v>0.6</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B76" s="8" t="n"/>
-      <c r="C76" s="7" t="n"/>
-      <c r="D76" s="8" t="n"/>
-      <c r="E76" s="7" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="C76" s="7" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="D76" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E76" s="7" t="n">
+        <v>21.9</v>
+      </c>
       <c r="F76" s="8" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B77" s="8" t="n">
-        <v>73.2</v>
+        <v>72.8</v>
       </c>
       <c r="C77" s="7" t="n">
-        <v>73.2</v>
+        <v>73</v>
       </c>
       <c r="D77" s="8" t="n">
         <v>21.9</v>
@@ -5536,395 +5536,395 @@
         <v>21.9</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>3.5</v>
+        <v>-9.4</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C78" s="7" t="n">
-        <v>73</v>
+        <v>72.97</v>
       </c>
       <c r="D78" s="8" t="n">
-        <v>21.9</v>
+        <v>21.3</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>-9.4</v>
+        <v>-6.9</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="H78" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>72.97</v>
+        <v>72.88</v>
       </c>
       <c r="D79" s="8" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>-6.9</v>
+        <v>-3.2</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r=